--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -806,7 +806,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="25" name="Image 25" descr="Picture"/>
@@ -831,7 +831,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -856,7 +856,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="27" name="Image 27" descr="Picture"/>
@@ -881,7 +881,7 @@
       <row>41</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -906,7 +906,7 @@
       <row>41</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="29" name="Image 29" descr="Picture"/>
@@ -931,7 +931,7 @@
       <row>41</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -956,7 +956,7 @@
       <row>41</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="31" name="Image 31" descr="Picture"/>
@@ -981,7 +981,7 @@
       <row>41</row>
       <rowOff>1085850</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="32" name="Image 32" descr="Picture"/>
@@ -1006,7 +1006,7 @@
       <row>41</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="33" name="Image 33" descr="Picture"/>
@@ -1031,7 +1031,7 @@
       <row>41</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1056,7 +1056,7 @@
       <row>41</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1081,7 +1081,7 @@
       <row>41</row>
       <rowOff>2171700</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="7404100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="7404100"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="7404100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="7404100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>10</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>10</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="17856200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="17856200"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="17856200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="17856200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>24</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>24</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>24</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>24</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>24</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>24</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="23399750"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>24</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="23399750"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="25323800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="25323800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="25323800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>38</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="25323800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>38</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>38</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>38</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>38</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>38</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>38</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>38</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="30867350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>38</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="30867350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>38</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="30867350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="32791400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="32791400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="32791400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="32791400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>53</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>53</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>53</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>53</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="37960300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="37960300"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="37960300"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>62</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="37960300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>62</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>62</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>62</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>62</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>62</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>62</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>62</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>62</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>62</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>62</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="45351700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="47275750"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="47275750"/>
     <ext cx="1809750" cy="781050"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="47275750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="47275750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>76</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>76</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>76</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>76</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="56591200"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="56591200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="56591200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>86</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="56591200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>86</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>86</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>86</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>86</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>86</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>86</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>86</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>86</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>86</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>86</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>86</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>86</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="65830450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="67754500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="67754500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="67754500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="67754500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>96</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>96</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>96</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>96</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>96</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>96</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>96</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>96</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>96</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="75145900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>96</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="75145900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="77069950"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="77069950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="77069950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="77069950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>109</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="80765649"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="88538050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="88538050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="88538050"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>128</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="88538050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>128</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>128</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>128</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>128</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>128</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>128</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>128</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>128</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>128</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>128</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>128</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>128</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>128</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="97777300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="99701350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="99701350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="99701350"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="99701350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>139</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>139</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>139</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>9239250</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="108940600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>150</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="110864650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4873,14 +3938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>150</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="110864650"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4898,14 +3958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>150</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="110864650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4923,14 +3978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>150</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="110864650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4948,14 +3998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>150</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4973,14 +4018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>150</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4998,14 +4038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>150</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5023,14 +4058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>150</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5048,14 +4078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>150</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5073,14 +4098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>150</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5098,14 +4118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>150</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5123,14 +4138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>150</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5148,14 +4158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>150</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5173,14 +4178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>150</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5198,14 +4198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>150</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5223,14 +4218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>150</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5248,14 +4238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>150</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5273,14 +4258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>150</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5298,14 +4278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>150</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5323,14 +4298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>150</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5348,14 +4318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>160</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="120910350"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -5373,14 +4338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>160</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="120910350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5398,14 +4358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>160</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="120910350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5423,14 +4378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>160</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="120910350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5448,14 +4398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>160</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5473,14 +4418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>160</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5498,14 +4438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>160</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5523,14 +4458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>160</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5548,14 +4478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>160</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="124606050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5573,14 +4498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>160</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="124606050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5598,14 +4518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>160</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="124606050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5623,14 +4538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="127501650"/>
     <ext cx="1809750" cy="1019175"/>
     <pic>
       <nvPicPr>
@@ -5648,14 +4558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="127501650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5673,14 +4578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="127501650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5698,14 +4598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>172</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="127501650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5723,14 +4618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>172</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="129349500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5748,14 +4638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>172</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="129349500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5773,14 +4658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>172</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="129349500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5798,14 +4678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="135718550"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5823,14 +4698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="135718550"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5848,14 +4718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="135718550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5873,14 +4738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>181</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="135718550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5898,14 +4758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5923,14 +4778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5948,14 +4798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5973,14 +4818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>181</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5998,14 +4838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>193</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="145764250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6023,14 +4858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>193</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="145764250"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -6048,14 +4878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>193</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="145764250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6073,14 +4898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>193</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="145764250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6098,14 +4918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>193</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6123,14 +4938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>193</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6148,14 +4958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>193</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6173,14 +4978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>193</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6198,14 +4998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="154793950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -6223,14 +5018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="154793950"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -6248,14 +5038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="154793950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6273,14 +5058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>206</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="154793950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6298,14 +5078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>206</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6323,14 +5098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>206</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6348,14 +5118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>206</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6373,14 +5138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>206</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6398,14 +5158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>206</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="158489650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6423,14 +5178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>206</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="158489650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6448,14 +5198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>206</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="158489650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -6473,7 +5218,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="1847850"/>
+    <pos x="12934950" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="3695700"/>
+    <pos x="7391400" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="3695700"/>
+    <pos x="9239250" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="7404100"/>
+    <pos x="7391400" y="7404100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="7404100"/>
+    <pos x="9239250" y="7404100"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="7404100"/>
+    <pos x="11087100" y="7404100"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="7404100"/>
+    <pos x="12934950" y="7404100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="9251950"/>
+    <pos x="7391400" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="9251950"/>
+    <pos x="9239250" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="9251950"/>
+    <pos x="11087100" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="9251950"/>
+    <pos x="12934950" y="9251950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="11099800"/>
+    <pos x="7391400" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="11099800"/>
+    <pos x="9239250" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="11099800"/>
+    <pos x="11087100" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="11099800"/>
+    <pos x="12934950" y="11099800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="17856200"/>
+    <pos x="7391400" y="17856200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="17856200"/>
+    <pos x="9239250" y="17856200"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="17856200"/>
+    <pos x="11087100" y="17856200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="17856200"/>
+    <pos x="12934950" y="17856200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="19704050"/>
+    <pos x="7391400" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="19704050"/>
+    <pos x="9239250" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="19704050"/>
+    <pos x="11087100" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="19704050"/>
+    <pos x="12934950" y="19704050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="21551900"/>
+    <pos x="7391400" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="21551900"/>
+    <pos x="9239250" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="21551900"/>
+    <pos x="11087100" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="21551900"/>
+    <pos x="12934950" y="21551900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="23399750"/>
+    <pos x="7391400" y="23399750"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="23399750"/>
+    <pos x="9239250" y="23399750"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="25323800"/>
+    <pos x="7391400" y="25323800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="25323800"/>
+    <pos x="9239250" y="25323800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="25323800"/>
+    <pos x="11087100" y="25323800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="25323800"/>
+    <pos x="12934950" y="25323800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="27171650"/>
+    <pos x="7391400" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="27171650"/>
+    <pos x="9239250" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="27171650"/>
+    <pos x="11087100" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="27171650"/>
+    <pos x="12934950" y="27171650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="29019500"/>
+    <pos x="7391400" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="29019500"/>
+    <pos x="9239250" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="29019500"/>
+    <pos x="11087100" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="29019500"/>
+    <pos x="12934950" y="29019500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="30867350"/>
+    <pos x="7391400" y="30867350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="30867350"/>
+    <pos x="9239250" y="30867350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="30867350"/>
+    <pos x="11087100" y="30867350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="32791400"/>
+    <pos x="7391400" y="32791400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="32791400"/>
+    <pos x="9239250" y="32791400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="32791400"/>
+    <pos x="11087100" y="32791400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="32791400"/>
+    <pos x="12934950" y="32791400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="34639250"/>
+    <pos x="7391400" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="34639250"/>
+    <pos x="9239250" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="34639250"/>
+    <pos x="11087100" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="34639250"/>
+    <pos x="12934950" y="34639250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="37960300"/>
+    <pos x="7391400" y="37960300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="37960300"/>
+    <pos x="9239250" y="37960300"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="37960300"/>
+    <pos x="11087100" y="37960300"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="37960300"/>
+    <pos x="12934950" y="37960300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="39808150"/>
+    <pos x="7391400" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="39808150"/>
+    <pos x="9239250" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="39808150"/>
+    <pos x="11087100" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="39808150"/>
+    <pos x="12934950" y="39808150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="41656000"/>
+    <pos x="7391400" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="41656000"/>
+    <pos x="9239250" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="41656000"/>
+    <pos x="11087100" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="41656000"/>
+    <pos x="12934950" y="41656000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="43503850"/>
+    <pos x="7391400" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="43503850"/>
+    <pos x="9239250" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="43503850"/>
+    <pos x="11087100" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="43503850"/>
+    <pos x="12934950" y="43503850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="45351700"/>
+    <pos x="7391400" y="45351700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="47275750"/>
+    <pos x="7391400" y="47275750"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="47275750"/>
+    <pos x="9239250" y="47275750"/>
     <ext cx="1809750" cy="781050"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="47275750"/>
+    <pos x="11087100" y="47275750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="47275750"/>
+    <pos x="12934950" y="47275750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="49123600"/>
+    <pos x="7391400" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="49123600"/>
+    <pos x="9239250" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="49123600"/>
+    <pos x="11087100" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="49123600"/>
+    <pos x="12934950" y="49123600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="50971450"/>
+    <pos x="7391400" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="50971450"/>
+    <pos x="9239250" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="50971450"/>
+    <pos x="11087100" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="50971450"/>
+    <pos x="12934950" y="50971450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="52819300"/>
+    <pos x="7391400" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="52819300"/>
+    <pos x="9239250" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="52819300"/>
+    <pos x="11087100" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="52819300"/>
+    <pos x="12934950" y="52819300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="54667150"/>
+    <pos x="7391400" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="54667150"/>
+    <pos x="9239250" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="54667150"/>
+    <pos x="11087100" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="54667150"/>
+    <pos x="12934950" y="54667150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="56591200"/>
+    <pos x="7391400" y="56591200"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="56591200"/>
+    <pos x="9239250" y="56591200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="56591200"/>
+    <pos x="11087100" y="56591200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="56591200"/>
+    <pos x="12934950" y="56591200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58439050"/>
+    <pos x="7391400" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58439050"/>
+    <pos x="9239250" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="58439050"/>
+    <pos x="11087100" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="58439050"/>
+    <pos x="12934950" y="58439050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="60286900"/>
+    <pos x="7391400" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="60286900"/>
+    <pos x="9239250" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="60286900"/>
+    <pos x="11087100" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="60286900"/>
+    <pos x="12934950" y="60286900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="62134750"/>
+    <pos x="7391400" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="62134750"/>
+    <pos x="9239250" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="62134750"/>
+    <pos x="11087100" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="62134750"/>
+    <pos x="12934950" y="62134750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="63982600"/>
+    <pos x="7391400" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="63982600"/>
+    <pos x="9239250" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="63982600"/>
+    <pos x="11087100" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="63982600"/>
+    <pos x="12934950" y="63982600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="65830450"/>
+    <pos x="7391400" y="65830450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="67754500"/>
+    <pos x="7391400" y="67754500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="67754500"/>
+    <pos x="9239250" y="67754500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="67754500"/>
+    <pos x="11087100" y="67754500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="67754500"/>
+    <pos x="12934950" y="67754500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="69602350"/>
+    <pos x="7391400" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="69602350"/>
+    <pos x="9239250" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="69602350"/>
+    <pos x="11087100" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="69602350"/>
+    <pos x="12934950" y="69602350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71450200"/>
+    <pos x="7391400" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71450200"/>
+    <pos x="9239250" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71450200"/>
+    <pos x="11087100" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71450200"/>
+    <pos x="12934950" y="71450200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73298050"/>
+    <pos x="7391400" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73298050"/>
+    <pos x="9239250" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73298050"/>
+    <pos x="11087100" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="73298050"/>
+    <pos x="12934950" y="73298050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="75145900"/>
+    <pos x="7391400" y="75145900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="75145900"/>
+    <pos x="9239250" y="75145900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="77069950"/>
+    <pos x="7391400" y="77069950"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="77069950"/>
+    <pos x="9239250" y="77069950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="77069950"/>
+    <pos x="11087100" y="77069950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="77069950"/>
+    <pos x="12934950" y="77069950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="78917799"/>
+    <pos x="7391400" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="78917799"/>
+    <pos x="9239250" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="78917799"/>
+    <pos x="11087100" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="78917799"/>
+    <pos x="12934950" y="78917799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="80765649"/>
+    <pos x="7391400" y="80765649"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="88538050"/>
+    <pos x="7391400" y="88538050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="88538050"/>
+    <pos x="9239250" y="88538050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="88538050"/>
+    <pos x="11087100" y="88538050"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="88538050"/>
+    <pos x="12934950" y="88538050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90385900"/>
+    <pos x="7391400" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="90385900"/>
+    <pos x="9239250" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="90385900"/>
+    <pos x="11087100" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="90385900"/>
+    <pos x="12934950" y="90385900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="92233750"/>
+    <pos x="7391400" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="92233750"/>
+    <pos x="9239250" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="92233750"/>
+    <pos x="11087100" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="92233750"/>
+    <pos x="12934950" y="92233750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="94081600"/>
+    <pos x="7391400" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="94081600"/>
+    <pos x="9239250" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="94081600"/>
+    <pos x="11087100" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="94081600"/>
+    <pos x="12934950" y="94081600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="95929450"/>
+    <pos x="7391400" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="95929450"/>
+    <pos x="9239250" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="95929450"/>
+    <pos x="11087100" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="95929450"/>
+    <pos x="12934950" y="95929450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="97777300"/>
+    <pos x="7391400" y="97777300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="99701350"/>
+    <pos x="7391400" y="99701350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="99701350"/>
+    <pos x="9239250" y="99701350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="99701350"/>
+    <pos x="11087100" y="99701350"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="99701350"/>
+    <pos x="12934950" y="99701350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="101549200"/>
+    <pos x="7391400" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="101549200"/>
+    <pos x="9239250" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="101549200"/>
+    <pos x="11087100" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="101549200"/>
+    <pos x="12934950" y="101549200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="103397050"/>
+    <pos x="7391400" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="103397050"/>
+    <pos x="9239250" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="103397050"/>
+    <pos x="11087100" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="103397050"/>
+    <pos x="12934950" y="103397050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="105244900"/>
+    <pos x="7391400" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="105244900"/>
+    <pos x="9239250" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="105244900"/>
+    <pos x="11087100" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="105244900"/>
+    <pos x="12934950" y="105244900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="107092750"/>
+    <pos x="7391400" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="107092750"/>
+    <pos x="9239250" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="107092750"/>
+    <pos x="11087100" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="107092750"/>
+    <pos x="12934950" y="107092750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="108940600"/>
+    <pos x="7391400" y="108940600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="110864650"/>
+    <pos x="7391400" y="110864650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +3940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="110864650"/>
+    <pos x="9239250" y="110864650"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +3960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="110864650"/>
+    <pos x="11087100" y="110864650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +3980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="110864650"/>
+    <pos x="12934950" y="110864650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="112712500"/>
+    <pos x="7391400" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="112712500"/>
+    <pos x="9239250" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="112712500"/>
+    <pos x="11087100" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="112712500"/>
+    <pos x="12934950" y="112712500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="114560350"/>
+    <pos x="7391400" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="114560350"/>
+    <pos x="9239250" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="114560350"/>
+    <pos x="11087100" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="114560350"/>
+    <pos x="12934950" y="114560350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="116408200"/>
+    <pos x="7391400" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="116408200"/>
+    <pos x="9239250" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="116408200"/>
+    <pos x="11087100" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="116408200"/>
+    <pos x="12934950" y="116408200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="118256050"/>
+    <pos x="7391400" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="118256050"/>
+    <pos x="9239250" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="118256050"/>
+    <pos x="11087100" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="118256050"/>
+    <pos x="12934950" y="118256050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="120910350"/>
+    <pos x="7391400" y="120910350"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="120910350"/>
+    <pos x="9239250" y="120910350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="120910350"/>
+    <pos x="11087100" y="120910350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="120910350"/>
+    <pos x="12934950" y="120910350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="122758200"/>
+    <pos x="7391400" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="122758200"/>
+    <pos x="9239250" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="122758200"/>
+    <pos x="11087100" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="122758200"/>
+    <pos x="12934950" y="122758200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="124606050"/>
+    <pos x="7391400" y="124606050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="124606050"/>
+    <pos x="9239250" y="124606050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="124606050"/>
+    <pos x="11087100" y="124606050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="127501650"/>
+    <pos x="7391400" y="127501650"/>
     <ext cx="1809750" cy="1019175"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="127501650"/>
+    <pos x="9239250" y="127501650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="127501650"/>
+    <pos x="11087100" y="127501650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="127501650"/>
+    <pos x="12934950" y="127501650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="129349500"/>
+    <pos x="7391400" y="129349500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="129349500"/>
+    <pos x="9239250" y="129349500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="129349500"/>
+    <pos x="11087100" y="129349500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="135718550"/>
+    <pos x="7391400" y="135718550"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="135718550"/>
+    <pos x="9239250" y="135718550"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="135718550"/>
+    <pos x="11087100" y="135718550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="135718550"/>
+    <pos x="12934950" y="135718550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="137566400"/>
+    <pos x="7391400" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="137566400"/>
+    <pos x="9239250" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="137566400"/>
+    <pos x="11087100" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="137566400"/>
+    <pos x="12934950" y="137566400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="145764250"/>
+    <pos x="7391400" y="145764250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="145764250"/>
+    <pos x="9239250" y="145764250"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="145764250"/>
+    <pos x="11087100" y="145764250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +4900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="145764250"/>
+    <pos x="12934950" y="145764250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +4920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="147612100"/>
+    <pos x="7391400" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +4940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="147612100"/>
+    <pos x="9239250" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +4960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="147612100"/>
+    <pos x="11087100" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +4980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="147612100"/>
+    <pos x="12934950" y="147612100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="154793950"/>
+    <pos x="7391400" y="154793950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="154793950"/>
+    <pos x="9239250" y="154793950"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="154793950"/>
+    <pos x="11087100" y="154793950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="154793950"/>
+    <pos x="12934950" y="154793950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="156641800"/>
+    <pos x="7391400" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="156641800"/>
+    <pos x="9239250" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="156641800"/>
+    <pos x="11087100" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="156641800"/>
+    <pos x="12934950" y="156641800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="158489650"/>
+    <pos x="7391400" y="158489650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="158489650"/>
+    <pos x="9239250" y="158489650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="158489650"/>
+    <pos x="11087100" y="158489650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5518,7 +5518,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B5900"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,16 +46,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002A4A6B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEFBE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,7 +84,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF0CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,32 +169,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -200,7 +319,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7391400" y="0"/>
+    <pos x="7848600" y="1092200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="0"/>
+    <pos x="9696450" y="1092200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="0"/>
+    <pos x="11544300" y="1092200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="0"/>
+    <pos x="13392150" y="1092200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="1847850"/>
+    <pos x="7848600" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="1847850"/>
+    <pos x="9696450" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="1847850"/>
+    <pos x="11544300" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="1847850"/>
+    <pos x="13392150" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="3695700"/>
+    <pos x="7848600" y="4787900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="3695700"/>
+    <pos x="9696450" y="4787900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="7404100"/>
+    <pos x="7848600" y="9080500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -420,7 +539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="7404100"/>
+    <pos x="9696450" y="9080500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -440,7 +559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="7404100"/>
+    <pos x="11544300" y="9080500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -460,7 +579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="7404100"/>
+    <pos x="13392150" y="9080500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="9251950"/>
+    <pos x="7848600" y="10928350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="9251950"/>
+    <pos x="9696450" y="10928350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="9251950"/>
+    <pos x="11544300" y="10928350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="9251950"/>
+    <pos x="13392150" y="10928350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="11099800"/>
+    <pos x="7848600" y="12776200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="11099800"/>
+    <pos x="9696450" y="12776200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="11099800"/>
+    <pos x="11544300" y="12776200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="11099800"/>
+    <pos x="13392150" y="12776200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="17856200"/>
+    <pos x="7848600" y="19913600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -660,7 +779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="17856200"/>
+    <pos x="9696450" y="19913600"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -680,7 +799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="17856200"/>
+    <pos x="11544300" y="19913600"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="17856200"/>
+    <pos x="13392150" y="19913600"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="19704050"/>
+    <pos x="7848600" y="21761450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="19704050"/>
+    <pos x="9696450" y="21761450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="19704050"/>
+    <pos x="11544300" y="21761450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="19704050"/>
+    <pos x="13392150" y="21761450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="21551900"/>
+    <pos x="7848600" y="23609300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="21551900"/>
+    <pos x="9696450" y="23609300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="21551900"/>
+    <pos x="11544300" y="23609300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="21551900"/>
+    <pos x="13392150" y="23609300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="23399750"/>
+    <pos x="7848600" y="25457150"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +1019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="23399750"/>
+    <pos x="9696450" y="25457150"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +1039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="25323800"/>
+    <pos x="7848600" y="27381200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -940,7 +1059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="25323800"/>
+    <pos x="9696450" y="27381200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +1079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="25323800"/>
+    <pos x="11544300" y="27381200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +1099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="25323800"/>
+    <pos x="13392150" y="27381200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="27171650"/>
+    <pos x="7848600" y="29229050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="27171650"/>
+    <pos x="9696450" y="29229050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="27171650"/>
+    <pos x="11544300" y="29229050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="27171650"/>
+    <pos x="13392150" y="29229050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="29019500"/>
+    <pos x="7848600" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="29019500"/>
+    <pos x="9696450" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="29019500"/>
+    <pos x="11544300" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="29019500"/>
+    <pos x="13392150" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="30867350"/>
+    <pos x="7848600" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="30867350"/>
+    <pos x="9696450" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="30867350"/>
+    <pos x="11544300" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="32791400"/>
+    <pos x="7848600" y="35369500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="32791400"/>
+    <pos x="9696450" y="35369500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="32791400"/>
+    <pos x="11544300" y="35369500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="32791400"/>
+    <pos x="13392150" y="35369500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="34639250"/>
+    <pos x="7848600" y="37217350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="34639250"/>
+    <pos x="9696450" y="37217350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="34639250"/>
+    <pos x="11544300" y="37217350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="34639250"/>
+    <pos x="13392150" y="37217350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="37960300"/>
+    <pos x="7848600" y="40716200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="37960300"/>
+    <pos x="9696450" y="40716200"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="37960300"/>
+    <pos x="11544300" y="40716200"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="37960300"/>
+    <pos x="13392150" y="40716200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="39808150"/>
+    <pos x="7848600" y="42564050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="39808150"/>
+    <pos x="9696450" y="42564050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="39808150"/>
+    <pos x="11544300" y="42564050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="39808150"/>
+    <pos x="13392150" y="42564050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="41656000"/>
+    <pos x="7848600" y="44411900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="41656000"/>
+    <pos x="9696450" y="44411900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="41656000"/>
+    <pos x="11544300" y="44411900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="41656000"/>
+    <pos x="13392150" y="44411900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="43503850"/>
+    <pos x="7848600" y="46259750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="43503850"/>
+    <pos x="9696450" y="46259750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="43503850"/>
+    <pos x="11544300" y="46259750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="43503850"/>
+    <pos x="13392150" y="46259750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="45351700"/>
+    <pos x="7848600" y="48107600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="47275750"/>
+    <pos x="7848600" y="50031650"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="47275750"/>
+    <pos x="9696450" y="50031650"/>
     <ext cx="1809750" cy="781050"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="47275750"/>
+    <pos x="11544300" y="50031650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="47275750"/>
+    <pos x="13392150" y="50031650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="49123600"/>
+    <pos x="7848600" y="51879500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="49123600"/>
+    <pos x="9696450" y="51879500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="49123600"/>
+    <pos x="11544300" y="51879500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="49123600"/>
+    <pos x="13392150" y="51879500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="50971450"/>
+    <pos x="7848600" y="53727350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +2019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="50971450"/>
+    <pos x="9696450" y="53727350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +2039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="50971450"/>
+    <pos x="11544300" y="53727350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +2059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="50971450"/>
+    <pos x="13392150" y="53727350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +2079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="52819300"/>
+    <pos x="7848600" y="55575200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +2099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="52819300"/>
+    <pos x="9696450" y="55575200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="52819300"/>
+    <pos x="11544300" y="55575200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="52819300"/>
+    <pos x="13392150" y="55575200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="54667150"/>
+    <pos x="7848600" y="57423050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="54667150"/>
+    <pos x="9696450" y="57423050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="54667150"/>
+    <pos x="11544300" y="57423050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="54667150"/>
+    <pos x="13392150" y="57423050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="56591200"/>
+    <pos x="7848600" y="59347100"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="56591200"/>
+    <pos x="9696450" y="59347100"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="56591200"/>
+    <pos x="11544300" y="59347100"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="56591200"/>
+    <pos x="13392150" y="59347100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="58439050"/>
+    <pos x="7848600" y="61194950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="58439050"/>
+    <pos x="9696450" y="61194950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="58439050"/>
+    <pos x="11544300" y="61194950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="58439050"/>
+    <pos x="13392150" y="61194950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="60286900"/>
+    <pos x="7848600" y="63042800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="60286900"/>
+    <pos x="9696450" y="63042800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="60286900"/>
+    <pos x="11544300" y="63042800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="60286900"/>
+    <pos x="13392150" y="63042800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="62134750"/>
+    <pos x="7848600" y="64890650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="62134750"/>
+    <pos x="9696450" y="64890650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="62134750"/>
+    <pos x="11544300" y="64890650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="62134750"/>
+    <pos x="13392150" y="64890650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="63982600"/>
+    <pos x="7848600" y="66738500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="63982600"/>
+    <pos x="9696450" y="66738500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="63982600"/>
+    <pos x="11544300" y="66738500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="63982600"/>
+    <pos x="13392150" y="66738500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="65830450"/>
+    <pos x="7848600" y="68586350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="67754500"/>
+    <pos x="7848600" y="70510400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="67754500"/>
+    <pos x="9696450" y="70510400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="67754500"/>
+    <pos x="11544300" y="70510400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="67754500"/>
+    <pos x="13392150" y="70510400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="69602350"/>
+    <pos x="7848600" y="72358250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="69602350"/>
+    <pos x="9696450" y="72358250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="69602350"/>
+    <pos x="11544300" y="72358250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="69602350"/>
+    <pos x="13392150" y="72358250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="71450200"/>
+    <pos x="7848600" y="74206100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="71450200"/>
+    <pos x="9696450" y="74206100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="71450200"/>
+    <pos x="11544300" y="74206100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="71450200"/>
+    <pos x="13392150" y="74206100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="73298050"/>
+    <pos x="7848600" y="76053950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="73298050"/>
+    <pos x="9696450" y="76053950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="73298050"/>
+    <pos x="11544300" y="76053950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="73298050"/>
+    <pos x="13392150" y="76053950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="75145900"/>
+    <pos x="7848600" y="77901800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="75145900"/>
+    <pos x="9696450" y="77901800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +3019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="77069950"/>
+    <pos x="7848600" y="79825850"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +3039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="77069950"/>
+    <pos x="9696450" y="79825850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +3059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="77069950"/>
+    <pos x="11544300" y="79825850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +3079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="77069950"/>
+    <pos x="13392150" y="79825850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +3099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="78917799"/>
+    <pos x="7848600" y="81673700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="78917799"/>
+    <pos x="9696450" y="81673700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="78917799"/>
+    <pos x="11544300" y="81673700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="78917799"/>
+    <pos x="13392150" y="81673700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="80765649"/>
+    <pos x="7848600" y="83521550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="88538050"/>
+    <pos x="7848600" y="92894150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="88538050"/>
+    <pos x="9696450" y="92894150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="88538050"/>
+    <pos x="11544300" y="92894150"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="88538050"/>
+    <pos x="13392150" y="92894150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="90385900"/>
+    <pos x="7848600" y="94742000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="90385900"/>
+    <pos x="9696450" y="94742000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="90385900"/>
+    <pos x="11544300" y="94742000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="90385900"/>
+    <pos x="13392150" y="94742000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="92233750"/>
+    <pos x="7848600" y="96589850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="92233750"/>
+    <pos x="9696450" y="96589850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="92233750"/>
+    <pos x="11544300" y="96589850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="92233750"/>
+    <pos x="13392150" y="96589850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="94081600"/>
+    <pos x="7848600" y="98437700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="94081600"/>
+    <pos x="9696450" y="98437700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="94081600"/>
+    <pos x="11544300" y="98437700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="94081600"/>
+    <pos x="13392150" y="98437700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="95929450"/>
+    <pos x="7848600" y="100285550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="95929450"/>
+    <pos x="9696450" y="100285550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="95929450"/>
+    <pos x="11544300" y="100285550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="95929450"/>
+    <pos x="13392150" y="100285550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="97777300"/>
+    <pos x="7848600" y="102133400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="99701350"/>
+    <pos x="7848600" y="104057450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="99701350"/>
+    <pos x="9696450" y="104057450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="99701350"/>
+    <pos x="11544300" y="104057450"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="99701350"/>
+    <pos x="13392150" y="104057450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="101549200"/>
+    <pos x="7848600" y="105905300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="101549200"/>
+    <pos x="9696450" y="105905300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="101549200"/>
+    <pos x="11544300" y="105905300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="101549200"/>
+    <pos x="13392150" y="105905300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="103397050"/>
+    <pos x="7848600" y="107753150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="103397050"/>
+    <pos x="9696450" y="107753150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="103397050"/>
+    <pos x="11544300" y="107753150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="103397050"/>
+    <pos x="13392150" y="107753150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="105244900"/>
+    <pos x="7848600" y="109601000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="105244900"/>
+    <pos x="9696450" y="109601000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="105244900"/>
+    <pos x="11544300" y="109601000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="105244900"/>
+    <pos x="13392150" y="109601000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="107092750"/>
+    <pos x="7848600" y="111448850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="107092750"/>
+    <pos x="9696450" y="111448850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="107092750"/>
+    <pos x="11544300" y="111448850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="107092750"/>
+    <pos x="13392150" y="111448850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +4019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="108940600"/>
+    <pos x="7848600" y="113296700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +4039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="110864650"/>
+    <pos x="7848600" y="115220750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3940,7 +4059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="110864650"/>
+    <pos x="9696450" y="115220750"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3960,7 +4079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="110864650"/>
+    <pos x="11544300" y="115220750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3980,7 +4099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="110864650"/>
+    <pos x="13392150" y="115220750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4000,7 +4119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="112712500"/>
+    <pos x="7848600" y="117068600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4020,7 +4139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="112712500"/>
+    <pos x="9696450" y="117068600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4040,7 +4159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="112712500"/>
+    <pos x="11544300" y="117068600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4060,7 +4179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="112712500"/>
+    <pos x="13392150" y="117068600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4080,7 +4199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="114560350"/>
+    <pos x="7848600" y="118916450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4100,7 +4219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="114560350"/>
+    <pos x="9696450" y="118916450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4120,7 +4239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="114560350"/>
+    <pos x="11544300" y="118916450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4140,7 +4259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="114560350"/>
+    <pos x="13392150" y="118916450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4160,7 +4279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="116408200"/>
+    <pos x="7848600" y="120764300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4180,7 +4299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="116408200"/>
+    <pos x="9696450" y="120764300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4200,7 +4319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="116408200"/>
+    <pos x="11544300" y="120764300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4220,7 +4339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="116408200"/>
+    <pos x="13392150" y="120764300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4240,7 +4359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="118256050"/>
+    <pos x="7848600" y="122612150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4260,7 +4379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="118256050"/>
+    <pos x="9696450" y="122612150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4280,7 +4399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="118256050"/>
+    <pos x="11544300" y="122612150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4300,7 +4419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="118256050"/>
+    <pos x="13392150" y="122612150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4320,7 +4439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="120910350"/>
+    <pos x="7848600" y="125444250"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4340,7 +4459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="120910350"/>
+    <pos x="9696450" y="125444250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4360,7 +4479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="120910350"/>
+    <pos x="11544300" y="125444250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4380,7 +4499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="120910350"/>
+    <pos x="13392150" y="125444250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4400,7 +4519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="122758200"/>
+    <pos x="7848600" y="127292100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4420,7 +4539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="122758200"/>
+    <pos x="9696450" y="127292100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4440,7 +4559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="122758200"/>
+    <pos x="11544300" y="127292100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4460,7 +4579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="122758200"/>
+    <pos x="13392150" y="127292100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4480,7 +4599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="124606050"/>
+    <pos x="7848600" y="129139950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4500,7 +4619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="124606050"/>
+    <pos x="9696450" y="129139950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4520,7 +4639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="124606050"/>
+    <pos x="11544300" y="129139950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4540,7 +4659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="127501650"/>
+    <pos x="7848600" y="132619750"/>
     <ext cx="1809750" cy="1019175"/>
     <pic>
       <nvPicPr>
@@ -4560,7 +4679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="127501650"/>
+    <pos x="9696450" y="132619750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4580,7 +4699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="127501650"/>
+    <pos x="11544300" y="132619750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4600,7 +4719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="127501650"/>
+    <pos x="13392150" y="132619750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4620,7 +4739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="129349500"/>
+    <pos x="7848600" y="134467600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4640,7 +4759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="129349500"/>
+    <pos x="9696450" y="134467600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4660,7 +4779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="129349500"/>
+    <pos x="11544300" y="134467600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4680,7 +4799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="135718550"/>
+    <pos x="7848600" y="141014450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4700,7 +4819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="135718550"/>
+    <pos x="9696450" y="141014450"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4720,7 +4839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="135718550"/>
+    <pos x="11544300" y="141014450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4740,7 +4859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="135718550"/>
+    <pos x="13392150" y="141014450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4760,7 +4879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="137566400"/>
+    <pos x="7848600" y="142862300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4780,7 +4899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="137566400"/>
+    <pos x="9696450" y="142862300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4800,7 +4919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="137566400"/>
+    <pos x="11544300" y="142862300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4820,7 +4939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="137566400"/>
+    <pos x="13392150" y="142862300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4840,7 +4959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="145764250"/>
+    <pos x="7848600" y="151644350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4860,7 +4979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="145764250"/>
+    <pos x="9696450" y="151644350"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4880,7 +4999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="145764250"/>
+    <pos x="11544300" y="151644350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4900,7 +5019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="145764250"/>
+    <pos x="13392150" y="151644350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4920,7 +5039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="147612100"/>
+    <pos x="7848600" y="153492200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4940,7 +5059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="147612100"/>
+    <pos x="9696450" y="153492200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4960,7 +5079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="147612100"/>
+    <pos x="11544300" y="153492200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4980,7 +5099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="147612100"/>
+    <pos x="13392150" y="153492200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5000,7 +5119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="154793950"/>
+    <pos x="7848600" y="161055050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5020,7 +5139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="154793950"/>
+    <pos x="9696450" y="161055050"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5040,7 +5159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="154793950"/>
+    <pos x="11544300" y="161055050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5060,7 +5179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="154793950"/>
+    <pos x="13392150" y="161055050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5080,7 +5199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="156641800"/>
+    <pos x="7848600" y="162902900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5100,7 +5219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="156641800"/>
+    <pos x="9696450" y="162902900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5120,7 +5239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="156641800"/>
+    <pos x="11544300" y="162902900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5140,7 +5259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="156641800"/>
+    <pos x="13392150" y="162902900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5160,7 +5279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="158489650"/>
+    <pos x="7848600" y="164750750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5180,7 +5299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="158489650"/>
+    <pos x="9696450" y="164750750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5200,7 +5319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="158489650"/>
+    <pos x="11544300" y="164750750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5511,126 +5630,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:F240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>촉촉 글로우 립스틱    ↗ 원본</t>
+          <t>━  색조 골격 치트시트  (이 파일 18종 기준)  ━</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>전형 구성(%):  수상 32~76% · 유상 58~88% · 경화 6~17% · 활성 14~29% · 향 1~3% · 색소 13~15% · 기타 8~24%</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>자주 쓰는 원료:  칸데릴라왁스×6 · 립스틱베이스×5 · 비타민E×3 · 피마자오일×3 · 호호바오일×2 · 카렌듈라오일×2 · 라벤더에센셜오일×2 · 에센셜오일×2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>촉촉 글로우 립스틱    ↗ 원본</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>(겁나게 촉촉) 립밤</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>멀티밤오일 +멀티밤 왁스</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>(로즈우드)에센셜오일</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>2~3방울</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>향, 향기 테라피</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>립컬러 베이스</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>레드6(0.3), 아이론 옐로우 (0.1), 레드27 (0.2), 화이트 (0.2)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>사용하던 립스틱</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 88 · 향 1 · 기타 11</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
+    </row>
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="256" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
+    </row>
+    <row r="12" ht="256" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>겁나게 촉촉~
 글로우 립스틱
@@ -5650,18 +5864,20 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="176" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="176" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>촉촉 글로우 립스틱만들기
 1. 비커에 립컬러를 계량하세요.
@@ -5677,201 +5893,297 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>멀티밤 bb    [1..베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>멀티오일베이스</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>MCT, 로즈힙, 유기농 호호바, 녹차씨, 발효동백, 스쿠알란, 비타민E 등</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>유기농 / 코포아수버터</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>식물성 버터, / 끈적임 적고 수분함량 높고 아주 부드러움</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>망고버터 등</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>식물성 왁스, 단단하게.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>칼라믹스 / 파운데이션</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 함유, / 파운데이션 파우더</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="F21" s="18" t="n"/>
+    </row>
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>보르피린</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>볼륨업, 주름</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>10 g(10%)을 원한다면 로즈워터를 5g 줄여서 40g이 되도록 해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>알파 비사보롤</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>0.3g / (10방울)</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>식약처 인증, 미백 원료</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>버가못에센셜오일</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>0.7g / 10~14방울</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>FCF, 버갑텐 프리, / 감귤껍질오일, 아로마테라피</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 61 · 경화 16 · 활성 6 · 향 2 · 색소 13 · 기타 1</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="336" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+    </row>
+    <row r="27" ht="336" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>이 레시피는 2015년에
 문화센터에서 반응이 좋다며
@@ -5896,22 +6208,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="176" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+    </row>
+    <row r="29" ht="176" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>1. 멀티오일베이스를 계량하세요.
 2. 왁스와 버터를 계량한 후
@@ -5926,204 +6242,294 @@
 굳으면 완성</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="6" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>카렌듈라 썬밤    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>피지성분 비슷, / 가벼운 오일 또는 액상왁스</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일, 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>캐모마일인퓨즈오일</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>산화방지.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>산화 아연 분말</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>전체양의 23%</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>3~9방울</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>썬번, 진정, 아로마테라피</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 47 · 경화 27 · 활성 1 · 향 1 · 기타 24</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>초정밀 과정</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-    </row>
-    <row r="36" ht="192" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="192" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>1. 징크옥사이드를 종이에 계량하세요.
 2. 비커에 1번 재료를 계량합니다.
@@ -6140,228 +6546,328 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="133" customHeight="1"/>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
+    <row r="44" ht="103" customHeight="1"/>
+    <row r="45" ht="6" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>내추럴 립스틱    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>정제 호호바오일</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B48" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
         <is>
           <t>가벼운오일, 보습</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="F48" s="18" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>립베이스 레드27</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
         <is>
           <t>0.4g</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="F49" s="18" t="inlineStr">
         <is>
           <t>더 진한 색을 원하면 / 양을 추가하세요.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B50" s="18" t="inlineStr">
         <is>
           <t>3.5g</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
         <is>
           <t>식물성왁스. 경화제</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>발효 동백오일</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>아르간, 마유 등</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="53" ht="64" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B53" s="18" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
         <is>
           <t>산화방지, 고보습</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="F53" s="18" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B54" s="18" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
         <is>
           <t>아로마테라피효과 / 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 58 · 경화 23 · 활성 14 · 향 2 · 기타 3</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="14" t="n"/>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="14" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>촉촉한 립밤에 색상을 더했습니다. 내추럴 립스틱!
 가루날림이 없는 립베이스로 원하는 색상을 만들어보세요.
 오일에 미리 개어서 원하는 색상을 만든 후 적용하면 됩니다.</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="B57" s="24" t="n"/>
+      <c r="C57" s="24" t="n"/>
+      <c r="D57" s="24" t="n"/>
+      <c r="E57" s="24" t="n"/>
+      <c r="F57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-    </row>
-    <row r="51" ht="208" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B58" s="16" t="n"/>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="16" t="n"/>
+    </row>
+    <row r="59" ht="208" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 속뚜껑을 닫고 뒤집어 주세요.
@@ -6378,105 +6884,147 @@
 12.꺼내서 넘친 부분도 다듬어 닦습니다. 스티커를 붙이고 겉뚜껑을 닫으면 완성.</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-    </row>
-    <row r="52" ht="37.00000000000003" customHeight="1">
-      <c r="A52" s="10" t="n"/>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="B59" s="24" t="n"/>
+      <c r="C59" s="24" t="n"/>
+      <c r="D59" s="24" t="n"/>
+      <c r="E59" s="24" t="n"/>
+      <c r="F59" s="24" t="n"/>
+    </row>
+    <row r="60" ht="6" customHeight="1"/>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>립스틱/글로스 컬러베이스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>(골든)호호바오일</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>액상왁스, 가벼운 오일</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>마카다미아넛오일</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>립 컬러베이스 7</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 89 · 기타 11</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n"/>
+      <c r="C65" s="14" t="n"/>
+      <c r="D65" s="14" t="n"/>
+      <c r="E65" s="14" t="n"/>
+      <c r="F65" s="14" t="n"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-    </row>
-    <row r="59" ht="192" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="B66" s="16" t="n"/>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="16" t="n"/>
+    </row>
+    <row r="67" ht="192" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>원하는 색상의 립제품 만들기 좋은 립컬러 베이스가 나왔습니다.
 쉽게 활용하는 법을 안내해드립니다.
@@ -6493,18 +7041,20 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-    </row>
-    <row r="61" ht="96" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="B68" s="16" t="n"/>
+      <c r="C68" s="16" t="n"/>
+      <c r="D68" s="16" t="n"/>
+      <c r="E68" s="16" t="n"/>
+      <c r="F68" s="16" t="n"/>
+    </row>
+    <row r="69" ht="96" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>1. (골든)호호바오일 4g을 먼저 계량합니다.
 2.원하는 립컬러 베이스를 비커에 발라주세요.
@@ -6514,183 +7064,269 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="6" customHeight="1"/>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="1" t="inlineStr">
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>블루밍 립글로스    [1]    ↗ 원본</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n"/>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>용량</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
-        <is>
-          <t>발효 마유</t>
-        </is>
-      </c>
-      <c r="B65" s="8" t="inlineStr">
-        <is>
-          <t>2g</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>오래가는 보습</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>동백, 아르간오일 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>피마자유</t>
-        </is>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>5g</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>끈적, 오래가는 보습, / 아주까리유</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="48" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>비타민E</t>
-        </is>
-      </c>
-      <c r="B67" s="8" t="inlineStr">
-        <is>
-          <t>0.1g</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>산화방지제</t>
-        </is>
-      </c>
-      <c r="D67" s="8" t="inlineStr">
-        <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>칸데릴라왁스</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>1g</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>경화제</t>
-        </is>
-      </c>
-      <c r="D68" s="8" t="inlineStr">
-        <is>
-          <t>밀랍</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>립 컬러베이스 / (액상)</t>
-        </is>
-      </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>4.5g</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>미리 만들어놓으세요. / 호호바오일 4g, / 원하는 립컬러베이스 0.5g / 상세 만들기 방법 참고</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="inlineStr">
-        <is>
-          <t>미리 만들어놓은 / 9가지 립컬러베이스 중 원하는 것</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
-        <is>
-          <t>로즈우드EO</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>5방울</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>향, 아로마테라피효과</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>원하는에센셜오일</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>— 상세내용 —</t>
         </is>
       </c>
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6" t="n"/>
-    </row>
-    <row r="72" ht="112" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>용량</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>대체재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>발효 마유</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>2g</t>
+        </is>
+      </c>
+      <c r="C73" s="19" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>오래가는 보습</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>동백, 아르간오일 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>피마자유</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="C74" s="19" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>끈적, 오래가는 보습, / 아주까리유</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>비타민E</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>0.1g</t>
+        </is>
+      </c>
+      <c r="C75" s="19" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>산화방지제</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>칸데릴라왁스</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>1g</t>
+        </is>
+      </c>
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>경화제</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>밀랍</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="64" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>립 컬러베이스 / (액상)</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>4.5g</t>
+        </is>
+      </c>
+      <c r="C77" s="19" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>미리 만들어놓으세요. / 호호바오일 4g, / 원하는 립컬러베이스 0.5g / 상세 만들기 방법 참고</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>미리 만들어놓은 / 9가지 립컬러베이스 중 원하는 것</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>로즈우드EO</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>5방울</t>
+        </is>
+      </c>
+      <c r="C78" s="19" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>향, 아로마테라피효과</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>원하는에센셜오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 35 · 경화 8 · 활성 16 · 향 2 · 기타 39</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n"/>
+      <c r="C79" s="14" t="n"/>
+      <c r="D79" s="14" t="n"/>
+      <c r="E79" s="14" t="n"/>
+      <c r="F79" s="14" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="15" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="16" t="n"/>
+      <c r="E80" s="16" t="n"/>
+      <c r="F80" s="16" t="n"/>
+    </row>
+    <row r="81" ht="112" customHeight="1">
+      <c r="A81" s="23" t="inlineStr">
         <is>
           <t>위)달달한 핑크, 아래)갸우뚱 레드
 위)알쏭달쏭 핑크레드(27번+ 레드6) , 아래)단물 빠진 와인 (레드33)
@@ -6701,22 +7337,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="10" t="n"/>
-    </row>
-    <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="B81" s="24" t="n"/>
+      <c r="C81" s="24" t="n"/>
+      <c r="D81" s="24" t="n"/>
+      <c r="E81" s="24" t="n"/>
+      <c r="F81" s="24" t="n"/>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="n"/>
-    </row>
-    <row r="74" ht="160" customHeight="1">
-      <c r="A74" s="9" t="inlineStr">
+      <c r="B82" s="16" t="n"/>
+      <c r="C82" s="16" t="n"/>
+      <c r="D82" s="16" t="n"/>
+      <c r="E82" s="16" t="n"/>
+      <c r="F82" s="16" t="n"/>
+    </row>
+    <row r="83" ht="160" customHeight="1">
+      <c r="A83" s="23" t="inlineStr">
         <is>
           <t>1.미리 만들어놓은 색을 먼저 선택하세요. (달달한 핑크나
 2.잘익은 홍시 등 색상표를 참고해 만들어보세요.)
@@ -6729,105 +7369,155 @@
 9.용기에 담아서 속뚜껑 닫으면 완성~!</t>
         </is>
       </c>
-      <c r="B74" s="10" t="n"/>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="10" t="n"/>
-    </row>
-    <row r="75" ht="214.5" customHeight="1">
-      <c r="A75" s="10" t="n"/>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="10" t="n"/>
-    </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="B83" s="24" t="n"/>
+      <c r="C83" s="24" t="n"/>
+      <c r="D83" s="24" t="n"/>
+      <c r="E83" s="24" t="n"/>
+      <c r="F83" s="24" t="n"/>
+    </row>
+    <row r="84" ht="136.5" customHeight="1">
+      <c r="A84" s="24" t="n"/>
+      <c r="B84" s="24" t="n"/>
+      <c r="C84" s="24" t="n"/>
+      <c r="D84" s="24" t="n"/>
+      <c r="E84" s="24" t="n"/>
+      <c r="F84" s="24" t="n"/>
+    </row>
+    <row r="85" ht="6" customHeight="1"/>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>촉촉 쁘띠 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n"/>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="F89" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 95 · 향 5</t>
+        </is>
+      </c>
+      <c r="B90" s="14" t="n"/>
+      <c r="C90" s="14" t="n"/>
+      <c r="D90" s="14" t="n"/>
+      <c r="E90" s="14" t="n"/>
+      <c r="F90" s="14" t="n"/>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="n"/>
-    </row>
-    <row r="82" ht="80" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+      <c r="B91" s="16" t="n"/>
+      <c r="C91" s="16" t="n"/>
+      <c r="D91" s="16" t="n"/>
+      <c r="E91" s="16" t="n"/>
+      <c r="F91" s="16" t="n"/>
+    </row>
+    <row r="92" ht="80" customHeight="1">
+      <c r="A92" s="17" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -6837,18 +7527,20 @@
         </is>
       </c>
     </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="5" t="inlineStr">
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="6" t="n"/>
-      <c r="D83" s="6" t="n"/>
-    </row>
-    <row r="84" ht="384" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="B93" s="16" t="n"/>
+      <c r="C93" s="16" t="n"/>
+      <c r="D93" s="16" t="n"/>
+      <c r="E93" s="16" t="n"/>
+      <c r="F93" s="16" t="n"/>
+    </row>
+    <row r="94" ht="384" customHeight="1">
+      <c r="A94" s="17" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -6875,96 +7567,142 @@
         </is>
       </c>
     </row>
-    <row r="85" ht="134.5" customHeight="1"/>
-    <row r="86" ht="6" customHeight="1"/>
-    <row r="87" ht="22" customHeight="1">
-      <c r="A87" s="1" t="inlineStr">
+    <row r="95" ht="120.5" customHeight="1"/>
+    <row r="96" ht="6" customHeight="1"/>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>픽미업 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B87" s="2" t="n"/>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n"/>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="n"/>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="48" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B99" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C99" s="19" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="F99" s="18" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="8" t="inlineStr">
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="18" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B100" s="18" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C100" s="19" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="F100" s="18" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="5" t="inlineStr">
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 95 · 향 5</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="n"/>
+      <c r="C101" s="14" t="n"/>
+      <c r="D101" s="14" t="n"/>
+      <c r="E101" s="14" t="n"/>
+      <c r="F101" s="14" t="n"/>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="6" t="n"/>
-      <c r="D91" s="6" t="n"/>
-    </row>
-    <row r="92" ht="224" customHeight="1">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="B102" s="16" t="n"/>
+      <c r="C102" s="16" t="n"/>
+      <c r="D102" s="16" t="n"/>
+      <c r="E102" s="16" t="n"/>
+      <c r="F102" s="16" t="n"/>
+    </row>
+    <row r="103" ht="224" customHeight="1">
+      <c r="A103" s="23" t="inlineStr">
         <is>
           <t>와인, 브라운, 오렌지...
 가을, 겨울에 잘 어울리는 색상을
@@ -6982,22 +7720,26 @@
 진하기를 조절하세요.</t>
         </is>
       </c>
-      <c r="B92" s="10" t="n"/>
-      <c r="C92" s="10" t="n"/>
-      <c r="D92" s="10" t="n"/>
-    </row>
-    <row r="93" ht="14" customHeight="1">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="B103" s="24" t="n"/>
+      <c r="C103" s="24" t="n"/>
+      <c r="D103" s="24" t="n"/>
+      <c r="E103" s="24" t="n"/>
+      <c r="F103" s="24" t="n"/>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6" t="n"/>
-    </row>
-    <row r="94" ht="384" customHeight="1">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="B104" s="16" t="n"/>
+      <c r="C104" s="16" t="n"/>
+      <c r="D104" s="16" t="n"/>
+      <c r="E104" s="16" t="n"/>
+      <c r="F104" s="16" t="n"/>
+    </row>
+    <row r="105" ht="384" customHeight="1">
+      <c r="A105" s="23" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7023,167 +7765,247 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B94" s="10" t="n"/>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="10" t="n"/>
-    </row>
-    <row r="95" ht="135.9999999999999" customHeight="1">
-      <c r="A95" s="10" t="n"/>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="10" t="n"/>
-      <c r="D95" s="10" t="n"/>
-    </row>
-    <row r="96" ht="6" customHeight="1"/>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="1" t="inlineStr">
+      <c r="B105" s="24" t="n"/>
+      <c r="C105" s="24" t="n"/>
+      <c r="D105" s="24" t="n"/>
+      <c r="E105" s="24" t="n"/>
+      <c r="F105" s="24" t="n"/>
+    </row>
+    <row r="106" ht="122" customHeight="1">
+      <c r="A106" s="24" t="n"/>
+      <c r="B106" s="24" t="n"/>
+      <c r="C106" s="24" t="n"/>
+      <c r="D106" s="24" t="n"/>
+      <c r="E106" s="24" t="n"/>
+      <c r="F106" s="24" t="n"/>
+    </row>
+    <row r="107" ht="6" customHeight="1"/>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>생기ON~ 립스틱    [1. 립밤 베이스 / (52.5g)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B97" s="2" t="n"/>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n"/>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+      <c r="E108" s="6" t="n"/>
+      <c r="F108" s="6" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+    <row r="110" ht="48" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>자초립밤 / 오일 베이스</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>43g</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>자근추출물, 호호바오일, 아몬드오일, 피마자오일, 해바라기씨오일, 비타민E</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>자초인퓨즈오일, 원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>9.5g</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>식물성 경화제</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>립밤 베이스</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>위의 레시피로 / 미리 만들것.</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>립 컬러 베이스</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>레드27 + 레드21</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>원하는 / 색상</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>에센셜오일 (EO)</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C103" s="4" t="n"/>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="n"/>
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="14" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 75 · 경화 17 · 향 0 · 기타 8</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="n"/>
+      <c r="C115" s="14" t="n"/>
+      <c r="D115" s="14" t="n"/>
+      <c r="E115" s="14" t="n"/>
+      <c r="F115" s="14" t="n"/>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-    </row>
-    <row r="105" ht="176" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="B116" s="16" t="n"/>
+      <c r="C116" s="16" t="n"/>
+      <c r="D116" s="16" t="n"/>
+      <c r="E116" s="16" t="n"/>
+      <c r="F116" s="16" t="n"/>
+    </row>
+    <row r="117" ht="176" customHeight="1">
+      <c r="A117" s="17" t="inlineStr">
         <is>
           <t>가볍고 촉촉한 자초립밤오일베이스로 립스틱들 만들어보세요.
 호호바오일, 피마자오일, 해바라기오일, 비타민E에
@@ -7199,18 +8021,20 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-    </row>
-    <row r="107" ht="352" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="B118" s="16" t="n"/>
+      <c r="C118" s="16" t="n"/>
+      <c r="D118" s="16" t="n"/>
+      <c r="E118" s="16" t="n"/>
+      <c r="F118" s="16" t="n"/>
+    </row>
+    <row r="119" ht="352" customHeight="1">
+      <c r="A119" s="17" t="inlineStr">
         <is>
           <t>1.자초립밤오일베이스와 칸데릴라왁스를 계량한 후
 2. 섞으면서 녹입니다.
@@ -7237,308 +8061,454 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="22.5" customHeight="1"/>
-    <row r="109" ht="6" customHeight="1"/>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="1" t="inlineStr">
+    <row r="120" ht="8.500000000000028" customHeight="1"/>
+    <row r="121" ht="6" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>수딩썬로션    [오일/ / 유화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B110" s="2" t="n"/>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="6" t="n"/>
+      <c r="F122" s="6" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="18" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B124" s="18" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일, / 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="D112" s="8" t="inlineStr">
+      <c r="F124" s="18" t="inlineStr">
         <is>
           <t>캐모마일 / 오일</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="125" ht="48" customHeight="1">
+      <c r="A125" s="18" t="inlineStr">
         <is>
           <t>올리브에스터오일</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B125" s="18" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr">
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E125" s="18" t="inlineStr">
         <is>
           <t>올리브오일유래, 초기사용감은 / 실리콘오일처럼 가볍지만 보습력지속</t>
         </is>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="F125" s="18" t="inlineStr">
         <is>
           <t>호호바</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="48" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+    <row r="126" ht="48" customHeight="1">
+      <c r="A126" s="18" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B126" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D126" s="25" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E126" s="18" t="inlineStr">
         <is>
           <t>에코인증, / 물/오일분리 저지</t>
         </is>
       </c>
-      <c r="D114" s="8" t="inlineStr">
+      <c r="F126" s="18" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="8" t="inlineStr">
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="18" t="inlineStr">
         <is>
           <t>올리왁스LC</t>
         </is>
       </c>
-      <c r="B115" s="8" t="inlineStr">
+      <c r="B127" s="18" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr">
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D127" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E127" s="18" t="inlineStr">
         <is>
           <t>유화 보조제, / 백탁 현상 완화</t>
         </is>
       </c>
-      <c r="D115" s="8" t="inlineStr">
+      <c r="F127" s="18" t="inlineStr">
         <is>
           <t>세틸알콜</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="18" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B128" s="18" t="inlineStr">
         <is>
           <t>32g</t>
         </is>
       </c>
-      <c r="C116" s="8" t="inlineStr">
+      <c r="C128" s="19" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="D128" s="26" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E128" s="18" t="inlineStr">
         <is>
           <t>5차 필터링, / UV살균처리 정제수</t>
         </is>
       </c>
-      <c r="D116" s="8" t="inlineStr">
+      <c r="F128" s="18" t="inlineStr">
         <is>
           <t>원하는 / 플로럴워터</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="32" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="129" ht="48" customHeight="1">
+      <c r="A129" s="18" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B129" s="18" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E129" s="18" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은 / 수분감이 풍부한 겔</t>
         </is>
       </c>
-      <c r="D117" s="8" t="inlineStr">
+      <c r="F129" s="18" t="inlineStr">
         <is>
           <t>허브누리 베라겔, / 네롤리 / 플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="18" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B130" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E130" s="18" t="inlineStr">
         <is>
           <t>고중저분자, / 트리플 히아루론산,</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
+      <c r="F130" s="18" t="inlineStr">
         <is>
           <t>에코 / 보습제</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="48" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="131" ht="48" customHeight="1">
+      <c r="A131" s="18" t="inlineStr">
         <is>
           <t>수딩4 컴플렉스</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B131" s="18" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C131" s="19" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
         <is>
           <t>알로에베라잎추출물, 참마뿌리추출물, / 흰목이버섯추출물, 미역추출물 복합추출물</t>
         </is>
       </c>
-      <c r="D119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="48" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="F131" s="18" t="n"/>
+    </row>
+    <row r="132" ht="64" customHeight="1">
+      <c r="A132" s="18" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B132" s="18" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C132" s="19" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D132" s="27" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="F132" s="18" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (정제수의 양을 31g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="18" t="inlineStr">
         <is>
           <t>징크옥사이드분산액</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B133" s="18" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C133" s="19" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D133" s="21" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E133" s="18" t="inlineStr">
         <is>
           <t>UV-A를 주로 난반사</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="F133" s="18" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="32" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="18" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 / 분산액</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B134" s="18" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C134" s="19" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D134" s="21" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
         <is>
           <t>자외선UV-B를 주로 난반사</t>
         </is>
       </c>
-      <c r="D122" s="8" t="n"/>
-    </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="F134" s="18" t="n"/>
+    </row>
+    <row r="135" ht="48" customHeight="1">
+      <c r="A135" s="18" t="inlineStr">
         <is>
           <t>베베보 블렌딩오일</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B135" s="18" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C135" s="19" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E135" s="18" t="inlineStr">
         <is>
           <t>라벤더. 만다린 로먼캐모마일 에센셜오일, / 민감피부를 위한 블렌딩</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="F135" s="18" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 32 · 유상 17 · 유화 4 · 경화 2 · 활성 29 · 색소 15 · 방부 1</t>
+        </is>
+      </c>
+      <c r="B136" s="14" t="n"/>
+      <c r="C136" s="14" t="n"/>
+      <c r="D136" s="14" t="n"/>
+      <c r="E136" s="14" t="n"/>
+      <c r="F136" s="14" t="n"/>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6" t="n"/>
-    </row>
-    <row r="125" ht="352" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="B137" s="16" t="n"/>
+      <c r="C137" s="16" t="n"/>
+      <c r="D137" s="16" t="n"/>
+      <c r="E137" s="16" t="n"/>
+      <c r="F137" s="16" t="n"/>
+    </row>
+    <row r="138" ht="352" customHeight="1">
+      <c r="A138" s="23" t="inlineStr">
         <is>
           <t>수딩썬로션
 (100g)
@@ -7564,22 +8534,26 @@
 우리 가족 안심 썬로션 만들기해보세요 .</t>
         </is>
       </c>
-      <c r="B125" s="10" t="n"/>
-      <c r="C125" s="10" t="n"/>
-      <c r="D125" s="10" t="n"/>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="B138" s="24" t="n"/>
+      <c r="C138" s="24" t="n"/>
+      <c r="D138" s="24" t="n"/>
+      <c r="E138" s="24" t="n"/>
+      <c r="F138" s="24" t="n"/>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B126" s="6" t="n"/>
-      <c r="C126" s="6" t="n"/>
-      <c r="D126" s="6" t="n"/>
-    </row>
-    <row r="127" ht="112" customHeight="1">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="B139" s="16" t="n"/>
+      <c r="C139" s="16" t="n"/>
+      <c r="D139" s="16" t="n"/>
+      <c r="E139" s="16" t="n"/>
+      <c r="F139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="112" customHeight="1">
+      <c r="A140" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 2개의 비커에 오일/유화제, 워터를 계량합니다.
@@ -7590,117 +8564,175 @@
 6. 골고루 섞어주면 완성.</t>
         </is>
       </c>
-      <c r="B127" s="10" t="n"/>
-      <c r="C127" s="10" t="n"/>
-      <c r="D127" s="10" t="n"/>
-    </row>
-    <row r="128" ht="6" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="B140" s="24" t="n"/>
+      <c r="C140" s="24" t="n"/>
+      <c r="D140" s="24" t="n"/>
+      <c r="E140" s="24" t="n"/>
+      <c r="F140" s="24" t="n"/>
+    </row>
+    <row r="141" ht="6" customHeight="1"/>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>레드 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B129" s="2" t="n"/>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n"/>
-    </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="B142" s="6" t="n"/>
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="n"/>
+      <c r="E142" s="6" t="n"/>
+      <c r="F142" s="6" t="n"/>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D143" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="48" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
+    <row r="144" ht="48" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D144" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="F144" s="8" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="64" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
+    <row r="145" ht="64" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>레드 립 컬러</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
         <is>
           <t>레드21번 0.5g + 레드7번 0.2g+ 옐로우6번 0.1g+ 레드6번 0.2g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="D132" s="4" t="n"/>
-    </row>
-    <row r="133" ht="32" customHeight="1">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="F145" s="8" t="n"/>
+    </row>
+    <row r="146" ht="32" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>브라이트닝블렌딩오일</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C133" s="4" t="inlineStr">
+      <c r="C146" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
         <is>
           <t>네롤리, 프랑킨센스, 버가못EO 블렌딩</t>
         </is>
       </c>
-      <c r="D133" s="4" t="inlineStr">
+      <c r="F146" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="14" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="n"/>
+      <c r="C147" s="14" t="n"/>
+      <c r="D147" s="14" t="n"/>
+      <c r="E147" s="14" t="n"/>
+      <c r="F147" s="14" t="n"/>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B134" s="6" t="n"/>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="n"/>
-    </row>
-    <row r="135" ht="224" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+      <c r="B148" s="16" t="n"/>
+      <c r="C148" s="16" t="n"/>
+      <c r="D148" s="16" t="n"/>
+      <c r="E148" s="16" t="n"/>
+      <c r="F148" s="16" t="n"/>
+    </row>
+    <row r="149" ht="224" customHeight="1">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -7719,18 +8751,20 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="14" customHeight="1">
-      <c r="A136" s="5" t="inlineStr">
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B136" s="6" t="n"/>
-      <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6" t="n"/>
-    </row>
-    <row r="137" ht="304" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
+      <c r="B150" s="16" t="n"/>
+      <c r="C150" s="16" t="n"/>
+      <c r="D150" s="16" t="n"/>
+      <c r="E150" s="16" t="n"/>
+      <c r="F150" s="16" t="n"/>
+    </row>
+    <row r="151" ht="304" customHeight="1">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t>2.녹인 것을 캔용기에 부어서
 4. 굳히세요. 식히면 단단해집니다.
@@ -7753,114 +8787,170 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="136" customHeight="1"/>
-    <row r="139" ht="6" customHeight="1"/>
-    <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="1" t="inlineStr">
+    <row r="152" ht="122" customHeight="1"/>
+    <row r="153" ht="6" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>벚꽃 썸띵 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B140" s="2" t="n"/>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n"/>
-    </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="6" t="n"/>
+    </row>
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="F155" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="48" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+    <row r="156" ht="48" customHeight="1">
+      <c r="A156" s="18" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="B156" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C142" s="8" t="inlineStr">
+      <c r="C156" s="19" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E156" s="18" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="D142" s="8" t="inlineStr">
+      <c r="F156" s="18" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="64" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="157" ht="64" customHeight="1">
+      <c r="A157" s="18" t="inlineStr">
         <is>
           <t>벚꽃 립 컬러</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B157" s="18" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C143" s="8" t="inlineStr">
+      <c r="C157" s="19" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E157" s="18" t="inlineStr">
         <is>
           <t>레드27번 0.3g + 레드40번 0.2g+ 아이론옐로우 0.1g+ 화이트 0.4g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="D143" s="8" t="n"/>
-    </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+      <c r="F157" s="18" t="n"/>
+    </row>
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="18" t="inlineStr">
         <is>
           <t>레몬쥬스블렌딩오일</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B158" s="18" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C144" s="8" t="inlineStr">
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D158" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E158" s="18" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드 / 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="D144" s="8" t="inlineStr">
+      <c r="F158" s="18" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="14" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="n"/>
+      <c r="C159" s="14" t="n"/>
+      <c r="D159" s="14" t="n"/>
+      <c r="E159" s="14" t="n"/>
+      <c r="F159" s="14" t="n"/>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B145" s="6" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="n"/>
-    </row>
-    <row r="146" ht="192" customHeight="1">
-      <c r="A146" s="9" t="inlineStr">
+      <c r="B160" s="16" t="n"/>
+      <c r="C160" s="16" t="n"/>
+      <c r="D160" s="16" t="n"/>
+      <c r="E160" s="16" t="n"/>
+      <c r="F160" s="16" t="n"/>
+    </row>
+    <row r="161" ht="192" customHeight="1">
+      <c r="A161" s="23" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -7876,22 +8966,26 @@
 완성도 높은 립스틱 만들기해보세요.</t>
         </is>
       </c>
-      <c r="B146" s="10" t="n"/>
-      <c r="C146" s="10" t="n"/>
-      <c r="D146" s="10" t="n"/>
-    </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+      <c r="B161" s="24" t="n"/>
+      <c r="C161" s="24" t="n"/>
+      <c r="D161" s="24" t="n"/>
+      <c r="E161" s="24" t="n"/>
+      <c r="F161" s="24" t="n"/>
+    </row>
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B147" s="6" t="n"/>
-      <c r="C147" s="6" t="n"/>
-      <c r="D147" s="6" t="n"/>
-    </row>
-    <row r="148" ht="384" customHeight="1">
-      <c r="A148" s="9" t="inlineStr">
+      <c r="B162" s="16" t="n"/>
+      <c r="C162" s="16" t="n"/>
+      <c r="D162" s="16" t="n"/>
+      <c r="E162" s="16" t="n"/>
+      <c r="F162" s="16" t="n"/>
+    </row>
+    <row r="163" ht="384" customHeight="1">
+      <c r="A163" s="23" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7918,123 +9012,183 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B148" s="10" t="n"/>
-      <c r="C148" s="10" t="n"/>
-      <c r="D148" s="10" t="n"/>
-    </row>
-    <row r="149" ht="87.99999999999994" customHeight="1">
-      <c r="A149" s="10" t="n"/>
-      <c r="B149" s="10" t="n"/>
-      <c r="C149" s="10" t="n"/>
-      <c r="D149" s="10" t="n"/>
-    </row>
-    <row r="150" ht="6" customHeight="1"/>
-    <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="1" t="inlineStr">
+      <c r="B163" s="24" t="n"/>
+      <c r="C163" s="24" t="n"/>
+      <c r="D163" s="24" t="n"/>
+      <c r="E163" s="24" t="n"/>
+      <c r="F163" s="24" t="n"/>
+    </row>
+    <row r="164" ht="74.00000000000006" customHeight="1">
+      <c r="A164" s="24" t="n"/>
+      <c r="B164" s="24" t="n"/>
+      <c r="C164" s="24" t="n"/>
+      <c r="D164" s="24" t="n"/>
+      <c r="E164" s="24" t="n"/>
+      <c r="F164" s="24" t="n"/>
+    </row>
+    <row r="165" ht="6" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>피치코랄 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B151" s="2" t="n"/>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n"/>
-    </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="6" t="n"/>
+      <c r="F166" s="6" t="n"/>
+    </row>
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="48" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 / 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="F168" s="8" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="64" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="169" ht="64" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>피치코랄 립 컬러</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
         <is>
           <t>레드6번 0.3g + 아이론옐로우 0.1g / + 레드27번 0.2g + 화이트 0.2g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="D154" s="4" t="n"/>
-    </row>
-    <row r="155" ht="32" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
+      <c r="F169" s="8" t="n"/>
+    </row>
+    <row r="170" ht="32" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t>라임캔디 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
         <is>
           <t>라임, 스윗오렌지, 레몬, 로즈마리 / 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="F170" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="14" customHeight="1">
-      <c r="A156" s="5" t="inlineStr">
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
+        </is>
+      </c>
+      <c r="B171" s="14" t="n"/>
+      <c r="C171" s="14" t="n"/>
+      <c r="D171" s="14" t="n"/>
+      <c r="E171" s="14" t="n"/>
+      <c r="F171" s="14" t="n"/>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B156" s="6" t="n"/>
-      <c r="C156" s="6" t="n"/>
-      <c r="D156" s="6" t="n"/>
-    </row>
-    <row r="157" ht="192" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
+      <c r="B172" s="16" t="n"/>
+      <c r="C172" s="16" t="n"/>
+      <c r="D172" s="16" t="n"/>
+      <c r="E172" s="16" t="n"/>
+      <c r="F172" s="16" t="n"/>
+    </row>
+    <row r="173" ht="192" customHeight="1">
+      <c r="A173" s="17" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -8051,18 +9205,20 @@
         </is>
       </c>
     </row>
-    <row r="158" ht="14" customHeight="1">
-      <c r="A158" s="5" t="inlineStr">
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B158" s="6" t="n"/>
-      <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6" t="n"/>
-    </row>
-    <row r="159" ht="384" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
+      <c r="B174" s="16" t="n"/>
+      <c r="C174" s="16" t="n"/>
+      <c r="D174" s="16" t="n"/>
+      <c r="E174" s="16" t="n"/>
+      <c r="F174" s="16" t="n"/>
+    </row>
+    <row r="175" ht="384" customHeight="1">
+      <c r="A175" s="17" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -8090,157 +9246,233 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="6" customHeight="1"/>
-    <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="1" t="inlineStr">
+    <row r="176" ht="6" customHeight="1"/>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>워터리 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B161" s="2" t="n"/>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n"/>
-    </row>
-    <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="3" t="inlineStr">
+      <c r="B177" s="6" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+      <c r="E177" s="6" t="n"/>
+      <c r="F177" s="6" t="n"/>
+    </row>
+    <row r="178" ht="15" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr">
+      <c r="B178" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="8" t="inlineStr">
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="18" t="inlineStr">
         <is>
           <t>립밤베이스</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B179" s="18" t="inlineStr">
         <is>
           <t>4.6g</t>
         </is>
       </c>
-      <c r="C163" s="8" t="inlineStr">
+      <c r="C179" s="19" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="D179" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E179" s="18" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서</t>
         </is>
       </c>
-      <c r="D163" s="8" t="inlineStr">
+      <c r="F179" s="18" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="32" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="18" t="inlineStr">
         <is>
           <t>립 컬러</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B180" s="18" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C180" s="19" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D180" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E180" s="18" t="inlineStr">
         <is>
           <t>색상사진은 아래의 / 립스틱 발색 사진과 처방 참고</t>
         </is>
       </c>
-      <c r="D164" s="8" t="n"/>
-    </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
+      <c r="F180" s="18" t="n"/>
+    </row>
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="18" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B181" s="18" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C165" s="8" t="inlineStr">
+      <c r="C181" s="19" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="D181" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E181" s="18" t="inlineStr">
         <is>
           <t>피지성분과 비슷, / 가벼운 사용감</t>
         </is>
       </c>
-      <c r="D165" s="8" t="inlineStr">
+      <c r="F181" s="18" t="inlineStr">
         <is>
           <t>스위트아몬드오일, / 동백오일 등</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="32" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+    <row r="182" ht="48" customHeight="1">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B182" s="18" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C166" s="8" t="inlineStr">
+      <c r="C182" s="19" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E182" s="18" t="inlineStr">
         <is>
           <t>오래가는 보습오일</t>
         </is>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="F182" s="18" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="32" customHeight="1">
-      <c r="A167" s="8" t="inlineStr">
+    <row r="183" ht="48" customHeight="1">
+      <c r="A183" s="18" t="inlineStr">
         <is>
           <t>로즈파워 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B183" s="18" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C167" s="8" t="inlineStr">
+      <c r="C183" s="19" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D183" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E183" s="18" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄, 로즈우드, 프랑킨센스 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="D167" s="8" t="inlineStr">
+      <c r="F183" s="18" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="14" customHeight="1">
-      <c r="A168" s="5" t="inlineStr">
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 94 · 기타 6</t>
+        </is>
+      </c>
+      <c r="B184" s="14" t="n"/>
+      <c r="C184" s="14" t="n"/>
+      <c r="D184" s="14" t="n"/>
+      <c r="E184" s="14" t="n"/>
+      <c r="F184" s="14" t="n"/>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B168" s="6" t="n"/>
-      <c r="C168" s="6" t="n"/>
-      <c r="D168" s="6" t="n"/>
-    </row>
-    <row r="169" ht="96" customHeight="1">
-      <c r="A169" s="9" t="inlineStr">
+      <c r="B185" s="16" t="n"/>
+      <c r="C185" s="16" t="n"/>
+      <c r="D185" s="16" t="n"/>
+      <c r="E185" s="16" t="n"/>
+      <c r="F185" s="16" t="n"/>
+    </row>
+    <row r="186" ht="96" customHeight="1">
+      <c r="A186" s="23" t="inlineStr">
         <is>
           <t>무제 문서
 워터리 립글로스는
@@ -8250,22 +9482,26 @@
 다양한 색상처방은 아래에서 참고하세요.</t>
         </is>
       </c>
-      <c r="B169" s="10" t="n"/>
-      <c r="C169" s="10" t="n"/>
-      <c r="D169" s="10" t="n"/>
-    </row>
-    <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="5" t="inlineStr">
+      <c r="B186" s="24" t="n"/>
+      <c r="C186" s="24" t="n"/>
+      <c r="D186" s="24" t="n"/>
+      <c r="E186" s="24" t="n"/>
+      <c r="F186" s="24" t="n"/>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B170" s="6" t="n"/>
-      <c r="C170" s="6" t="n"/>
-      <c r="D170" s="6" t="n"/>
-    </row>
-    <row r="171" ht="192" customHeight="1">
-      <c r="A171" s="9" t="inlineStr">
+      <c r="B187" s="16" t="n"/>
+      <c r="C187" s="16" t="n"/>
+      <c r="D187" s="16" t="n"/>
+      <c r="E187" s="16" t="n"/>
+      <c r="F187" s="16" t="n"/>
+    </row>
+    <row r="188" ht="192" customHeight="1">
+      <c r="A188" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 [립밤베이스 만들기]
@@ -8281,95 +9517,143 @@
 9. 튜브나 립솔용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B171" s="10" t="n"/>
-      <c r="C171" s="10" t="n"/>
-      <c r="D171" s="10" t="n"/>
-    </row>
-    <row r="172" ht="6" customHeight="1"/>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="B188" s="24" t="n"/>
+      <c r="C188" s="24" t="n"/>
+      <c r="D188" s="24" t="n"/>
+      <c r="E188" s="24" t="n"/>
+      <c r="F188" s="24" t="n"/>
+    </row>
+    <row r="189" ht="6" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="5" t="inlineStr">
         <is>
           <t>커피헤나염색    ↗ 원본</t>
         </is>
       </c>
-      <c r="B173" s="2" t="n"/>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n"/>
-    </row>
-    <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="3" t="inlineStr">
+      <c r="B190" s="6" t="n"/>
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+      <c r="E190" s="6" t="n"/>
+      <c r="F190" s="6" t="n"/>
+    </row>
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr">
+      <c r="B191" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C174" s="3" t="inlineStr">
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="F191" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="4" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="8" t="inlineStr">
         <is>
           <t>헤나분말</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B192" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C175" s="4" t="inlineStr">
+      <c r="C192" s="9" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
         <is>
           <t>100% 헤나 분말</t>
         </is>
       </c>
-      <c r="D175" s="4" t="n"/>
-    </row>
-    <row r="176" ht="48" customHeight="1">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="F192" s="8" t="n"/>
+    </row>
+    <row r="193" ht="64" customHeight="1">
+      <c r="A193" s="8" t="inlineStr">
         <is>
           <t>물</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>130g 내외</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C193" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="D193" s="26" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
         <is>
           <t>맑은 물(정수기, 수돗물 등등)</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="F193" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="14" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 76 · 기타 24</t>
+        </is>
+      </c>
+      <c r="B194" s="14" t="n"/>
+      <c r="C194" s="14" t="n"/>
+      <c r="D194" s="14" t="n"/>
+      <c r="E194" s="14" t="n"/>
+      <c r="F194" s="14" t="n"/>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B177" s="6" t="n"/>
-      <c r="C177" s="6" t="n"/>
-      <c r="D177" s="6" t="n"/>
-    </row>
-    <row r="178" ht="352" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
+      <c r="B195" s="16" t="n"/>
+      <c r="C195" s="16" t="n"/>
+      <c r="D195" s="16" t="n"/>
+      <c r="E195" s="16" t="n"/>
+      <c r="F195" s="16" t="n"/>
+    </row>
+    <row r="196" ht="352" customHeight="1">
+      <c r="A196" s="17" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -8395,18 +9679,20 @@
         </is>
       </c>
     </row>
-    <row r="179" ht="14" customHeight="1">
-      <c r="A179" s="5" t="inlineStr">
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B179" s="6" t="n"/>
-      <c r="C179" s="6" t="n"/>
-      <c r="D179" s="6" t="n"/>
-    </row>
-    <row r="180" ht="160" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
+      <c r="B197" s="16" t="n"/>
+      <c r="C197" s="16" t="n"/>
+      <c r="D197" s="16" t="n"/>
+      <c r="E197" s="16" t="n"/>
+      <c r="F197" s="16" t="n"/>
+    </row>
+    <row r="198" ht="144" customHeight="1">
+      <c r="A198" s="17" t="inlineStr">
         <is>
           <t>1. 염색 전 샴푸한 후 물기를 닦아주세요. 두피 피지와 오염물이 없으면 염색이 더 잘 됩니다.
 2. 인스턴트 커피 40~60g
@@ -8419,161 +9705,237 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="6" customHeight="1"/>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="1" t="inlineStr">
+    <row r="199" ht="6" customHeight="1"/>
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="5" t="inlineStr">
         <is>
           <t>자초딸기립글로스(솔타입)    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B182" s="2" t="n"/>
-      <c r="C182" s="2" t="n"/>
-      <c r="D182" s="2" t="n"/>
-    </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="3" t="inlineStr">
+      <c r="B200" s="6" t="n"/>
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+      <c r="E200" s="6" t="n"/>
+      <c r="F200" s="6" t="n"/>
+    </row>
+    <row r="201" ht="15" customHeight="1">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
+      <c r="F201" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="96" customHeight="1">
-      <c r="A184" s="8" t="inlineStr">
+    <row r="202" ht="112" customHeight="1">
+      <c r="A202" s="18" t="inlineStr">
         <is>
           <t>자초인퓨즈 / 호호바오일</t>
         </is>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B202" s="18" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C184" s="8" t="inlineStr">
+      <c r="C202" s="19" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="D202" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E202" s="18" t="inlineStr">
         <is>
           <t>한약재, 자초, 지치의 뿌리, 자주색을 띈다하여 자초, 뿌리는 굵고 자주색, 오일에는 붉은 색이 우러나지만 알콜, 물에는 갈변합니다. 천연염색, 민간 약재로 사용, 호호바오일에 담궈서 유효성분을 우림</t>
         </is>
       </c>
-      <c r="D184" s="8" t="inlineStr">
+      <c r="F202" s="18" t="inlineStr">
         <is>
           <t>원하는 / 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="80" customHeight="1">
-      <c r="A185" s="8" t="inlineStr">
+    <row r="203" ht="80" customHeight="1">
+      <c r="A203" s="18" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B185" s="8" t="inlineStr">
+      <c r="B203" s="18" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C185" s="8" t="inlineStr">
+      <c r="C203" s="19" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E203" s="18" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="D185" s="8" t="inlineStr">
+      <c r="F203" s="18" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="8" t="inlineStr">
+    <row r="204" ht="48" customHeight="1">
+      <c r="A204" s="18" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B186" s="8" t="inlineStr">
+      <c r="B204" s="18" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C186" s="8" t="inlineStr">
+      <c r="C204" s="19" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D204" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E204" s="18" t="inlineStr">
         <is>
           <t>식물성 버터, 카리테나무 열매에서 채취, / 보습효과짱^^</t>
         </is>
       </c>
-      <c r="D186" s="8" t="inlineStr">
+      <c r="F204" s="18" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="32" customHeight="1">
-      <c r="A187" s="8" t="inlineStr">
+    <row r="205" ht="32" customHeight="1">
+      <c r="A205" s="18" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B187" s="8" t="inlineStr">
+      <c r="B205" s="18" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C187" s="8" t="inlineStr">
+      <c r="C205" s="19" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D205" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E205" s="18" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취, / 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="D187" s="8" t="inlineStr">
+      <c r="F205" s="18" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="8" t="inlineStr">
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="18" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B188" s="8" t="inlineStr">
+      <c r="B206" s="18" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr">
+      <c r="C206" s="19" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D206" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E206" s="18" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="D188" s="8" t="inlineStr">
+      <c r="F206" s="18" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 65 · 경화 4 · 활성 29 · 향 2</t>
+        </is>
+      </c>
+      <c r="B207" s="14" t="n"/>
+      <c r="C207" s="14" t="n"/>
+      <c r="D207" s="14" t="n"/>
+      <c r="E207" s="14" t="n"/>
+      <c r="F207" s="14" t="n"/>
+    </row>
+    <row r="208" ht="14" customHeight="1">
+      <c r="A208" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="6" t="n"/>
-      <c r="D189" s="6" t="n"/>
-    </row>
-    <row r="190" ht="288" customHeight="1">
-      <c r="A190" s="9" t="inlineStr">
+      <c r="B208" s="16" t="n"/>
+      <c r="C208" s="16" t="n"/>
+      <c r="D208" s="16" t="n"/>
+      <c r="E208" s="16" t="n"/>
+      <c r="F208" s="16" t="n"/>
+    </row>
+    <row r="209" ht="288" customHeight="1">
+      <c r="A209" s="23" t="inlineStr">
         <is>
           <t>2009년부터 만들기 시작한 자초인퓨즈오일로 만든 립밤이 있었죠.
 자초인퓨즈오일, 피마자오일, 시어버터, 칸데릴라왁스, 딸기플레이버오일로 만든 겁나게 촉촉한 립밤인데요
@@ -8591,22 +9953,26 @@
 5ml블랙캡립글로스</t>
         </is>
       </c>
-      <c r="B190" s="10" t="n"/>
-      <c r="C190" s="10" t="n"/>
-      <c r="D190" s="10" t="n"/>
-    </row>
-    <row r="191" ht="14" customHeight="1">
-      <c r="A191" s="5" t="inlineStr">
+      <c r="B209" s="24" t="n"/>
+      <c r="C209" s="24" t="n"/>
+      <c r="D209" s="24" t="n"/>
+      <c r="E209" s="24" t="n"/>
+      <c r="F209" s="24" t="n"/>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B191" s="6" t="n"/>
-      <c r="C191" s="6" t="n"/>
-      <c r="D191" s="6" t="n"/>
-    </row>
-    <row r="192" ht="176" customHeight="1">
-      <c r="A192" s="9" t="inlineStr">
+      <c r="B210" s="16" t="n"/>
+      <c r="C210" s="16" t="n"/>
+      <c r="D210" s="16" t="n"/>
+      <c r="E210" s="16" t="n"/>
+      <c r="F210" s="16" t="n"/>
+    </row>
+    <row r="211" ht="176" customHeight="1">
+      <c r="A211" s="23" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -8618,179 +9984,267 @@
 3. 체에 걸러 낸 후 사용한다.</t>
         </is>
       </c>
-      <c r="B192" s="10" t="n"/>
-      <c r="C192" s="10" t="n"/>
-      <c r="D192" s="10" t="n"/>
-    </row>
-    <row r="193" ht="6" customHeight="1"/>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="1" t="inlineStr">
+      <c r="B211" s="24" t="n"/>
+      <c r="C211" s="24" t="n"/>
+      <c r="D211" s="24" t="n"/>
+      <c r="E211" s="24" t="n"/>
+      <c r="F211" s="24" t="n"/>
+    </row>
+    <row r="212" ht="6" customHeight="1"/>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="5" t="inlineStr">
         <is>
           <t>레드(펄)립글로스    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B194" s="2" t="n"/>
-      <c r="C194" s="2" t="n"/>
-      <c r="D194" s="2" t="n"/>
-    </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="3" t="inlineStr">
+      <c r="B213" s="6" t="n"/>
+      <c r="C213" s="6" t="n"/>
+      <c r="D213" s="6" t="n"/>
+      <c r="E213" s="6" t="n"/>
+      <c r="F213" s="6" t="n"/>
+    </row>
+    <row r="214" ht="15" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B195" s="3" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C195" s="3" t="inlineStr">
+      <c r="C214" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D195" s="3" t="inlineStr">
+      <c r="F214" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="48" customHeight="1">
-      <c r="A196" s="4" t="inlineStr">
+    <row r="215" ht="64" customHeight="1">
+      <c r="A215" s="8" t="inlineStr">
         <is>
           <t>유기농아르간오일</t>
         </is>
       </c>
-      <c r="B196" s="4" t="inlineStr">
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C196" s="4" t="inlineStr">
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="D215" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E215" s="8" t="inlineStr">
         <is>
           <t>전통적으로 모로코 원주민들의 치료와 섭생의 목적으로 사용, 모로코의 올리브오일, 천연비타민E풍부</t>
         </is>
       </c>
-      <c r="D196" s="4" t="inlineStr">
+      <c r="F215" s="8" t="inlineStr">
         <is>
           <t>원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="80" customHeight="1">
-      <c r="A197" s="4" t="inlineStr">
+    <row r="216" ht="80" customHeight="1">
+      <c r="A216" s="8" t="inlineStr">
         <is>
           <t>(자초인퓨즈) / 피마자오일</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr">
+      <c r="B216" s="8" t="inlineStr">
         <is>
           <t>9g</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr">
+      <c r="C216" s="9" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E216" s="8" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="D197" s="4" t="n"/>
-    </row>
-    <row r="198" ht="64" customHeight="1">
-      <c r="A198" s="4" t="inlineStr">
+      <c r="F216" s="8" t="n"/>
+    </row>
+    <row r="217" ht="64" customHeight="1">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>코코아버터</t>
         </is>
       </c>
-      <c r="B198" s="4" t="inlineStr">
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C198" s="4" t="inlineStr">
+      <c r="C217" s="9" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D217" s="10" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E217" s="8" t="inlineStr">
         <is>
           <t>알려진 오일 중 가장 안정적인 것 중 하나 자연적인 산화방지제가 들어있어 산패를 막아주며 부드러운 향, 촉감제공</t>
         </is>
       </c>
-      <c r="D198" s="4" t="inlineStr">
+      <c r="F217" s="8" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="32" customHeight="1">
-      <c r="A199" s="4" t="inlineStr">
+    <row r="218" ht="32" customHeight="1">
+      <c r="A218" s="8" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B199" s="4" t="inlineStr">
+      <c r="B218" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C218" s="9" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D218" s="20" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="E218" s="8" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취, 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="D199" s="4" t="inlineStr">
+      <c r="F218" s="8" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="32" customHeight="1">
-      <c r="A200" s="4" t="inlineStr">
+    <row r="219" ht="32" customHeight="1">
+      <c r="A219" s="8" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B200" s="4" t="inlineStr">
+      <c r="B219" s="8" t="inlineStr">
         <is>
           <t>9방울</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr">
+      <c r="C219" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D219" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E219" s="8" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="D200" s="4" t="inlineStr">
+      <c r="F219" s="8" t="inlineStr">
         <is>
           <t>원하는 플레이버오일, 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="32" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
+    <row r="220" ht="32" customHeight="1">
+      <c r="A220" s="8" t="inlineStr">
         <is>
           <t>실버펄</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr">
+      <c r="B220" s="8" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="C220" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D220" s="21" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E220" s="8" t="inlineStr">
         <is>
           <t>글로시한 느낌, / 기호에 맞게 조절, 넣지 않아도 됨</t>
         </is>
       </c>
-      <c r="D201" s="4" t="n"/>
-    </row>
-    <row r="202" ht="14" customHeight="1">
-      <c r="A202" s="5" t="inlineStr">
+      <c r="F220" s="8" t="n"/>
+    </row>
+    <row r="221" ht="14" customHeight="1">
+      <c r="A221" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 39 · 경화 6 · 활성 51 · 향 3 · 색소 2</t>
+        </is>
+      </c>
+      <c r="B221" s="14" t="n"/>
+      <c r="C221" s="14" t="n"/>
+      <c r="D221" s="14" t="n"/>
+      <c r="E221" s="14" t="n"/>
+      <c r="F221" s="14" t="n"/>
+    </row>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B202" s="6" t="n"/>
-      <c r="C202" s="6" t="n"/>
-      <c r="D202" s="6" t="n"/>
-    </row>
-    <row r="203" ht="192" customHeight="1">
-      <c r="A203" s="7" t="inlineStr">
+      <c r="B222" s="16" t="n"/>
+      <c r="C222" s="16" t="n"/>
+      <c r="D222" s="16" t="n"/>
+      <c r="E222" s="16" t="n"/>
+      <c r="F222" s="16" t="n"/>
+    </row>
+    <row r="223" ht="192" customHeight="1">
+      <c r="A223" s="17" t="inlineStr">
         <is>
           <t>입술에 영양과 윤기를 동시에 줄 수 있는립글로스입니다.
 튜브용기에 넣어서 사용하기 더욱 더 간편하게 만들어봤어요.
@@ -8807,18 +10261,20 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="14" customHeight="1">
-      <c r="A204" s="5" t="inlineStr">
+    <row r="224" ht="14" customHeight="1">
+      <c r="A224" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B204" s="6" t="n"/>
-      <c r="C204" s="6" t="n"/>
-      <c r="D204" s="6" t="n"/>
-    </row>
-    <row r="205" ht="160" customHeight="1">
-      <c r="A205" s="7" t="inlineStr">
+      <c r="B224" s="16" t="n"/>
+      <c r="C224" s="16" t="n"/>
+      <c r="D224" s="16" t="n"/>
+      <c r="E224" s="16" t="n"/>
+      <c r="F224" s="16" t="n"/>
+    </row>
+    <row r="225" ht="160" customHeight="1">
+      <c r="A225" s="17" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -8831,179 +10287,265 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="6" customHeight="1"/>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="1" t="inlineStr">
+    <row r="226" ht="6" customHeight="1"/>
+    <row r="227" ht="22" customHeight="1">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>진주 피지컨트롤 파우더    [진주 / 피지컨트롤 / 파우더]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B207" s="2" t="n"/>
-      <c r="C207" s="2" t="n"/>
-      <c r="D207" s="2" t="n"/>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="3" t="inlineStr">
+      <c r="B227" s="6" t="n"/>
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+      <c r="E227" s="6" t="n"/>
+      <c r="F227" s="6" t="n"/>
+    </row>
+    <row r="228" ht="15" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B208" s="3" t="inlineStr">
+      <c r="B228" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C208" s="3" t="inlineStr">
+      <c r="C228" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D208" s="3" t="inlineStr">
+      <c r="F228" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="8" t="inlineStr">
+    <row r="229" ht="32" customHeight="1">
+      <c r="A229" s="18" t="inlineStr">
         <is>
           <t>진주분말</t>
         </is>
       </c>
-      <c r="B209" s="8" t="inlineStr">
+      <c r="B229" s="18" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C209" s="8" t="inlineStr">
+      <c r="C229" s="19" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D229" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E229" s="18" t="inlineStr">
         <is>
           <t>진주분말, 미네럴 공급, 피지컨트롤</t>
         </is>
       </c>
-      <c r="D209" s="8" t="n"/>
-    </row>
-    <row r="210" ht="80" customHeight="1">
-      <c r="A210" s="8" t="inlineStr">
+      <c r="F229" s="18" t="n"/>
+    </row>
+    <row r="230" ht="96" customHeight="1">
+      <c r="A230" s="18" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B210" s="8" t="inlineStr">
+      <c r="B230" s="18" t="inlineStr">
         <is>
           <t>29g</t>
         </is>
       </c>
-      <c r="C210" s="8" t="inlineStr">
+      <c r="C230" s="19" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="D230" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E230" s="18" t="inlineStr">
         <is>
           <t>피지흡착, 뽀송뽀송</t>
         </is>
       </c>
-      <c r="D210" s="8" t="inlineStr">
+      <c r="F230" s="18" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="32" customHeight="1">
-      <c r="A211" s="8" t="inlineStr">
+    <row r="231" ht="48" customHeight="1">
+      <c r="A231" s="18" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B211" s="8" t="inlineStr">
+      <c r="B231" s="18" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C211" s="8" t="inlineStr">
+      <c r="C231" s="19" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D231" s="22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E231" s="18" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="D211" s="8" t="inlineStr">
+      <c r="F231" s="18" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="48" customHeight="1">
-      <c r="A212" s="8" t="inlineStr">
+    <row r="232" ht="48" customHeight="1">
+      <c r="A232" s="18" t="inlineStr">
         <is>
           <t>로즈제라늄 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B212" s="8" t="inlineStr">
+      <c r="B232" s="18" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C212" s="8" t="inlineStr">
+      <c r="C232" s="19" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D232" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E232" s="18" t="inlineStr">
         <is>
           <t>고가의 장미오일은 아니지만 장미향이 나는 제라늄. 모든 피부 사용. 피지조절</t>
         </is>
       </c>
-      <c r="D212" s="8" t="inlineStr">
+      <c r="F232" s="18" t="inlineStr">
         <is>
           <t>원하는 에센셜오일.</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="80" customHeight="1">
-      <c r="A213" s="8" t="inlineStr">
+    <row r="233" ht="96" customHeight="1">
+      <c r="A233" s="18" t="inlineStr">
         <is>
           <t>카오링클레이</t>
         </is>
       </c>
-      <c r="B213" s="8" t="inlineStr">
+      <c r="B233" s="18" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C213" s="8" t="inlineStr">
+      <c r="C233" s="19" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D233" s="21" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E233" s="18" t="inlineStr">
         <is>
           <t>중국 고령이 원산지인 클레이, 영어발음은 카오링, 현재 세계 다양한 지역에 분포, 채취. 미네럴공급, 화장품, 제약, 식품 등 다양한 용도로 사용됨. 피지컨트롤</t>
         </is>
       </c>
-      <c r="D213" s="8" t="inlineStr">
+      <c r="F233" s="18" t="inlineStr">
         <is>
           <t>화이트클레이</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="48" customHeight="1">
-      <c r="A214" s="8" t="inlineStr">
+    <row r="234" ht="64" customHeight="1">
+      <c r="A234" s="18" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B214" s="8" t="inlineStr">
+      <c r="B234" s="18" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C214" s="8" t="inlineStr">
+      <c r="C234" s="19" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D234" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E234" s="18" t="inlineStr">
         <is>
           <t>진정, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="D214" s="8" t="inlineStr">
+      <c r="F234" s="18" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="14" customHeight="1">
-      <c r="A215" s="5" t="inlineStr">
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="13" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  활성 18 · 향 1 · 색소 16 · 기타 65</t>
+        </is>
+      </c>
+      <c r="B235" s="14" t="n"/>
+      <c r="C235" s="14" t="n"/>
+      <c r="D235" s="14" t="n"/>
+      <c r="E235" s="14" t="n"/>
+      <c r="F235" s="14" t="n"/>
+    </row>
+    <row r="236" ht="14" customHeight="1">
+      <c r="A236" s="15" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B215" s="6" t="n"/>
-      <c r="C215" s="6" t="n"/>
-      <c r="D215" s="6" t="n"/>
-    </row>
-    <row r="216" ht="384" customHeight="1">
-      <c r="A216" s="9" t="inlineStr">
+      <c r="B236" s="16" t="n"/>
+      <c r="C236" s="16" t="n"/>
+      <c r="D236" s="16" t="n"/>
+      <c r="E236" s="16" t="n"/>
+      <c r="F236" s="16" t="n"/>
+    </row>
+    <row r="237" ht="384" customHeight="1">
+      <c r="A237" s="23" t="inlineStr">
         <is>
           <t>여름이면 저에게 고민이 하나 생기는데요..
 오전에는 괜찮지만 오후가 되면 번들녀로 변합니다. (변신~)
@@ -9028,12 +10570,14 @@
 허준 선생이 동의보감에 기술한 진주(珍珠)의 효능을 보면</t>
         </is>
       </c>
-      <c r="B216" s="10" t="n"/>
-      <c r="C216" s="10" t="n"/>
-      <c r="D216" s="10" t="n"/>
-    </row>
-    <row r="217" ht="208" customHeight="1">
-      <c r="A217" s="9" t="inlineStr">
+      <c r="B237" s="24" t="n"/>
+      <c r="C237" s="24" t="n"/>
+      <c r="D237" s="24" t="n"/>
+      <c r="E237" s="24" t="n"/>
+      <c r="F237" s="24" t="n"/>
+    </row>
+    <row r="238" ht="208" customHeight="1">
+      <c r="A238" s="23" t="inlineStr">
         <is>
           <t>"진주가루를 유즙(乳汁)에 섞어 바르면 검은 반점을 제거하며, 얼굴을 윤기나게하여 안색을 좋게한다.",
 "진주는 성질이 차고 무독(無毒)하여 심신을 평안케하며 눈을 밝게 하고 피부의 종기를 다스린다."라고
@@ -9048,22 +10592,26 @@
 위생상 퍼프만 새로 바꿔주세요.</t>
         </is>
       </c>
-      <c r="B217" s="10" t="n"/>
-      <c r="C217" s="10" t="n"/>
-      <c r="D217" s="10" t="n"/>
-    </row>
-    <row r="218" ht="14" customHeight="1">
-      <c r="A218" s="5" t="inlineStr">
+      <c r="B238" s="24" t="n"/>
+      <c r="C238" s="24" t="n"/>
+      <c r="D238" s="24" t="n"/>
+      <c r="E238" s="24" t="n"/>
+      <c r="F238" s="24" t="n"/>
+    </row>
+    <row r="239" ht="14" customHeight="1">
+      <c r="A239" s="15" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B218" s="6" t="n"/>
-      <c r="C218" s="6" t="n"/>
-      <c r="D218" s="6" t="n"/>
-    </row>
-    <row r="219" ht="176" customHeight="1">
-      <c r="A219" s="9" t="inlineStr">
+      <c r="B239" s="16" t="n"/>
+      <c r="C239" s="16" t="n"/>
+      <c r="D239" s="16" t="n"/>
+      <c r="E239" s="16" t="n"/>
+      <c r="F239" s="16" t="n"/>
+    </row>
+    <row r="240" ht="176" customHeight="1">
+      <c r="A240" s="23" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.지퍼백에 모든 재료를 계량하세요.
@@ -9077,124 +10625,147 @@
 9. 완성</t>
         </is>
       </c>
-      <c r="B219" s="10" t="n"/>
-      <c r="C219" s="10" t="n"/>
-      <c r="D219" s="10" t="n"/>
-    </row>
-    <row r="220" ht="6" customHeight="1"/>
+      <c r="B240" s="24" t="n"/>
+      <c r="C240" s="24" t="n"/>
+      <c r="D240" s="24" t="n"/>
+      <c r="E240" s="24" t="n"/>
+      <c r="F240" s="24" t="n"/>
+    </row>
+    <row r="241" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="91">
-    <mergeCell ref="A159:D159"/>
-    <mergeCell ref="A215:D215"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A161:D161"/>
-    <mergeCell ref="A202:D202"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A107:D107"/>
-    <mergeCell ref="A178:D178"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A204:D204"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A135:D135"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A191:D191"/>
-    <mergeCell ref="A169:D169"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A218:D218"/>
-    <mergeCell ref="A137:D137"/>
-    <mergeCell ref="A177:D177"/>
-    <mergeCell ref="A217:D217"/>
-    <mergeCell ref="A136:D136"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A145:D145"/>
-    <mergeCell ref="A179:D179"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A194:D194"/>
-    <mergeCell ref="A203:D203"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A140:D140"/>
-    <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A180:D180"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A93:D93"/>
-    <mergeCell ref="A173:D173"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A83:D83"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A157:D157"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A207:D207"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="A168:D168"/>
-    <mergeCell ref="A205:D205"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="A219:D219"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A106:D106"/>
-    <mergeCell ref="A147:D147"/>
-    <mergeCell ref="A156:D156"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="A148:D148"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A146:D146"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A189:D189"/>
-    <mergeCell ref="A158:D158"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A151:D151"/>
+  <mergeCells count="112">
+    <mergeCell ref="A174:F174"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A238:F238"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A239:F239"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A224:F224"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A237:F237"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A221:F221"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A236:F236"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A223:F223"/>
+    <mergeCell ref="A195:F195"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A213:F213"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A227:F227"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A235:F235"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A222:F222"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A207" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,10 @@
     </font>
     <font>
       <color rgb="003A3A3A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="007A4A2A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +59,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECE0"/>
       </patternFill>
     </fill>
     <fill>
@@ -169,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -179,11 +188,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,31 +205,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -227,17 +237,20 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -319,7 +332,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1092200"/>
+    <pos x="7848600" y="1854200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -339,7 +352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1092200"/>
+    <pos x="9696450" y="1854200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -359,7 +372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1092200"/>
+    <pos x="11544300" y="1854200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -379,7 +392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1092200"/>
+    <pos x="13392150" y="1854200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -399,7 +412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="2940050"/>
+    <pos x="7848600" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -419,7 +432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="2940050"/>
+    <pos x="9696450" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -439,7 +452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="2940050"/>
+    <pos x="11544300" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -459,7 +472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="2940050"/>
+    <pos x="13392150" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -479,7 +492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="4787900"/>
+    <pos x="7848600" y="5549900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -499,7 +512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="4787900"/>
+    <pos x="9696450" y="5549900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -519,7 +532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="9080500"/>
+    <pos x="7848600" y="9842500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -539,7 +552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="9080500"/>
+    <pos x="9696450" y="9842500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -559,7 +572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="9080500"/>
+    <pos x="11544300" y="9842500"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -579,7 +592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="9080500"/>
+    <pos x="13392150" y="9842500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -599,7 +612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="10928350"/>
+    <pos x="7848600" y="11690350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -619,7 +632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="10928350"/>
+    <pos x="9696450" y="11690350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -639,7 +652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="10928350"/>
+    <pos x="11544300" y="11690350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -659,7 +672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="10928350"/>
+    <pos x="13392150" y="11690350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -679,7 +692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="12776200"/>
+    <pos x="7848600" y="13538200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -699,7 +712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="12776200"/>
+    <pos x="9696450" y="13538200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -719,7 +732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="12776200"/>
+    <pos x="11544300" y="13538200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -739,7 +752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="12776200"/>
+    <pos x="13392150" y="13538200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -759,7 +772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19913600"/>
+    <pos x="7848600" y="20675600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -779,7 +792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="19913600"/>
+    <pos x="9696450" y="20675600"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -799,7 +812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="19913600"/>
+    <pos x="11544300" y="20675600"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -819,7 +832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="19913600"/>
+    <pos x="13392150" y="20675600"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -839,7 +852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="21761450"/>
+    <pos x="7848600" y="22523450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -859,7 +872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="21761450"/>
+    <pos x="9696450" y="22523450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -879,7 +892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="21761450"/>
+    <pos x="11544300" y="22523450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -899,7 +912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="21761450"/>
+    <pos x="13392150" y="22523450"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -919,7 +932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="23609300"/>
+    <pos x="7848600" y="24371300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -939,7 +952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="23609300"/>
+    <pos x="9696450" y="24371300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -959,7 +972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="23609300"/>
+    <pos x="11544300" y="24371300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -979,7 +992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="23609300"/>
+    <pos x="13392150" y="24371300"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -999,7 +1012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25457150"/>
+    <pos x="7848600" y="26219150"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1019,7 +1032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="25457150"/>
+    <pos x="9696450" y="26219150"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1039,7 +1052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27381200"/>
+    <pos x="7848600" y="28143200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1059,7 +1072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="27381200"/>
+    <pos x="9696450" y="28143200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1079,7 +1092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="27381200"/>
+    <pos x="11544300" y="28143200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1099,7 +1112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="27381200"/>
+    <pos x="13392150" y="28143200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1119,7 +1132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="29229050"/>
+    <pos x="7848600" y="29991050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1139,7 +1152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="29229050"/>
+    <pos x="9696450" y="29991050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1159,7 +1172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="29229050"/>
+    <pos x="11544300" y="29991050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1179,7 +1192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="29229050"/>
+    <pos x="13392150" y="29991050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1199,7 +1212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31076900"/>
+    <pos x="7848600" y="31838900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1219,7 +1232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31076900"/>
+    <pos x="9696450" y="31838900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1239,7 +1252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31076900"/>
+    <pos x="11544300" y="31838900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1259,7 +1272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31076900"/>
+    <pos x="13392150" y="31838900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1279,7 +1292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="32924750"/>
+    <pos x="7848600" y="33686750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1299,7 +1312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="32924750"/>
+    <pos x="9696450" y="33686750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1319,7 +1332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="32924750"/>
+    <pos x="11544300" y="33686750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1339,7 +1352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="35369500"/>
+    <pos x="7848600" y="36131500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1359,7 +1372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="35369500"/>
+    <pos x="9696450" y="36131500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1379,7 +1392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="35369500"/>
+    <pos x="11544300" y="36131500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1399,7 +1412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="35369500"/>
+    <pos x="13392150" y="36131500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1419,7 +1432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37217350"/>
+    <pos x="7848600" y="37979350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1439,7 +1452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37217350"/>
+    <pos x="9696450" y="37979350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1459,7 +1472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="37217350"/>
+    <pos x="11544300" y="37979350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1479,7 +1492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="37217350"/>
+    <pos x="13392150" y="37979350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1499,7 +1512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="40716200"/>
+    <pos x="7848600" y="41478200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1519,7 +1532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="40716200"/>
+    <pos x="9696450" y="41478200"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1539,7 +1552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="40716200"/>
+    <pos x="11544300" y="41478200"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1559,7 +1572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="40716200"/>
+    <pos x="13392150" y="41478200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1579,7 +1592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="42564050"/>
+    <pos x="7848600" y="43326050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1599,7 +1612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="42564050"/>
+    <pos x="9696450" y="43326050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1619,7 +1632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="42564050"/>
+    <pos x="11544300" y="43326050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1639,7 +1652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="42564050"/>
+    <pos x="13392150" y="43326050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1659,7 +1672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="44411900"/>
+    <pos x="7848600" y="45173900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1679,7 +1692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="44411900"/>
+    <pos x="9696450" y="45173900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1699,7 +1712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="44411900"/>
+    <pos x="11544300" y="45173900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1719,7 +1732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="44411900"/>
+    <pos x="13392150" y="45173900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1739,7 +1752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46259750"/>
+    <pos x="7848600" y="47021750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1759,7 +1772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="46259750"/>
+    <pos x="9696450" y="47021750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1779,7 +1792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="46259750"/>
+    <pos x="11544300" y="47021750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1799,7 +1812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="46259750"/>
+    <pos x="13392150" y="47021750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1819,7 +1832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="48107600"/>
+    <pos x="7848600" y="48869600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1839,7 +1852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="50031650"/>
+    <pos x="7848600" y="50793650"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1859,7 +1872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="50031650"/>
+    <pos x="9696450" y="50793650"/>
     <ext cx="1809750" cy="781050"/>
     <pic>
       <nvPicPr>
@@ -1879,7 +1892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="50031650"/>
+    <pos x="11544300" y="50793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1899,7 +1912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="50031650"/>
+    <pos x="13392150" y="50793650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1919,7 +1932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="51879500"/>
+    <pos x="7848600" y="52641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1939,7 +1952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="51879500"/>
+    <pos x="9696450" y="52641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1959,7 +1972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="51879500"/>
+    <pos x="11544300" y="52641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1979,7 +1992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="51879500"/>
+    <pos x="13392150" y="52641500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1999,7 +2012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="53727350"/>
+    <pos x="7848600" y="54489350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2019,7 +2032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="53727350"/>
+    <pos x="9696450" y="54489350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2039,7 +2052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="53727350"/>
+    <pos x="11544300" y="54489350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2059,7 +2072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="53727350"/>
+    <pos x="13392150" y="54489350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2079,7 +2092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="55575200"/>
+    <pos x="7848600" y="56337200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2099,7 +2112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="55575200"/>
+    <pos x="9696450" y="56337200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2119,7 +2132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="55575200"/>
+    <pos x="11544300" y="56337200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2139,7 +2152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="55575200"/>
+    <pos x="13392150" y="56337200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2159,7 +2172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="57423050"/>
+    <pos x="7848600" y="58185050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2179,7 +2192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="57423050"/>
+    <pos x="9696450" y="58185050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2199,7 +2212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="57423050"/>
+    <pos x="11544300" y="58185050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2219,7 +2232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="57423050"/>
+    <pos x="13392150" y="58185050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2239,7 +2252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="59347100"/>
+    <pos x="7848600" y="60109100"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2259,7 +2272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="59347100"/>
+    <pos x="9696450" y="60109100"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2279,7 +2292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="59347100"/>
+    <pos x="11544300" y="60109100"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2299,7 +2312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="59347100"/>
+    <pos x="13392150" y="60109100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2319,7 +2332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61194950"/>
+    <pos x="7848600" y="61956950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2339,7 +2352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="61194950"/>
+    <pos x="9696450" y="61956950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2359,7 +2372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="61194950"/>
+    <pos x="11544300" y="61956950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2379,7 +2392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="61194950"/>
+    <pos x="13392150" y="61956950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2399,7 +2412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="63042800"/>
+    <pos x="7848600" y="63804800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2419,7 +2432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="63042800"/>
+    <pos x="9696450" y="63804800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2439,7 +2452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="63042800"/>
+    <pos x="11544300" y="63804800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2459,7 +2472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="63042800"/>
+    <pos x="13392150" y="63804800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2479,7 +2492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="64890650"/>
+    <pos x="7848600" y="65652650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2499,7 +2512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="64890650"/>
+    <pos x="9696450" y="65652650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2519,7 +2532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="64890650"/>
+    <pos x="11544300" y="65652650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2539,7 +2552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="64890650"/>
+    <pos x="13392150" y="65652650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2559,7 +2572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="66738500"/>
+    <pos x="7848600" y="67500500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2579,7 +2592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="66738500"/>
+    <pos x="9696450" y="67500500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2599,7 +2612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="66738500"/>
+    <pos x="11544300" y="67500500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2619,7 +2632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="66738500"/>
+    <pos x="13392150" y="67500500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2639,7 +2652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68586350"/>
+    <pos x="7848600" y="69348350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2659,7 +2672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="70510400"/>
+    <pos x="7848600" y="71272400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2679,7 +2692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="70510400"/>
+    <pos x="9696450" y="71272400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2699,7 +2712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="70510400"/>
+    <pos x="11544300" y="71272400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2719,7 +2732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="70510400"/>
+    <pos x="13392150" y="71272400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2739,7 +2752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="72358250"/>
+    <pos x="7848600" y="73120250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2759,7 +2772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="72358250"/>
+    <pos x="9696450" y="73120250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2779,7 +2792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="72358250"/>
+    <pos x="11544300" y="73120250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2799,7 +2812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="72358250"/>
+    <pos x="13392150" y="73120250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2819,7 +2832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="74206100"/>
+    <pos x="7848600" y="74968100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2839,7 +2852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="74206100"/>
+    <pos x="9696450" y="74968100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2859,7 +2872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="74206100"/>
+    <pos x="11544300" y="74968100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2879,7 +2892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="74206100"/>
+    <pos x="13392150" y="74968100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2899,7 +2912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="76053950"/>
+    <pos x="7848600" y="76815950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2919,7 +2932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="76053950"/>
+    <pos x="9696450" y="76815950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2939,7 +2952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="76053950"/>
+    <pos x="11544300" y="76815950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2959,7 +2972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="76053950"/>
+    <pos x="13392150" y="76815950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2979,7 +2992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="77901800"/>
+    <pos x="7848600" y="78663800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2999,7 +3012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="77901800"/>
+    <pos x="9696450" y="78663800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3019,7 +3032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="79825850"/>
+    <pos x="7848600" y="80587850"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -3039,7 +3052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="79825850"/>
+    <pos x="9696450" y="80587850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3059,7 +3072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="79825850"/>
+    <pos x="11544300" y="80587850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3079,7 +3092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="79825850"/>
+    <pos x="13392150" y="80587850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3099,7 +3112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81673700"/>
+    <pos x="7848600" y="82435700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3119,7 +3132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="81673700"/>
+    <pos x="9696450" y="82435700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3139,7 +3152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="81673700"/>
+    <pos x="11544300" y="82435700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3159,7 +3172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="81673700"/>
+    <pos x="13392150" y="82435700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3179,7 +3192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="83521550"/>
+    <pos x="7848600" y="84283550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3199,7 +3212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92894150"/>
+    <pos x="7848600" y="93656150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3219,7 +3232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="92894150"/>
+    <pos x="9696450" y="93656150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3239,7 +3252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="92894150"/>
+    <pos x="11544300" y="93656150"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3259,7 +3272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="92894150"/>
+    <pos x="13392150" y="93656150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3279,7 +3292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="94742000"/>
+    <pos x="7848600" y="95504000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3299,7 +3312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="94742000"/>
+    <pos x="9696450" y="95504000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3319,7 +3332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="94742000"/>
+    <pos x="11544300" y="95504000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3339,7 +3352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="94742000"/>
+    <pos x="13392150" y="95504000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3359,7 +3372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="96589850"/>
+    <pos x="7848600" y="97351850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3379,7 +3392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="96589850"/>
+    <pos x="9696450" y="97351850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3399,7 +3412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="96589850"/>
+    <pos x="11544300" y="97351850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3419,7 +3432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="96589850"/>
+    <pos x="13392150" y="97351850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3439,7 +3452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="98437700"/>
+    <pos x="7848600" y="99199700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3459,7 +3472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="98437700"/>
+    <pos x="9696450" y="99199700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3479,7 +3492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="98437700"/>
+    <pos x="11544300" y="99199700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3499,7 +3512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="98437700"/>
+    <pos x="13392150" y="99199700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3519,7 +3532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="100285550"/>
+    <pos x="7848600" y="101047550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3539,7 +3552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="100285550"/>
+    <pos x="9696450" y="101047550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3559,7 +3572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="100285550"/>
+    <pos x="11544300" y="101047550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3579,7 +3592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="100285550"/>
+    <pos x="13392150" y="101047550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3599,7 +3612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="102133400"/>
+    <pos x="7848600" y="102895400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3619,7 +3632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="104057450"/>
+    <pos x="7848600" y="104819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3639,7 +3652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="104057450"/>
+    <pos x="9696450" y="104819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3659,7 +3672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="104057450"/>
+    <pos x="11544300" y="104819450"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3679,7 +3692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="104057450"/>
+    <pos x="13392150" y="104819450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3699,7 +3712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="105905300"/>
+    <pos x="7848600" y="106667300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3719,7 +3732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="105905300"/>
+    <pos x="9696450" y="106667300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3739,7 +3752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="105905300"/>
+    <pos x="11544300" y="106667300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3759,7 +3772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="105905300"/>
+    <pos x="13392150" y="106667300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3779,7 +3792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="107753150"/>
+    <pos x="7848600" y="108515150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3799,7 +3812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="107753150"/>
+    <pos x="9696450" y="108515150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3819,7 +3832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="107753150"/>
+    <pos x="11544300" y="108515150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3839,7 +3852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="107753150"/>
+    <pos x="13392150" y="108515150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3859,7 +3872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="109601000"/>
+    <pos x="7848600" y="110363000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3879,7 +3892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="109601000"/>
+    <pos x="9696450" y="110363000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3899,7 +3912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="109601000"/>
+    <pos x="11544300" y="110363000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3919,7 +3932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="109601000"/>
+    <pos x="13392150" y="110363000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3939,7 +3952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="111448850"/>
+    <pos x="7848600" y="112210850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3959,7 +3972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="111448850"/>
+    <pos x="9696450" y="112210850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3979,7 +3992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="111448850"/>
+    <pos x="11544300" y="112210850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3999,7 +4012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="111448850"/>
+    <pos x="13392150" y="112210850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4019,7 +4032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="113296700"/>
+    <pos x="7848600" y="114058700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4039,7 +4052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="115220750"/>
+    <pos x="7848600" y="115982750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4059,7 +4072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="115220750"/>
+    <pos x="9696450" y="115982750"/>
     <ext cx="1428750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4079,7 +4092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="115220750"/>
+    <pos x="11544300" y="115982750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4099,7 +4112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="115220750"/>
+    <pos x="13392150" y="115982750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4119,7 +4132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="117068600"/>
+    <pos x="7848600" y="117830600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4139,7 +4152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="117068600"/>
+    <pos x="9696450" y="117830600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4159,7 +4172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="117068600"/>
+    <pos x="11544300" y="117830600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4179,7 +4192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="117068600"/>
+    <pos x="13392150" y="117830600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4199,7 +4212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118916450"/>
+    <pos x="7848600" y="119678450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4219,7 +4232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="118916450"/>
+    <pos x="9696450" y="119678450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4239,7 +4252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="118916450"/>
+    <pos x="11544300" y="119678450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4259,7 +4272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="118916450"/>
+    <pos x="13392150" y="119678450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4279,7 +4292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="120764300"/>
+    <pos x="7848600" y="121526300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4299,7 +4312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="120764300"/>
+    <pos x="9696450" y="121526300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4319,7 +4332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="120764300"/>
+    <pos x="11544300" y="121526300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4339,7 +4352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="120764300"/>
+    <pos x="13392150" y="121526300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4359,7 +4372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="122612150"/>
+    <pos x="7848600" y="123374150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4379,7 +4392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="122612150"/>
+    <pos x="9696450" y="123374150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4399,7 +4412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="122612150"/>
+    <pos x="11544300" y="123374150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4419,7 +4432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="122612150"/>
+    <pos x="13392150" y="123374150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4439,7 +4452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="125444250"/>
+    <pos x="7848600" y="126206250"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4459,7 +4472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="125444250"/>
+    <pos x="9696450" y="126206250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4479,7 +4492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="125444250"/>
+    <pos x="11544300" y="126206250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4499,7 +4512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="125444250"/>
+    <pos x="13392150" y="126206250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4519,7 +4532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="127292100"/>
+    <pos x="7848600" y="128054100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4539,7 +4552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="127292100"/>
+    <pos x="9696450" y="128054100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4559,7 +4572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="127292100"/>
+    <pos x="11544300" y="128054100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4579,7 +4592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="127292100"/>
+    <pos x="13392150" y="128054100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4599,7 +4612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="129139950"/>
+    <pos x="7848600" y="129901950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4619,7 +4632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="129139950"/>
+    <pos x="9696450" y="129901950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4639,7 +4652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="129139950"/>
+    <pos x="11544300" y="129901950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4659,7 +4672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="132619750"/>
+    <pos x="7848600" y="133381750"/>
     <ext cx="1809750" cy="1019175"/>
     <pic>
       <nvPicPr>
@@ -4679,7 +4692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="132619750"/>
+    <pos x="9696450" y="133381750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4699,7 +4712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="132619750"/>
+    <pos x="11544300" y="133381750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4719,7 +4732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="132619750"/>
+    <pos x="13392150" y="133381750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4739,7 +4752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="134467600"/>
+    <pos x="7848600" y="135229600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4759,7 +4772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="134467600"/>
+    <pos x="9696450" y="135229600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4779,7 +4792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="134467600"/>
+    <pos x="11544300" y="135229600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4799,7 +4812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="141014450"/>
+    <pos x="7848600" y="141776450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4819,7 +4832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="141014450"/>
+    <pos x="9696450" y="141776450"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4839,7 +4852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="141014450"/>
+    <pos x="11544300" y="141776450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4859,7 +4872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="141014450"/>
+    <pos x="13392150" y="141776450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4879,7 +4892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="142862300"/>
+    <pos x="7848600" y="143624300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4899,7 +4912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="142862300"/>
+    <pos x="9696450" y="143624300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4919,7 +4932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="142862300"/>
+    <pos x="11544300" y="143624300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4939,7 +4952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="142862300"/>
+    <pos x="13392150" y="143624300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4959,7 +4972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="151644350"/>
+    <pos x="7848600" y="152406350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4979,7 +4992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="151644350"/>
+    <pos x="9696450" y="152406350"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4999,7 +5012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="151644350"/>
+    <pos x="11544300" y="152406350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5019,7 +5032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="151644350"/>
+    <pos x="13392150" y="152406350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5039,7 +5052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="153492200"/>
+    <pos x="7848600" y="154254200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5059,7 +5072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="153492200"/>
+    <pos x="9696450" y="154254200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5079,7 +5092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="153492200"/>
+    <pos x="11544300" y="154254200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5099,7 +5112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="153492200"/>
+    <pos x="13392150" y="154254200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5119,7 +5132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="161055050"/>
+    <pos x="7848600" y="161817050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5139,7 +5152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="161055050"/>
+    <pos x="9696450" y="161817050"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5159,7 +5172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="161055050"/>
+    <pos x="11544300" y="161817050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5179,7 +5192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="161055050"/>
+    <pos x="13392150" y="161817050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5199,7 +5212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="162902900"/>
+    <pos x="7848600" y="163664900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5219,7 +5232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="162902900"/>
+    <pos x="9696450" y="163664900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5239,7 +5252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="162902900"/>
+    <pos x="11544300" y="163664900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5259,7 +5272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="162902900"/>
+    <pos x="13392150" y="163664900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5279,7 +5292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="164750750"/>
+    <pos x="7848600" y="165512750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5299,7 +5312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="164750750"/>
+    <pos x="9696450" y="165512750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5319,7 +5332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="164750750"/>
+    <pos x="11544300" y="165512750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5630,7 +5643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5678,163 +5691,166 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
     </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 이 제형 배합 주의·기본원칙
+· 파우더(색소·마이카)는 뭉치면 색 얼룩 → 미리 갈거나 분산제로 분산.
+· 립·무수 색조는 방부 불필요, 수분 유입만 주의.
+· 눈가·입술용은 사용 허가된 색소인지 확인(안전성·규제).</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>촉촉 글로우 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>(겁나게 촉촉) 립밤</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>멀티밤오일 +멀티밤 왁스</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>(로즈우드)에센셜오일</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2~3방울</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>향, 향기 테라피</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>립컬러 베이스</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>레드6(0.3), 아이론 옐로우 (0.1), 레드27 (0.2), 화이트 (0.2)</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>사용하던 립스틱</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 88 · 향 1 · 기타 11</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 88 · 향 1 · 기타 11</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
@@ -5843,8 +5859,20 @@
       <c r="E11" s="16" t="n"/>
       <c r="F11" s="16" t="n"/>
     </row>
-    <row r="12" ht="256" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="256" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>겁나게 촉촉~
 글로우 립스틱
@@ -5864,20 +5892,20 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="176" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="176" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>촉촉 글로우 립스틱만들기
 1. 비커에 립컬러를 계량하세요.
@@ -5893,287 +5921,275 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>멀티밤 bb    [1..베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>멀티오일베이스</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>MCT, 로즈힙, 유기농 호호바, 녹차씨, 발효동백, 스쿠알란, 비타민E 등</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>유기농 / 코포아수버터</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>식물성 버터, / 끈적임 적고 수분함량 높고 아주 부드러움</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>망고버터 등</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>식물성 왁스, 단단하게.</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>칼라믹스 / 파운데이션</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 함유, / 파운데이션 파우더</t>
         </is>
       </c>
-      <c r="F21" s="18" t="n"/>
-    </row>
-    <row r="22" ht="64" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="F22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>보르피린</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>볼륨업, 주름</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>10 g(10%)을 원한다면 로즈워터를 5g 줄여서 40g이 되도록 해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>알파 비사보롤</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>0.3g / (10방울)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>식약처 인증, 미백 원료</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>버가못에센셜오일</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>0.7g / 10~14방울</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>FCF, 버갑텐 프리, / 감귤껍질오일, 아로마테라피</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 61 · 경화 16 · 활성 6 · 향 2 · 색소 13 · 기타 1</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="14" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="14" t="n"/>
     </row>
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 61 · 경화 16 · 활성 6 · 향 2 · 색소 13 · 기타 1</t>
         </is>
       </c>
       <c r="B26" s="16" t="n"/>
@@ -6182,8 +6198,20 @@
       <c r="E26" s="16" t="n"/>
       <c r="F26" s="16" t="n"/>
     </row>
-    <row r="27" ht="336" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+    </row>
+    <row r="28" ht="336" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>이 레시피는 2015년에
 문화센터에서 반응이 좋다며
@@ -6208,26 +6236,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="24" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="26" t="n"/>
+      <c r="F28" s="26" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-    </row>
-    <row r="29" ht="176" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="176" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>1. 멀티오일베이스를 계량하세요.
 2. 왁스와 버터를 계량한 후
@@ -6242,265 +6270,253 @@
 굳으면 완성</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>카렌듈라 썬밤    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>피지성분 비슷, / 가벼운 오일 또는 액상왁스</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D34" s="10" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일, 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>캐모마일인퓨즈오일</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="64" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>산화방지.</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D37" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>산화 아연 분말</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>전체양의 23%</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>3~9방울</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>썬번, 진정, 아로마테라피</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 47 · 경화 27 · 활성 1 · 향 1 · 기타 24</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="n"/>
-      <c r="C39" s="14" t="n"/>
-      <c r="D39" s="14" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="14" t="n"/>
     </row>
     <row r="40" ht="14" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 47 · 경화 27 · 활성 1 · 향 1 · 기타 24</t>
         </is>
       </c>
       <c r="B40" s="16" t="n"/>
@@ -6509,27 +6525,39 @@
       <c r="E40" s="16" t="n"/>
       <c r="F40" s="16" t="n"/>
     </row>
-    <row r="41" ht="16" customHeight="1">
+    <row r="41" ht="14" customHeight="1">
       <c r="A41" s="17" t="inlineStr">
         <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
           <t>초정밀 과정</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="192" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="192" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>1. 징크옥사이드를 종이에 계량하세요.
 2. 비커에 1번 재료를 계량합니다.
@@ -6546,292 +6574,280 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="103" customHeight="1"/>
-    <row r="45" ht="6" customHeight="1"/>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="45" ht="103" customHeight="1"/>
+    <row r="46" ht="6" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>내추럴 립스틱    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="8" t="n"/>
+      <c r="F47" s="8" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>정제 호호바오일</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C48" s="19" t="inlineStr">
+      <c r="C49" s="21" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="D48" s="10" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E49" s="20" t="inlineStr">
         <is>
           <t>가벼운오일, 보습</t>
         </is>
       </c>
-      <c r="F48" s="18" t="inlineStr">
+      <c r="F49" s="20" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="50" ht="48" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>립베이스 레드27</t>
         </is>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>0.4g</t>
         </is>
       </c>
-      <c r="C49" s="19" t="inlineStr">
+      <c r="C50" s="21" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E49" s="18" t="inlineStr">
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="F49" s="18" t="inlineStr">
+      <c r="F50" s="20" t="inlineStr">
         <is>
           <t>더 진한 색을 원하면 / 양을 추가하세요.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="18" t="inlineStr">
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>3.5g</t>
         </is>
       </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="C51" s="21" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D51" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>식물성왁스. 경화제</t>
         </is>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C51" s="19" t="inlineStr">
+      <c r="C52" s="21" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E51" s="18" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습</t>
         </is>
       </c>
-      <c r="F51" s="18" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="18" t="inlineStr">
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>발효 동백오일</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C52" s="19" t="inlineStr">
+      <c r="C53" s="21" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D52" s="22" t="inlineStr">
+      <c r="D53" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E52" s="18" t="inlineStr">
+      <c r="E53" s="20" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F52" s="18" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>아르간, 마유 등</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="64" customHeight="1">
-      <c r="A53" s="18" t="inlineStr">
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C53" s="19" t="inlineStr">
+      <c r="C54" s="21" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D53" s="22" t="inlineStr">
+      <c r="D54" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E53" s="18" t="inlineStr">
+      <c r="E54" s="20" t="inlineStr">
         <is>
           <t>산화방지, 고보습</t>
         </is>
       </c>
-      <c r="F53" s="18" t="inlineStr">
+      <c r="F54" s="20" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="18" t="inlineStr">
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C54" s="19" t="inlineStr">
+      <c r="C55" s="21" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E54" s="18" t="inlineStr">
+      <c r="E55" s="20" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F54" s="18" t="inlineStr">
+      <c r="F55" s="20" t="inlineStr">
         <is>
           <t>아로마테라피효과 / 원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 58 · 경화 23 · 활성 14 · 향 2 · 기타 3</t>
-        </is>
-      </c>
-      <c r="B55" s="14" t="n"/>
-      <c r="C55" s="14" t="n"/>
-      <c r="D55" s="14" t="n"/>
-      <c r="E55" s="14" t="n"/>
-      <c r="F55" s="14" t="n"/>
     </row>
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 58 · 경화 23 · 활성 14 · 향 2 · 기타 3</t>
         </is>
       </c>
       <c r="B56" s="16" t="n"/>
@@ -6840,34 +6856,46 @@
       <c r="E56" s="16" t="n"/>
       <c r="F56" s="16" t="n"/>
     </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="23" t="inlineStr">
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+    </row>
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>촉촉한 립밤에 색상을 더했습니다. 내추럴 립스틱!
 가루날림이 없는 립베이스로 원하는 색상을 만들어보세요.
 오일에 미리 개어서 원하는 색상을 만든 후 적용하면 됩니다.</t>
         </is>
       </c>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="24" t="n"/>
-      <c r="D57" s="24" t="n"/>
-      <c r="E57" s="24" t="n"/>
-      <c r="F57" s="24" t="n"/>
-    </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="15" t="inlineStr">
+      <c r="B58" s="26" t="n"/>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="26" t="n"/>
+      <c r="E58" s="26" t="n"/>
+      <c r="F58" s="26" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="16" t="n"/>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
-    </row>
-    <row r="59" ht="208" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+    </row>
+    <row r="60" ht="208" customHeight="1">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 속뚜껑을 닫고 뒤집어 주세요.
@@ -6884,137 +6912,125 @@
 12.꺼내서 넘친 부분도 다듬어 닦습니다. 스티커를 붙이고 겉뚜껑을 닫으면 완성.</t>
         </is>
       </c>
-      <c r="B59" s="24" t="n"/>
-      <c r="C59" s="24" t="n"/>
-      <c r="D59" s="24" t="n"/>
-      <c r="E59" s="24" t="n"/>
-      <c r="F59" s="24" t="n"/>
-    </row>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="B60" s="26" t="n"/>
+      <c r="C60" s="26" t="n"/>
+      <c r="D60" s="26" t="n"/>
+      <c r="E60" s="26" t="n"/>
+      <c r="F60" s="26" t="n"/>
+    </row>
+    <row r="61" ht="6" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>립스틱/글로스 컬러베이스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B62" s="7" t="inlineStr">
+      <c r="B63" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D63" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F63" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>(골든)호호바오일</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D63" s="10" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>액상왁스, 가벼운 오일</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>마카다미아넛오일</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>립 컬러베이스 7</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D64" s="12" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 89 · 기타 11</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="n"/>
-      <c r="C65" s="14" t="n"/>
-      <c r="D65" s="14" t="n"/>
-      <c r="E65" s="14" t="n"/>
-      <c r="F65" s="14" t="n"/>
     </row>
     <row r="66" ht="14" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 89 · 기타 11</t>
         </is>
       </c>
       <c r="B66" s="16" t="n"/>
@@ -7023,8 +7039,20 @@
       <c r="E66" s="16" t="n"/>
       <c r="F66" s="16" t="n"/>
     </row>
-    <row r="67" ht="192" customHeight="1">
+    <row r="67" ht="14" customHeight="1">
       <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+    </row>
+    <row r="68" ht="192" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>원하는 색상의 립제품 만들기 좋은 립컬러 베이스가 나왔습니다.
 쉽게 활용하는 법을 안내해드립니다.
@@ -7041,20 +7069,20 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="16" t="n"/>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
-    </row>
-    <row r="69" ht="96" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="B69" s="18" t="n"/>
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+    </row>
+    <row r="70" ht="96" customHeight="1">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>1. (골든)호호바오일 4g을 먼저 계량합니다.
 2.원하는 립컬러 베이스를 비커에 발라주세요.
@@ -7064,259 +7092,247 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="6" customHeight="1"/>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="71" ht="6" customHeight="1"/>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>블루밍 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="18" t="inlineStr">
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>발효 마유</t>
         </is>
       </c>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C73" s="19" t="inlineStr">
+      <c r="C74" s="21" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D73" s="22" t="inlineStr">
+      <c r="D74" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E73" s="18" t="inlineStr">
+      <c r="E74" s="20" t="inlineStr">
         <is>
           <t>오래가는 보습</t>
         </is>
       </c>
-      <c r="F73" s="18" t="inlineStr">
+      <c r="F74" s="20" t="inlineStr">
         <is>
           <t>동백, 아르간오일 등</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="18" t="inlineStr">
+    <row r="75" ht="48" customHeight="1">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>피마자유</t>
         </is>
       </c>
-      <c r="B74" s="18" t="inlineStr">
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C74" s="19" t="inlineStr">
+      <c r="C75" s="21" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D74" s="12" t="inlineStr">
+      <c r="D75" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E74" s="18" t="inlineStr">
+      <c r="E75" s="20" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습, / 아주까리유</t>
         </is>
       </c>
-      <c r="F74" s="18" t="inlineStr">
+      <c r="F75" s="20" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="64" customHeight="1">
-      <c r="A75" s="18" t="inlineStr">
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B75" s="18" t="inlineStr">
+      <c r="B76" s="20" t="inlineStr">
         <is>
           <t>0.1g</t>
         </is>
       </c>
-      <c r="C75" s="19" t="inlineStr">
+      <c r="C76" s="21" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D75" s="22" t="inlineStr">
+      <c r="D76" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E75" s="18" t="inlineStr">
+      <c r="E76" s="20" t="inlineStr">
         <is>
           <t>산화방지제</t>
         </is>
       </c>
-      <c r="F75" s="18" t="inlineStr">
+      <c r="F76" s="20" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="18" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="20" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C76" s="19" t="inlineStr">
+      <c r="C77" s="21" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="D76" s="20" t="inlineStr">
+      <c r="D77" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E76" s="18" t="inlineStr">
+      <c r="E77" s="20" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="F76" s="18" t="inlineStr">
+      <c r="F77" s="20" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="64" customHeight="1">
-      <c r="A77" s="18" t="inlineStr">
+    <row r="78" ht="64" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t>립 컬러베이스 / (액상)</t>
         </is>
       </c>
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B78" s="20" t="inlineStr">
         <is>
           <t>4.5g</t>
         </is>
       </c>
-      <c r="C77" s="19" t="inlineStr">
+      <c r="C78" s="21" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="D77" s="10" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E77" s="18" t="inlineStr">
+      <c r="E78" s="20" t="inlineStr">
         <is>
           <t>미리 만들어놓으세요. / 호호바오일 4g, / 원하는 립컬러베이스 0.5g / 상세 만들기 방법 참고</t>
         </is>
       </c>
-      <c r="F77" s="18" t="inlineStr">
+      <c r="F78" s="20" t="inlineStr">
         <is>
           <t>미리 만들어놓은 / 9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="18" t="inlineStr">
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="20" t="inlineStr">
         <is>
           <t>로즈우드EO</t>
         </is>
       </c>
-      <c r="B78" s="18" t="inlineStr">
+      <c r="B79" s="20" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C78" s="19" t="inlineStr">
+      <c r="C79" s="21" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D79" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E78" s="18" t="inlineStr">
+      <c r="E79" s="20" t="inlineStr">
         <is>
           <t>향, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="F78" s="18" t="inlineStr">
+      <c r="F79" s="20" t="inlineStr">
         <is>
           <t>원하는에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 35 · 경화 8 · 활성 16 · 향 2 · 기타 39</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="n"/>
-      <c r="C79" s="14" t="n"/>
-      <c r="D79" s="14" t="n"/>
-      <c r="E79" s="14" t="n"/>
-      <c r="F79" s="14" t="n"/>
     </row>
     <row r="80" ht="14" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 35 · 경화 8 · 활성 16 · 향 2 · 기타 39</t>
         </is>
       </c>
       <c r="B80" s="16" t="n"/>
@@ -7325,8 +7341,20 @@
       <c r="E80" s="16" t="n"/>
       <c r="F80" s="16" t="n"/>
     </row>
-    <row r="81" ht="112" customHeight="1">
-      <c r="A81" s="23" t="inlineStr">
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="n"/>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+    </row>
+    <row r="82" ht="112" customHeight="1">
+      <c r="A82" s="25" t="inlineStr">
         <is>
           <t>위)달달한 핑크, 아래)갸우뚱 레드
 위)알쏭달쏭 핑크레드(27번+ 레드6) , 아래)단물 빠진 와인 (레드33)
@@ -7337,26 +7365,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B81" s="24" t="n"/>
-      <c r="C81" s="24" t="n"/>
-      <c r="D81" s="24" t="n"/>
-      <c r="E81" s="24" t="n"/>
-      <c r="F81" s="24" t="n"/>
-    </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="15" t="inlineStr">
+      <c r="B82" s="26" t="n"/>
+      <c r="C82" s="26" t="n"/>
+      <c r="D82" s="26" t="n"/>
+      <c r="E82" s="26" t="n"/>
+      <c r="F82" s="26" t="n"/>
+    </row>
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B82" s="16" t="n"/>
-      <c r="C82" s="16" t="n"/>
-      <c r="D82" s="16" t="n"/>
-      <c r="E82" s="16" t="n"/>
-      <c r="F82" s="16" t="n"/>
-    </row>
-    <row r="83" ht="160" customHeight="1">
-      <c r="A83" s="23" t="inlineStr">
+      <c r="B83" s="18" t="n"/>
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+    </row>
+    <row r="84" ht="160" customHeight="1">
+      <c r="A84" s="25" t="inlineStr">
         <is>
           <t>1.미리 만들어놓은 색을 먼저 선택하세요. (달달한 핑크나
 2.잘익은 홍시 등 색상표를 참고해 만들어보세요.)
@@ -7369,145 +7397,133 @@
 9.용기에 담아서 속뚜껑 닫으면 완성~!</t>
         </is>
       </c>
-      <c r="B83" s="24" t="n"/>
-      <c r="C83" s="24" t="n"/>
-      <c r="D83" s="24" t="n"/>
-      <c r="E83" s="24" t="n"/>
-      <c r="F83" s="24" t="n"/>
-    </row>
-    <row r="84" ht="136.5" customHeight="1">
-      <c r="A84" s="24" t="n"/>
-      <c r="B84" s="24" t="n"/>
-      <c r="C84" s="24" t="n"/>
-      <c r="D84" s="24" t="n"/>
-      <c r="E84" s="24" t="n"/>
-      <c r="F84" s="24" t="n"/>
-    </row>
-    <row r="85" ht="6" customHeight="1"/>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B84" s="26" t="n"/>
+      <c r="C84" s="26" t="n"/>
+      <c r="D84" s="26" t="n"/>
+      <c r="E84" s="26" t="n"/>
+      <c r="F84" s="26" t="n"/>
+    </row>
+    <row r="85" ht="136.5" customHeight="1">
+      <c r="A85" s="26" t="n"/>
+      <c r="B85" s="26" t="n"/>
+      <c r="C85" s="26" t="n"/>
+      <c r="D85" s="26" t="n"/>
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="26" t="n"/>
+    </row>
+    <row r="86" ht="6" customHeight="1"/>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>촉촉 쁘띠 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="8" t="n"/>
+      <c r="D87" s="8" t="n"/>
+      <c r="E87" s="8" t="n"/>
+      <c r="F87" s="8" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C88" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D88" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F87" s="7" t="inlineStr">
+      <c r="F88" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="48" customHeight="1">
-      <c r="A88" s="8" t="inlineStr">
+    <row r="89" ht="48" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D88" s="10" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E89" s="10" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F89" s="10" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="8" t="inlineStr">
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C89" s="9" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E90" s="10" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F90" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 95 · 향 5</t>
-        </is>
-      </c>
-      <c r="B90" s="14" t="n"/>
-      <c r="C90" s="14" t="n"/>
-      <c r="D90" s="14" t="n"/>
-      <c r="E90" s="14" t="n"/>
-      <c r="F90" s="14" t="n"/>
     </row>
     <row r="91" ht="14" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 95 · 향 5</t>
         </is>
       </c>
       <c r="B91" s="16" t="n"/>
@@ -7516,8 +7532,20 @@
       <c r="E91" s="16" t="n"/>
       <c r="F91" s="16" t="n"/>
     </row>
-    <row r="92" ht="80" customHeight="1">
+    <row r="92" ht="14" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="n"/>
+      <c r="C92" s="18" t="n"/>
+      <c r="D92" s="18" t="n"/>
+      <c r="E92" s="18" t="n"/>
+      <c r="F92" s="18" t="n"/>
+    </row>
+    <row r="93" ht="80" customHeight="1">
+      <c r="A93" s="19" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -7527,20 +7555,20 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="14" customHeight="1">
-      <c r="A93" s="15" t="inlineStr">
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B93" s="16" t="n"/>
-      <c r="C93" s="16" t="n"/>
-      <c r="D93" s="16" t="n"/>
-      <c r="E93" s="16" t="n"/>
-      <c r="F93" s="16" t="n"/>
-    </row>
-    <row r="94" ht="384" customHeight="1">
-      <c r="A94" s="17" t="inlineStr">
+      <c r="B94" s="18" t="n"/>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+    </row>
+    <row r="95" ht="384" customHeight="1">
+      <c r="A95" s="19" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7567,132 +7595,120 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="120.5" customHeight="1"/>
-    <row r="96" ht="6" customHeight="1"/>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="96" ht="120.5" customHeight="1"/>
+    <row r="97" ht="6" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>픽미업 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="8" t="n"/>
+      <c r="D98" s="8" t="n"/>
+      <c r="E98" s="8" t="n"/>
+      <c r="F98" s="8" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B99" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C99" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
+      <c r="D99" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E98" s="7" t="inlineStr">
+      <c r="E99" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F98" s="7" t="inlineStr">
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="18" t="inlineStr">
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B99" s="18" t="inlineStr">
+      <c r="B100" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C99" s="19" t="inlineStr">
+      <c r="C100" s="21" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D99" s="10" t="inlineStr">
+      <c r="D100" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E99" s="18" t="inlineStr">
+      <c r="E100" s="20" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F99" s="18" t="inlineStr">
+      <c r="F100" s="20" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="18" t="inlineStr">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="20" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B100" s="18" t="inlineStr">
+      <c r="B101" s="20" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C100" s="19" t="inlineStr">
+      <c r="C101" s="21" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D101" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E100" s="18" t="inlineStr">
+      <c r="E101" s="20" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="F100" s="18" t="inlineStr">
+      <c r="F101" s="20" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="101" ht="14" customHeight="1">
-      <c r="A101" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 95 · 향 5</t>
-        </is>
-      </c>
-      <c r="B101" s="14" t="n"/>
-      <c r="C101" s="14" t="n"/>
-      <c r="D101" s="14" t="n"/>
-      <c r="E101" s="14" t="n"/>
-      <c r="F101" s="14" t="n"/>
     </row>
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 95 · 향 5</t>
         </is>
       </c>
       <c r="B102" s="16" t="n"/>
@@ -7701,8 +7717,20 @@
       <c r="E102" s="16" t="n"/>
       <c r="F102" s="16" t="n"/>
     </row>
-    <row r="103" ht="224" customHeight="1">
-      <c r="A103" s="23" t="inlineStr">
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="n"/>
+      <c r="C103" s="18" t="n"/>
+      <c r="D103" s="18" t="n"/>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+    </row>
+    <row r="104" ht="224" customHeight="1">
+      <c r="A104" s="25" t="inlineStr">
         <is>
           <t>와인, 브라운, 오렌지...
 가을, 겨울에 잘 어울리는 색상을
@@ -7720,26 +7748,26 @@
 진하기를 조절하세요.</t>
         </is>
       </c>
-      <c r="B103" s="24" t="n"/>
-      <c r="C103" s="24" t="n"/>
-      <c r="D103" s="24" t="n"/>
-      <c r="E103" s="24" t="n"/>
-      <c r="F103" s="24" t="n"/>
-    </row>
-    <row r="104" ht="14" customHeight="1">
-      <c r="A104" s="15" t="inlineStr">
+      <c r="B104" s="26" t="n"/>
+      <c r="C104" s="26" t="n"/>
+      <c r="D104" s="26" t="n"/>
+      <c r="E104" s="26" t="n"/>
+      <c r="F104" s="26" t="n"/>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B104" s="16" t="n"/>
-      <c r="C104" s="16" t="n"/>
-      <c r="D104" s="16" t="n"/>
-      <c r="E104" s="16" t="n"/>
-      <c r="F104" s="16" t="n"/>
-    </row>
-    <row r="105" ht="384" customHeight="1">
-      <c r="A105" s="23" t="inlineStr">
+      <c r="B105" s="18" t="n"/>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="18" t="n"/>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="18" t="n"/>
+    </row>
+    <row r="106" ht="384" customHeight="1">
+      <c r="A106" s="25" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7765,237 +7793,225 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B105" s="24" t="n"/>
-      <c r="C105" s="24" t="n"/>
-      <c r="D105" s="24" t="n"/>
-      <c r="E105" s="24" t="n"/>
-      <c r="F105" s="24" t="n"/>
-    </row>
-    <row r="106" ht="122" customHeight="1">
-      <c r="A106" s="24" t="n"/>
-      <c r="B106" s="24" t="n"/>
-      <c r="C106" s="24" t="n"/>
-      <c r="D106" s="24" t="n"/>
-      <c r="E106" s="24" t="n"/>
-      <c r="F106" s="24" t="n"/>
-    </row>
-    <row r="107" ht="6" customHeight="1"/>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="B106" s="26" t="n"/>
+      <c r="C106" s="26" t="n"/>
+      <c r="D106" s="26" t="n"/>
+      <c r="E106" s="26" t="n"/>
+      <c r="F106" s="26" t="n"/>
+    </row>
+    <row r="107" ht="122" customHeight="1">
+      <c r="A107" s="26" t="n"/>
+      <c r="B107" s="26" t="n"/>
+      <c r="C107" s="26" t="n"/>
+      <c r="D107" s="26" t="n"/>
+      <c r="E107" s="26" t="n"/>
+      <c r="F107" s="26" t="n"/>
+    </row>
+    <row r="108" ht="6" customHeight="1"/>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="7" t="inlineStr">
         <is>
           <t>생기ON~ 립스틱    [1. 립밤 베이스 / (52.5g)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="7" t="inlineStr">
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="8" t="n"/>
+      <c r="D109" s="8" t="n"/>
+      <c r="E109" s="8" t="n"/>
+      <c r="F109" s="8" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B110" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D109" s="7" t="inlineStr">
+      <c r="D110" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E109" s="7" t="inlineStr">
+      <c r="E110" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
+      <c r="F110" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="111" ht="48" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>자초립밤 / 오일 베이스</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>43g</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>자근추출물, 호호바오일, 아몬드오일, 피마자오일, 해바라기씨오일, 비타민E</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>자초인퓨즈오일, 원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>9.5g</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="D111" s="20" t="inlineStr">
+      <c r="D112" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
+      <c r="E112" s="10" t="inlineStr">
         <is>
           <t>식물성 경화제</t>
         </is>
       </c>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="F112" s="10" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>립밤 베이스</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D112" s="12" t="inlineStr">
+      <c r="D113" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
+      <c r="E113" s="10" t="inlineStr">
         <is>
           <t>위의 레시피로 / 미리 만들것.</t>
         </is>
       </c>
-      <c r="F112" s="8" t="inlineStr">
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>립 컬러 베이스</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D113" s="12" t="inlineStr">
+      <c r="D114" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E114" s="10" t="inlineStr">
         <is>
           <t>레드27 + 레드21</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>원하는 / 색상</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>에센셜오일 (EO)</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="10" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E114" s="8" t="n"/>
-      <c r="F114" s="8" t="inlineStr">
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
-    </row>
-    <row r="115" ht="14" customHeight="1">
-      <c r="A115" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 75 · 경화 17 · 향 0 · 기타 8</t>
-        </is>
-      </c>
-      <c r="B115" s="14" t="n"/>
-      <c r="C115" s="14" t="n"/>
-      <c r="D115" s="14" t="n"/>
-      <c r="E115" s="14" t="n"/>
-      <c r="F115" s="14" t="n"/>
     </row>
     <row r="116" ht="14" customHeight="1">
       <c r="A116" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 75 · 경화 17 · 향 0 · 기타 8</t>
         </is>
       </c>
       <c r="B116" s="16" t="n"/>
@@ -8004,8 +8020,20 @@
       <c r="E116" s="16" t="n"/>
       <c r="F116" s="16" t="n"/>
     </row>
-    <row r="117" ht="176" customHeight="1">
+    <row r="117" ht="14" customHeight="1">
       <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B117" s="18" t="n"/>
+      <c r="C117" s="18" t="n"/>
+      <c r="D117" s="18" t="n"/>
+      <c r="E117" s="18" t="n"/>
+      <c r="F117" s="18" t="n"/>
+    </row>
+    <row r="118" ht="176" customHeight="1">
+      <c r="A118" s="19" t="inlineStr">
         <is>
           <t>가볍고 촉촉한 자초립밤오일베이스로 립스틱들 만들어보세요.
 호호바오일, 피마자오일, 해바라기오일, 비타민E에
@@ -8021,20 +8049,20 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="14" customHeight="1">
-      <c r="A118" s="15" t="inlineStr">
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B118" s="16" t="n"/>
-      <c r="C118" s="16" t="n"/>
-      <c r="D118" s="16" t="n"/>
-      <c r="E118" s="16" t="n"/>
-      <c r="F118" s="16" t="n"/>
-    </row>
-    <row r="119" ht="352" customHeight="1">
-      <c r="A119" s="17" t="inlineStr">
+      <c r="B119" s="18" t="n"/>
+      <c r="C119" s="18" t="n"/>
+      <c r="D119" s="18" t="n"/>
+      <c r="E119" s="18" t="n"/>
+      <c r="F119" s="18" t="n"/>
+    </row>
+    <row r="120" ht="352" customHeight="1">
+      <c r="A120" s="19" t="inlineStr">
         <is>
           <t>1.자초립밤오일베이스와 칸데릴라왁스를 계량한 후
 2. 섞으면서 녹입니다.
@@ -8061,444 +8089,432 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="8.500000000000028" customHeight="1"/>
-    <row r="121" ht="6" customHeight="1"/>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+    <row r="121" ht="8.500000000000028" customHeight="1"/>
+    <row r="122" ht="6" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="7" t="inlineStr">
         <is>
           <t>수딩썬로션    [오일/ / 유화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="7" t="inlineStr">
+      <c r="B123" s="8" t="n"/>
+      <c r="C123" s="8" t="n"/>
+      <c r="D123" s="8" t="n"/>
+      <c r="E123" s="8" t="n"/>
+      <c r="F123" s="8" t="n"/>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B124" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C123" s="7" t="inlineStr">
+      <c r="C124" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="D124" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E123" s="7" t="inlineStr">
+      <c r="E124" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F123" s="7" t="inlineStr">
+      <c r="F124" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="18" t="inlineStr">
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B124" s="18" t="inlineStr">
+      <c r="B125" s="20" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C124" s="19" t="inlineStr">
+      <c r="C125" s="21" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D125" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E124" s="18" t="inlineStr">
+      <c r="E125" s="20" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일, / 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="F124" s="18" t="inlineStr">
+      <c r="F125" s="20" t="inlineStr">
         <is>
           <t>캐모마일 / 오일</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="18" t="inlineStr">
+    <row r="126" ht="48" customHeight="1">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>올리브에스터오일</t>
         </is>
       </c>
-      <c r="B125" s="18" t="inlineStr">
+      <c r="B126" s="20" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C125" s="19" t="inlineStr">
+      <c r="C126" s="21" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D125" s="10" t="inlineStr">
+      <c r="D126" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E125" s="18" t="inlineStr">
+      <c r="E126" s="20" t="inlineStr">
         <is>
           <t>올리브오일유래, 초기사용감은 / 실리콘오일처럼 가볍지만 보습력지속</t>
         </is>
       </c>
-      <c r="F125" s="18" t="inlineStr">
+      <c r="F126" s="20" t="inlineStr">
         <is>
           <t>호호바</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="48" customHeight="1">
-      <c r="A126" s="18" t="inlineStr">
+    <row r="127" ht="48" customHeight="1">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B126" s="18" t="inlineStr">
+      <c r="B127" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C126" s="19" t="inlineStr">
+      <c r="C127" s="21" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D126" s="25" t="inlineStr">
+      <c r="D127" s="27" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E126" s="18" t="inlineStr">
+      <c r="E127" s="20" t="inlineStr">
         <is>
           <t>에코인증, / 물/오일분리 저지</t>
         </is>
       </c>
-      <c r="F126" s="18" t="inlineStr">
+      <c r="F127" s="20" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="18" t="inlineStr">
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>올리왁스LC</t>
         </is>
       </c>
-      <c r="B127" s="18" t="inlineStr">
+      <c r="B128" s="20" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C127" s="19" t="inlineStr">
+      <c r="C128" s="21" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D127" s="20" t="inlineStr">
+      <c r="D128" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E127" s="18" t="inlineStr">
+      <c r="E128" s="20" t="inlineStr">
         <is>
           <t>유화 보조제, / 백탁 현상 완화</t>
         </is>
       </c>
-      <c r="F127" s="18" t="inlineStr">
+      <c r="F128" s="20" t="inlineStr">
         <is>
           <t>세틸알콜</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="32" customHeight="1">
-      <c r="A128" s="18" t="inlineStr">
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="20" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B128" s="18" t="inlineStr">
+      <c r="B129" s="20" t="inlineStr">
         <is>
           <t>32g</t>
         </is>
       </c>
-      <c r="C128" s="19" t="inlineStr">
+      <c r="C129" s="21" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="D128" s="26" t="inlineStr">
+      <c r="D129" s="28" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E128" s="18" t="inlineStr">
+      <c r="E129" s="20" t="inlineStr">
         <is>
           <t>5차 필터링, / UV살균처리 정제수</t>
         </is>
       </c>
-      <c r="F128" s="18" t="inlineStr">
+      <c r="F129" s="20" t="inlineStr">
         <is>
           <t>원하는 / 플로럴워터</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="48" customHeight="1">
-      <c r="A129" s="18" t="inlineStr">
+    <row r="130" ht="48" customHeight="1">
+      <c r="A130" s="20" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B129" s="18" t="inlineStr">
+      <c r="B130" s="20" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C129" s="19" t="inlineStr">
+      <c r="C130" s="21" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D129" s="22" t="inlineStr">
+      <c r="D130" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E129" s="18" t="inlineStr">
+      <c r="E130" s="20" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은 / 수분감이 풍부한 겔</t>
         </is>
       </c>
-      <c r="F129" s="18" t="inlineStr">
+      <c r="F130" s="20" t="inlineStr">
         <is>
           <t>허브누리 베라겔, / 네롤리 / 플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="32" customHeight="1">
-      <c r="A130" s="18" t="inlineStr">
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="20" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
-      <c r="B130" s="18" t="inlineStr">
+      <c r="B131" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C130" s="19" t="inlineStr">
+      <c r="C131" s="21" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D130" s="22" t="inlineStr">
+      <c r="D131" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E130" s="18" t="inlineStr">
+      <c r="E131" s="20" t="inlineStr">
         <is>
           <t>고중저분자, / 트리플 히아루론산,</t>
         </is>
       </c>
-      <c r="F130" s="18" t="inlineStr">
+      <c r="F131" s="20" t="inlineStr">
         <is>
           <t>에코 / 보습제</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="48" customHeight="1">
-      <c r="A131" s="18" t="inlineStr">
+    <row r="132" ht="48" customHeight="1">
+      <c r="A132" s="20" t="inlineStr">
         <is>
           <t>수딩4 컴플렉스</t>
         </is>
       </c>
-      <c r="B131" s="18" t="inlineStr">
+      <c r="B132" s="20" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C131" s="19" t="inlineStr">
+      <c r="C132" s="21" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr">
+      <c r="D132" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E131" s="18" t="inlineStr">
+      <c r="E132" s="20" t="inlineStr">
         <is>
           <t>알로에베라잎추출물, 참마뿌리추출물, / 흰목이버섯추출물, 미역추출물 복합추출물</t>
         </is>
       </c>
-      <c r="F131" s="18" t="n"/>
-    </row>
-    <row r="132" ht="64" customHeight="1">
-      <c r="A132" s="18" t="inlineStr">
+      <c r="F132" s="20" t="n"/>
+    </row>
+    <row r="133" ht="64" customHeight="1">
+      <c r="A133" s="20" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B132" s="18" t="inlineStr">
+      <c r="B133" s="20" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C132" s="19" t="inlineStr">
+      <c r="C133" s="21" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D132" s="27" t="inlineStr">
+      <c r="D133" s="29" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E132" s="18" t="inlineStr">
+      <c r="E133" s="20" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="F132" s="18" t="inlineStr">
+      <c r="F133" s="20" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (정제수의 양을 31g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="32" customHeight="1">
-      <c r="A133" s="18" t="inlineStr">
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="20" t="inlineStr">
         <is>
           <t>징크옥사이드분산액</t>
         </is>
       </c>
-      <c r="B133" s="18" t="inlineStr">
+      <c r="B134" s="20" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C133" s="19" t="inlineStr">
+      <c r="C134" s="21" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D133" s="21" t="inlineStr">
+      <c r="D134" s="23" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E133" s="18" t="inlineStr">
+      <c r="E134" s="20" t="inlineStr">
         <is>
           <t>UV-A를 주로 난반사</t>
         </is>
       </c>
-      <c r="F133" s="18" t="inlineStr">
+      <c r="F134" s="20" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="32" customHeight="1">
-      <c r="A134" s="18" t="inlineStr">
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" s="20" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 / 분산액</t>
         </is>
       </c>
-      <c r="B134" s="18" t="inlineStr">
+      <c r="B135" s="20" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C134" s="19" t="inlineStr">
+      <c r="C135" s="21" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D134" s="21" t="inlineStr">
+      <c r="D135" s="23" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E134" s="18" t="inlineStr">
+      <c r="E135" s="20" t="inlineStr">
         <is>
           <t>자외선UV-B를 주로 난반사</t>
         </is>
       </c>
-      <c r="F134" s="18" t="n"/>
-    </row>
-    <row r="135" ht="48" customHeight="1">
-      <c r="A135" s="18" t="inlineStr">
+      <c r="F135" s="20" t="n"/>
+    </row>
+    <row r="136" ht="48" customHeight="1">
+      <c r="A136" s="20" t="inlineStr">
         <is>
           <t>베베보 블렌딩오일</t>
         </is>
       </c>
-      <c r="B135" s="18" t="inlineStr">
+      <c r="B136" s="20" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C135" s="19" t="inlineStr">
+      <c r="C136" s="21" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="D136" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E135" s="18" t="inlineStr">
+      <c r="E136" s="20" t="inlineStr">
         <is>
           <t>라벤더. 만다린 로먼캐모마일 에센셜오일, / 민감피부를 위한 블렌딩</t>
         </is>
       </c>
-      <c r="F135" s="18" t="inlineStr">
+      <c r="F136" s="20" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-    </row>
-    <row r="136" ht="14" customHeight="1">
-      <c r="A136" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 32 · 유상 17 · 유화 4 · 경화 2 · 활성 29 · 색소 15 · 방부 1</t>
-        </is>
-      </c>
-      <c r="B136" s="14" t="n"/>
-      <c r="C136" s="14" t="n"/>
-      <c r="D136" s="14" t="n"/>
-      <c r="E136" s="14" t="n"/>
-      <c r="F136" s="14" t="n"/>
     </row>
     <row r="137" ht="14" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 32 · 유상 17 · 유화 4 · 경화 2 · 활성 29 · 색소 15 · 방부 1</t>
         </is>
       </c>
       <c r="B137" s="16" t="n"/>
@@ -8507,8 +8523,20 @@
       <c r="E137" s="16" t="n"/>
       <c r="F137" s="16" t="n"/>
     </row>
-    <row r="138" ht="352" customHeight="1">
-      <c r="A138" s="23" t="inlineStr">
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="n"/>
+      <c r="C138" s="18" t="n"/>
+      <c r="D138" s="18" t="n"/>
+      <c r="E138" s="18" t="n"/>
+      <c r="F138" s="18" t="n"/>
+    </row>
+    <row r="139" ht="352" customHeight="1">
+      <c r="A139" s="25" t="inlineStr">
         <is>
           <t>수딩썬로션
 (100g)
@@ -8534,26 +8562,26 @@
 우리 가족 안심 썬로션 만들기해보세요 .</t>
         </is>
       </c>
-      <c r="B138" s="24" t="n"/>
-      <c r="C138" s="24" t="n"/>
-      <c r="D138" s="24" t="n"/>
-      <c r="E138" s="24" t="n"/>
-      <c r="F138" s="24" t="n"/>
-    </row>
-    <row r="139" ht="14" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
+      <c r="B139" s="26" t="n"/>
+      <c r="C139" s="26" t="n"/>
+      <c r="D139" s="26" t="n"/>
+      <c r="E139" s="26" t="n"/>
+      <c r="F139" s="26" t="n"/>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B139" s="16" t="n"/>
-      <c r="C139" s="16" t="n"/>
-      <c r="D139" s="16" t="n"/>
-      <c r="E139" s="16" t="n"/>
-      <c r="F139" s="16" t="n"/>
-    </row>
-    <row r="140" ht="112" customHeight="1">
-      <c r="A140" s="23" t="inlineStr">
+      <c r="B140" s="18" t="n"/>
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="18" t="n"/>
+      <c r="E140" s="18" t="n"/>
+      <c r="F140" s="18" t="n"/>
+    </row>
+    <row r="141" ht="112" customHeight="1">
+      <c r="A141" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 2개의 비커에 오일/유화제, 워터를 계량합니다.
@@ -8564,165 +8592,153 @@
 6. 골고루 섞어주면 완성.</t>
         </is>
       </c>
-      <c r="B140" s="24" t="n"/>
-      <c r="C140" s="24" t="n"/>
-      <c r="D140" s="24" t="n"/>
-      <c r="E140" s="24" t="n"/>
-      <c r="F140" s="24" t="n"/>
-    </row>
-    <row r="141" ht="6" customHeight="1"/>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="B141" s="26" t="n"/>
+      <c r="C141" s="26" t="n"/>
+      <c r="D141" s="26" t="n"/>
+      <c r="E141" s="26" t="n"/>
+      <c r="F141" s="26" t="n"/>
+    </row>
+    <row r="142" ht="6" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>레드 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="6" t="n"/>
-    </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
+      <c r="B143" s="8" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="8" t="n"/>
+      <c r="F143" s="8" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C143" s="7" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D143" s="7" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E143" s="7" t="inlineStr">
+      <c r="E144" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F143" s="7" t="inlineStr">
+      <c r="F144" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="48" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="145" ht="48" customHeight="1">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C145" s="11" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D144" s="10" t="inlineStr">
+      <c r="D145" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E144" s="8" t="inlineStr">
+      <c r="E145" s="10" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F144" s="8" t="inlineStr">
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="64" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="146" ht="64" customHeight="1">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>레드 립 컬러</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C146" s="11" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D145" s="12" t="inlineStr">
+      <c r="D146" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
+      <c r="E146" s="10" t="inlineStr">
         <is>
           <t>레드21번 0.5g + 레드7번 0.2g+ 옐로우6번 0.1g+ 레드6번 0.2g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F145" s="8" t="n"/>
-    </row>
-    <row r="146" ht="32" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="F146" s="10" t="n"/>
+    </row>
+    <row r="147" ht="32" customHeight="1">
+      <c r="A147" s="10" t="inlineStr">
         <is>
           <t>브라이트닝블렌딩오일</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C146" s="9" t="inlineStr">
+      <c r="C147" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D147" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E146" s="8" t="inlineStr">
+      <c r="E147" s="10" t="inlineStr">
         <is>
           <t>네롤리, 프랑킨센스, 버가못EO 블렌딩</t>
         </is>
       </c>
-      <c r="F146" s="8" t="inlineStr">
+      <c r="F147" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
-        </is>
-      </c>
-      <c r="B147" s="14" t="n"/>
-      <c r="C147" s="14" t="n"/>
-      <c r="D147" s="14" t="n"/>
-      <c r="E147" s="14" t="n"/>
-      <c r="F147" s="14" t="n"/>
     </row>
     <row r="148" ht="14" customHeight="1">
       <c r="A148" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
       <c r="B148" s="16" t="n"/>
@@ -8731,8 +8747,20 @@
       <c r="E148" s="16" t="n"/>
       <c r="F148" s="16" t="n"/>
     </row>
-    <row r="149" ht="224" customHeight="1">
+    <row r="149" ht="14" customHeight="1">
       <c r="A149" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B149" s="18" t="n"/>
+      <c r="C149" s="18" t="n"/>
+      <c r="D149" s="18" t="n"/>
+      <c r="E149" s="18" t="n"/>
+      <c r="F149" s="18" t="n"/>
+    </row>
+    <row r="150" ht="224" customHeight="1">
+      <c r="A150" s="19" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -8751,20 +8779,20 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="14" customHeight="1">
-      <c r="A150" s="15" t="inlineStr">
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B150" s="16" t="n"/>
-      <c r="C150" s="16" t="n"/>
-      <c r="D150" s="16" t="n"/>
-      <c r="E150" s="16" t="n"/>
-      <c r="F150" s="16" t="n"/>
-    </row>
-    <row r="151" ht="304" customHeight="1">
-      <c r="A151" s="17" t="inlineStr">
+      <c r="B151" s="18" t="n"/>
+      <c r="C151" s="18" t="n"/>
+      <c r="D151" s="18" t="n"/>
+      <c r="E151" s="18" t="n"/>
+      <c r="F151" s="18" t="n"/>
+    </row>
+    <row r="152" ht="304" customHeight="1">
+      <c r="A152" s="19" t="inlineStr">
         <is>
           <t>2.녹인 것을 캔용기에 부어서
 4. 굳히세요. 식히면 단단해집니다.
@@ -8787,160 +8815,148 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="122" customHeight="1"/>
-    <row r="153" ht="6" customHeight="1"/>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
+    <row r="153" ht="122" customHeight="1"/>
+    <row r="154" ht="6" customHeight="1"/>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>벚꽃 썸띵 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B154" s="6" t="n"/>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="n"/>
-      <c r="E154" s="6" t="n"/>
-      <c r="F154" s="6" t="n"/>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="8" t="n"/>
+      <c r="F155" s="8" t="n"/>
+    </row>
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B155" s="7" t="inlineStr">
+      <c r="B156" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C155" s="7" t="inlineStr">
+      <c r="C156" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D155" s="7" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E155" s="7" t="inlineStr">
+      <c r="E156" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F155" s="7" t="inlineStr">
+      <c r="F156" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="48" customHeight="1">
-      <c r="A156" s="18" t="inlineStr">
+    <row r="157" ht="48" customHeight="1">
+      <c r="A157" s="20" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B156" s="18" t="inlineStr">
+      <c r="B157" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C156" s="19" t="inlineStr">
+      <c r="C157" s="21" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D156" s="10" t="inlineStr">
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E156" s="18" t="inlineStr">
+      <c r="E157" s="20" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F156" s="18" t="inlineStr">
+      <c r="F157" s="20" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="64" customHeight="1">
-      <c r="A157" s="18" t="inlineStr">
+    <row r="158" ht="64" customHeight="1">
+      <c r="A158" s="20" t="inlineStr">
         <is>
           <t>벚꽃 립 컬러</t>
         </is>
       </c>
-      <c r="B157" s="18" t="inlineStr">
+      <c r="B158" s="20" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C157" s="19" t="inlineStr">
+      <c r="C158" s="21" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D157" s="12" t="inlineStr">
+      <c r="D158" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E157" s="18" t="inlineStr">
+      <c r="E158" s="20" t="inlineStr">
         <is>
           <t>레드27번 0.3g + 레드40번 0.2g+ 아이론옐로우 0.1g+ 화이트 0.4g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F157" s="18" t="n"/>
-    </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="18" t="inlineStr">
+      <c r="F158" s="20" t="n"/>
+    </row>
+    <row r="159" ht="32" customHeight="1">
+      <c r="A159" s="20" t="inlineStr">
         <is>
           <t>레몬쥬스블렌딩오일</t>
         </is>
       </c>
-      <c r="B158" s="18" t="inlineStr">
+      <c r="B159" s="20" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C158" s="19" t="inlineStr">
+      <c r="C159" s="21" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E158" s="18" t="inlineStr">
+      <c r="E159" s="20" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드 / 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F158" s="18" t="inlineStr">
+      <c r="F159" s="20" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="159" ht="14" customHeight="1">
-      <c r="A159" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
-        </is>
-      </c>
-      <c r="B159" s="14" t="n"/>
-      <c r="C159" s="14" t="n"/>
-      <c r="D159" s="14" t="n"/>
-      <c r="E159" s="14" t="n"/>
-      <c r="F159" s="14" t="n"/>
     </row>
     <row r="160" ht="14" customHeight="1">
       <c r="A160" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
       <c r="B160" s="16" t="n"/>
@@ -8949,8 +8965,20 @@
       <c r="E160" s="16" t="n"/>
       <c r="F160" s="16" t="n"/>
     </row>
-    <row r="161" ht="192" customHeight="1">
-      <c r="A161" s="23" t="inlineStr">
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B161" s="18" t="n"/>
+      <c r="C161" s="18" t="n"/>
+      <c r="D161" s="18" t="n"/>
+      <c r="E161" s="18" t="n"/>
+      <c r="F161" s="18" t="n"/>
+    </row>
+    <row r="162" ht="192" customHeight="1">
+      <c r="A162" s="25" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -8966,26 +8994,26 @@
 완성도 높은 립스틱 만들기해보세요.</t>
         </is>
       </c>
-      <c r="B161" s="24" t="n"/>
-      <c r="C161" s="24" t="n"/>
-      <c r="D161" s="24" t="n"/>
-      <c r="E161" s="24" t="n"/>
-      <c r="F161" s="24" t="n"/>
-    </row>
-    <row r="162" ht="14" customHeight="1">
-      <c r="A162" s="15" t="inlineStr">
+      <c r="B162" s="26" t="n"/>
+      <c r="C162" s="26" t="n"/>
+      <c r="D162" s="26" t="n"/>
+      <c r="E162" s="26" t="n"/>
+      <c r="F162" s="26" t="n"/>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B162" s="16" t="n"/>
-      <c r="C162" s="16" t="n"/>
-      <c r="D162" s="16" t="n"/>
-      <c r="E162" s="16" t="n"/>
-      <c r="F162" s="16" t="n"/>
-    </row>
-    <row r="163" ht="384" customHeight="1">
-      <c r="A163" s="23" t="inlineStr">
+      <c r="B163" s="18" t="n"/>
+      <c r="C163" s="18" t="n"/>
+      <c r="D163" s="18" t="n"/>
+      <c r="E163" s="18" t="n"/>
+      <c r="F163" s="18" t="n"/>
+    </row>
+    <row r="164" ht="384" customHeight="1">
+      <c r="A164" s="25" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -9012,173 +9040,161 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B163" s="24" t="n"/>
-      <c r="C163" s="24" t="n"/>
-      <c r="D163" s="24" t="n"/>
-      <c r="E163" s="24" t="n"/>
-      <c r="F163" s="24" t="n"/>
-    </row>
-    <row r="164" ht="74.00000000000006" customHeight="1">
-      <c r="A164" s="24" t="n"/>
-      <c r="B164" s="24" t="n"/>
-      <c r="C164" s="24" t="n"/>
-      <c r="D164" s="24" t="n"/>
-      <c r="E164" s="24" t="n"/>
-      <c r="F164" s="24" t="n"/>
-    </row>
-    <row r="165" ht="6" customHeight="1"/>
-    <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
+      <c r="B164" s="26" t="n"/>
+      <c r="C164" s="26" t="n"/>
+      <c r="D164" s="26" t="n"/>
+      <c r="E164" s="26" t="n"/>
+      <c r="F164" s="26" t="n"/>
+    </row>
+    <row r="165" ht="74.00000000000006" customHeight="1">
+      <c r="A165" s="26" t="n"/>
+      <c r="B165" s="26" t="n"/>
+      <c r="C165" s="26" t="n"/>
+      <c r="D165" s="26" t="n"/>
+      <c r="E165" s="26" t="n"/>
+      <c r="F165" s="26" t="n"/>
+    </row>
+    <row r="166" ht="6" customHeight="1"/>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>피치코랄 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-    </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
+      <c r="B167" s="8" t="n"/>
+      <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="8" t="n"/>
+    </row>
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E167" s="7" t="inlineStr">
+      <c r="E168" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="F168" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="48" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+    <row r="169" ht="48" customHeight="1">
+      <c r="A169" s="10" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="C169" s="11" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D168" s="10" t="inlineStr">
+      <c r="D169" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E168" s="8" t="inlineStr">
+      <c r="E169" s="10" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 / 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F168" s="8" t="inlineStr">
+      <c r="F169" s="10" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="64" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
+    <row r="170" ht="64" customHeight="1">
+      <c r="A170" s="10" t="inlineStr">
         <is>
           <t>피치코랄 립 컬러</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="10" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
+      <c r="C170" s="11" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D169" s="12" t="inlineStr">
+      <c r="D170" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E169" s="8" t="inlineStr">
+      <c r="E170" s="10" t="inlineStr">
         <is>
           <t>레드6번 0.3g + 아이론옐로우 0.1g / + 레드27번 0.2g + 화이트 0.2g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F169" s="8" t="n"/>
-    </row>
-    <row r="170" ht="32" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+      <c r="F170" s="10" t="n"/>
+    </row>
+    <row r="171" ht="32" customHeight="1">
+      <c r="A171" s="10" t="inlineStr">
         <is>
           <t>라임캔디 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="10" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C170" s="9" t="inlineStr">
+      <c r="C171" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D170" s="10" t="inlineStr">
+      <c r="D171" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E170" s="8" t="inlineStr">
+      <c r="E171" s="10" t="inlineStr">
         <is>
           <t>라임, 스윗오렌지, 레몬, 로즈마리 / 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F170" s="8" t="inlineStr">
+      <c r="F171" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
-        </is>
-      </c>
-      <c r="B171" s="14" t="n"/>
-      <c r="C171" s="14" t="n"/>
-      <c r="D171" s="14" t="n"/>
-      <c r="E171" s="14" t="n"/>
-      <c r="F171" s="14" t="n"/>
     </row>
     <row r="172" ht="14" customHeight="1">
       <c r="A172" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
       <c r="B172" s="16" t="n"/>
@@ -9187,8 +9203,20 @@
       <c r="E172" s="16" t="n"/>
       <c r="F172" s="16" t="n"/>
     </row>
-    <row r="173" ht="192" customHeight="1">
+    <row r="173" ht="14" customHeight="1">
       <c r="A173" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B173" s="18" t="n"/>
+      <c r="C173" s="18" t="n"/>
+      <c r="D173" s="18" t="n"/>
+      <c r="E173" s="18" t="n"/>
+      <c r="F173" s="18" t="n"/>
+    </row>
+    <row r="174" ht="192" customHeight="1">
+      <c r="A174" s="19" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -9205,20 +9233,20 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="14" customHeight="1">
-      <c r="A174" s="15" t="inlineStr">
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B174" s="16" t="n"/>
-      <c r="C174" s="16" t="n"/>
-      <c r="D174" s="16" t="n"/>
-      <c r="E174" s="16" t="n"/>
-      <c r="F174" s="16" t="n"/>
-    </row>
-    <row r="175" ht="384" customHeight="1">
-      <c r="A175" s="17" t="inlineStr">
+      <c r="B175" s="18" t="n"/>
+      <c r="C175" s="18" t="n"/>
+      <c r="D175" s="18" t="n"/>
+      <c r="E175" s="18" t="n"/>
+      <c r="F175" s="18" t="n"/>
+    </row>
+    <row r="176" ht="384" customHeight="1">
+      <c r="A176" s="19" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -9246,223 +9274,211 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="6" customHeight="1"/>
-    <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="5" t="inlineStr">
+    <row r="177" ht="6" customHeight="1"/>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>워터리 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B177" s="6" t="n"/>
-      <c r="C177" s="6" t="n"/>
-      <c r="D177" s="6" t="n"/>
-      <c r="E177" s="6" t="n"/>
-      <c r="F177" s="6" t="n"/>
-    </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
+      <c r="B178" s="8" t="n"/>
+      <c r="C178" s="8" t="n"/>
+      <c r="D178" s="8" t="n"/>
+      <c r="E178" s="8" t="n"/>
+      <c r="F178" s="8" t="n"/>
+    </row>
+    <row r="179" ht="15" customHeight="1">
+      <c r="A179" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B178" s="7" t="inlineStr">
+      <c r="B179" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C178" s="7" t="inlineStr">
+      <c r="C179" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D178" s="7" t="inlineStr">
+      <c r="D179" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E178" s="7" t="inlineStr">
+      <c r="E179" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="F179" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="32" customHeight="1">
-      <c r="A179" s="18" t="inlineStr">
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="20" t="inlineStr">
         <is>
           <t>립밤베이스</t>
         </is>
       </c>
-      <c r="B179" s="18" t="inlineStr">
+      <c r="B180" s="20" t="inlineStr">
         <is>
           <t>4.6g</t>
         </is>
       </c>
-      <c r="C179" s="19" t="inlineStr">
+      <c r="C180" s="21" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="D179" s="10" t="inlineStr">
+      <c r="D180" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E179" s="18" t="inlineStr">
+      <c r="E180" s="20" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서</t>
         </is>
       </c>
-      <c r="F179" s="18" t="inlineStr">
+      <c r="F180" s="20" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="18" t="inlineStr">
+    <row r="181" ht="32" customHeight="1">
+      <c r="A181" s="20" t="inlineStr">
         <is>
           <t>립 컬러</t>
         </is>
       </c>
-      <c r="B180" s="18" t="inlineStr">
+      <c r="B181" s="20" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C180" s="19" t="inlineStr">
+      <c r="C181" s="21" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D180" s="12" t="inlineStr">
+      <c r="D181" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E180" s="18" t="inlineStr">
+      <c r="E181" s="20" t="inlineStr">
         <is>
           <t>색상사진은 아래의 / 립스틱 발색 사진과 처방 참고</t>
         </is>
       </c>
-      <c r="F180" s="18" t="n"/>
-    </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="18" t="inlineStr">
+      <c r="F181" s="20" t="n"/>
+    </row>
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="20" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B181" s="18" t="inlineStr">
+      <c r="B182" s="20" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C181" s="19" t="inlineStr">
+      <c r="C182" s="21" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D181" s="10" t="inlineStr">
+      <c r="D182" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E181" s="18" t="inlineStr">
+      <c r="E182" s="20" t="inlineStr">
         <is>
           <t>피지성분과 비슷, / 가벼운 사용감</t>
         </is>
       </c>
-      <c r="F181" s="18" t="inlineStr">
+      <c r="F182" s="20" t="inlineStr">
         <is>
           <t>스위트아몬드오일, / 동백오일 등</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="48" customHeight="1">
-      <c r="A182" s="18" t="inlineStr">
+    <row r="183" ht="48" customHeight="1">
+      <c r="A183" s="20" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B182" s="18" t="inlineStr">
+      <c r="B183" s="20" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C182" s="19" t="inlineStr">
+      <c r="C183" s="21" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D182" s="10" t="inlineStr">
+      <c r="D183" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E182" s="18" t="inlineStr">
+      <c r="E183" s="20" t="inlineStr">
         <is>
           <t>오래가는 보습오일</t>
         </is>
       </c>
-      <c r="F182" s="18" t="inlineStr">
+      <c r="F183" s="20" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="48" customHeight="1">
-      <c r="A183" s="18" t="inlineStr">
+    <row r="184" ht="48" customHeight="1">
+      <c r="A184" s="20" t="inlineStr">
         <is>
           <t>로즈파워 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B183" s="18" t="inlineStr">
+      <c r="B184" s="20" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C183" s="19" t="inlineStr">
+      <c r="C184" s="21" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D183" s="10" t="inlineStr">
+      <c r="D184" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E183" s="18" t="inlineStr">
+      <c r="E184" s="20" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄, 로즈우드, 프랑킨센스 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F183" s="18" t="inlineStr">
+      <c r="F184" s="20" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="184" ht="14" customHeight="1">
-      <c r="A184" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 94 · 기타 6</t>
-        </is>
-      </c>
-      <c r="B184" s="14" t="n"/>
-      <c r="C184" s="14" t="n"/>
-      <c r="D184" s="14" t="n"/>
-      <c r="E184" s="14" t="n"/>
-      <c r="F184" s="14" t="n"/>
     </row>
     <row r="185" ht="14" customHeight="1">
       <c r="A185" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 94 · 기타 6</t>
         </is>
       </c>
       <c r="B185" s="16" t="n"/>
@@ -9471,8 +9487,20 @@
       <c r="E185" s="16" t="n"/>
       <c r="F185" s="16" t="n"/>
     </row>
-    <row r="186" ht="96" customHeight="1">
-      <c r="A186" s="23" t="inlineStr">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B186" s="18" t="n"/>
+      <c r="C186" s="18" t="n"/>
+      <c r="D186" s="18" t="n"/>
+      <c r="E186" s="18" t="n"/>
+      <c r="F186" s="18" t="n"/>
+    </row>
+    <row r="187" ht="96" customHeight="1">
+      <c r="A187" s="25" t="inlineStr">
         <is>
           <t>무제 문서
 워터리 립글로스는
@@ -9482,26 +9510,26 @@
 다양한 색상처방은 아래에서 참고하세요.</t>
         </is>
       </c>
-      <c r="B186" s="24" t="n"/>
-      <c r="C186" s="24" t="n"/>
-      <c r="D186" s="24" t="n"/>
-      <c r="E186" s="24" t="n"/>
-      <c r="F186" s="24" t="n"/>
-    </row>
-    <row r="187" ht="14" customHeight="1">
-      <c r="A187" s="15" t="inlineStr">
+      <c r="B187" s="26" t="n"/>
+      <c r="C187" s="26" t="n"/>
+      <c r="D187" s="26" t="n"/>
+      <c r="E187" s="26" t="n"/>
+      <c r="F187" s="26" t="n"/>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B187" s="16" t="n"/>
-      <c r="C187" s="16" t="n"/>
-      <c r="D187" s="16" t="n"/>
-      <c r="E187" s="16" t="n"/>
-      <c r="F187" s="16" t="n"/>
-    </row>
-    <row r="188" ht="192" customHeight="1">
-      <c r="A188" s="23" t="inlineStr">
+      <c r="B188" s="18" t="n"/>
+      <c r="C188" s="18" t="n"/>
+      <c r="D188" s="18" t="n"/>
+      <c r="E188" s="18" t="n"/>
+      <c r="F188" s="18" t="n"/>
+    </row>
+    <row r="189" ht="192" customHeight="1">
+      <c r="A189" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 [립밤베이스 만들기]
@@ -9517,133 +9545,121 @@
 9. 튜브나 립솔용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B188" s="24" t="n"/>
-      <c r="C188" s="24" t="n"/>
-      <c r="D188" s="24" t="n"/>
-      <c r="E188" s="24" t="n"/>
-      <c r="F188" s="24" t="n"/>
-    </row>
-    <row r="189" ht="6" customHeight="1"/>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="5" t="inlineStr">
+      <c r="B189" s="26" t="n"/>
+      <c r="C189" s="26" t="n"/>
+      <c r="D189" s="26" t="n"/>
+      <c r="E189" s="26" t="n"/>
+      <c r="F189" s="26" t="n"/>
+    </row>
+    <row r="190" ht="6" customHeight="1"/>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="7" t="inlineStr">
         <is>
           <t>커피헤나염색    ↗ 원본</t>
         </is>
       </c>
-      <c r="B190" s="6" t="n"/>
-      <c r="C190" s="6" t="n"/>
-      <c r="D190" s="6" t="n"/>
-      <c r="E190" s="6" t="n"/>
-      <c r="F190" s="6" t="n"/>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="7" t="inlineStr">
+      <c r="B191" s="8" t="n"/>
+      <c r="C191" s="8" t="n"/>
+      <c r="D191" s="8" t="n"/>
+      <c r="E191" s="8" t="n"/>
+      <c r="F191" s="8" t="n"/>
+    </row>
+    <row r="192" ht="15" customHeight="1">
+      <c r="A192" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="B192" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C191" s="7" t="inlineStr">
+      <c r="C192" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D191" s="7" t="inlineStr">
+      <c r="D192" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="E192" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F192" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="8" t="inlineStr">
+    <row r="193" ht="16" customHeight="1">
+      <c r="A193" s="10" t="inlineStr">
         <is>
           <t>헤나분말</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B193" s="10" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C192" s="9" t="inlineStr">
+      <c r="C193" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D192" s="12" t="inlineStr">
+      <c r="D193" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E192" s="8" t="inlineStr">
+      <c r="E193" s="10" t="inlineStr">
         <is>
           <t>100% 헤나 분말</t>
         </is>
       </c>
-      <c r="F192" s="8" t="n"/>
-    </row>
-    <row r="193" ht="64" customHeight="1">
-      <c r="A193" s="8" t="inlineStr">
+      <c r="F193" s="10" t="n"/>
+    </row>
+    <row r="194" ht="64" customHeight="1">
+      <c r="A194" s="10" t="inlineStr">
         <is>
           <t>물</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B194" s="10" t="inlineStr">
         <is>
           <t>130g 내외</t>
         </is>
       </c>
-      <c r="C193" s="9" t="inlineStr">
+      <c r="C194" s="11" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="D193" s="26" t="inlineStr">
+      <c r="D194" s="28" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E193" s="8" t="inlineStr">
+      <c r="E194" s="10" t="inlineStr">
         <is>
           <t>맑은 물(정수기, 수돗물 등등)</t>
         </is>
       </c>
-      <c r="F193" s="8" t="inlineStr">
+      <c r="F194" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
-    </row>
-    <row r="194" ht="14" customHeight="1">
-      <c r="A194" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 76 · 기타 24</t>
-        </is>
-      </c>
-      <c r="B194" s="14" t="n"/>
-      <c r="C194" s="14" t="n"/>
-      <c r="D194" s="14" t="n"/>
-      <c r="E194" s="14" t="n"/>
-      <c r="F194" s="14" t="n"/>
     </row>
     <row r="195" ht="14" customHeight="1">
       <c r="A195" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 76 · 기타 24</t>
         </is>
       </c>
       <c r="B195" s="16" t="n"/>
@@ -9652,8 +9668,20 @@
       <c r="E195" s="16" t="n"/>
       <c r="F195" s="16" t="n"/>
     </row>
-    <row r="196" ht="352" customHeight="1">
+    <row r="196" ht="14" customHeight="1">
       <c r="A196" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B196" s="18" t="n"/>
+      <c r="C196" s="18" t="n"/>
+      <c r="D196" s="18" t="n"/>
+      <c r="E196" s="18" t="n"/>
+      <c r="F196" s="18" t="n"/>
+    </row>
+    <row r="197" ht="352" customHeight="1">
+      <c r="A197" s="19" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -9679,20 +9707,20 @@
         </is>
       </c>
     </row>
-    <row r="197" ht="14" customHeight="1">
-      <c r="A197" s="15" t="inlineStr">
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B197" s="16" t="n"/>
-      <c r="C197" s="16" t="n"/>
-      <c r="D197" s="16" t="n"/>
-      <c r="E197" s="16" t="n"/>
-      <c r="F197" s="16" t="n"/>
-    </row>
-    <row r="198" ht="144" customHeight="1">
-      <c r="A198" s="17" t="inlineStr">
+      <c r="B198" s="18" t="n"/>
+      <c r="C198" s="18" t="n"/>
+      <c r="D198" s="18" t="n"/>
+      <c r="E198" s="18" t="n"/>
+      <c r="F198" s="18" t="n"/>
+    </row>
+    <row r="199" ht="144" customHeight="1">
+      <c r="A199" s="19" t="inlineStr">
         <is>
           <t>1. 염색 전 샴푸한 후 물기를 닦아주세요. 두피 피지와 오염물이 없으면 염색이 더 잘 됩니다.
 2. 인스턴트 커피 40~60g
@@ -9705,227 +9733,215 @@
         </is>
       </c>
     </row>
-    <row r="199" ht="6" customHeight="1"/>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
+    <row r="200" ht="6" customHeight="1"/>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>자초딸기립글로스(솔타입)    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B200" s="6" t="n"/>
-      <c r="C200" s="6" t="n"/>
-      <c r="D200" s="6" t="n"/>
-      <c r="E200" s="6" t="n"/>
-      <c r="F200" s="6" t="n"/>
-    </row>
-    <row r="201" ht="15" customHeight="1">
-      <c r="A201" s="7" t="inlineStr">
+      <c r="B201" s="8" t="n"/>
+      <c r="C201" s="8" t="n"/>
+      <c r="D201" s="8" t="n"/>
+      <c r="E201" s="8" t="n"/>
+      <c r="F201" s="8" t="n"/>
+    </row>
+    <row r="202" ht="15" customHeight="1">
+      <c r="A202" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B202" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C201" s="7" t="inlineStr">
+      <c r="C202" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D201" s="7" t="inlineStr">
+      <c r="D202" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E201" s="7" t="inlineStr">
+      <c r="E202" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
+      <c r="F202" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="112" customHeight="1">
-      <c r="A202" s="18" t="inlineStr">
+    <row r="203" ht="112" customHeight="1">
+      <c r="A203" s="20" t="inlineStr">
         <is>
           <t>자초인퓨즈 / 호호바오일</t>
         </is>
       </c>
-      <c r="B202" s="18" t="inlineStr">
+      <c r="B203" s="20" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C202" s="19" t="inlineStr">
+      <c r="C203" s="21" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="D202" s="22" t="inlineStr">
+      <c r="D203" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E202" s="18" t="inlineStr">
+      <c r="E203" s="20" t="inlineStr">
         <is>
           <t>한약재, 자초, 지치의 뿌리, 자주색을 띈다하여 자초, 뿌리는 굵고 자주색, 오일에는 붉은 색이 우러나지만 알콜, 물에는 갈변합니다. 천연염색, 민간 약재로 사용, 호호바오일에 담궈서 유효성분을 우림</t>
         </is>
       </c>
-      <c r="F202" s="18" t="inlineStr">
+      <c r="F203" s="20" t="inlineStr">
         <is>
           <t>원하는 / 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="80" customHeight="1">
-      <c r="A203" s="18" t="inlineStr">
+    <row r="204" ht="80" customHeight="1">
+      <c r="A204" s="20" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B203" s="18" t="inlineStr">
+      <c r="B204" s="20" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C203" s="19" t="inlineStr">
+      <c r="C204" s="21" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D203" s="10" t="inlineStr">
+      <c r="D204" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E203" s="18" t="inlineStr">
+      <c r="E204" s="20" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F203" s="18" t="inlineStr">
+      <c r="F204" s="20" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체,</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="48" customHeight="1">
-      <c r="A204" s="18" t="inlineStr">
+    <row r="205" ht="48" customHeight="1">
+      <c r="A205" s="20" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B204" s="18" t="inlineStr">
+      <c r="B205" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C204" s="19" t="inlineStr">
+      <c r="C205" s="21" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D204" s="10" t="inlineStr">
+      <c r="D205" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E204" s="18" t="inlineStr">
+      <c r="E205" s="20" t="inlineStr">
         <is>
           <t>식물성 버터, 카리테나무 열매에서 채취, / 보습효과짱^^</t>
         </is>
       </c>
-      <c r="F204" s="18" t="inlineStr">
+      <c r="F205" s="20" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="32" customHeight="1">
-      <c r="A205" s="18" t="inlineStr">
+    <row r="206" ht="32" customHeight="1">
+      <c r="A206" s="20" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B205" s="18" t="inlineStr">
+      <c r="B206" s="20" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C205" s="19" t="inlineStr">
+      <c r="C206" s="21" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D205" s="20" t="inlineStr">
+      <c r="D206" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E205" s="18" t="inlineStr">
+      <c r="E206" s="20" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취, / 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="F205" s="18" t="inlineStr">
+      <c r="F206" s="20" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="18" t="inlineStr">
+    <row r="207" ht="16" customHeight="1">
+      <c r="A207" s="20" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B206" s="18" t="inlineStr">
+      <c r="B207" s="20" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C206" s="19" t="inlineStr">
+      <c r="C207" s="21" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D206" s="11" t="inlineStr">
+      <c r="D207" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E206" s="18" t="inlineStr">
+      <c r="E207" s="20" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="F206" s="18" t="inlineStr">
+      <c r="F207" s="20" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="207" ht="14" customHeight="1">
-      <c r="A207" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 65 · 경화 4 · 활성 29 · 향 2</t>
-        </is>
-      </c>
-      <c r="B207" s="14" t="n"/>
-      <c r="C207" s="14" t="n"/>
-      <c r="D207" s="14" t="n"/>
-      <c r="E207" s="14" t="n"/>
-      <c r="F207" s="14" t="n"/>
     </row>
     <row r="208" ht="14" customHeight="1">
       <c r="A208" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 65 · 경화 4 · 활성 29 · 향 2</t>
         </is>
       </c>
       <c r="B208" s="16" t="n"/>
@@ -9934,8 +9950,20 @@
       <c r="E208" s="16" t="n"/>
       <c r="F208" s="16" t="n"/>
     </row>
-    <row r="209" ht="288" customHeight="1">
-      <c r="A209" s="23" t="inlineStr">
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B209" s="18" t="n"/>
+      <c r="C209" s="18" t="n"/>
+      <c r="D209" s="18" t="n"/>
+      <c r="E209" s="18" t="n"/>
+      <c r="F209" s="18" t="n"/>
+    </row>
+    <row r="210" ht="288" customHeight="1">
+      <c r="A210" s="25" t="inlineStr">
         <is>
           <t>2009년부터 만들기 시작한 자초인퓨즈오일로 만든 립밤이 있었죠.
 자초인퓨즈오일, 피마자오일, 시어버터, 칸데릴라왁스, 딸기플레이버오일로 만든 겁나게 촉촉한 립밤인데요
@@ -9953,26 +9981,26 @@
 5ml블랙캡립글로스</t>
         </is>
       </c>
-      <c r="B209" s="24" t="n"/>
-      <c r="C209" s="24" t="n"/>
-      <c r="D209" s="24" t="n"/>
-      <c r="E209" s="24" t="n"/>
-      <c r="F209" s="24" t="n"/>
-    </row>
-    <row r="210" ht="14" customHeight="1">
-      <c r="A210" s="15" t="inlineStr">
+      <c r="B210" s="26" t="n"/>
+      <c r="C210" s="26" t="n"/>
+      <c r="D210" s="26" t="n"/>
+      <c r="E210" s="26" t="n"/>
+      <c r="F210" s="26" t="n"/>
+    </row>
+    <row r="211" ht="14" customHeight="1">
+      <c r="A211" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B210" s="16" t="n"/>
-      <c r="C210" s="16" t="n"/>
-      <c r="D210" s="16" t="n"/>
-      <c r="E210" s="16" t="n"/>
-      <c r="F210" s="16" t="n"/>
-    </row>
-    <row r="211" ht="176" customHeight="1">
-      <c r="A211" s="23" t="inlineStr">
+      <c r="B211" s="18" t="n"/>
+      <c r="C211" s="18" t="n"/>
+      <c r="D211" s="18" t="n"/>
+      <c r="E211" s="18" t="n"/>
+      <c r="F211" s="18" t="n"/>
+    </row>
+    <row r="212" ht="176" customHeight="1">
+      <c r="A212" s="25" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -9984,257 +10012,245 @@
 3. 체에 걸러 낸 후 사용한다.</t>
         </is>
       </c>
-      <c r="B211" s="24" t="n"/>
-      <c r="C211" s="24" t="n"/>
-      <c r="D211" s="24" t="n"/>
-      <c r="E211" s="24" t="n"/>
-      <c r="F211" s="24" t="n"/>
-    </row>
-    <row r="212" ht="6" customHeight="1"/>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="5" t="inlineStr">
+      <c r="B212" s="26" t="n"/>
+      <c r="C212" s="26" t="n"/>
+      <c r="D212" s="26" t="n"/>
+      <c r="E212" s="26" t="n"/>
+      <c r="F212" s="26" t="n"/>
+    </row>
+    <row r="213" ht="6" customHeight="1"/>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>레드(펄)립글로스    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B213" s="6" t="n"/>
-      <c r="C213" s="6" t="n"/>
-      <c r="D213" s="6" t="n"/>
-      <c r="E213" s="6" t="n"/>
-      <c r="F213" s="6" t="n"/>
-    </row>
-    <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="7" t="inlineStr">
+      <c r="B214" s="8" t="n"/>
+      <c r="C214" s="8" t="n"/>
+      <c r="D214" s="8" t="n"/>
+      <c r="E214" s="8" t="n"/>
+      <c r="F214" s="8" t="n"/>
+    </row>
+    <row r="215" ht="15" customHeight="1">
+      <c r="A215" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B214" s="7" t="inlineStr">
+      <c r="B215" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C214" s="7" t="inlineStr">
+      <c r="C215" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D214" s="7" t="inlineStr">
+      <c r="D215" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E214" s="7" t="inlineStr">
+      <c r="E215" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F214" s="7" t="inlineStr">
+      <c r="F215" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="64" customHeight="1">
-      <c r="A215" s="8" t="inlineStr">
+    <row r="216" ht="64" customHeight="1">
+      <c r="A216" s="10" t="inlineStr">
         <is>
           <t>유기농아르간오일</t>
         </is>
       </c>
-      <c r="B215" s="8" t="inlineStr">
+      <c r="B216" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C215" s="9" t="inlineStr">
+      <c r="C216" s="11" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D215" s="10" t="inlineStr">
+      <c r="D216" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E215" s="8" t="inlineStr">
+      <c r="E216" s="10" t="inlineStr">
         <is>
           <t>전통적으로 모로코 원주민들의 치료와 섭생의 목적으로 사용, 모로코의 올리브오일, 천연비타민E풍부</t>
         </is>
       </c>
-      <c r="F215" s="8" t="inlineStr">
+      <c r="F216" s="10" t="inlineStr">
         <is>
           <t>원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="80" customHeight="1">
-      <c r="A216" s="8" t="inlineStr">
+    <row r="217" ht="80" customHeight="1">
+      <c r="A217" s="10" t="inlineStr">
         <is>
           <t>(자초인퓨즈) / 피마자오일</t>
         </is>
       </c>
-      <c r="B216" s="8" t="inlineStr">
+      <c r="B217" s="10" t="inlineStr">
         <is>
           <t>9g</t>
         </is>
       </c>
-      <c r="C216" s="9" t="inlineStr">
+      <c r="C217" s="11" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D216" s="22" t="inlineStr">
+      <c r="D217" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E216" s="8" t="inlineStr">
+      <c r="E217" s="10" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F216" s="8" t="n"/>
-    </row>
-    <row r="217" ht="64" customHeight="1">
-      <c r="A217" s="8" t="inlineStr">
+      <c r="F217" s="10" t="n"/>
+    </row>
+    <row r="218" ht="64" customHeight="1">
+      <c r="A218" s="10" t="inlineStr">
         <is>
           <t>코코아버터</t>
         </is>
       </c>
-      <c r="B217" s="8" t="inlineStr">
+      <c r="B218" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C217" s="9" t="inlineStr">
+      <c r="C218" s="11" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D217" s="10" t="inlineStr">
+      <c r="D218" s="12" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E217" s="8" t="inlineStr">
+      <c r="E218" s="10" t="inlineStr">
         <is>
           <t>알려진 오일 중 가장 안정적인 것 중 하나 자연적인 산화방지제가 들어있어 산패를 막아주며 부드러운 향, 촉감제공</t>
         </is>
       </c>
-      <c r="F217" s="8" t="inlineStr">
+      <c r="F218" s="10" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="32" customHeight="1">
-      <c r="A218" s="8" t="inlineStr">
+    <row r="219" ht="32" customHeight="1">
+      <c r="A219" s="10" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B218" s="8" t="inlineStr">
+      <c r="B219" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C218" s="9" t="inlineStr">
+      <c r="C219" s="11" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D218" s="20" t="inlineStr">
+      <c r="D219" s="22" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E218" s="8" t="inlineStr">
+      <c r="E219" s="10" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취, 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="F218" s="8" t="inlineStr">
+      <c r="F219" s="10" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="32" customHeight="1">
-      <c r="A219" s="8" t="inlineStr">
+    <row r="220" ht="32" customHeight="1">
+      <c r="A220" s="10" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B219" s="8" t="inlineStr">
+      <c r="B220" s="10" t="inlineStr">
         <is>
           <t>9방울</t>
         </is>
       </c>
-      <c r="C219" s="9" t="inlineStr">
+      <c r="C220" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D219" s="11" t="inlineStr">
+      <c r="D220" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E219" s="8" t="inlineStr">
+      <c r="E220" s="10" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="F219" s="8" t="inlineStr">
+      <c r="F220" s="10" t="inlineStr">
         <is>
           <t>원하는 플레이버오일, 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="32" customHeight="1">
-      <c r="A220" s="8" t="inlineStr">
+    <row r="221" ht="32" customHeight="1">
+      <c r="A221" s="10" t="inlineStr">
         <is>
           <t>실버펄</t>
         </is>
       </c>
-      <c r="B220" s="8" t="inlineStr">
+      <c r="B221" s="10" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C220" s="9" t="inlineStr">
+      <c r="C221" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D220" s="21" t="inlineStr">
+      <c r="D221" s="23" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E220" s="8" t="inlineStr">
+      <c r="E221" s="10" t="inlineStr">
         <is>
           <t>글로시한 느낌, / 기호에 맞게 조절, 넣지 않아도 됨</t>
         </is>
       </c>
-      <c r="F220" s="8" t="n"/>
-    </row>
-    <row r="221" ht="14" customHeight="1">
-      <c r="A221" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 39 · 경화 6 · 활성 51 · 향 3 · 색소 2</t>
-        </is>
-      </c>
-      <c r="B221" s="14" t="n"/>
-      <c r="C221" s="14" t="n"/>
-      <c r="D221" s="14" t="n"/>
-      <c r="E221" s="14" t="n"/>
-      <c r="F221" s="14" t="n"/>
+      <c r="F221" s="10" t="n"/>
     </row>
     <row r="222" ht="14" customHeight="1">
       <c r="A222" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 39 · 경화 6 · 활성 51 · 향 3 · 색소 2</t>
         </is>
       </c>
       <c r="B222" s="16" t="n"/>
@@ -10243,8 +10259,20 @@
       <c r="E222" s="16" t="n"/>
       <c r="F222" s="16" t="n"/>
     </row>
-    <row r="223" ht="192" customHeight="1">
+    <row r="223" ht="14" customHeight="1">
       <c r="A223" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B223" s="18" t="n"/>
+      <c r="C223" s="18" t="n"/>
+      <c r="D223" s="18" t="n"/>
+      <c r="E223" s="18" t="n"/>
+      <c r="F223" s="18" t="n"/>
+    </row>
+    <row r="224" ht="192" customHeight="1">
+      <c r="A224" s="19" t="inlineStr">
         <is>
           <t>입술에 영양과 윤기를 동시에 줄 수 있는립글로스입니다.
 튜브용기에 넣어서 사용하기 더욱 더 간편하게 만들어봤어요.
@@ -10261,20 +10289,20 @@
         </is>
       </c>
     </row>
-    <row r="224" ht="14" customHeight="1">
-      <c r="A224" s="15" t="inlineStr">
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B224" s="16" t="n"/>
-      <c r="C224" s="16" t="n"/>
-      <c r="D224" s="16" t="n"/>
-      <c r="E224" s="16" t="n"/>
-      <c r="F224" s="16" t="n"/>
-    </row>
-    <row r="225" ht="160" customHeight="1">
-      <c r="A225" s="17" t="inlineStr">
+      <c r="B225" s="18" t="n"/>
+      <c r="C225" s="18" t="n"/>
+      <c r="D225" s="18" t="n"/>
+      <c r="E225" s="18" t="n"/>
+      <c r="F225" s="18" t="n"/>
+    </row>
+    <row r="226" ht="160" customHeight="1">
+      <c r="A226" s="19" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -10287,255 +10315,243 @@
         </is>
       </c>
     </row>
-    <row r="226" ht="6" customHeight="1"/>
-    <row r="227" ht="22" customHeight="1">
-      <c r="A227" s="5" t="inlineStr">
+    <row r="227" ht="6" customHeight="1"/>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t>진주 피지컨트롤 파우더    [진주 / 피지컨트롤 / 파우더]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B227" s="6" t="n"/>
-      <c r="C227" s="6" t="n"/>
-      <c r="D227" s="6" t="n"/>
-      <c r="E227" s="6" t="n"/>
-      <c r="F227" s="6" t="n"/>
-    </row>
-    <row r="228" ht="15" customHeight="1">
-      <c r="A228" s="7" t="inlineStr">
+      <c r="B228" s="8" t="n"/>
+      <c r="C228" s="8" t="n"/>
+      <c r="D228" s="8" t="n"/>
+      <c r="E228" s="8" t="n"/>
+      <c r="F228" s="8" t="n"/>
+    </row>
+    <row r="229" ht="15" customHeight="1">
+      <c r="A229" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B228" s="7" t="inlineStr">
+      <c r="B229" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C228" s="7" t="inlineStr">
+      <c r="C229" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D228" s="7" t="inlineStr">
+      <c r="D229" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E228" s="7" t="inlineStr">
+      <c r="E229" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F228" s="7" t="inlineStr">
+      <c r="F229" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="32" customHeight="1">
-      <c r="A229" s="18" t="inlineStr">
+    <row r="230" ht="32" customHeight="1">
+      <c r="A230" s="20" t="inlineStr">
         <is>
           <t>진주분말</t>
         </is>
       </c>
-      <c r="B229" s="18" t="inlineStr">
+      <c r="B230" s="20" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C229" s="19" t="inlineStr">
+      <c r="C230" s="21" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D229" s="22" t="inlineStr">
+      <c r="D230" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E229" s="18" t="inlineStr">
+      <c r="E230" s="20" t="inlineStr">
         <is>
           <t>진주분말, 미네럴 공급, 피지컨트롤</t>
         </is>
       </c>
-      <c r="F229" s="18" t="n"/>
-    </row>
-    <row r="230" ht="96" customHeight="1">
-      <c r="A230" s="18" t="inlineStr">
+      <c r="F230" s="20" t="n"/>
+    </row>
+    <row r="231" ht="96" customHeight="1">
+      <c r="A231" s="20" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B230" s="18" t="inlineStr">
+      <c r="B231" s="20" t="inlineStr">
         <is>
           <t>29g</t>
         </is>
       </c>
-      <c r="C230" s="19" t="inlineStr">
+      <c r="C231" s="21" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D230" s="12" t="inlineStr">
+      <c r="D231" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E230" s="18" t="inlineStr">
+      <c r="E231" s="20" t="inlineStr">
         <is>
           <t>피지흡착, 뽀송뽀송</t>
         </is>
       </c>
-      <c r="F230" s="18" t="inlineStr">
+      <c r="F231" s="20" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="48" customHeight="1">
-      <c r="A231" s="18" t="inlineStr">
+    <row r="232" ht="48" customHeight="1">
+      <c r="A232" s="20" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B231" s="18" t="inlineStr">
+      <c r="B232" s="20" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C231" s="19" t="inlineStr">
+      <c r="C232" s="21" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D231" s="22" t="inlineStr">
+      <c r="D232" s="24" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E231" s="18" t="inlineStr">
+      <c r="E232" s="20" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F231" s="18" t="inlineStr">
+      <c r="F232" s="20" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="48" customHeight="1">
-      <c r="A232" s="18" t="inlineStr">
+    <row r="233" ht="48" customHeight="1">
+      <c r="A233" s="20" t="inlineStr">
         <is>
           <t>로즈제라늄 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B232" s="18" t="inlineStr">
+      <c r="B233" s="20" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C232" s="19" t="inlineStr">
+      <c r="C233" s="21" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D232" s="11" t="inlineStr">
+      <c r="D233" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E232" s="18" t="inlineStr">
+      <c r="E233" s="20" t="inlineStr">
         <is>
           <t>고가의 장미오일은 아니지만 장미향이 나는 제라늄. 모든 피부 사용. 피지조절</t>
         </is>
       </c>
-      <c r="F232" s="18" t="inlineStr">
+      <c r="F233" s="20" t="inlineStr">
         <is>
           <t>원하는 에센셜오일.</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="96" customHeight="1">
-      <c r="A233" s="18" t="inlineStr">
+    <row r="234" ht="96" customHeight="1">
+      <c r="A234" s="20" t="inlineStr">
         <is>
           <t>카오링클레이</t>
         </is>
       </c>
-      <c r="B233" s="18" t="inlineStr">
+      <c r="B234" s="20" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C233" s="19" t="inlineStr">
+      <c r="C234" s="21" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D233" s="21" t="inlineStr">
+      <c r="D234" s="23" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E233" s="18" t="inlineStr">
+      <c r="E234" s="20" t="inlineStr">
         <is>
           <t>중국 고령이 원산지인 클레이, 영어발음은 카오링, 현재 세계 다양한 지역에 분포, 채취. 미네럴공급, 화장품, 제약, 식품 등 다양한 용도로 사용됨. 피지컨트롤</t>
         </is>
       </c>
-      <c r="F233" s="18" t="inlineStr">
+      <c r="F234" s="20" t="inlineStr">
         <is>
           <t>화이트클레이</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="64" customHeight="1">
-      <c r="A234" s="18" t="inlineStr">
+    <row r="235" ht="64" customHeight="1">
+      <c r="A235" s="20" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B234" s="18" t="inlineStr">
+      <c r="B235" s="20" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C234" s="19" t="inlineStr">
+      <c r="C235" s="21" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D234" s="11" t="inlineStr">
+      <c r="D235" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E234" s="18" t="inlineStr">
+      <c r="E235" s="20" t="inlineStr">
         <is>
           <t>진정, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="F234" s="18" t="inlineStr">
+      <c r="F235" s="20" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
-    </row>
-    <row r="235" ht="14" customHeight="1">
-      <c r="A235" s="13" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  활성 18 · 향 1 · 색소 16 · 기타 65</t>
-        </is>
-      </c>
-      <c r="B235" s="14" t="n"/>
-      <c r="C235" s="14" t="n"/>
-      <c r="D235" s="14" t="n"/>
-      <c r="E235" s="14" t="n"/>
-      <c r="F235" s="14" t="n"/>
     </row>
     <row r="236" ht="14" customHeight="1">
       <c r="A236" s="15" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  활성 18 · 향 1 · 색소 16 · 기타 65</t>
         </is>
       </c>
       <c r="B236" s="16" t="n"/>
@@ -10544,8 +10560,20 @@
       <c r="E236" s="16" t="n"/>
       <c r="F236" s="16" t="n"/>
     </row>
-    <row r="237" ht="384" customHeight="1">
-      <c r="A237" s="23" t="inlineStr">
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="17" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B237" s="18" t="n"/>
+      <c r="C237" s="18" t="n"/>
+      <c r="D237" s="18" t="n"/>
+      <c r="E237" s="18" t="n"/>
+      <c r="F237" s="18" t="n"/>
+    </row>
+    <row r="238" ht="384" customHeight="1">
+      <c r="A238" s="25" t="inlineStr">
         <is>
           <t>여름이면 저에게 고민이 하나 생기는데요..
 오전에는 괜찮지만 오후가 되면 번들녀로 변합니다. (변신~)
@@ -10570,14 +10598,14 @@
 허준 선생이 동의보감에 기술한 진주(珍珠)의 효능을 보면</t>
         </is>
       </c>
-      <c r="B237" s="24" t="n"/>
-      <c r="C237" s="24" t="n"/>
-      <c r="D237" s="24" t="n"/>
-      <c r="E237" s="24" t="n"/>
-      <c r="F237" s="24" t="n"/>
-    </row>
-    <row r="238" ht="208" customHeight="1">
-      <c r="A238" s="23" t="inlineStr">
+      <c r="B238" s="26" t="n"/>
+      <c r="C238" s="26" t="n"/>
+      <c r="D238" s="26" t="n"/>
+      <c r="E238" s="26" t="n"/>
+      <c r="F238" s="26" t="n"/>
+    </row>
+    <row r="239" ht="208" customHeight="1">
+      <c r="A239" s="25" t="inlineStr">
         <is>
           <t>"진주가루를 유즙(乳汁)에 섞어 바르면 검은 반점을 제거하며, 얼굴을 윤기나게하여 안색을 좋게한다.",
 "진주는 성질이 차고 무독(無毒)하여 심신을 평안케하며 눈을 밝게 하고 피부의 종기를 다스린다."라고
@@ -10592,26 +10620,26 @@
 위생상 퍼프만 새로 바꿔주세요.</t>
         </is>
       </c>
-      <c r="B238" s="24" t="n"/>
-      <c r="C238" s="24" t="n"/>
-      <c r="D238" s="24" t="n"/>
-      <c r="E238" s="24" t="n"/>
-      <c r="F238" s="24" t="n"/>
-    </row>
-    <row r="239" ht="14" customHeight="1">
-      <c r="A239" s="15" t="inlineStr">
+      <c r="B239" s="26" t="n"/>
+      <c r="C239" s="26" t="n"/>
+      <c r="D239" s="26" t="n"/>
+      <c r="E239" s="26" t="n"/>
+      <c r="F239" s="26" t="n"/>
+    </row>
+    <row r="240" ht="14" customHeight="1">
+      <c r="A240" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B239" s="16" t="n"/>
-      <c r="C239" s="16" t="n"/>
-      <c r="D239" s="16" t="n"/>
-      <c r="E239" s="16" t="n"/>
-      <c r="F239" s="16" t="n"/>
-    </row>
-    <row r="240" ht="176" customHeight="1">
-      <c r="A240" s="23" t="inlineStr">
+      <c r="B240" s="18" t="n"/>
+      <c r="C240" s="18" t="n"/>
+      <c r="D240" s="18" t="n"/>
+      <c r="E240" s="18" t="n"/>
+      <c r="F240" s="18" t="n"/>
+    </row>
+    <row r="241" ht="176" customHeight="1">
+      <c r="A241" s="25" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.지퍼백에 모든 재료를 계량하세요.
@@ -10625,147 +10653,148 @@
 9. 완성</t>
         </is>
       </c>
-      <c r="B240" s="24" t="n"/>
-      <c r="C240" s="24" t="n"/>
-      <c r="D240" s="24" t="n"/>
-      <c r="E240" s="24" t="n"/>
-      <c r="F240" s="24" t="n"/>
-    </row>
-    <row r="241" ht="6" customHeight="1"/>
+      <c r="B241" s="26" t="n"/>
+      <c r="C241" s="26" t="n"/>
+      <c r="D241" s="26" t="n"/>
+      <c r="E241" s="26" t="n"/>
+      <c r="F241" s="26" t="n"/>
+    </row>
+    <row r="242" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="113">
     <mergeCell ref="A174:F174"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A189:F189"/>
     <mergeCell ref="A198:F198"/>
     <mergeCell ref="A238:F238"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A86:F86"/>
     <mergeCell ref="A239:F239"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A160:F160"/>
     <mergeCell ref="A175:F175"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A150:F150"/>
-    <mergeCell ref="A159:F159"/>
-    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A224:F224"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A200:F200"/>
     <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A161:F161"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A226:F226"/>
     <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="A228:F228"/>
     <mergeCell ref="A237:F237"/>
     <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A221:F221"/>
-    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A212:F212"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A236:F236"/>
     <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A214:F214"/>
     <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A223:F223"/>
     <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A213:F213"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A62:F62"/>
     <mergeCell ref="A240:F240"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="A190:F190"/>
     <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A142:F142"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A191:F191"/>
     <mergeCell ref="A225:F225"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A178:F178"/>
     <mergeCell ref="A162:F162"/>
-    <mergeCell ref="A227:F227"/>
     <mergeCell ref="A137:F137"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A208:F208"/>
-    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A105:F105"/>
     <mergeCell ref="A56:F56"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A210:F210"/>
-    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A171:F171"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A109:F109"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A117:F117"/>
     <mergeCell ref="A173:F173"/>
     <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A166:F166"/>
-    <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A120:F120"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A235:F235"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A185:F185"/>
-    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A209:F209"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A211:F211"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A201:F201"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="A222:F222"/>
+    <mergeCell ref="A123:F123"/>
     <mergeCell ref="A138:F138"/>
     <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A227" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A228" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -6021,7 +6021,7 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>식물성 버터, / 끈적임 적고 수분함량 높고 아주 부드러움</t>
+          <t>식물성 버터 · 끈적임 적고 수분함량 높고 아주 부드러움</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -6085,10 +6085,10 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>티타늄디옥사이드 함유, / 파운데이션 파우더</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="n"/>
+          <t>티타늄디옥사이드 함유 · 파운데이션 파우더</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr"/>
     </row>
     <row r="23" ht="64" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>FCF, 버갑텐 프리, / 감귤껍질오일, 아로마테라피</t>
+          <t>FCF, 버갑텐 프리 · 감귤껍질오일, 아로마테라피</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>피지성분 비슷, / 가벼운 오일 또는 액상왁스</t>
+          <t>피지성분 비슷 · 가벼운 오일 또는 액상왁스</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
-          <t>더 진한 색을 원하면 / 양을 추가하세요.</t>
+          <t>더 진한 색을 원하면 · 양을 추가하세요.</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -7192,12 +7192,12 @@
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>끈적, 오래가는 보습, / 아주까리유</t>
+          <t>끈적, 오래가는 보습 · 아주까리유</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7265,7 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="64" customHeight="1">
+    <row r="78" ht="48" customHeight="1">
       <c r="A78" s="20" t="inlineStr">
         <is>
           <t>립 컬러베이스 / (액상)</t>
@@ -7288,12 +7288,12 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>미리 만들어놓으세요. / 호호바오일 4g, / 원하는 립컬러베이스 0.5g / 상세 만들기 방법 참고</t>
+          <t>미리 만들어놓으세요. · 호호바오일 4g · 원하는 립컬러베이스 0.5g · 상세 만들기 방법 참고</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
-          <t>미리 만들어놓은 / 9가지 립컬러베이스 중 원하는 것</t>
+          <t>미리 만들어놓은 · 9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7403,7 @@
       <c r="E84" s="26" t="n"/>
       <c r="F84" s="26" t="n"/>
     </row>
-    <row r="85" ht="136.5" customHeight="1">
+    <row r="85" ht="152.5" customHeight="1">
       <c r="A85" s="26" t="n"/>
       <c r="B85" s="26" t="n"/>
       <c r="C85" s="26" t="n"/>
@@ -7479,12 +7479,12 @@
       </c>
       <c r="E89" s="10" t="inlineStr">
         <is>
-          <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
+          <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>립스틱베이스 / (불투명)</t>
+          <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
@@ -7664,12 +7664,12 @@
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
+          <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
       <c r="F100" s="20" t="inlineStr">
         <is>
-          <t>립스틱베이스 / (불투명)</t>
+          <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="E113" s="10" t="inlineStr">
         <is>
-          <t>위의 레시피로 / 미리 만들것.</t>
+          <t>위의 레시피로 · 미리 만들것.</t>
         </is>
       </c>
       <c r="F113" s="10" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="F114" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 색상</t>
+          <t>원하는 · 색상</t>
         </is>
       </c>
     </row>
@@ -8001,7 +8001,7 @@
           <t>향</t>
         </is>
       </c>
-      <c r="E115" s="10" t="n"/>
+      <c r="E115" s="10" t="inlineStr"/>
       <c r="F115" s="10" t="inlineStr">
         <is>
           <t>원하는 EO</t>
@@ -8158,12 +8158,12 @@
       </c>
       <c r="E125" s="20" t="inlineStr">
         <is>
-          <t>금잔화 인퓨즈오일, / 민감, 트러블 피부</t>
+          <t>금잔화 인퓨즈오일 · 민감, 트러블 피부</t>
         </is>
       </c>
       <c r="F125" s="20" t="inlineStr">
         <is>
-          <t>캐모마일 / 오일</t>
+          <t>캐모마일 · 오일</t>
         </is>
       </c>
     </row>
@@ -8190,7 +8190,7 @@
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>올리브오일유래, 초기사용감은 / 실리콘오일처럼 가볍지만 보습력지속</t>
+          <t>올리브오일유래, 초기사용감은 · 실리콘오일처럼 가볍지만 보습력지속</t>
         </is>
       </c>
       <c r="F126" s="20" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>에코인증, / 물/오일분리 저지</t>
+          <t>에코인증 · 물 · 오일분리 저지</t>
         </is>
       </c>
       <c r="F127" s="20" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>유화 보조제, / 백탁 현상 완화</t>
+          <t>유화 보조제 · 백탁 현상 완화</t>
         </is>
       </c>
       <c r="F128" s="20" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="E129" s="20" t="inlineStr">
         <is>
-          <t>5차 필터링, / UV살균처리 정제수</t>
+          <t>5차 필터링 · UV살균처리 정제수</t>
         </is>
       </c>
       <c r="F129" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 플로럴워터</t>
+          <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
@@ -8318,12 +8318,12 @@
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수를 듬뿍 담은 / 수분감이 풍부한 겔</t>
+          <t>불가리아 다마스크 장미수를 듬뿍 담은 · 수분감이 풍부한 겔</t>
         </is>
       </c>
       <c r="F130" s="20" t="inlineStr">
         <is>
-          <t>허브누리 베라겔, / 네롤리 / 플라워겔</t>
+          <t>허브누리 베라겔 · 네롤리 · 플라워겔</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E131" s="20" t="inlineStr">
         <is>
-          <t>고중저분자, / 트리플 히아루론산,</t>
+          <t>고중저분자 · 트리플 히아루론산</t>
         </is>
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>에코 / 보습제</t>
+          <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
@@ -8382,10 +8382,10 @@
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>알로에베라잎추출물, 참마뿌리추출물, / 흰목이버섯추출물, 미역추출물 복합추출물</t>
-        </is>
-      </c>
-      <c r="F132" s="20" t="n"/>
+          <t>알로에베라잎추출물, 참마뿌리추출물 · 흰목이버섯추출물, 미역추출물 복합추출물</t>
+        </is>
+      </c>
+      <c r="F132" s="20" t="inlineStr"/>
     </row>
     <row r="133" ht="64" customHeight="1">
       <c r="A133" s="20" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="F133" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (정제수의 양을 31g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (정제수의 양을 31g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
           <t>자외선UV-B를 주로 난반사</t>
         </is>
       </c>
-      <c r="F135" s="20" t="n"/>
+      <c r="F135" s="20" t="inlineStr"/>
     </row>
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="20" t="inlineStr">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="E136" s="20" t="inlineStr">
         <is>
-          <t>라벤더. 만다린 로먼캐모마일 에센셜오일, / 민감피부를 위한 블렌딩</t>
+          <t>라벤더. 만다린 로먼캐모마일 에센셜오일 · 민감피부를 위한 블렌딩</t>
         </is>
       </c>
       <c r="F136" s="20" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
+          <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>립스틱베이스 / (불투명)</t>
+          <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
@@ -8698,10 +8698,10 @@
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>레드21번 0.5g + 레드7번 0.2g+ 옐로우6번 0.1g+ 레드6번 0.2g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
-        </is>
-      </c>
-      <c r="F146" s="10" t="n"/>
+          <t>레드21번 0.5g + 레드7번 0.2g+ 옐로우6번 0.1g+ 레드6번 0.2g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr"/>
     </row>
     <row r="147" ht="32" customHeight="1">
       <c r="A147" s="10" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="E157" s="20" t="inlineStr">
         <is>
-          <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
+          <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>립스틱베이스 / (불투명)</t>
+          <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
@@ -8916,10 +8916,10 @@
       </c>
       <c r="E158" s="20" t="inlineStr">
         <is>
-          <t>레드27번 0.3g + 레드40번 0.2g+ 아이론옐로우 0.1g+ 화이트 0.4g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
-        </is>
-      </c>
-      <c r="F158" s="20" t="n"/>
+          <t>레드27번 0.3g + 레드40번 0.2g+ 아이론옐로우 0.1g+ 화이트 0.4g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
+        </is>
+      </c>
+      <c r="F158" s="20" t="inlineStr"/>
     </row>
     <row r="159" ht="32" customHeight="1">
       <c r="A159" s="20" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="E159" s="20" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, 로즈우드 / 에센셜오일 블렌딩</t>
+          <t>레몬, 레몬글라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서 / 사용해도 됩니다.</t>
+          <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 · 사용해도 됩니다.</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
         <is>
-          <t>립스틱베이스 / (불투명)</t>
+          <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
@@ -9154,10 +9154,10 @@
       </c>
       <c r="E170" s="10" t="inlineStr">
         <is>
-          <t>레드6번 0.3g + 아이론옐로우 0.1g / + 레드27번 0.2g + 화이트 0.2g / 0.5g은 촉촉, / 1g은 좀더 매트 색상 색양 조절가능.</t>
-        </is>
-      </c>
-      <c r="F170" s="10" t="n"/>
+          <t>레드6번 0.3g + 아이론옐로우 0.1g · + 레드27번 0.2g + 화이트 0.2g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
+        </is>
+      </c>
+      <c r="F170" s="10" t="inlineStr"/>
     </row>
     <row r="171" ht="32" customHeight="1">
       <c r="A171" s="10" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>라임, 스윗오렌지, 레몬, 로즈마리 / 에센셜오일 블렌딩</t>
+          <t>라임, 스윗오렌지, 레몬, 로즈마리 · 에센셜오일 블렌딩</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="E180" s="20" t="inlineStr">
         <is>
-          <t>멀티밤오일베이스 43g+ / 멀티왁스9.5g 로 미리 굳혀서</t>
+          <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서</t>
         </is>
       </c>
       <c r="F180" s="20" t="inlineStr">
@@ -9374,10 +9374,10 @@
       </c>
       <c r="E181" s="20" t="inlineStr">
         <is>
-          <t>색상사진은 아래의 / 립스틱 발색 사진과 처방 참고</t>
-        </is>
-      </c>
-      <c r="F181" s="20" t="n"/>
+          <t>색상사진은 아래의 · 립스틱 발색 사진과 처방 참고</t>
+        </is>
+      </c>
+      <c r="F181" s="20" t="inlineStr"/>
     </row>
     <row r="182" ht="32" customHeight="1">
       <c r="A182" s="20" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="E182" s="20" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 가벼운 사용감</t>
+          <t>피지성분과 비슷 · 가벼운 사용감</t>
         </is>
       </c>
       <c r="F182" s="20" t="inlineStr">
         <is>
-          <t>스위트아몬드오일, / 동백오일 등</t>
+          <t>스위트아몬드오일 · 동백오일 등</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="F183" s="20" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
           <t>100% 헤나 분말</t>
         </is>
       </c>
-      <c r="F193" s="10" t="n"/>
+      <c r="F193" s="10" t="inlineStr"/>
     </row>
     <row r="194" ht="64" customHeight="1">
       <c r="A194" s="10" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="F194" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="F203" s="20" t="inlineStr">
         <is>
-          <t>원하는 / 베이스오일</t>
+          <t>원하는 · 베이스오일</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F204" s="20" t="inlineStr">
         <is>
-          <t>비타민E를 피마자오일양 중 일부로 대체,</t>
+          <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="E205" s="20" t="inlineStr">
         <is>
-          <t>식물성 버터, 카리테나무 열매에서 채취, / 보습효과짱^^</t>
+          <t>식물성 버터, 카리테나무 열매에서 채취 · 보습효과짱^^</t>
         </is>
       </c>
       <c r="F205" s="20" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="E206" s="20" t="inlineStr">
         <is>
-          <t>칸데릴라라는 식물에서 채취, / 단단하게 굳히는 역할</t>
+          <t>칸데릴라라는 식물에서 채취 · 단단하게 굳히는 역할</t>
         </is>
       </c>
       <c r="F206" s="20" t="inlineStr">
@@ -10121,7 +10121,7 @@
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F217" s="10" t="n"/>
+      <c r="F217" s="10" t="inlineStr"/>
     </row>
     <row r="218" ht="64" customHeight="1">
       <c r="A218" s="10" t="inlineStr">
@@ -10242,10 +10242,10 @@
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
-          <t>글로시한 느낌, / 기호에 맞게 조절, 넣지 않아도 됨</t>
-        </is>
-      </c>
-      <c r="F221" s="10" t="n"/>
+          <t>글로시한 느낌 · 기호에 맞게 조절, 넣지 않아도 됨</t>
+        </is>
+      </c>
+      <c r="F221" s="10" t="inlineStr"/>
     </row>
     <row r="222" ht="14" customHeight="1">
       <c r="A222" s="15" t="inlineStr">
@@ -10386,7 +10386,7 @@
           <t>진주분말, 미네럴 공급, 피지컨트롤</t>
         </is>
       </c>
-      <c r="F230" s="20" t="n"/>
+      <c r="F230" s="20" t="inlineStr"/>
     </row>
     <row r="231" ht="96" customHeight="1">
       <c r="A231" s="20" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="F231" s="20" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="F232" s="20" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
       </c>
       <c r="F235" s="20" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,13 +40,25 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001155CC"/>
-      <sz val="12"/>
-      <u val="single"/>
+      <color rgb="0033475B"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001155CC"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,7 +71,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +95,76 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EFF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
@@ -93,57 +175,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBD9E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEF3F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FAFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8E0D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5D9C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD9F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8F5D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCEBFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,11 +186,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="008A94A6"/>
-      </top>
     </border>
     <border>
       <left style="thin">
@@ -174,11 +201,16 @@
         <color rgb="00D0D5DD"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="008A94A6"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -192,65 +224,111 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -332,7 +410,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1854200"/>
+    <pos x="7848600" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -352,7 +430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1854200"/>
+    <pos x="9696450" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -372,7 +450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1854200"/>
+    <pos x="11544300" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -392,7 +470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1854200"/>
+    <pos x="13392150" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -412,7 +490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="3702049"/>
+    <pos x="7848600" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -432,7 +510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="3702049"/>
+    <pos x="9696450" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -452,7 +530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="3702049"/>
+    <pos x="11544300" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -472,7 +550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="3702049"/>
+    <pos x="13392150" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -492,7 +570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="5549900"/>
+    <pos x="7848600" y="13093699"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -512,7 +590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="7397750"/>
+    <pos x="7848600" y="14941549"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -532,7 +610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="12655549"/>
+    <pos x="7848600" y="20199350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -552,7 +630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="12655549"/>
+    <pos x="9696450" y="20199350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -572,7 +650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="12655549"/>
+    <pos x="11544300" y="20199350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -592,7 +670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="12655549"/>
+    <pos x="13392150" y="20199350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -612,7 +690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="14503399"/>
+    <pos x="7848600" y="22047200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -632,7 +710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="14503399"/>
+    <pos x="9696450" y="22047200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -652,7 +730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="14503399"/>
+    <pos x="11544300" y="22047200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -672,7 +750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="14503399"/>
+    <pos x="13392150" y="22047200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -692,7 +770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="16351249"/>
+    <pos x="7848600" y="23895050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -712,7 +790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="16351249"/>
+    <pos x="9696450" y="23895050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -732,7 +810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="18199100"/>
+    <pos x="7848600" y="25742900"/>
     <ext cx="5143500" cy="4286250"/>
     <pic>
       <nvPicPr>
@@ -752,7 +830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="22523450"/>
+    <pos x="7848600" y="30067250"/>
     <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -772,7 +850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="24266525"/>
+    <pos x="7848600" y="31810325"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -792,7 +870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="24266525"/>
+    <pos x="9696450" y="31810325"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -812,7 +890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="24266525"/>
+    <pos x="11544300" y="31810325"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -832,7 +910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="24266525"/>
+    <pos x="13392150" y="31810325"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -852,7 +930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="26114375"/>
+    <pos x="7848600" y="33658175"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -872,7 +950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="26114375"/>
+    <pos x="9696450" y="33658175"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -892,7 +970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="26114375"/>
+    <pos x="11544300" y="33658175"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -912,7 +990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="26114375"/>
+    <pos x="13392150" y="33658175"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -932,7 +1010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27962225"/>
+    <pos x="7848600" y="35506025"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -952,7 +1030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="27962225"/>
+    <pos x="9696450" y="35506025"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -972,7 +1050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="27962225"/>
+    <pos x="11544300" y="35506025"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -992,7 +1070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="27962225"/>
+    <pos x="13392150" y="35506025"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1012,7 +1090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="29810075"/>
+    <pos x="7848600" y="37353875"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1032,7 +1110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="29810075"/>
+    <pos x="9696450" y="37353875"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1052,7 +1130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31734125"/>
+    <pos x="7848600" y="39277925"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1072,7 +1150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31734125"/>
+    <pos x="9696450" y="39277925"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1092,7 +1170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31734125"/>
+    <pos x="11544300" y="39277925"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1112,7 +1190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31734125"/>
+    <pos x="13392150" y="39277925"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1132,7 +1210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33581975"/>
+    <pos x="7848600" y="41125775"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1152,7 +1230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="33581975"/>
+    <pos x="9696450" y="41125775"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1172,7 +1250,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="33581975"/>
+    <pos x="11544300" y="41125775"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1192,7 +1270,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="33581975"/>
+    <pos x="13392150" y="41125775"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1212,7 +1290,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="35429825"/>
+    <pos x="7848600" y="42973625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1232,7 +1310,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="35429825"/>
+    <pos x="9696450" y="42973625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1252,7 +1330,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="35429825"/>
+    <pos x="11544300" y="42973625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1272,7 +1350,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="35429825"/>
+    <pos x="13392150" y="42973625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1292,7 +1370,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37277675"/>
+    <pos x="7848600" y="44821475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1312,7 +1390,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37277675"/>
+    <pos x="9696450" y="44821475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1332,7 +1410,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="37277675"/>
+    <pos x="11544300" y="44821475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1352,7 +1430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39722425"/>
+    <pos x="7848600" y="47266225"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1372,7 +1450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="39722425"/>
+    <pos x="9696450" y="47266225"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1392,7 +1470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="39722425"/>
+    <pos x="11544300" y="47266225"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1412,7 +1490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="39722425"/>
+    <pos x="13392150" y="47266225"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1432,7 +1510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="41570275"/>
+    <pos x="7848600" y="49114075"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1452,7 +1530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="41570275"/>
+    <pos x="9696450" y="49114075"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1472,7 +1550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="41570275"/>
+    <pos x="11544300" y="49114075"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1492,7 +1570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="41570275"/>
+    <pos x="13392150" y="49114075"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1512,7 +1590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45069125"/>
+    <pos x="7848600" y="52612925"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1532,7 +1610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45069125"/>
+    <pos x="9696450" y="52612925"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1552,7 +1630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="45069125"/>
+    <pos x="11544300" y="52612925"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1572,7 +1650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="45069125"/>
+    <pos x="13392150" y="52612925"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1592,7 +1670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46916975"/>
+    <pos x="7848600" y="54460775"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1612,7 +1690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="46916975"/>
+    <pos x="9696450" y="54460775"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1632,7 +1710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="46916975"/>
+    <pos x="11544300" y="54460775"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1652,7 +1730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="46916975"/>
+    <pos x="13392150" y="54460775"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1672,7 +1750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="48764825"/>
+    <pos x="7848600" y="56308625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1692,7 +1770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="48764825"/>
+    <pos x="9696450" y="56308625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1712,7 +1790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="48764825"/>
+    <pos x="11544300" y="56308625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1732,7 +1810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="48764825"/>
+    <pos x="13392150" y="56308625"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1752,7 +1830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="50612675"/>
+    <pos x="7848600" y="58156475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1772,7 +1850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="50612675"/>
+    <pos x="9696450" y="58156475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1792,7 +1870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="50612675"/>
+    <pos x="11544300" y="58156475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1812,7 +1890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="50612675"/>
+    <pos x="13392150" y="58156475"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1832,7 +1910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="52460525"/>
+    <pos x="7848600" y="60004325"/>
     <ext cx="3857625" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1852,7 +1930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="57718325"/>
+    <pos x="7848600" y="65262125"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1872,7 +1950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="57718325"/>
+    <pos x="9696450" y="65262125"/>
     <ext cx="1809750" cy="781050"/>
     <pic>
       <nvPicPr>
@@ -1892,7 +1970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="57718325"/>
+    <pos x="11544300" y="65262125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1912,7 +1990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="57718325"/>
+    <pos x="13392150" y="65262125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1932,7 +2010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="59566175"/>
+    <pos x="7848600" y="67109975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1952,7 +2030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="59566175"/>
+    <pos x="9696450" y="67109975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1972,7 +2050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="59566175"/>
+    <pos x="11544300" y="67109975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1992,7 +2070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="59566175"/>
+    <pos x="13392150" y="67109975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2012,7 +2090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61414025"/>
+    <pos x="7848600" y="68957825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2032,7 +2110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="61414025"/>
+    <pos x="9696450" y="68957825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2052,7 +2130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="61414025"/>
+    <pos x="11544300" y="68957825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2072,7 +2150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="61414025"/>
+    <pos x="13392150" y="68957825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2092,7 +2170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="63261875"/>
+    <pos x="7848600" y="70805675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2112,7 +2190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="63261875"/>
+    <pos x="9696450" y="70805675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2132,7 +2210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="63261875"/>
+    <pos x="11544300" y="70805675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2152,7 +2230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="63261875"/>
+    <pos x="13392150" y="70805675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2172,7 +2250,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="65109725"/>
+    <pos x="7848600" y="72653525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2192,7 +2270,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="65109725"/>
+    <pos x="9696450" y="72653525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2212,7 +2290,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="65109725"/>
+    <pos x="11544300" y="72653525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2232,7 +2310,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="65109725"/>
+    <pos x="13392150" y="72653525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2252,7 +2330,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="67033775"/>
+    <pos x="7848600" y="74577575"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2272,7 +2350,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="67033775"/>
+    <pos x="9696450" y="74577575"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2292,7 +2370,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="67033775"/>
+    <pos x="11544300" y="74577575"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2312,7 +2390,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="67033775"/>
+    <pos x="13392150" y="74577575"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2332,7 +2410,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68881625"/>
+    <pos x="7848600" y="76425425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2352,7 +2430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="68881625"/>
+    <pos x="9696450" y="76425425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2372,7 +2450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="68881625"/>
+    <pos x="11544300" y="76425425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2392,7 +2470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="68881625"/>
+    <pos x="13392150" y="76425425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2412,7 +2490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="70729475"/>
+    <pos x="7848600" y="78273275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2432,7 +2510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="70729475"/>
+    <pos x="9696450" y="78273275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2452,7 +2530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="70729475"/>
+    <pos x="11544300" y="78273275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2472,7 +2550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="70729475"/>
+    <pos x="13392150" y="78273275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2492,7 +2570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="72577325"/>
+    <pos x="7848600" y="80121125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2512,7 +2590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="72577325"/>
+    <pos x="9696450" y="80121125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2532,7 +2610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="72577325"/>
+    <pos x="11544300" y="80121125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2552,7 +2630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="72577325"/>
+    <pos x="13392150" y="80121125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2572,7 +2650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="74425175"/>
+    <pos x="7848600" y="81968975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2592,7 +2670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="74425175"/>
+    <pos x="9696450" y="81968975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2612,7 +2690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="74425175"/>
+    <pos x="11544300" y="81968975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2632,7 +2710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="74425175"/>
+    <pos x="13392150" y="81968975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2652,7 +2730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="76273025"/>
+    <pos x="7848600" y="83816825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2672,7 +2750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78197075"/>
+    <pos x="7848600" y="85740875"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2692,7 +2770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78197075"/>
+    <pos x="9696450" y="85740875"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2712,7 +2790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78197075"/>
+    <pos x="11544300" y="85740875"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2732,7 +2810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78197075"/>
+    <pos x="13392150" y="85740875"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2752,7 +2830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="80044925"/>
+    <pos x="7848600" y="87588725"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2772,7 +2850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="80044925"/>
+    <pos x="9696450" y="87588725"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2792,7 +2870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="80044925"/>
+    <pos x="11544300" y="87588725"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2812,7 +2890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="80044925"/>
+    <pos x="13392150" y="87588725"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2832,7 +2910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81892775"/>
+    <pos x="7848600" y="89436575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2852,7 +2930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="81892775"/>
+    <pos x="9696450" y="89436575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2872,7 +2950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="81892775"/>
+    <pos x="11544300" y="89436575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2892,7 +2970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="81892775"/>
+    <pos x="13392150" y="89436575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2912,7 +2990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="83740625"/>
+    <pos x="7848600" y="91284425"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2932,7 +3010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="83740625"/>
+    <pos x="9696450" y="91284425"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2952,7 +3030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="83740625"/>
+    <pos x="11544300" y="91284425"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2972,7 +3050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="83740625"/>
+    <pos x="13392150" y="91284425"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2992,7 +3070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85588475"/>
+    <pos x="7848600" y="93132275"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3012,7 +3090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="85588475"/>
+    <pos x="9696450" y="93132275"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3032,7 +3110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87512525"/>
+    <pos x="7848600" y="95056325"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -3052,7 +3130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="87512525"/>
+    <pos x="9696450" y="95056325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3072,7 +3150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="87512525"/>
+    <pos x="11544300" y="95056325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3092,7 +3170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="87512525"/>
+    <pos x="13392150" y="95056325"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3112,7 +3190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="89360375"/>
+    <pos x="7848600" y="96904175"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3132,7 +3210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="89360375"/>
+    <pos x="9696450" y="96904175"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3152,7 +3230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="89360375"/>
+    <pos x="11544300" y="96904175"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3172,7 +3250,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="89360375"/>
+    <pos x="13392150" y="96904175"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3192,7 +3270,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91208225"/>
+    <pos x="7848600" y="98752025"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3212,7 +3290,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="100580825"/>
+    <pos x="7848600" y="108124625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3232,7 +3310,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="100580825"/>
+    <pos x="9696450" y="108124625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3252,7 +3330,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="100580825"/>
+    <pos x="11544300" y="108124625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3272,7 +3350,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="100580825"/>
+    <pos x="13392150" y="108124625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3292,7 +3370,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="102428675"/>
+    <pos x="7848600" y="109972475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3312,7 +3390,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="102428675"/>
+    <pos x="9696450" y="109972475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3332,7 +3410,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="102428675"/>
+    <pos x="11544300" y="109972475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3352,7 +3430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="102428675"/>
+    <pos x="13392150" y="109972475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3372,7 +3450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="104276525"/>
+    <pos x="7848600" y="111820325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3392,7 +3470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="104276525"/>
+    <pos x="9696450" y="111820325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3412,7 +3490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="104276525"/>
+    <pos x="11544300" y="111820325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3432,7 +3510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="104276525"/>
+    <pos x="13392150" y="111820325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3452,7 +3530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="106124375"/>
+    <pos x="7848600" y="113668175"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3472,7 +3550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="106124375"/>
+    <pos x="9696450" y="113668175"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3492,7 +3570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="106124375"/>
+    <pos x="11544300" y="113668175"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3512,7 +3590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="106124375"/>
+    <pos x="13392150" y="113668175"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3532,7 +3610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="107972225"/>
+    <pos x="7848600" y="115516025"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3552,7 +3630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="107972225"/>
+    <pos x="9696450" y="115516025"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3572,7 +3650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="107972225"/>
+    <pos x="11544300" y="115516025"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3592,7 +3670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="107972225"/>
+    <pos x="13392150" y="115516025"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3612,7 +3690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="109820075"/>
+    <pos x="7848600" y="117363875"/>
     <ext cx="4057650" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -3632,7 +3710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="115077875"/>
+    <pos x="7848600" y="122621675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3652,7 +3730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="115077875"/>
+    <pos x="9696450" y="122621675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3672,7 +3750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="115077875"/>
+    <pos x="11544300" y="122621675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3692,7 +3770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="115077875"/>
+    <pos x="13392150" y="122621675"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3712,7 +3790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="116925725"/>
+    <pos x="7848600" y="124469525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3732,7 +3810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="116925725"/>
+    <pos x="9696450" y="124469525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3752,7 +3830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="116925725"/>
+    <pos x="11544300" y="124469525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3772,7 +3850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="116925725"/>
+    <pos x="13392150" y="124469525"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3792,7 +3870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118773575"/>
+    <pos x="7848600" y="126317375"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3812,7 +3890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="118773575"/>
+    <pos x="9696450" y="126317375"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3832,7 +3910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="118773575"/>
+    <pos x="11544300" y="126317375"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3852,7 +3930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="118773575"/>
+    <pos x="13392150" y="126317375"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3872,7 +3950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="120621425"/>
+    <pos x="7848600" y="128165225"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3892,7 +3970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="120621425"/>
+    <pos x="9696450" y="128165225"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3912,7 +3990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="120621425"/>
+    <pos x="11544300" y="128165225"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3932,7 +4010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="120621425"/>
+    <pos x="13392150" y="128165225"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3952,7 +4030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="122469275"/>
+    <pos x="7848600" y="130013075"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3972,7 +4050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="122469275"/>
+    <pos x="9696450" y="130013075"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3992,7 +4070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="122469275"/>
+    <pos x="11544300" y="130013075"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4012,7 +4090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="122469275"/>
+    <pos x="13392150" y="130013075"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4032,7 +4110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="124317125"/>
+    <pos x="7848600" y="131860925"/>
     <ext cx="4057650" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -4052,7 +4130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="129574925"/>
+    <pos x="7848600" y="137118725"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4072,7 +4150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="129574925"/>
+    <pos x="9696450" y="137118725"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4092,7 +4170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="129574925"/>
+    <pos x="11544300" y="137118725"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4112,7 +4190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="129574925"/>
+    <pos x="13392150" y="137118725"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4132,7 +4210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="131422775"/>
+    <pos x="7848600" y="138966575"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4152,7 +4230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="131422775"/>
+    <pos x="9696450" y="138966575"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4172,7 +4250,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="131422775"/>
+    <pos x="11544300" y="138966575"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4192,7 +4270,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="131422775"/>
+    <pos x="13392150" y="138966575"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4212,7 +4290,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="133270625"/>
+    <pos x="7848600" y="140814425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4232,7 +4310,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="133270625"/>
+    <pos x="9696450" y="140814425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4252,7 +4330,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="133270625"/>
+    <pos x="11544300" y="140814425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4272,7 +4350,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="133270625"/>
+    <pos x="13392150" y="140814425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4292,7 +4370,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="135118475"/>
+    <pos x="7848600" y="142662275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4312,7 +4390,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="135118475"/>
+    <pos x="9696450" y="142662275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4332,7 +4410,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="135118475"/>
+    <pos x="11544300" y="142662275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4352,7 +4430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="135118475"/>
+    <pos x="13392150" y="142662275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4372,7 +4450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="136966325"/>
+    <pos x="7848600" y="144510125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4392,7 +4470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="136966325"/>
+    <pos x="9696450" y="144510125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4412,7 +4490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="136966325"/>
+    <pos x="11544300" y="144510125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4432,7 +4510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="138814175"/>
+    <pos x="7848600" y="146357975"/>
     <ext cx="4057650" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -4452,7 +4530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="144071975"/>
+    <pos x="7848600" y="151615775"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4472,7 +4550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="144071975"/>
+    <pos x="9696450" y="151615775"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4492,7 +4570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="144071975"/>
+    <pos x="11544300" y="151615775"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4512,7 +4590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="144071975"/>
+    <pos x="13392150" y="151615775"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4532,7 +4610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="145919825"/>
+    <pos x="7848600" y="153463625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4552,7 +4630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="145919825"/>
+    <pos x="9696450" y="153463625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4572,7 +4650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="145919825"/>
+    <pos x="11544300" y="153463625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4592,7 +4670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="145919825"/>
+    <pos x="13392150" y="153463625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4612,7 +4690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="147767675"/>
+    <pos x="7848600" y="155311475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4632,7 +4710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="147767675"/>
+    <pos x="9696450" y="155311475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4652,7 +4730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="147767675"/>
+    <pos x="11544300" y="155311475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4672,7 +4750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="151247475"/>
+    <pos x="7848600" y="158791275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4692,7 +4770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="151247475"/>
+    <pos x="9696450" y="158791275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4712,7 +4790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="151247475"/>
+    <pos x="11544300" y="158791275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4732,7 +4810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="151247475"/>
+    <pos x="13392150" y="158791275"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4752,7 +4830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="153095325"/>
+    <pos x="7848600" y="160639125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4772,7 +4850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="153095325"/>
+    <pos x="9696450" y="160639125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4792,7 +4870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="154943175"/>
+    <pos x="7848600" y="162486975"/>
     <ext cx="5143500" cy="2895600"/>
     <pic>
       <nvPicPr>
@@ -4812,7 +4890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="159642175"/>
+    <pos x="7848600" y="167185975"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4832,7 +4910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="159642175"/>
+    <pos x="9696450" y="167185975"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4852,7 +4930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="159642175"/>
+    <pos x="11544300" y="167185975"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4872,7 +4950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="159642175"/>
+    <pos x="13392150" y="167185975"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4892,7 +4970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="161490025"/>
+    <pos x="7848600" y="169033825"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4912,7 +4990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="161490025"/>
+    <pos x="9696450" y="169033825"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4932,7 +5010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="161490025"/>
+    <pos x="11544300" y="169033825"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4952,7 +5030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="163337875"/>
+    <pos x="7848600" y="170881675"/>
     <ext cx="4276725" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -4972,7 +5050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="170272075"/>
+    <pos x="7848600" y="177815875"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4992,7 +5070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="170272075"/>
+    <pos x="9696450" y="177815875"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -5012,7 +5090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="170272075"/>
+    <pos x="11544300" y="177815875"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5032,7 +5110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="170272075"/>
+    <pos x="13392150" y="177815875"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5052,7 +5130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="172119925"/>
+    <pos x="7848600" y="179663725"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5072,7 +5150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="172119925"/>
+    <pos x="9696450" y="179663725"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5092,7 +5170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="172119925"/>
+    <pos x="11544300" y="179663725"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5112,7 +5190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="172119925"/>
+    <pos x="13392150" y="179663725"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5132,7 +5210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179682775"/>
+    <pos x="7848600" y="187226575"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5152,7 +5230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179682775"/>
+    <pos x="9696450" y="187226575"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5172,7 +5250,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179682775"/>
+    <pos x="11544300" y="187226575"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5192,7 +5270,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179682775"/>
+    <pos x="13392150" y="187226575"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5212,7 +5290,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="181530625"/>
+    <pos x="7848600" y="189074425"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5232,7 +5310,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="181530625"/>
+    <pos x="9696450" y="189074425"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5252,7 +5330,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="181530625"/>
+    <pos x="11544300" y="189074425"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5272,7 +5350,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="181530625"/>
+    <pos x="13392150" y="189074425"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5292,7 +5370,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="183378475"/>
+    <pos x="7848600" y="190922275"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5312,7 +5390,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="183378475"/>
+    <pos x="9696450" y="190922275"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5332,7 +5410,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="183378475"/>
+    <pos x="11544300" y="190922275"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5643,7 +5721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F245"/>
+  <dimension ref="A1:F265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5706,173 +5784,419 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
-    <row r="5" ht="6" customHeight="1"/>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>🎨 역할(phase) 읽는 법 — 아래 미니표 '역할' 색상의 뜻</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>물·수용성 베이스. 제형의 대부분을 차지하는 뼈대이고, 수용성 활성·보습제가 여기 녹는다.   예) 정제수, 로즈워터, 알로에워터</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>오일·버터 등 지용성. 피부에 유연·보습막·영양을 주고 발림성·리치함을 결정한다.   예) 호호바오일, 시어버터, 스쿠알란</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>안 섞이는 물과 오일을 하나로 묶는 '다리'. 없으면 분리된다. 양으로 로션↔크림 점도도 좌우.   예) 올리브유화왁스, 몬타노브68</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>왁스·고형. 제형을 굳혀 밤·스틱 형태를 만든다. 비율로 말랑↔단단이 갈린다.   예) 밀랍, 칸데릴라왁스</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>피지·노폐물을 물에 씻겨나가게 하는 세정 성분. 거품·세정력을 담당.   예) 코코베타인, 데실글루코사이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>공기·진피의 수분을 끌어와 붙잡는 습윤제. 촉촉함을 유지.   예) 글리세린, 프로판다이올, 솔비톨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>특정 효능(미백·진정·탄력 등)을 노리는 기능 성분. '이 제품의 컨셉'을 만든다.   예) 나이아신아마이드, 세라마이드, 추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>향·아로마(에센셜오일 등). 소량(보통 ≤1%)으로 감성·아로마테라피.   예) 라벤더EO, 네롤리</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>색을 내는 안료·펄. 색조·틴트 제형의 핵심.   예) 마이카, 산화철, 이산화티탄</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>세균·곰팡이 번식을 억제. 물 있는 제형엔 사실상 필수.   예) 1,2-헥산디올, 천연한방보존제</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>점도 조절(젤화)과 산도(pH) 조절. 사용감·안정성·방부 효력에 영향.   예) 잔탄검, 카보머, 구연산</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>위 분류에 안 잡힌 것(완제 베이스·충전제 등).   예) 크림베이스, 옥수수전분</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>📖 배합 기본원리 — 왜 그렇게 하나</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Q. 유화는 왜 같은 온도(65~75℃)에서?
+→ 오일상 왁스가 녹아 액체이고 수상도 같은 온도여야 미세하게 섞인다. 온도차가 크면 닿는 순간 왁스가 굳어 알갱이·분리가 생긴다.</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Q. 왜 식으며 저어주나 / 핸드블렌더?
+→ 유화 입자를 더 잘고 고르게 쪼개면 분리가 줄고 발림·안정성이 좋아진다. 찬물에 받쳐 식히면 유화가 빨리·안정적으로 잡힌다.</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Q. 물 있는 제형은 왜 방부 필수?
+→ 물은 세균·곰팡이의 번식 배지다. 무방부는 수일 내 변질 → 냉장·소량 제조만. 방부력은 실제 챌린지(방부력) 테스트로 확인해야 한다.</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Q. 왜 약산성(pH 5~6)?
+→ 건강한 피부는 pH 4.5~5.5. 알칼리는 장벽을 들뜨게 하고, 적정 산성은 방부 효력과 일부 활성(산성 영역) 안정에 유리하다.</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Q. 가루(점증·활성)는 왜 미리 분산?
+→ 가루가 물에 닿자마자 겉만 수화돼 '덩어리(fish-eye)'가 진다. 글리세린 등에 미리 적셔 분산하거나 천천히 뿌리며 교반해야 곱게 풀린다.</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Q. 무수(오일·밤)는 왜 방부 불필요하지만 물 유입 금지?
+→ 물이 없으면 미생물이 못 큰다. 대신 사용 중 물이 들어가면 그 지점부터 상한다. 산패는 비타민E 등 항산화와 차광·밀폐로 늦춘다.</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>촉촉 글로우 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>(겁나게 촉촉) 립밤</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일 +멀티밤 왁스</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>(로즈우드)에센셜오일</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>2~3방울</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>향, 향기 테라피</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>립컬러 베이스</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>레드6(0.3), 아이론 옐로우 (0.1), 레드27 (0.2), 화이트 (0.2)</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>사용하던 립스틱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 88 · 향 1 · 기타 11</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
-    </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="B31" s="33" t="n"/>
+      <c r="C31" s="33" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="33" t="n"/>
+      <c r="F31" s="33" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-    </row>
-    <row r="13" ht="256" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="B32" s="35" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+    </row>
+    <row r="33" ht="256" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>겁나게 촉촉~
 글로우 립스틱
@@ -5892,20 +6216,20 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="176" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="B34" s="35" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="176" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>촉촉 글로우 립스틱만들기
 1. 비커에 립컬러를 계량하세요.
@@ -5921,298 +6245,298 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="221.4999999999999" customHeight="1"/>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="36" ht="221.5" customHeight="1"/>
+    <row r="37" ht="6" customHeight="1"/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>멀티밤 bb    [1..베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="25" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="25" t="n"/>
+      <c r="F38" s="25" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F39" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="37" t="inlineStr">
         <is>
           <t>멀티오일베이스</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C20" s="21" t="inlineStr">
+      <c r="C40" s="38" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D40" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E40" s="37" t="inlineStr">
         <is>
           <t>MCT, 로즈힙, 유기농 호호바, 녹차씨, 발효동백, 스쿠알란, 비타민E 등</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>유기농 / 코포아수버터</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C41" s="38" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E41" s="37" t="inlineStr">
         <is>
           <t>식물성 버터 · 끈적임 적고 수분함량 높고 아주 부드러움</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>망고버터 등</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="37" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B42" s="37" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C42" s="38" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D42" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E42" s="37" t="inlineStr">
         <is>
           <t>식물성 왁스, 단단하게.</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>칼라믹스 / 파운데이션</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B43" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C43" s="38" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D43" s="40" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 함유 · 파운데이션 파우더</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr"/>
-    </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr"/>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="37" t="inlineStr">
         <is>
           <t>보르피린</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C44" s="38" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D44" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E44" s="37" t="inlineStr">
         <is>
           <t>볼륨업, 주름</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>10 g(10%)을 원한다면 로즈워터를 5g 줄여서 40g이 되도록 해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="37" t="inlineStr">
         <is>
           <t>알파 비사보롤</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>0.3g / (10방울)</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C45" s="38" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E45" s="37" t="inlineStr">
         <is>
           <t>식약처 인증, 미백 원료</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="37" t="inlineStr">
         <is>
           <t>버가못에센셜오일</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>0.7g / 10~14방울</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C46" s="38" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E46" s="37" t="inlineStr">
         <is>
           <t>FCF, 버갑텐 프리 · 감귤껍질오일, 아로마테라피</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 61 · 경화 16 · 활성 6 · 향 2 · 색소 13 · 기타 1</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-    </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="B47" s="33" t="n"/>
+      <c r="C47" s="33" t="n"/>
+      <c r="D47" s="33" t="n"/>
+      <c r="E47" s="33" t="n"/>
+      <c r="F47" s="33" t="n"/>
+    </row>
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="336" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+      <c r="E48" s="35" t="n"/>
+      <c r="F48" s="35" t="n"/>
+    </row>
+    <row r="49" ht="336" customHeight="1">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>이 레시피는 2015년에
 문화센터에서 반응이 좋다며
@@ -6237,26 +6561,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="23" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-    </row>
-    <row r="31" ht="176" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="B50" s="35" t="n"/>
+      <c r="C50" s="35" t="n"/>
+      <c r="D50" s="35" t="n"/>
+      <c r="E50" s="35" t="n"/>
+      <c r="F50" s="35" t="n"/>
+    </row>
+    <row r="51" ht="176" customHeight="1">
+      <c r="A51" s="42" t="inlineStr">
         <is>
           <t>1. 멀티오일베이스를 계량하세요.
 2. 왁스와 버터를 계량한 후
@@ -6271,302 +6595,302 @@
 굳으면 완성</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
-    </row>
-    <row r="32" ht="61.25000000000006" customHeight="1">
-      <c r="A32" s="26" t="n"/>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="23" t="n"/>
+    </row>
+    <row r="52" ht="61.25000000000006" customHeight="1">
+      <c r="A52" s="23" t="n"/>
+      <c r="B52" s="23" t="n"/>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="23" t="n"/>
+      <c r="F52" s="23" t="n"/>
+    </row>
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>카렌듈라 썬밤    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F55" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="48" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B56" s="27" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C56" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D56" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>피지성분 비슷 · 가벼운 오일 또는 액상왁스</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F56" s="27" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E57" s="27" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일, 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F57" s="27" t="inlineStr">
         <is>
           <t>캐모마일인퓨즈오일</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D38" s="24" t="inlineStr">
+      <c r="D58" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>산화방지.</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F58" s="27" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="D39" s="22" t="inlineStr">
+      <c r="D59" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E59" s="27" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F59" s="27" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>산화 아연 분말</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D60" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>전체양의 23%</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>3~9방울</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D61" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E61" s="27" t="inlineStr">
         <is>
           <t>썬번, 진정, 아로마테라피</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F61" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 47 · 경화 27 · 활성 1 · 향 1 · 기타 24</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="B62" s="33" t="n"/>
+      <c r="C62" s="33" t="n"/>
+      <c r="D62" s="33" t="n"/>
+      <c r="E62" s="33" t="n"/>
+      <c r="F62" s="33" t="n"/>
+    </row>
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="B63" s="35" t="n"/>
+      <c r="C63" s="35" t="n"/>
+      <c r="D63" s="35" t="n"/>
+      <c r="E63" s="35" t="n"/>
+      <c r="F63" s="35" t="n"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="36" t="inlineStr">
         <is>
           <t>초정밀 과정</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-    </row>
-    <row r="46" ht="192" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="B65" s="35" t="n"/>
+      <c r="C65" s="35" t="n"/>
+      <c r="D65" s="35" t="n"/>
+      <c r="E65" s="35" t="n"/>
+      <c r="F65" s="35" t="n"/>
+    </row>
+    <row r="66" ht="192" customHeight="1">
+      <c r="A66" s="36" t="inlineStr">
         <is>
           <t>1. 징크옥사이드를 종이에 계량하세요.
 2. 비커에 1번 재료를 계량합니다.
@@ -6583,328 +6907,328 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="103" customHeight="1"/>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="67" ht="102.9999999999997" customHeight="1"/>
+    <row r="68" ht="6" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
         <is>
           <t>내추럴 립스틱    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="B69" s="25" t="n"/>
+      <c r="C69" s="25" t="n"/>
+      <c r="D69" s="25" t="n"/>
+      <c r="E69" s="25" t="n"/>
+      <c r="F69" s="25" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C70" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E70" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F70" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="20" t="inlineStr">
+    <row r="71" ht="48" customHeight="1">
+      <c r="A71" s="37" t="inlineStr">
         <is>
           <t>정제 호호바오일</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B71" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C51" s="21" t="inlineStr">
+      <c r="C71" s="38" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E71" s="37" t="inlineStr">
         <is>
           <t>가벼운오일, 보습</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
+      <c r="F71" s="37" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>립베이스 레드27</t>
         </is>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B72" s="37" t="inlineStr">
         <is>
           <t>0.4g</t>
         </is>
       </c>
-      <c r="C52" s="21" t="inlineStr">
+      <c r="C72" s="38" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D72" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="E72" s="37" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="F72" s="37" t="inlineStr">
         <is>
           <t>더 진한 색을 원하면 · 양을 추가하세요.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B73" s="37" t="inlineStr">
         <is>
           <t>3.5g</t>
         </is>
       </c>
-      <c r="C53" s="21" t="inlineStr">
+      <c r="C73" s="38" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D53" s="22" t="inlineStr">
+      <c r="D73" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E73" s="37" t="inlineStr">
         <is>
           <t>식물성왁스. 경화제</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F73" s="37" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="37" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B74" s="37" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C54" s="21" t="inlineStr">
+      <c r="C74" s="38" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D74" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="E74" s="37" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F74" s="37" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="20" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>발효 동백오일</t>
         </is>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B75" s="37" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C55" s="21" t="inlineStr">
+      <c r="C75" s="38" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D75" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E75" s="37" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="F75" s="37" t="inlineStr">
         <is>
           <t>아르간, 마유 등</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="64" customHeight="1">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="37" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B76" s="37" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C56" s="21" t="inlineStr">
+      <c r="C76" s="38" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D76" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="E76" s="37" t="inlineStr">
         <is>
           <t>산화방지, 고보습</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="F76" s="37" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="20" t="inlineStr">
+    <row r="77" ht="48" customHeight="1">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B77" s="37" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C57" s="21" t="inlineStr">
+      <c r="C77" s="38" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D57" s="13" t="inlineStr">
+      <c r="D77" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E77" s="37" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F77" s="37" t="inlineStr">
         <is>
           <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="15" t="inlineStr">
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 58 · 경화 23 · 활성 14 · 향 2 · 기타 3</t>
         </is>
       </c>
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="16" t="n"/>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="B78" s="33" t="n"/>
+      <c r="C78" s="33" t="n"/>
+      <c r="D78" s="33" t="n"/>
+      <c r="E78" s="33" t="n"/>
+      <c r="F78" s="33" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B59" s="18" t="n"/>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-    </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
+      <c r="B79" s="35" t="n"/>
+      <c r="C79" s="35" t="n"/>
+      <c r="D79" s="35" t="n"/>
+      <c r="E79" s="35" t="n"/>
+      <c r="F79" s="35" t="n"/>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="42" t="inlineStr">
         <is>
           <t>촉촉한 립밤에 색상을 더했습니다. 내추럴 립스틱!
 가루날림이 없는 립베이스로 원하는 색상을 만들어보세요.
 오일에 미리 개어서 원하는 색상을 만든 후 적용하면 됩니다.</t>
         </is>
       </c>
-      <c r="B60" s="26" t="n"/>
-      <c r="C60" s="26" t="n"/>
-      <c r="D60" s="26" t="n"/>
-      <c r="E60" s="26" t="n"/>
-      <c r="F60" s="26" t="n"/>
-    </row>
-    <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="B80" s="23" t="n"/>
+      <c r="C80" s="23" t="n"/>
+      <c r="D80" s="23" t="n"/>
+      <c r="E80" s="23" t="n"/>
+      <c r="F80" s="23" t="n"/>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B61" s="18" t="n"/>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-    </row>
-    <row r="62" ht="208" customHeight="1">
-      <c r="A62" s="25" t="inlineStr">
+      <c r="B81" s="35" t="n"/>
+      <c r="C81" s="35" t="n"/>
+      <c r="D81" s="35" t="n"/>
+      <c r="E81" s="35" t="n"/>
+      <c r="F81" s="35" t="n"/>
+    </row>
+    <row r="82" ht="208" customHeight="1">
+      <c r="A82" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 속뚜껑을 닫고 뒤집어 주세요.
@@ -6921,147 +7245,147 @@
 12.꺼내서 넘친 부분도 다듬어 닦습니다. 스티커를 붙이고 겉뚜껑을 닫으면 완성.</t>
         </is>
       </c>
-      <c r="B62" s="26" t="n"/>
-      <c r="C62" s="26" t="n"/>
-      <c r="D62" s="26" t="n"/>
-      <c r="E62" s="26" t="n"/>
-      <c r="F62" s="26" t="n"/>
-    </row>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="B82" s="23" t="n"/>
+      <c r="C82" s="23" t="n"/>
+      <c r="D82" s="23" t="n"/>
+      <c r="E82" s="23" t="n"/>
+      <c r="F82" s="23" t="n"/>
+    </row>
+    <row r="83" ht="6" customHeight="1"/>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
         <is>
           <t>립스틱/글로스 컬러베이스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="B84" s="25" t="n"/>
+      <c r="C84" s="25" t="n"/>
+      <c r="D84" s="25" t="n"/>
+      <c r="E84" s="25" t="n"/>
+      <c r="F84" s="25" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B85" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C85" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D85" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E85" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F85" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>(골든)호호바오일</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C86" s="28" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D86" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E86" s="27" t="inlineStr">
         <is>
           <t>액상왁스, 가벼운 오일</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F86" s="27" t="inlineStr">
         <is>
           <t>마카다미아넛오일</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="32" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
         <is>
           <t>립 컬러베이스 7</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C87" s="28" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D87" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E87" s="27" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F87" s="27" t="inlineStr">
         <is>
           <t>9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 89 · 기타 11</t>
         </is>
       </c>
-      <c r="B68" s="16" t="n"/>
-      <c r="C68" s="16" t="n"/>
-      <c r="D68" s="16" t="n"/>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
-    </row>
-    <row r="69" ht="14" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="B88" s="33" t="n"/>
+      <c r="C88" s="33" t="n"/>
+      <c r="D88" s="33" t="n"/>
+      <c r="E88" s="33" t="n"/>
+      <c r="F88" s="33" t="n"/>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B69" s="18" t="n"/>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-    </row>
-    <row r="70" ht="192" customHeight="1">
-      <c r="A70" s="19" t="inlineStr">
+      <c r="B89" s="35" t="n"/>
+      <c r="C89" s="35" t="n"/>
+      <c r="D89" s="35" t="n"/>
+      <c r="E89" s="35" t="n"/>
+      <c r="F89" s="35" t="n"/>
+    </row>
+    <row r="90" ht="192" customHeight="1">
+      <c r="A90" s="36" t="inlineStr">
         <is>
           <t>원하는 색상의 립제품 만들기 좋은 립컬러 베이스가 나왔습니다.
 쉽게 활용하는 법을 안내해드립니다.
@@ -7078,20 +7402,20 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B71" s="18" t="n"/>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-    </row>
-    <row r="72" ht="96" customHeight="1">
-      <c r="A72" s="19" t="inlineStr">
+      <c r="B91" s="35" t="n"/>
+      <c r="C91" s="35" t="n"/>
+      <c r="D91" s="35" t="n"/>
+      <c r="E91" s="35" t="n"/>
+      <c r="F91" s="35" t="n"/>
+    </row>
+    <row r="92" ht="96" customHeight="1">
+      <c r="A92" s="36" t="inlineStr">
         <is>
           <t>1. (골든)호호바오일 4g을 먼저 계량합니다.
 2.원하는 립컬러 베이스를 비커에 발라주세요.
@@ -7101,269 +7425,269 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="6" customHeight="1"/>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
+    <row r="93" ht="6" customHeight="1"/>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
         <is>
           <t>블루밍 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B74" s="8" t="n"/>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="B94" s="25" t="n"/>
+      <c r="C94" s="25" t="n"/>
+      <c r="D94" s="25" t="n"/>
+      <c r="E94" s="25" t="n"/>
+      <c r="F94" s="25" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
+      <c r="B95" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C95" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D95" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
+      <c r="E95" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="F95" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="20" t="inlineStr">
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="37" t="inlineStr">
         <is>
           <t>발효 마유</t>
         </is>
       </c>
-      <c r="B76" s="20" t="inlineStr">
+      <c r="B96" s="37" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C76" s="21" t="inlineStr">
+      <c r="C96" s="38" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D76" s="24" t="inlineStr">
+      <c r="D96" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E76" s="20" t="inlineStr">
+      <c r="E96" s="37" t="inlineStr">
         <is>
           <t>오래가는 보습</t>
         </is>
       </c>
-      <c r="F76" s="20" t="inlineStr">
+      <c r="F96" s="37" t="inlineStr">
         <is>
           <t>동백, 아르간오일 등</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="48" customHeight="1">
-      <c r="A77" s="20" t="inlineStr">
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="37" t="inlineStr">
         <is>
           <t>피마자유</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B97" s="37" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C77" s="21" t="inlineStr">
+      <c r="C97" s="38" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D77" s="14" t="inlineStr">
+      <c r="D97" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E97" s="37" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습 · 아주까리유</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F97" s="37" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="64" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
+    <row r="98" ht="64" customHeight="1">
+      <c r="A98" s="37" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B98" s="37" t="inlineStr">
         <is>
           <t>0.1g</t>
         </is>
       </c>
-      <c r="C78" s="21" t="inlineStr">
+      <c r="C98" s="38" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D78" s="24" t="inlineStr">
+      <c r="D98" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E78" s="20" t="inlineStr">
+      <c r="E98" s="37" t="inlineStr">
         <is>
           <t>산화방지제</t>
         </is>
       </c>
-      <c r="F78" s="20" t="inlineStr">
+      <c r="F98" s="37" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="20" t="inlineStr">
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="37" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B99" s="37" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C79" s="21" t="inlineStr">
+      <c r="C99" s="38" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="D79" s="22" t="inlineStr">
+      <c r="D99" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E99" s="37" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
+      <c r="F99" s="37" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>립 컬러베이스 / (액상)</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B100" s="37" t="inlineStr">
         <is>
           <t>4.5g</t>
         </is>
       </c>
-      <c r="C80" s="21" t="inlineStr">
+      <c r="C100" s="38" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D100" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E100" s="37" t="inlineStr">
         <is>
           <t>미리 만들어놓으세요. · 호호바오일 4g · 원하는 립컬러베이스 0.5g · 상세 만들기 방법 참고</t>
         </is>
       </c>
-      <c r="F80" s="20" t="inlineStr">
+      <c r="F100" s="37" t="inlineStr">
         <is>
           <t>미리 만들어놓은 · 9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="20" t="inlineStr">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="37" t="inlineStr">
         <is>
           <t>로즈우드EO</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B101" s="37" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C81" s="21" t="inlineStr">
+      <c r="C101" s="38" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="D101" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="E101" s="37" t="inlineStr">
         <is>
           <t>향, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F101" s="37" t="inlineStr">
         <is>
           <t>원하는에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="15" t="inlineStr">
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 35 · 경화 8 · 활성 16 · 향 2 · 기타 39</t>
         </is>
       </c>
-      <c r="B82" s="16" t="n"/>
-      <c r="C82" s="16" t="n"/>
-      <c r="D82" s="16" t="n"/>
-      <c r="E82" s="16" t="n"/>
-      <c r="F82" s="16" t="n"/>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="B102" s="33" t="n"/>
+      <c r="C102" s="33" t="n"/>
+      <c r="D102" s="33" t="n"/>
+      <c r="E102" s="33" t="n"/>
+      <c r="F102" s="33" t="n"/>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B83" s="18" t="n"/>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-    </row>
-    <row r="84" ht="112" customHeight="1">
-      <c r="A84" s="25" t="inlineStr">
+      <c r="B103" s="35" t="n"/>
+      <c r="C103" s="35" t="n"/>
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="35" t="n"/>
+      <c r="F103" s="35" t="n"/>
+    </row>
+    <row r="104" ht="112" customHeight="1">
+      <c r="A104" s="42" t="inlineStr">
         <is>
           <t>위)달달한 핑크, 아래)갸우뚱 레드
 위)알쏭달쏭 핑크레드(27번+ 레드6) , 아래)단물 빠진 와인 (레드33)
@@ -7374,26 +7698,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B84" s="26" t="n"/>
-      <c r="C84" s="26" t="n"/>
-      <c r="D84" s="26" t="n"/>
-      <c r="E84" s="26" t="n"/>
-      <c r="F84" s="26" t="n"/>
-    </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="17" t="inlineStr">
+      <c r="B104" s="23" t="n"/>
+      <c r="C104" s="23" t="n"/>
+      <c r="D104" s="23" t="n"/>
+      <c r="E104" s="23" t="n"/>
+      <c r="F104" s="23" t="n"/>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B85" s="18" t="n"/>
-      <c r="C85" s="18" t="n"/>
-      <c r="D85" s="18" t="n"/>
-      <c r="E85" s="18" t="n"/>
-      <c r="F85" s="18" t="n"/>
-    </row>
-    <row r="86" ht="160" customHeight="1">
-      <c r="A86" s="25" t="inlineStr">
+      <c r="B105" s="35" t="n"/>
+      <c r="C105" s="35" t="n"/>
+      <c r="D105" s="35" t="n"/>
+      <c r="E105" s="35" t="n"/>
+      <c r="F105" s="35" t="n"/>
+    </row>
+    <row r="106" ht="160" customHeight="1">
+      <c r="A106" s="42" t="inlineStr">
         <is>
           <t>1.미리 만들어놓은 색을 먼저 선택하세요. (달달한 핑크나
 2.잘익은 홍시 등 색상표를 참고해 만들어보세요.)
@@ -7406,163 +7730,163 @@
 9.용기에 담아서 속뚜껑 닫으면 완성~!</t>
         </is>
       </c>
-      <c r="B86" s="26" t="n"/>
-      <c r="C86" s="26" t="n"/>
-      <c r="D86" s="26" t="n"/>
-      <c r="E86" s="26" t="n"/>
-      <c r="F86" s="26" t="n"/>
-    </row>
-    <row r="87" ht="409" customHeight="1">
-      <c r="A87" s="26" t="n"/>
-      <c r="B87" s="26" t="n"/>
-      <c r="C87" s="26" t="n"/>
-      <c r="D87" s="26" t="n"/>
-      <c r="E87" s="26" t="n"/>
-      <c r="F87" s="26" t="n"/>
-    </row>
-    <row r="88" ht="6" customHeight="1">
-      <c r="A88" s="26" t="n"/>
-      <c r="B88" s="26" t="n"/>
-      <c r="C88" s="26" t="n"/>
-      <c r="D88" s="26" t="n"/>
-      <c r="E88" s="26" t="n"/>
-      <c r="F88" s="26" t="n"/>
-    </row>
-    <row r="89" ht="6" customHeight="1"/>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="B106" s="23" t="n"/>
+      <c r="C106" s="23" t="n"/>
+      <c r="D106" s="23" t="n"/>
+      <c r="E106" s="23" t="n"/>
+      <c r="F106" s="23" t="n"/>
+    </row>
+    <row r="107" ht="409" customHeight="1">
+      <c r="A107" s="23" t="n"/>
+      <c r="B107" s="23" t="n"/>
+      <c r="C107" s="23" t="n"/>
+      <c r="D107" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="23" t="n"/>
+    </row>
+    <row r="108" ht="6" customHeight="1">
+      <c r="A108" s="23" t="n"/>
+      <c r="B108" s="23" t="n"/>
+      <c r="C108" s="23" t="n"/>
+      <c r="D108" s="23" t="n"/>
+      <c r="E108" s="23" t="n"/>
+      <c r="F108" s="23" t="n"/>
+    </row>
+    <row r="109" ht="6" customHeight="1"/>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="24" t="inlineStr">
         <is>
           <t>촉촉 쁘띠 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="8" t="n"/>
-      <c r="F90" s="8" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="B110" s="25" t="n"/>
+      <c r="C110" s="25" t="n"/>
+      <c r="D110" s="25" t="n"/>
+      <c r="E110" s="25" t="n"/>
+      <c r="F110" s="25" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B111" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C111" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D111" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E111" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F111" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="48" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
+    <row r="112" ht="48" customHeight="1">
+      <c r="A112" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B112" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C112" s="28" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D112" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E112" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F112" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C113" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
+      <c r="D113" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E113" s="27" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F113" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="14" customHeight="1">
-      <c r="A94" s="15" t="inlineStr">
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 95 · 향 5</t>
         </is>
       </c>
-      <c r="B94" s="16" t="n"/>
-      <c r="C94" s="16" t="n"/>
-      <c r="D94" s="16" t="n"/>
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="16" t="n"/>
-    </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="B114" s="33" t="n"/>
+      <c r="C114" s="33" t="n"/>
+      <c r="D114" s="33" t="n"/>
+      <c r="E114" s="33" t="n"/>
+      <c r="F114" s="33" t="n"/>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B95" s="18" t="n"/>
-      <c r="C95" s="18" t="n"/>
-      <c r="D95" s="18" t="n"/>
-      <c r="E95" s="18" t="n"/>
-      <c r="F95" s="18" t="n"/>
-    </row>
-    <row r="96" ht="80" customHeight="1">
-      <c r="A96" s="19" t="inlineStr">
+      <c r="B115" s="35" t="n"/>
+      <c r="C115" s="35" t="n"/>
+      <c r="D115" s="35" t="n"/>
+      <c r="E115" s="35" t="n"/>
+      <c r="F115" s="35" t="n"/>
+    </row>
+    <row r="116" ht="80" customHeight="1">
+      <c r="A116" s="36" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -7572,20 +7896,20 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="17" t="inlineStr">
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B97" s="18" t="n"/>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-    </row>
-    <row r="98" ht="384" customHeight="1">
-      <c r="A98" s="19" t="inlineStr">
+      <c r="B117" s="35" t="n"/>
+      <c r="C117" s="35" t="n"/>
+      <c r="D117" s="35" t="n"/>
+      <c r="E117" s="35" t="n"/>
+      <c r="F117" s="35" t="n"/>
+    </row>
+    <row r="118" ht="384" customHeight="1">
+      <c r="A118" s="36" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7612,142 +7936,142 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="120.5" customHeight="1"/>
-    <row r="100" ht="6" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+    <row r="119" ht="120.5" customHeight="1"/>
+    <row r="120" ht="6" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="24" t="inlineStr">
         <is>
           <t>픽미업 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="8" t="n"/>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="B121" s="25" t="n"/>
+      <c r="C121" s="25" t="n"/>
+      <c r="D121" s="25" t="n"/>
+      <c r="E121" s="25" t="n"/>
+      <c r="F121" s="25" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
+      <c r="B122" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C102" s="9" t="inlineStr">
+      <c r="C122" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D102" s="9" t="inlineStr">
+      <c r="D122" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E102" s="9" t="inlineStr">
+      <c r="E122" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F102" s="9" t="inlineStr">
+      <c r="F122" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="48" customHeight="1">
-      <c r="A103" s="20" t="inlineStr">
+    <row r="123" ht="48" customHeight="1">
+      <c r="A123" s="37" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B103" s="20" t="inlineStr">
+      <c r="B123" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C103" s="21" t="inlineStr">
+      <c r="C123" s="38" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D103" s="12" t="inlineStr">
+      <c r="D123" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E103" s="20" t="inlineStr">
+      <c r="E123" s="37" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F103" s="20" t="inlineStr">
+      <c r="F123" s="37" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="20" t="inlineStr">
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="37" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B104" s="20" t="inlineStr">
+      <c r="B124" s="37" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C104" s="21" t="inlineStr">
+      <c r="C124" s="38" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D104" s="13" t="inlineStr">
+      <c r="D124" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E104" s="20" t="inlineStr">
+      <c r="E124" s="37" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="F104" s="20" t="inlineStr">
+      <c r="F124" s="37" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="14" customHeight="1">
-      <c r="A105" s="15" t="inlineStr">
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 95 · 향 5</t>
         </is>
       </c>
-      <c r="B105" s="16" t="n"/>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="n"/>
-    </row>
-    <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="17" t="inlineStr">
+      <c r="B125" s="33" t="n"/>
+      <c r="C125" s="33" t="n"/>
+      <c r="D125" s="33" t="n"/>
+      <c r="E125" s="33" t="n"/>
+      <c r="F125" s="33" t="n"/>
+    </row>
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B106" s="18" t="n"/>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="18" t="n"/>
-      <c r="F106" s="18" t="n"/>
-    </row>
-    <row r="107" ht="224" customHeight="1">
-      <c r="A107" s="25" t="inlineStr">
+      <c r="B126" s="35" t="n"/>
+      <c r="C126" s="35" t="n"/>
+      <c r="D126" s="35" t="n"/>
+      <c r="E126" s="35" t="n"/>
+      <c r="F126" s="35" t="n"/>
+    </row>
+    <row r="127" ht="224" customHeight="1">
+      <c r="A127" s="42" t="inlineStr">
         <is>
           <t>와인, 브라운, 오렌지...
 가을, 겨울에 잘 어울리는 색상을
@@ -7765,26 +8089,26 @@
 진하기를 조절하세요.</t>
         </is>
       </c>
-      <c r="B107" s="26" t="n"/>
-      <c r="C107" s="26" t="n"/>
-      <c r="D107" s="26" t="n"/>
-      <c r="E107" s="26" t="n"/>
-      <c r="F107" s="26" t="n"/>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="17" t="inlineStr">
+      <c r="B127" s="23" t="n"/>
+      <c r="C127" s="23" t="n"/>
+      <c r="D127" s="23" t="n"/>
+      <c r="E127" s="23" t="n"/>
+      <c r="F127" s="23" t="n"/>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B108" s="18" t="n"/>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-    </row>
-    <row r="109" ht="384" customHeight="1">
-      <c r="A109" s="25" t="inlineStr">
+      <c r="B128" s="35" t="n"/>
+      <c r="C128" s="35" t="n"/>
+      <c r="D128" s="35" t="n"/>
+      <c r="E128" s="35" t="n"/>
+      <c r="F128" s="35" t="n"/>
+    </row>
+    <row r="129" ht="384" customHeight="1">
+      <c r="A129" s="42" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7810,247 +8134,247 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B109" s="26" t="n"/>
-      <c r="C109" s="26" t="n"/>
-      <c r="D109" s="26" t="n"/>
-      <c r="E109" s="26" t="n"/>
-      <c r="F109" s="26" t="n"/>
-    </row>
-    <row r="110" ht="122.0000000000007" customHeight="1">
-      <c r="A110" s="26" t="n"/>
-      <c r="B110" s="26" t="n"/>
-      <c r="C110" s="26" t="n"/>
-      <c r="D110" s="26" t="n"/>
-      <c r="E110" s="26" t="n"/>
-      <c r="F110" s="26" t="n"/>
-    </row>
-    <row r="111" ht="6" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="7" t="inlineStr">
+      <c r="B129" s="23" t="n"/>
+      <c r="C129" s="23" t="n"/>
+      <c r="D129" s="23" t="n"/>
+      <c r="E129" s="23" t="n"/>
+      <c r="F129" s="23" t="n"/>
+    </row>
+    <row r="130" ht="122.0000000000007" customHeight="1">
+      <c r="A130" s="23" t="n"/>
+      <c r="B130" s="23" t="n"/>
+      <c r="C130" s="23" t="n"/>
+      <c r="D130" s="23" t="n"/>
+      <c r="E130" s="23" t="n"/>
+      <c r="F130" s="23" t="n"/>
+    </row>
+    <row r="131" ht="6" customHeight="1"/>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="24" t="inlineStr">
         <is>
           <t>생기ON~ 립스틱    [1. 립밤 베이스 / (52.5g)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="8" t="n"/>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
-      <c r="F112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="B132" s="25" t="n"/>
+      <c r="C132" s="25" t="n"/>
+      <c r="D132" s="25" t="n"/>
+      <c r="E132" s="25" t="n"/>
+      <c r="F132" s="25" t="n"/>
+    </row>
+    <row r="133" ht="15" customHeight="1">
+      <c r="A133" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
+      <c r="B133" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C133" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D133" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="E133" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F133" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="48" customHeight="1">
-      <c r="A114" s="10" t="inlineStr">
+    <row r="134" ht="48" customHeight="1">
+      <c r="A134" s="27" t="inlineStr">
         <is>
           <t>자초립밤 / 오일 베이스</t>
         </is>
       </c>
-      <c r="B114" s="10" t="inlineStr">
+      <c r="B134" s="27" t="inlineStr">
         <is>
           <t>43g</t>
         </is>
       </c>
-      <c r="C114" s="11" t="inlineStr">
+      <c r="C134" s="28" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D114" s="12" t="inlineStr">
+      <c r="D134" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E114" s="10" t="inlineStr">
+      <c r="E134" s="27" t="inlineStr">
         <is>
           <t>자근추출물, 호호바오일, 아몬드오일, 피마자오일, 해바라기씨오일, 비타민E</t>
         </is>
       </c>
-      <c r="F114" s="10" t="inlineStr">
+      <c r="F134" s="27" t="inlineStr">
         <is>
           <t>자초인퓨즈오일, 원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="10" t="inlineStr">
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="27" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B115" s="10" t="inlineStr">
+      <c r="B135" s="27" t="inlineStr">
         <is>
           <t>9.5g</t>
         </is>
       </c>
-      <c r="C115" s="11" t="inlineStr">
+      <c r="C135" s="28" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="D115" s="22" t="inlineStr">
+      <c r="D135" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E115" s="10" t="inlineStr">
+      <c r="E135" s="27" t="inlineStr">
         <is>
           <t>식물성 경화제</t>
         </is>
       </c>
-      <c r="F115" s="10" t="inlineStr">
+      <c r="F135" s="27" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="10" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="27" t="inlineStr">
         <is>
           <t>립밤 베이스</t>
         </is>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B136" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C116" s="11" t="inlineStr">
+      <c r="C136" s="28" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D116" s="14" t="inlineStr">
+      <c r="D136" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E116" s="10" t="inlineStr">
+      <c r="E136" s="27" t="inlineStr">
         <is>
           <t>위의 레시피로 · 미리 만들것.</t>
         </is>
       </c>
-      <c r="F116" s="10" t="inlineStr">
+      <c r="F136" s="27" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="10" t="inlineStr">
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
         <is>
           <t>립 컬러 베이스</t>
         </is>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B137" s="27" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C117" s="11" t="inlineStr">
+      <c r="C137" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D117" s="14" t="inlineStr">
+      <c r="D137" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E117" s="10" t="inlineStr">
+      <c r="E137" s="27" t="inlineStr">
         <is>
           <t>레드27 + 레드21</t>
         </is>
       </c>
-      <c r="F117" s="10" t="inlineStr">
+      <c r="F137" s="27" t="inlineStr">
         <is>
           <t>원하는 · 색상</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="27" t="inlineStr">
         <is>
           <t>에센셜오일 (EO)</t>
         </is>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B138" s="27" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr">
+      <c r="C138" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D118" s="13" t="inlineStr">
+      <c r="D138" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E118" s="10" t="inlineStr"/>
-      <c r="F118" s="10" t="inlineStr">
+      <c r="E138" s="27" t="inlineStr"/>
+      <c r="F138" s="27" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="14" customHeight="1">
-      <c r="A119" s="15" t="inlineStr">
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 75 · 경화 17 · 향 0 · 기타 8</t>
         </is>
       </c>
-      <c r="B119" s="16" t="n"/>
-      <c r="C119" s="16" t="n"/>
-      <c r="D119" s="16" t="n"/>
-      <c r="E119" s="16" t="n"/>
-      <c r="F119" s="16" t="n"/>
-    </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="17" t="inlineStr">
+      <c r="B139" s="33" t="n"/>
+      <c r="C139" s="33" t="n"/>
+      <c r="D139" s="33" t="n"/>
+      <c r="E139" s="33" t="n"/>
+      <c r="F139" s="33" t="n"/>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B120" s="18" t="n"/>
-      <c r="C120" s="18" t="n"/>
-      <c r="D120" s="18" t="n"/>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-    </row>
-    <row r="121" ht="176" customHeight="1">
-      <c r="A121" s="19" t="inlineStr">
+      <c r="B140" s="35" t="n"/>
+      <c r="C140" s="35" t="n"/>
+      <c r="D140" s="35" t="n"/>
+      <c r="E140" s="35" t="n"/>
+      <c r="F140" s="35" t="n"/>
+    </row>
+    <row r="141" ht="176" customHeight="1">
+      <c r="A141" s="36" t="inlineStr">
         <is>
           <t>가볍고 촉촉한 자초립밤오일베이스로 립스틱들 만들어보세요.
 호호바오일, 피마자오일, 해바라기오일, 비타민E에
@@ -8066,20 +8390,20 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="17" t="inlineStr">
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B122" s="18" t="n"/>
-      <c r="C122" s="18" t="n"/>
-      <c r="D122" s="18" t="n"/>
-      <c r="E122" s="18" t="n"/>
-      <c r="F122" s="18" t="n"/>
-    </row>
-    <row r="123" ht="352" customHeight="1">
-      <c r="A123" s="19" t="inlineStr">
+      <c r="B142" s="35" t="n"/>
+      <c r="C142" s="35" t="n"/>
+      <c r="D142" s="35" t="n"/>
+      <c r="E142" s="35" t="n"/>
+      <c r="F142" s="35" t="n"/>
+    </row>
+    <row r="143" ht="352" customHeight="1">
+      <c r="A143" s="36" t="inlineStr">
         <is>
           <t>1.자초립밤오일베이스와 칸데릴라왁스를 계량한 후
 2. 섞으면서 녹입니다.
@@ -8106,454 +8430,454 @@
         </is>
       </c>
     </row>
-    <row r="124" ht="8.500000000000028" customHeight="1"/>
-    <row r="125" ht="6" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
+    <row r="144" ht="8.500000000000028" customHeight="1"/>
+    <row r="145" ht="6" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="24" t="inlineStr">
         <is>
           <t>수딩썬로션    [오일/ / 유화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B126" s="8" t="n"/>
-      <c r="C126" s="8" t="n"/>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
-      <c r="F126" s="8" t="n"/>
-    </row>
-    <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="9" t="inlineStr">
+      <c r="B146" s="25" t="n"/>
+      <c r="C146" s="25" t="n"/>
+      <c r="D146" s="25" t="n"/>
+      <c r="E146" s="25" t="n"/>
+      <c r="F146" s="25" t="n"/>
+    </row>
+    <row r="147" ht="15" customHeight="1">
+      <c r="A147" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
+      <c r="B147" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C147" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D147" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E147" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F127" s="9" t="inlineStr">
+      <c r="F147" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="32" customHeight="1">
-      <c r="A128" s="20" t="inlineStr">
+    <row r="148" ht="32" customHeight="1">
+      <c r="A148" s="37" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B128" s="20" t="inlineStr">
+      <c r="B148" s="37" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C128" s="21" t="inlineStr">
+      <c r="C148" s="38" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="D128" s="12" t="inlineStr">
+      <c r="D148" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E128" s="20" t="inlineStr">
+      <c r="E148" s="37" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일 · 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="F128" s="20" t="inlineStr">
+      <c r="F148" s="37" t="inlineStr">
         <is>
           <t>캐모마일 · 오일</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="48" customHeight="1">
-      <c r="A129" s="20" t="inlineStr">
+    <row r="149" ht="48" customHeight="1">
+      <c r="A149" s="37" t="inlineStr">
         <is>
           <t>올리브에스터오일</t>
         </is>
       </c>
-      <c r="B129" s="20" t="inlineStr">
+      <c r="B149" s="37" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C129" s="21" t="inlineStr">
+      <c r="C149" s="38" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D129" s="12" t="inlineStr">
+      <c r="D149" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E129" s="20" t="inlineStr">
+      <c r="E149" s="37" t="inlineStr">
         <is>
           <t>올리브오일유래, 초기사용감은 · 실리콘오일처럼 가볍지만 보습력지속</t>
         </is>
       </c>
-      <c r="F129" s="20" t="inlineStr">
+      <c r="F149" s="37" t="inlineStr">
         <is>
           <t>호호바</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="48" customHeight="1">
-      <c r="A130" s="20" t="inlineStr">
+    <row r="150" ht="48" customHeight="1">
+      <c r="A150" s="37" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B130" s="20" t="inlineStr">
+      <c r="B150" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C130" s="21" t="inlineStr">
+      <c r="C150" s="38" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D130" s="27" t="inlineStr">
+      <c r="D150" s="43" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E130" s="20" t="inlineStr">
+      <c r="E150" s="37" t="inlineStr">
         <is>
           <t>에코인증 · 물 · 오일분리 저지</t>
         </is>
       </c>
-      <c r="F130" s="20" t="inlineStr">
+      <c r="F150" s="37" t="inlineStr">
         <is>
           <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="20" t="inlineStr">
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="37" t="inlineStr">
         <is>
           <t>올리왁스LC</t>
         </is>
       </c>
-      <c r="B131" s="20" t="inlineStr">
+      <c r="B151" s="37" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C131" s="21" t="inlineStr">
+      <c r="C151" s="38" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D131" s="22" t="inlineStr">
+      <c r="D151" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E131" s="20" t="inlineStr">
+      <c r="E151" s="37" t="inlineStr">
         <is>
           <t>유화 보조제 · 백탁 현상 완화</t>
         </is>
       </c>
-      <c r="F131" s="20" t="inlineStr">
+      <c r="F151" s="37" t="inlineStr">
         <is>
           <t>세틸알콜</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="32" customHeight="1">
-      <c r="A132" s="20" t="inlineStr">
+    <row r="152" ht="32" customHeight="1">
+      <c r="A152" s="37" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B132" s="20" t="inlineStr">
+      <c r="B152" s="37" t="inlineStr">
         <is>
           <t>32g</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
+      <c r="C152" s="38" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="D132" s="28" t="inlineStr">
+      <c r="D152" s="44" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E132" s="20" t="inlineStr">
+      <c r="E152" s="37" t="inlineStr">
         <is>
           <t>5차 필터링 · UV살균처리 정제수</t>
         </is>
       </c>
-      <c r="F132" s="20" t="inlineStr">
+      <c r="F152" s="37" t="inlineStr">
         <is>
           <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="48" customHeight="1">
-      <c r="A133" s="20" t="inlineStr">
+    <row r="153" ht="48" customHeight="1">
+      <c r="A153" s="37" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B133" s="20" t="inlineStr">
+      <c r="B153" s="37" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C133" s="21" t="inlineStr">
+      <c r="C153" s="38" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D133" s="24" t="inlineStr">
+      <c r="D153" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E133" s="20" t="inlineStr">
+      <c r="E153" s="37" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은 · 수분감이 풍부한 겔</t>
         </is>
       </c>
-      <c r="F133" s="20" t="inlineStr">
+      <c r="F153" s="37" t="inlineStr">
         <is>
           <t>허브누리 베라겔 · 네롤리 · 플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="32" customHeight="1">
-      <c r="A134" s="20" t="inlineStr">
+    <row r="154" ht="32" customHeight="1">
+      <c r="A154" s="37" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
-      <c r="B134" s="20" t="inlineStr">
+      <c r="B154" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C134" s="21" t="inlineStr">
+      <c r="C154" s="38" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D134" s="24" t="inlineStr">
+      <c r="D154" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E134" s="20" t="inlineStr">
+      <c r="E154" s="37" t="inlineStr">
         <is>
           <t>고중저분자 · 트리플 히아루론산</t>
         </is>
       </c>
-      <c r="F134" s="20" t="inlineStr">
+      <c r="F154" s="37" t="inlineStr">
         <is>
           <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="48" customHeight="1">
-      <c r="A135" s="20" t="inlineStr">
+    <row r="155" ht="48" customHeight="1">
+      <c r="A155" s="37" t="inlineStr">
         <is>
           <t>수딩4 컴플렉스</t>
         </is>
       </c>
-      <c r="B135" s="20" t="inlineStr">
+      <c r="B155" s="37" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C135" s="21" t="inlineStr">
+      <c r="C155" s="38" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D135" s="24" t="inlineStr">
+      <c r="D155" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E135" s="20" t="inlineStr">
+      <c r="E155" s="37" t="inlineStr">
         <is>
           <t>알로에베라잎추출물, 참마뿌리추출물 · 흰목이버섯추출물, 미역추출물 복합추출물</t>
         </is>
       </c>
-      <c r="F135" s="20" t="inlineStr"/>
-    </row>
-    <row r="136" ht="64" customHeight="1">
-      <c r="A136" s="20" t="inlineStr">
+      <c r="F155" s="37" t="inlineStr"/>
+    </row>
+    <row r="156" ht="64" customHeight="1">
+      <c r="A156" s="37" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B136" s="20" t="inlineStr">
+      <c r="B156" s="37" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C136" s="21" t="inlineStr">
+      <c r="C156" s="38" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D136" s="29" t="inlineStr">
+      <c r="D156" s="45" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E136" s="20" t="inlineStr">
+      <c r="E156" s="37" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="F136" s="20" t="inlineStr">
+      <c r="F156" s="37" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (정제수의 양을 31g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="20" t="inlineStr">
+    <row r="157" ht="32" customHeight="1">
+      <c r="A157" s="37" t="inlineStr">
         <is>
           <t>징크옥사이드분산액</t>
         </is>
       </c>
-      <c r="B137" s="20" t="inlineStr">
+      <c r="B157" s="37" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C137" s="21" t="inlineStr">
+      <c r="C157" s="38" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D137" s="23" t="inlineStr">
+      <c r="D157" s="40" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E137" s="20" t="inlineStr">
+      <c r="E157" s="37" t="inlineStr">
         <is>
           <t>UV-A를 주로 난반사</t>
         </is>
       </c>
-      <c r="F137" s="20" t="inlineStr">
+      <c r="F157" s="37" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="32" customHeight="1">
-      <c r="A138" s="20" t="inlineStr">
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="37" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 / 분산액</t>
         </is>
       </c>
-      <c r="B138" s="20" t="inlineStr">
+      <c r="B158" s="37" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C138" s="21" t="inlineStr">
+      <c r="C158" s="38" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D138" s="23" t="inlineStr">
+      <c r="D158" s="40" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E138" s="20" t="inlineStr">
+      <c r="E158" s="37" t="inlineStr">
         <is>
           <t>자외선UV-B를 주로 난반사</t>
         </is>
       </c>
-      <c r="F138" s="20" t="inlineStr"/>
-    </row>
-    <row r="139" ht="48" customHeight="1">
-      <c r="A139" s="20" t="inlineStr">
+      <c r="F158" s="37" t="inlineStr"/>
+    </row>
+    <row r="159" ht="48" customHeight="1">
+      <c r="A159" s="37" t="inlineStr">
         <is>
           <t>베베보 블렌딩오일</t>
         </is>
       </c>
-      <c r="B139" s="20" t="inlineStr">
+      <c r="B159" s="37" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C139" s="21" t="inlineStr">
+      <c r="C159" s="38" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D139" s="12" t="inlineStr">
+      <c r="D159" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E139" s="20" t="inlineStr">
+      <c r="E159" s="37" t="inlineStr">
         <is>
           <t>라벤더. 만다린 로먼캐모마일 에센셜오일 · 민감피부를 위한 블렌딩</t>
         </is>
       </c>
-      <c r="F139" s="20" t="inlineStr">
+      <c r="F159" s="37" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="15" t="inlineStr">
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 32 · 유상 17 · 유화 4 · 경화 2 · 활성 29 · 색소 15 · 방부 1</t>
         </is>
       </c>
-      <c r="B140" s="16" t="n"/>
-      <c r="C140" s="16" t="n"/>
-      <c r="D140" s="16" t="n"/>
-      <c r="E140" s="16" t="n"/>
-      <c r="F140" s="16" t="n"/>
-    </row>
-    <row r="141" ht="14" customHeight="1">
-      <c r="A141" s="17" t="inlineStr">
+      <c r="B160" s="33" t="n"/>
+      <c r="C160" s="33" t="n"/>
+      <c r="D160" s="33" t="n"/>
+      <c r="E160" s="33" t="n"/>
+      <c r="F160" s="33" t="n"/>
+    </row>
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B141" s="18" t="n"/>
-      <c r="C141" s="18" t="n"/>
-      <c r="D141" s="18" t="n"/>
-      <c r="E141" s="18" t="n"/>
-      <c r="F141" s="18" t="n"/>
-    </row>
-    <row r="142" ht="352" customHeight="1">
-      <c r="A142" s="25" t="inlineStr">
+      <c r="B161" s="35" t="n"/>
+      <c r="C161" s="35" t="n"/>
+      <c r="D161" s="35" t="n"/>
+      <c r="E161" s="35" t="n"/>
+      <c r="F161" s="35" t="n"/>
+    </row>
+    <row r="162" ht="352" customHeight="1">
+      <c r="A162" s="42" t="inlineStr">
         <is>
           <t>수딩썬로션
 (100g)
@@ -8579,26 +8903,26 @@
 우리 가족 안심 썬로션 만들기해보세요 .</t>
         </is>
       </c>
-      <c r="B142" s="26" t="n"/>
-      <c r="C142" s="26" t="n"/>
-      <c r="D142" s="26" t="n"/>
-      <c r="E142" s="26" t="n"/>
-      <c r="F142" s="26" t="n"/>
-    </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="17" t="inlineStr">
+      <c r="B162" s="23" t="n"/>
+      <c r="C162" s="23" t="n"/>
+      <c r="D162" s="23" t="n"/>
+      <c r="E162" s="23" t="n"/>
+      <c r="F162" s="23" t="n"/>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B143" s="18" t="n"/>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="18" t="n"/>
-      <c r="F143" s="18" t="n"/>
-    </row>
-    <row r="144" ht="112" customHeight="1">
-      <c r="A144" s="25" t="inlineStr">
+      <c r="B163" s="35" t="n"/>
+      <c r="C163" s="35" t="n"/>
+      <c r="D163" s="35" t="n"/>
+      <c r="E163" s="35" t="n"/>
+      <c r="F163" s="35" t="n"/>
+    </row>
+    <row r="164" ht="112" customHeight="1">
+      <c r="A164" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 2개의 비커에 오일/유화제, 워터를 계량합니다.
@@ -8609,175 +8933,175 @@
 6. 골고루 섞어주면 완성.</t>
         </is>
       </c>
-      <c r="B144" s="26" t="n"/>
-      <c r="C144" s="26" t="n"/>
-      <c r="D144" s="26" t="n"/>
-      <c r="E144" s="26" t="n"/>
-      <c r="F144" s="26" t="n"/>
-    </row>
-    <row r="145" ht="6" customHeight="1"/>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
+      <c r="B164" s="23" t="n"/>
+      <c r="C164" s="23" t="n"/>
+      <c r="D164" s="23" t="n"/>
+      <c r="E164" s="23" t="n"/>
+      <c r="F164" s="23" t="n"/>
+    </row>
+    <row r="165" ht="6" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="24" t="inlineStr">
         <is>
           <t>레드 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
-      <c r="F146" s="8" t="n"/>
-    </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
+      <c r="B166" s="25" t="n"/>
+      <c r="C166" s="25" t="n"/>
+      <c r="D166" s="25" t="n"/>
+      <c r="E166" s="25" t="n"/>
+      <c r="F166" s="25" t="n"/>
+    </row>
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B147" s="9" t="inlineStr">
+      <c r="B167" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C147" s="9" t="inlineStr">
+      <c r="C167" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D147" s="9" t="inlineStr">
+      <c r="D167" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E147" s="9" t="inlineStr">
+      <c r="E167" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F147" s="9" t="inlineStr">
+      <c r="F167" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="48" customHeight="1">
-      <c r="A148" s="10" t="inlineStr">
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
-      <c r="B148" s="10" t="inlineStr">
+      <c r="B168" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C148" s="11" t="inlineStr">
+      <c r="C168" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D148" s="12" t="inlineStr">
+      <c r="D168" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E148" s="10" t="inlineStr">
+      <c r="E168" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F148" s="10" t="inlineStr">
+      <c r="F168" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="64" customHeight="1">
-      <c r="A149" s="10" t="inlineStr">
+    <row r="169" ht="64" customHeight="1">
+      <c r="A169" s="27" t="inlineStr">
         <is>
           <t>레드 립 컬러</t>
         </is>
       </c>
-      <c r="B149" s="10" t="inlineStr">
+      <c r="B169" s="27" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C149" s="11" t="inlineStr">
+      <c r="C169" s="28" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D149" s="14" t="inlineStr">
+      <c r="D169" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E149" s="10" t="inlineStr">
+      <c r="E169" s="27" t="inlineStr">
         <is>
           <t>레드21번 0.5g + 레드7번 0.2g+ 옐로우6번 0.1g+ 레드6번 0.2g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F149" s="10" t="inlineStr"/>
-    </row>
-    <row r="150" ht="32" customHeight="1">
-      <c r="A150" s="10" t="inlineStr">
+      <c r="F169" s="27" t="inlineStr"/>
+    </row>
+    <row r="170" ht="32" customHeight="1">
+      <c r="A170" s="27" t="inlineStr">
         <is>
           <t>브라이트닝블렌딩오일</t>
         </is>
       </c>
-      <c r="B150" s="10" t="inlineStr">
+      <c r="B170" s="27" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C150" s="11" t="inlineStr">
+      <c r="C170" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D150" s="12" t="inlineStr">
+      <c r="D170" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E150" s="10" t="inlineStr">
+      <c r="E170" s="27" t="inlineStr">
         <is>
           <t>네롤리, 프랑킨센스, 버가못EO 블렌딩</t>
         </is>
       </c>
-      <c r="F150" s="10" t="inlineStr">
+      <c r="F170" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="15" t="inlineStr">
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
-      <c r="B151" s="16" t="n"/>
-      <c r="C151" s="16" t="n"/>
-      <c r="D151" s="16" t="n"/>
-      <c r="E151" s="16" t="n"/>
-      <c r="F151" s="16" t="n"/>
-    </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="17" t="inlineStr">
+      <c r="B171" s="33" t="n"/>
+      <c r="C171" s="33" t="n"/>
+      <c r="D171" s="33" t="n"/>
+      <c r="E171" s="33" t="n"/>
+      <c r="F171" s="33" t="n"/>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B152" s="18" t="n"/>
-      <c r="C152" s="18" t="n"/>
-      <c r="D152" s="18" t="n"/>
-      <c r="E152" s="18" t="n"/>
-      <c r="F152" s="18" t="n"/>
-    </row>
-    <row r="153" ht="224" customHeight="1">
-      <c r="A153" s="19" t="inlineStr">
+      <c r="B172" s="35" t="n"/>
+      <c r="C172" s="35" t="n"/>
+      <c r="D172" s="35" t="n"/>
+      <c r="E172" s="35" t="n"/>
+      <c r="F172" s="35" t="n"/>
+    </row>
+    <row r="173" ht="224" customHeight="1">
+      <c r="A173" s="36" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -8796,20 +9120,20 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="14" customHeight="1">
-      <c r="A154" s="17" t="inlineStr">
+    <row r="174" ht="14" customHeight="1">
+      <c r="A174" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B154" s="18" t="n"/>
-      <c r="C154" s="18" t="n"/>
-      <c r="D154" s="18" t="n"/>
-      <c r="E154" s="18" t="n"/>
-      <c r="F154" s="18" t="n"/>
-    </row>
-    <row r="155" ht="304" customHeight="1">
-      <c r="A155" s="19" t="inlineStr">
+      <c r="B174" s="35" t="n"/>
+      <c r="C174" s="35" t="n"/>
+      <c r="D174" s="35" t="n"/>
+      <c r="E174" s="35" t="n"/>
+      <c r="F174" s="35" t="n"/>
+    </row>
+    <row r="175" ht="304" customHeight="1">
+      <c r="A175" s="36" t="inlineStr">
         <is>
           <t>2.녹인 것을 캔용기에 부어서
 4. 굳히세요. 식히면 단단해집니다.
@@ -8832,170 +9156,170 @@
         </is>
       </c>
     </row>
-    <row r="156" ht="384.5" customHeight="1"/>
-    <row r="157" ht="6" customHeight="1"/>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
+    <row r="176" ht="384.5" customHeight="1"/>
+    <row r="177" ht="6" customHeight="1"/>
+    <row r="178" ht="22" customHeight="1">
+      <c r="A178" s="24" t="inlineStr">
         <is>
           <t>벚꽃 썸띵 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B158" s="8" t="n"/>
-      <c r="C158" s="8" t="n"/>
-      <c r="D158" s="8" t="n"/>
-      <c r="E158" s="8" t="n"/>
-      <c r="F158" s="8" t="n"/>
-    </row>
-    <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="9" t="inlineStr">
+      <c r="B178" s="25" t="n"/>
+      <c r="C178" s="25" t="n"/>
+      <c r="D178" s="25" t="n"/>
+      <c r="E178" s="25" t="n"/>
+      <c r="F178" s="25" t="n"/>
+    </row>
+    <row r="179" ht="15" customHeight="1">
+      <c r="A179" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B159" s="9" t="inlineStr">
+      <c r="B179" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C159" s="9" t="inlineStr">
+      <c r="C179" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D159" s="9" t="inlineStr">
+      <c r="D179" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E159" s="9" t="inlineStr">
+      <c r="E179" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F159" s="9" t="inlineStr">
+      <c r="F179" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="48" customHeight="1">
-      <c r="A160" s="20" t="inlineStr">
+    <row r="180" ht="48" customHeight="1">
+      <c r="A180" s="37" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B160" s="20" t="inlineStr">
+      <c r="B180" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C160" s="21" t="inlineStr">
+      <c r="C180" s="38" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D160" s="12" t="inlineStr">
+      <c r="D180" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E160" s="20" t="inlineStr">
+      <c r="E180" s="37" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F160" s="20" t="inlineStr">
+      <c r="F180" s="37" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="64" customHeight="1">
-      <c r="A161" s="20" t="inlineStr">
+    <row r="181" ht="64" customHeight="1">
+      <c r="A181" s="37" t="inlineStr">
         <is>
           <t>벚꽃 립 컬러</t>
         </is>
       </c>
-      <c r="B161" s="20" t="inlineStr">
+      <c r="B181" s="37" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C161" s="21" t="inlineStr">
+      <c r="C181" s="38" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D161" s="14" t="inlineStr">
+      <c r="D181" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E161" s="20" t="inlineStr">
+      <c r="E181" s="37" t="inlineStr">
         <is>
           <t>레드27번 0.3g + 레드40번 0.2g+ 아이론옐로우 0.1g+ 화이트 0.4g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F161" s="20" t="inlineStr"/>
-    </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="20" t="inlineStr">
+      <c r="F181" s="37" t="inlineStr"/>
+    </row>
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="37" t="inlineStr">
         <is>
           <t>레몬쥬스블렌딩오일</t>
         </is>
       </c>
-      <c r="B162" s="20" t="inlineStr">
+      <c r="B182" s="37" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C162" s="21" t="inlineStr">
+      <c r="C182" s="38" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D162" s="12" t="inlineStr">
+      <c r="D182" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E162" s="20" t="inlineStr">
+      <c r="E182" s="37" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F162" s="20" t="inlineStr">
+      <c r="F182" s="37" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="15" t="inlineStr">
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
-      <c r="B163" s="16" t="n"/>
-      <c r="C163" s="16" t="n"/>
-      <c r="D163" s="16" t="n"/>
-      <c r="E163" s="16" t="n"/>
-      <c r="F163" s="16" t="n"/>
-    </row>
-    <row r="164" ht="14" customHeight="1">
-      <c r="A164" s="17" t="inlineStr">
+      <c r="B183" s="33" t="n"/>
+      <c r="C183" s="33" t="n"/>
+      <c r="D183" s="33" t="n"/>
+      <c r="E183" s="33" t="n"/>
+      <c r="F183" s="33" t="n"/>
+    </row>
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B164" s="18" t="n"/>
-      <c r="C164" s="18" t="n"/>
-      <c r="D164" s="18" t="n"/>
-      <c r="E164" s="18" t="n"/>
-      <c r="F164" s="18" t="n"/>
-    </row>
-    <row r="165" ht="192" customHeight="1">
-      <c r="A165" s="25" t="inlineStr">
+      <c r="B184" s="35" t="n"/>
+      <c r="C184" s="35" t="n"/>
+      <c r="D184" s="35" t="n"/>
+      <c r="E184" s="35" t="n"/>
+      <c r="F184" s="35" t="n"/>
+    </row>
+    <row r="185" ht="192" customHeight="1">
+      <c r="A185" s="42" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -9011,26 +9335,26 @@
 완성도 높은 립스틱 만들기해보세요.</t>
         </is>
       </c>
-      <c r="B165" s="26" t="n"/>
-      <c r="C165" s="26" t="n"/>
-      <c r="D165" s="26" t="n"/>
-      <c r="E165" s="26" t="n"/>
-      <c r="F165" s="26" t="n"/>
-    </row>
-    <row r="166" ht="14" customHeight="1">
-      <c r="A166" s="17" t="inlineStr">
+      <c r="B185" s="23" t="n"/>
+      <c r="C185" s="23" t="n"/>
+      <c r="D185" s="23" t="n"/>
+      <c r="E185" s="23" t="n"/>
+      <c r="F185" s="23" t="n"/>
+    </row>
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B166" s="18" t="n"/>
-      <c r="C166" s="18" t="n"/>
-      <c r="D166" s="18" t="n"/>
-      <c r="E166" s="18" t="n"/>
-      <c r="F166" s="18" t="n"/>
-    </row>
-    <row r="167" ht="384" customHeight="1">
-      <c r="A167" s="25" t="inlineStr">
+      <c r="B186" s="35" t="n"/>
+      <c r="C186" s="35" t="n"/>
+      <c r="D186" s="35" t="n"/>
+      <c r="E186" s="35" t="n"/>
+      <c r="F186" s="35" t="n"/>
+    </row>
+    <row r="187" ht="384" customHeight="1">
+      <c r="A187" s="42" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -9057,183 +9381,183 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B167" s="26" t="n"/>
-      <c r="C167" s="26" t="n"/>
-      <c r="D167" s="26" t="n"/>
-      <c r="E167" s="26" t="n"/>
-      <c r="F167" s="26" t="n"/>
-    </row>
-    <row r="168" ht="336.5000000000001" customHeight="1">
-      <c r="A168" s="26" t="n"/>
-      <c r="B168" s="26" t="n"/>
-      <c r="C168" s="26" t="n"/>
-      <c r="D168" s="26" t="n"/>
-      <c r="E168" s="26" t="n"/>
-      <c r="F168" s="26" t="n"/>
-    </row>
-    <row r="169" ht="6" customHeight="1"/>
-    <row r="170" ht="22" customHeight="1">
-      <c r="A170" s="7" t="inlineStr">
+      <c r="B187" s="23" t="n"/>
+      <c r="C187" s="23" t="n"/>
+      <c r="D187" s="23" t="n"/>
+      <c r="E187" s="23" t="n"/>
+      <c r="F187" s="23" t="n"/>
+    </row>
+    <row r="188" ht="336.5000000000001" customHeight="1">
+      <c r="A188" s="23" t="n"/>
+      <c r="B188" s="23" t="n"/>
+      <c r="C188" s="23" t="n"/>
+      <c r="D188" s="23" t="n"/>
+      <c r="E188" s="23" t="n"/>
+      <c r="F188" s="23" t="n"/>
+    </row>
+    <row r="189" ht="6" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="24" t="inlineStr">
         <is>
           <t>피치코랄 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B170" s="8" t="n"/>
-      <c r="C170" s="8" t="n"/>
-      <c r="D170" s="8" t="n"/>
-      <c r="E170" s="8" t="n"/>
-      <c r="F170" s="8" t="n"/>
-    </row>
-    <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="9" t="inlineStr">
+      <c r="B190" s="25" t="n"/>
+      <c r="C190" s="25" t="n"/>
+      <c r="D190" s="25" t="n"/>
+      <c r="E190" s="25" t="n"/>
+      <c r="F190" s="25" t="n"/>
+    </row>
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B171" s="9" t="inlineStr">
+      <c r="B191" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C171" s="9" t="inlineStr">
+      <c r="C191" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D171" s="9" t="inlineStr">
+      <c r="D191" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr">
+      <c r="E191" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F171" s="9" t="inlineStr">
+      <c r="F191" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="48" customHeight="1">
-      <c r="A172" s="10" t="inlineStr">
+    <row r="192" ht="48" customHeight="1">
+      <c r="A192" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B172" s="10" t="inlineStr">
+      <c r="B192" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C172" s="11" t="inlineStr">
+      <c r="C192" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D172" s="12" t="inlineStr">
+      <c r="D192" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E172" s="10" t="inlineStr">
+      <c r="E192" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 · 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F172" s="10" t="inlineStr">
+      <c r="F192" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="64" customHeight="1">
-      <c r="A173" s="10" t="inlineStr">
+    <row r="193" ht="64" customHeight="1">
+      <c r="A193" s="27" t="inlineStr">
         <is>
           <t>피치코랄 립 컬러</t>
         </is>
       </c>
-      <c r="B173" s="10" t="inlineStr">
+      <c r="B193" s="27" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C173" s="11" t="inlineStr">
+      <c r="C193" s="28" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D173" s="14" t="inlineStr">
+      <c r="D193" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E173" s="10" t="inlineStr">
+      <c r="E193" s="27" t="inlineStr">
         <is>
           <t>레드6번 0.3g + 아이론옐로우 0.1g · + 레드27번 0.2g + 화이트 0.2g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F173" s="10" t="inlineStr"/>
-    </row>
-    <row r="174" ht="32" customHeight="1">
-      <c r="A174" s="10" t="inlineStr">
+      <c r="F193" s="27" t="inlineStr"/>
+    </row>
+    <row r="194" ht="32" customHeight="1">
+      <c r="A194" s="27" t="inlineStr">
         <is>
           <t>라임캔디 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B174" s="10" t="inlineStr">
+      <c r="B194" s="27" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C174" s="11" t="inlineStr">
+      <c r="C194" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D174" s="12" t="inlineStr">
+      <c r="D194" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E174" s="10" t="inlineStr">
+      <c r="E194" s="27" t="inlineStr">
         <is>
           <t>라임, 스윗오렌지, 레몬, 로즈마리 · 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F174" s="10" t="inlineStr">
+      <c r="F194" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="14" customHeight="1">
-      <c r="A175" s="15" t="inlineStr">
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
-      <c r="B175" s="16" t="n"/>
-      <c r="C175" s="16" t="n"/>
-      <c r="D175" s="16" t="n"/>
-      <c r="E175" s="16" t="n"/>
-      <c r="F175" s="16" t="n"/>
-    </row>
-    <row r="176" ht="14" customHeight="1">
-      <c r="A176" s="17" t="inlineStr">
+      <c r="B195" s="33" t="n"/>
+      <c r="C195" s="33" t="n"/>
+      <c r="D195" s="33" t="n"/>
+      <c r="E195" s="33" t="n"/>
+      <c r="F195" s="33" t="n"/>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B176" s="18" t="n"/>
-      <c r="C176" s="18" t="n"/>
-      <c r="D176" s="18" t="n"/>
-      <c r="E176" s="18" t="n"/>
-      <c r="F176" s="18" t="n"/>
-    </row>
-    <row r="177" ht="192" customHeight="1">
-      <c r="A177" s="19" t="inlineStr">
+      <c r="B196" s="35" t="n"/>
+      <c r="C196" s="35" t="n"/>
+      <c r="D196" s="35" t="n"/>
+      <c r="E196" s="35" t="n"/>
+      <c r="F196" s="35" t="n"/>
+    </row>
+    <row r="197" ht="192" customHeight="1">
+      <c r="A197" s="36" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -9250,20 +9574,20 @@
         </is>
       </c>
     </row>
-    <row r="178" ht="14" customHeight="1">
-      <c r="A178" s="17" t="inlineStr">
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B178" s="18" t="n"/>
-      <c r="C178" s="18" t="n"/>
-      <c r="D178" s="18" t="n"/>
-      <c r="E178" s="18" t="n"/>
-      <c r="F178" s="18" t="n"/>
-    </row>
-    <row r="179" ht="384" customHeight="1">
-      <c r="A179" s="19" t="inlineStr">
+      <c r="B198" s="35" t="n"/>
+      <c r="C198" s="35" t="n"/>
+      <c r="D198" s="35" t="n"/>
+      <c r="E198" s="35" t="n"/>
+      <c r="F198" s="35" t="n"/>
+    </row>
+    <row r="199" ht="384" customHeight="1">
+      <c r="A199" s="36" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -9291,234 +9615,234 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="336.5000000000001" customHeight="1"/>
-    <row r="181" ht="6" customHeight="1"/>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
+    <row r="200" ht="336.5000000000001" customHeight="1"/>
+    <row r="201" ht="6" customHeight="1"/>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="24" t="inlineStr">
         <is>
           <t>워터리 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B182" s="8" t="n"/>
-      <c r="C182" s="8" t="n"/>
-      <c r="D182" s="8" t="n"/>
-      <c r="E182" s="8" t="n"/>
-      <c r="F182" s="8" t="n"/>
-    </row>
-    <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="9" t="inlineStr">
+      <c r="B202" s="25" t="n"/>
+      <c r="C202" s="25" t="n"/>
+      <c r="D202" s="25" t="n"/>
+      <c r="E202" s="25" t="n"/>
+      <c r="F202" s="25" t="n"/>
+    </row>
+    <row r="203" ht="15" customHeight="1">
+      <c r="A203" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B183" s="9" t="inlineStr">
+      <c r="B203" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
+      <c r="C203" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D183" s="9" t="inlineStr">
+      <c r="D203" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E183" s="9" t="inlineStr">
+      <c r="E203" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F183" s="9" t="inlineStr">
+      <c r="F203" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="32" customHeight="1">
-      <c r="A184" s="20" t="inlineStr">
+    <row r="204" ht="32" customHeight="1">
+      <c r="A204" s="37" t="inlineStr">
         <is>
           <t>립밤베이스</t>
         </is>
       </c>
-      <c r="B184" s="20" t="inlineStr">
+      <c r="B204" s="37" t="inlineStr">
         <is>
           <t>4.6g</t>
         </is>
       </c>
-      <c r="C184" s="21" t="inlineStr">
+      <c r="C204" s="38" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="D184" s="12" t="inlineStr">
+      <c r="D204" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E184" s="20" t="inlineStr">
+      <c r="E204" s="37" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서</t>
         </is>
       </c>
-      <c r="F184" s="20" t="inlineStr">
+      <c r="F204" s="37" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="32" customHeight="1">
-      <c r="A185" s="20" t="inlineStr">
+    <row r="205" ht="32" customHeight="1">
+      <c r="A205" s="37" t="inlineStr">
         <is>
           <t>립 컬러</t>
         </is>
       </c>
-      <c r="B185" s="20" t="inlineStr">
+      <c r="B205" s="37" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C185" s="21" t="inlineStr">
+      <c r="C205" s="38" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D185" s="14" t="inlineStr">
+      <c r="D205" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E185" s="20" t="inlineStr">
+      <c r="E205" s="37" t="inlineStr">
         <is>
           <t>색상사진은 아래의 · 립스틱 발색 사진과 처방 참고</t>
         </is>
       </c>
-      <c r="F185" s="20" t="inlineStr"/>
-    </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="20" t="inlineStr">
+      <c r="F205" s="37" t="inlineStr"/>
+    </row>
+    <row r="206" ht="32" customHeight="1">
+      <c r="A206" s="37" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B186" s="20" t="inlineStr">
+      <c r="B206" s="37" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C186" s="21" t="inlineStr">
+      <c r="C206" s="38" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D186" s="12" t="inlineStr">
+      <c r="D206" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E186" s="20" t="inlineStr">
+      <c r="E206" s="37" t="inlineStr">
         <is>
           <t>피지성분과 비슷 · 가벼운 사용감</t>
         </is>
       </c>
-      <c r="F186" s="20" t="inlineStr">
+      <c r="F206" s="37" t="inlineStr">
         <is>
           <t>스위트아몬드오일 · 동백오일 등</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="48" customHeight="1">
-      <c r="A187" s="20" t="inlineStr">
+    <row r="207" ht="48" customHeight="1">
+      <c r="A207" s="37" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B187" s="20" t="inlineStr">
+      <c r="B207" s="37" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C187" s="21" t="inlineStr">
+      <c r="C207" s="38" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D187" s="12" t="inlineStr">
+      <c r="D207" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E187" s="20" t="inlineStr">
+      <c r="E207" s="37" t="inlineStr">
         <is>
           <t>오래가는 보습오일</t>
         </is>
       </c>
-      <c r="F187" s="20" t="inlineStr">
+      <c r="F207" s="37" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="48" customHeight="1">
-      <c r="A188" s="20" t="inlineStr">
+    <row r="208" ht="48" customHeight="1">
+      <c r="A208" s="37" t="inlineStr">
         <is>
           <t>로즈파워 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B188" s="20" t="inlineStr">
+      <c r="B208" s="37" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C188" s="21" t="inlineStr">
+      <c r="C208" s="38" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D188" s="12" t="inlineStr">
+      <c r="D208" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E188" s="20" t="inlineStr">
+      <c r="E208" s="37" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄, 로즈우드, 프랑킨센스 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F188" s="20" t="inlineStr">
+      <c r="F208" s="37" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="15" t="inlineStr">
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 94 · 기타 6</t>
         </is>
       </c>
-      <c r="B189" s="16" t="n"/>
-      <c r="C189" s="16" t="n"/>
-      <c r="D189" s="16" t="n"/>
-      <c r="E189" s="16" t="n"/>
-      <c r="F189" s="16" t="n"/>
-    </row>
-    <row r="190" ht="14" customHeight="1">
-      <c r="A190" s="17" t="inlineStr">
+      <c r="B209" s="33" t="n"/>
+      <c r="C209" s="33" t="n"/>
+      <c r="D209" s="33" t="n"/>
+      <c r="E209" s="33" t="n"/>
+      <c r="F209" s="33" t="n"/>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B190" s="18" t="n"/>
-      <c r="C190" s="18" t="n"/>
-      <c r="D190" s="18" t="n"/>
-      <c r="E190" s="18" t="n"/>
-      <c r="F190" s="18" t="n"/>
-    </row>
-    <row r="191" ht="96" customHeight="1">
-      <c r="A191" s="25" t="inlineStr">
+      <c r="B210" s="35" t="n"/>
+      <c r="C210" s="35" t="n"/>
+      <c r="D210" s="35" t="n"/>
+      <c r="E210" s="35" t="n"/>
+      <c r="F210" s="35" t="n"/>
+    </row>
+    <row r="211" ht="96" customHeight="1">
+      <c r="A211" s="42" t="inlineStr">
         <is>
           <t>무제 문서
 워터리 립글로스는
@@ -9528,26 +9852,26 @@
 다양한 색상처방은 아래에서 참고하세요.</t>
         </is>
       </c>
-      <c r="B191" s="26" t="n"/>
-      <c r="C191" s="26" t="n"/>
-      <c r="D191" s="26" t="n"/>
-      <c r="E191" s="26" t="n"/>
-      <c r="F191" s="26" t="n"/>
-    </row>
-    <row r="192" ht="14" customHeight="1">
-      <c r="A192" s="17" t="inlineStr">
+      <c r="B211" s="23" t="n"/>
+      <c r="C211" s="23" t="n"/>
+      <c r="D211" s="23" t="n"/>
+      <c r="E211" s="23" t="n"/>
+      <c r="F211" s="23" t="n"/>
+    </row>
+    <row r="212" ht="14" customHeight="1">
+      <c r="A212" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B192" s="18" t="n"/>
-      <c r="C192" s="18" t="n"/>
-      <c r="D192" s="18" t="n"/>
-      <c r="E192" s="18" t="n"/>
-      <c r="F192" s="18" t="n"/>
-    </row>
-    <row r="193" ht="192" customHeight="1">
-      <c r="A193" s="25" t="inlineStr">
+      <c r="B212" s="35" t="n"/>
+      <c r="C212" s="35" t="n"/>
+      <c r="D212" s="35" t="n"/>
+      <c r="E212" s="35" t="n"/>
+      <c r="F212" s="35" t="n"/>
+    </row>
+    <row r="213" ht="192" customHeight="1">
+      <c r="A213" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 [립밤베이스 만들기]
@@ -9563,143 +9887,143 @@
 9. 튜브나 립솔용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B193" s="26" t="n"/>
-      <c r="C193" s="26" t="n"/>
-      <c r="D193" s="26" t="n"/>
-      <c r="E193" s="26" t="n"/>
-      <c r="F193" s="26" t="n"/>
-    </row>
-    <row r="194" ht="6" customHeight="1"/>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="7" t="inlineStr">
+      <c r="B213" s="23" t="n"/>
+      <c r="C213" s="23" t="n"/>
+      <c r="D213" s="23" t="n"/>
+      <c r="E213" s="23" t="n"/>
+      <c r="F213" s="23" t="n"/>
+    </row>
+    <row r="214" ht="6" customHeight="1"/>
+    <row r="215" ht="22" customHeight="1">
+      <c r="A215" s="24" t="inlineStr">
         <is>
           <t>커피헤나염색    ↗ 원본</t>
         </is>
       </c>
-      <c r="B195" s="8" t="n"/>
-      <c r="C195" s="8" t="n"/>
-      <c r="D195" s="8" t="n"/>
-      <c r="E195" s="8" t="n"/>
-      <c r="F195" s="8" t="n"/>
-    </row>
-    <row r="196" ht="15" customHeight="1">
-      <c r="A196" s="9" t="inlineStr">
+      <c r="B215" s="25" t="n"/>
+      <c r="C215" s="25" t="n"/>
+      <c r="D215" s="25" t="n"/>
+      <c r="E215" s="25" t="n"/>
+      <c r="F215" s="25" t="n"/>
+    </row>
+    <row r="216" ht="15" customHeight="1">
+      <c r="A216" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="B216" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
+      <c r="C216" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="D216" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E216" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
+      <c r="F216" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="10" t="inlineStr">
+    <row r="217" ht="16" customHeight="1">
+      <c r="A217" s="27" t="inlineStr">
         <is>
           <t>헤나분말</t>
         </is>
       </c>
-      <c r="B197" s="10" t="inlineStr">
+      <c r="B217" s="27" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C197" s="11" t="inlineStr">
+      <c r="C217" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D197" s="14" t="inlineStr">
+      <c r="D217" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E197" s="10" t="inlineStr">
+      <c r="E217" s="27" t="inlineStr">
         <is>
           <t>100% 헤나 분말</t>
         </is>
       </c>
-      <c r="F197" s="10" t="inlineStr"/>
-    </row>
-    <row r="198" ht="64" customHeight="1">
-      <c r="A198" s="10" t="inlineStr">
+      <c r="F217" s="27" t="inlineStr"/>
+    </row>
+    <row r="218" ht="64" customHeight="1">
+      <c r="A218" s="27" t="inlineStr">
         <is>
           <t>물</t>
         </is>
       </c>
-      <c r="B198" s="10" t="inlineStr">
+      <c r="B218" s="27" t="inlineStr">
         <is>
           <t>130g 내외</t>
         </is>
       </c>
-      <c r="C198" s="11" t="inlineStr">
+      <c r="C218" s="28" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="D198" s="28" t="inlineStr">
+      <c r="D218" s="44" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E198" s="10" t="inlineStr">
+      <c r="E218" s="27" t="inlineStr">
         <is>
           <t>맑은 물(정수기, 수돗물 등등)</t>
         </is>
       </c>
-      <c r="F198" s="10" t="inlineStr">
+      <c r="F218" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="14" customHeight="1">
-      <c r="A199" s="15" t="inlineStr">
+    <row r="219" ht="14" customHeight="1">
+      <c r="A219" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 76 · 기타 24</t>
         </is>
       </c>
-      <c r="B199" s="16" t="n"/>
-      <c r="C199" s="16" t="n"/>
-      <c r="D199" s="16" t="n"/>
-      <c r="E199" s="16" t="n"/>
-      <c r="F199" s="16" t="n"/>
-    </row>
-    <row r="200" ht="14" customHeight="1">
-      <c r="A200" s="17" t="inlineStr">
+      <c r="B219" s="33" t="n"/>
+      <c r="C219" s="33" t="n"/>
+      <c r="D219" s="33" t="n"/>
+      <c r="E219" s="33" t="n"/>
+      <c r="F219" s="33" t="n"/>
+    </row>
+    <row r="220" ht="14" customHeight="1">
+      <c r="A220" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B200" s="18" t="n"/>
-      <c r="C200" s="18" t="n"/>
-      <c r="D200" s="18" t="n"/>
-      <c r="E200" s="18" t="n"/>
-      <c r="F200" s="18" t="n"/>
-    </row>
-    <row r="201" ht="352" customHeight="1">
-      <c r="A201" s="19" t="inlineStr">
+      <c r="B220" s="35" t="n"/>
+      <c r="C220" s="35" t="n"/>
+      <c r="D220" s="35" t="n"/>
+      <c r="E220" s="35" t="n"/>
+      <c r="F220" s="35" t="n"/>
+    </row>
+    <row r="221" ht="352" customHeight="1">
+      <c r="A221" s="36" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -9725,20 +10049,20 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="14" customHeight="1">
-      <c r="A202" s="17" t="inlineStr">
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B202" s="18" t="n"/>
-      <c r="C202" s="18" t="n"/>
-      <c r="D202" s="18" t="n"/>
-      <c r="E202" s="18" t="n"/>
-      <c r="F202" s="18" t="n"/>
-    </row>
-    <row r="203" ht="144" customHeight="1">
-      <c r="A203" s="19" t="inlineStr">
+      <c r="B222" s="35" t="n"/>
+      <c r="C222" s="35" t="n"/>
+      <c r="D222" s="35" t="n"/>
+      <c r="E222" s="35" t="n"/>
+      <c r="F222" s="35" t="n"/>
+    </row>
+    <row r="223" ht="144" customHeight="1">
+      <c r="A223" s="36" t="inlineStr">
         <is>
           <t>1. 염색 전 샴푸한 후 물기를 닦아주세요. 두피 피지와 오염물이 없으면 염색이 더 잘 됩니다.
 2. 인스턴트 커피 40~60g
@@ -9751,237 +10075,237 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="6" customHeight="1"/>
-    <row r="205" ht="22" customHeight="1">
-      <c r="A205" s="7" t="inlineStr">
+    <row r="224" ht="6" customHeight="1"/>
+    <row r="225" ht="22" customHeight="1">
+      <c r="A225" s="24" t="inlineStr">
         <is>
           <t>자초딸기립글로스(솔타입)    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B205" s="8" t="n"/>
-      <c r="C205" s="8" t="n"/>
-      <c r="D205" s="8" t="n"/>
-      <c r="E205" s="8" t="n"/>
-      <c r="F205" s="8" t="n"/>
-    </row>
-    <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="9" t="inlineStr">
+      <c r="B225" s="25" t="n"/>
+      <c r="C225" s="25" t="n"/>
+      <c r="D225" s="25" t="n"/>
+      <c r="E225" s="25" t="n"/>
+      <c r="F225" s="25" t="n"/>
+    </row>
+    <row r="226" ht="15" customHeight="1">
+      <c r="A226" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B206" s="9" t="inlineStr">
+      <c r="B226" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C206" s="9" t="inlineStr">
+      <c r="C226" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D206" s="9" t="inlineStr">
+      <c r="D226" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E206" s="9" t="inlineStr">
+      <c r="E226" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F206" s="9" t="inlineStr">
+      <c r="F226" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="112" customHeight="1">
-      <c r="A207" s="20" t="inlineStr">
+    <row r="227" ht="112" customHeight="1">
+      <c r="A227" s="37" t="inlineStr">
         <is>
           <t>자초인퓨즈 / 호호바오일</t>
         </is>
       </c>
-      <c r="B207" s="20" t="inlineStr">
+      <c r="B227" s="37" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C207" s="21" t="inlineStr">
+      <c r="C227" s="38" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="D207" s="24" t="inlineStr">
+      <c r="D227" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E207" s="20" t="inlineStr">
+      <c r="E227" s="37" t="inlineStr">
         <is>
           <t>한약재, 자초, 지치의 뿌리, 자주색을 띈다하여 자초, 뿌리는 굵고 자주색, 오일에는 붉은 색이 우러나지만 알콜, 물에는 갈변합니다. 천연염색, 민간 약재로 사용, 호호바오일에 담궈서 유효성분을 우림</t>
         </is>
       </c>
-      <c r="F207" s="20" t="inlineStr">
+      <c r="F227" s="37" t="inlineStr">
         <is>
           <t>원하는 · 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="80" customHeight="1">
-      <c r="A208" s="20" t="inlineStr">
+    <row r="228" ht="80" customHeight="1">
+      <c r="A228" s="37" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B208" s="20" t="inlineStr">
+      <c r="B228" s="37" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C208" s="21" t="inlineStr">
+      <c r="C228" s="38" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D208" s="12" t="inlineStr">
+      <c r="D228" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E208" s="20" t="inlineStr">
+      <c r="E228" s="37" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F208" s="20" t="inlineStr">
+      <c r="F228" s="37" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="48" customHeight="1">
-      <c r="A209" s="20" t="inlineStr">
+    <row r="229" ht="48" customHeight="1">
+      <c r="A229" s="37" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B209" s="20" t="inlineStr">
+      <c r="B229" s="37" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C209" s="21" t="inlineStr">
+      <c r="C229" s="38" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D209" s="12" t="inlineStr">
+      <c r="D229" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E209" s="20" t="inlineStr">
+      <c r="E229" s="37" t="inlineStr">
         <is>
           <t>식물성 버터, 카리테나무 열매에서 채취 · 보습효과짱^^</t>
         </is>
       </c>
-      <c r="F209" s="20" t="inlineStr">
+      <c r="F229" s="37" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="32" customHeight="1">
-      <c r="A210" s="20" t="inlineStr">
+    <row r="230" ht="32" customHeight="1">
+      <c r="A230" s="37" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B210" s="20" t="inlineStr">
+      <c r="B230" s="37" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C210" s="21" t="inlineStr">
+      <c r="C230" s="38" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D210" s="22" t="inlineStr">
+      <c r="D230" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E210" s="20" t="inlineStr">
+      <c r="E230" s="37" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취 · 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="F210" s="20" t="inlineStr">
+      <c r="F230" s="37" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="20" t="inlineStr">
+    <row r="231" ht="16" customHeight="1">
+      <c r="A231" s="37" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B211" s="20" t="inlineStr">
+      <c r="B231" s="37" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C211" s="21" t="inlineStr">
+      <c r="C231" s="38" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D211" s="13" t="inlineStr">
+      <c r="D231" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E211" s="20" t="inlineStr">
+      <c r="E231" s="37" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="F211" s="20" t="inlineStr">
+      <c r="F231" s="37" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="14" customHeight="1">
-      <c r="A212" s="15" t="inlineStr">
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 65 · 경화 4 · 활성 29 · 향 2</t>
         </is>
       </c>
-      <c r="B212" s="16" t="n"/>
-      <c r="C212" s="16" t="n"/>
-      <c r="D212" s="16" t="n"/>
-      <c r="E212" s="16" t="n"/>
-      <c r="F212" s="16" t="n"/>
-    </row>
-    <row r="213" ht="14" customHeight="1">
-      <c r="A213" s="17" t="inlineStr">
+      <c r="B232" s="33" t="n"/>
+      <c r="C232" s="33" t="n"/>
+      <c r="D232" s="33" t="n"/>
+      <c r="E232" s="33" t="n"/>
+      <c r="F232" s="33" t="n"/>
+    </row>
+    <row r="233" ht="14" customHeight="1">
+      <c r="A233" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B213" s="18" t="n"/>
-      <c r="C213" s="18" t="n"/>
-      <c r="D213" s="18" t="n"/>
-      <c r="E213" s="18" t="n"/>
-      <c r="F213" s="18" t="n"/>
-    </row>
-    <row r="214" ht="288" customHeight="1">
-      <c r="A214" s="25" t="inlineStr">
+      <c r="B233" s="35" t="n"/>
+      <c r="C233" s="35" t="n"/>
+      <c r="D233" s="35" t="n"/>
+      <c r="E233" s="35" t="n"/>
+      <c r="F233" s="35" t="n"/>
+    </row>
+    <row r="234" ht="288" customHeight="1">
+      <c r="A234" s="42" t="inlineStr">
         <is>
           <t>2009년부터 만들기 시작한 자초인퓨즈오일로 만든 립밤이 있었죠.
 자초인퓨즈오일, 피마자오일, 시어버터, 칸데릴라왁스, 딸기플레이버오일로 만든 겁나게 촉촉한 립밤인데요
@@ -9999,26 +10323,26 @@
 5ml블랙캡립글로스</t>
         </is>
       </c>
-      <c r="B214" s="26" t="n"/>
-      <c r="C214" s="26" t="n"/>
-      <c r="D214" s="26" t="n"/>
-      <c r="E214" s="26" t="n"/>
-      <c r="F214" s="26" t="n"/>
-    </row>
-    <row r="215" ht="14" customHeight="1">
-      <c r="A215" s="17" t="inlineStr">
+      <c r="B234" s="23" t="n"/>
+      <c r="C234" s="23" t="n"/>
+      <c r="D234" s="23" t="n"/>
+      <c r="E234" s="23" t="n"/>
+      <c r="F234" s="23" t="n"/>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B215" s="18" t="n"/>
-      <c r="C215" s="18" t="n"/>
-      <c r="D215" s="18" t="n"/>
-      <c r="E215" s="18" t="n"/>
-      <c r="F215" s="18" t="n"/>
-    </row>
-    <row r="216" ht="176" customHeight="1">
-      <c r="A216" s="25" t="inlineStr">
+      <c r="B235" s="35" t="n"/>
+      <c r="C235" s="35" t="n"/>
+      <c r="D235" s="35" t="n"/>
+      <c r="E235" s="35" t="n"/>
+      <c r="F235" s="35" t="n"/>
+    </row>
+    <row r="236" ht="176" customHeight="1">
+      <c r="A236" s="42" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -10030,267 +10354,267 @@
 3. 체에 걸러 낸 후 사용한다.</t>
         </is>
       </c>
-      <c r="B216" s="26" t="n"/>
-      <c r="C216" s="26" t="n"/>
-      <c r="D216" s="26" t="n"/>
-      <c r="E216" s="26" t="n"/>
-      <c r="F216" s="26" t="n"/>
-    </row>
-    <row r="217" ht="6" customHeight="1"/>
-    <row r="218" ht="22" customHeight="1">
-      <c r="A218" s="7" t="inlineStr">
+      <c r="B236" s="23" t="n"/>
+      <c r="C236" s="23" t="n"/>
+      <c r="D236" s="23" t="n"/>
+      <c r="E236" s="23" t="n"/>
+      <c r="F236" s="23" t="n"/>
+    </row>
+    <row r="237" ht="6" customHeight="1"/>
+    <row r="238" ht="22" customHeight="1">
+      <c r="A238" s="24" t="inlineStr">
         <is>
           <t>레드(펄)립글로스    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B218" s="8" t="n"/>
-      <c r="C218" s="8" t="n"/>
-      <c r="D218" s="8" t="n"/>
-      <c r="E218" s="8" t="n"/>
-      <c r="F218" s="8" t="n"/>
-    </row>
-    <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="9" t="inlineStr">
+      <c r="B238" s="25" t="n"/>
+      <c r="C238" s="25" t="n"/>
+      <c r="D238" s="25" t="n"/>
+      <c r="E238" s="25" t="n"/>
+      <c r="F238" s="25" t="n"/>
+    </row>
+    <row r="239" ht="15" customHeight="1">
+      <c r="A239" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B219" s="9" t="inlineStr">
+      <c r="B239" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C219" s="9" t="inlineStr">
+      <c r="C239" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D219" s="9" t="inlineStr">
+      <c r="D239" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E219" s="9" t="inlineStr">
+      <c r="E239" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F219" s="9" t="inlineStr">
+      <c r="F239" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="64" customHeight="1">
-      <c r="A220" s="10" t="inlineStr">
+    <row r="240" ht="64" customHeight="1">
+      <c r="A240" s="27" t="inlineStr">
         <is>
           <t>유기농아르간오일</t>
         </is>
       </c>
-      <c r="B220" s="10" t="inlineStr">
+      <c r="B240" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C220" s="11" t="inlineStr">
+      <c r="C240" s="28" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D220" s="12" t="inlineStr">
+      <c r="D240" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E220" s="10" t="inlineStr">
+      <c r="E240" s="27" t="inlineStr">
         <is>
           <t>전통적으로 모로코 원주민들의 치료와 섭생의 목적으로 사용, 모로코의 올리브오일, 천연비타민E풍부</t>
         </is>
       </c>
-      <c r="F220" s="10" t="inlineStr">
+      <c r="F240" s="27" t="inlineStr">
         <is>
           <t>원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="80" customHeight="1">
-      <c r="A221" s="10" t="inlineStr">
+    <row r="241" ht="80" customHeight="1">
+      <c r="A241" s="27" t="inlineStr">
         <is>
           <t>(자초인퓨즈) / 피마자오일</t>
         </is>
       </c>
-      <c r="B221" s="10" t="inlineStr">
+      <c r="B241" s="27" t="inlineStr">
         <is>
           <t>9g</t>
         </is>
       </c>
-      <c r="C221" s="11" t="inlineStr">
+      <c r="C241" s="28" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D221" s="24" t="inlineStr">
+      <c r="D241" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E221" s="10" t="inlineStr">
+      <c r="E241" s="27" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F221" s="10" t="inlineStr"/>
-    </row>
-    <row r="222" ht="64" customHeight="1">
-      <c r="A222" s="10" t="inlineStr">
+      <c r="F241" s="27" t="inlineStr"/>
+    </row>
+    <row r="242" ht="64" customHeight="1">
+      <c r="A242" s="27" t="inlineStr">
         <is>
           <t>코코아버터</t>
         </is>
       </c>
-      <c r="B222" s="10" t="inlineStr">
+      <c r="B242" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C222" s="11" t="inlineStr">
+      <c r="C242" s="28" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D222" s="12" t="inlineStr">
+      <c r="D242" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E222" s="10" t="inlineStr">
+      <c r="E242" s="27" t="inlineStr">
         <is>
           <t>알려진 오일 중 가장 안정적인 것 중 하나 자연적인 산화방지제가 들어있어 산패를 막아주며 부드러운 향, 촉감제공</t>
         </is>
       </c>
-      <c r="F222" s="10" t="inlineStr">
+      <c r="F242" s="27" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="32" customHeight="1">
-      <c r="A223" s="10" t="inlineStr">
+    <row r="243" ht="32" customHeight="1">
+      <c r="A243" s="27" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B223" s="10" t="inlineStr">
+      <c r="B243" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C223" s="11" t="inlineStr">
+      <c r="C243" s="28" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D223" s="22" t="inlineStr">
+      <c r="D243" s="39" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E223" s="10" t="inlineStr">
+      <c r="E243" s="27" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취, 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="F223" s="10" t="inlineStr">
+      <c r="F243" s="27" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="32" customHeight="1">
-      <c r="A224" s="10" t="inlineStr">
+    <row r="244" ht="32" customHeight="1">
+      <c r="A244" s="27" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B224" s="10" t="inlineStr">
+      <c r="B244" s="27" t="inlineStr">
         <is>
           <t>9방울</t>
         </is>
       </c>
-      <c r="C224" s="11" t="inlineStr">
+      <c r="C244" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D224" s="13" t="inlineStr">
+      <c r="D244" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E224" s="10" t="inlineStr">
+      <c r="E244" s="27" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="F224" s="10" t="inlineStr">
+      <c r="F244" s="27" t="inlineStr">
         <is>
           <t>원하는 플레이버오일, 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="32" customHeight="1">
-      <c r="A225" s="10" t="inlineStr">
+    <row r="245" ht="32" customHeight="1">
+      <c r="A245" s="27" t="inlineStr">
         <is>
           <t>실버펄</t>
         </is>
       </c>
-      <c r="B225" s="10" t="inlineStr">
+      <c r="B245" s="27" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C225" s="11" t="inlineStr">
+      <c r="C245" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D225" s="23" t="inlineStr">
+      <c r="D245" s="40" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E225" s="10" t="inlineStr">
+      <c r="E245" s="27" t="inlineStr">
         <is>
           <t>글로시한 느낌 · 기호에 맞게 조절, 넣지 않아도 됨</t>
         </is>
       </c>
-      <c r="F225" s="10" t="inlineStr"/>
-    </row>
-    <row r="226" ht="14" customHeight="1">
-      <c r="A226" s="15" t="inlineStr">
+      <c r="F245" s="27" t="inlineStr"/>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 39 · 경화 6 · 활성 51 · 향 3 · 색소 2</t>
         </is>
       </c>
-      <c r="B226" s="16" t="n"/>
-      <c r="C226" s="16" t="n"/>
-      <c r="D226" s="16" t="n"/>
-      <c r="E226" s="16" t="n"/>
-      <c r="F226" s="16" t="n"/>
-    </row>
-    <row r="227" ht="14" customHeight="1">
-      <c r="A227" s="17" t="inlineStr">
+      <c r="B246" s="33" t="n"/>
+      <c r="C246" s="33" t="n"/>
+      <c r="D246" s="33" t="n"/>
+      <c r="E246" s="33" t="n"/>
+      <c r="F246" s="33" t="n"/>
+    </row>
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B227" s="18" t="n"/>
-      <c r="C227" s="18" t="n"/>
-      <c r="D227" s="18" t="n"/>
-      <c r="E227" s="18" t="n"/>
-      <c r="F227" s="18" t="n"/>
-    </row>
-    <row r="228" ht="192" customHeight="1">
-      <c r="A228" s="19" t="inlineStr">
+      <c r="B247" s="35" t="n"/>
+      <c r="C247" s="35" t="n"/>
+      <c r="D247" s="35" t="n"/>
+      <c r="E247" s="35" t="n"/>
+      <c r="F247" s="35" t="n"/>
+    </row>
+    <row r="248" ht="192" customHeight="1">
+      <c r="A248" s="36" t="inlineStr">
         <is>
           <t>입술에 영양과 윤기를 동시에 줄 수 있는립글로스입니다.
 튜브용기에 넣어서 사용하기 더욱 더 간편하게 만들어봤어요.
@@ -10307,20 +10631,20 @@
         </is>
       </c>
     </row>
-    <row r="229" ht="14" customHeight="1">
-      <c r="A229" s="17" t="inlineStr">
+    <row r="249" ht="14" customHeight="1">
+      <c r="A249" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B229" s="18" t="n"/>
-      <c r="C229" s="18" t="n"/>
-      <c r="D229" s="18" t="n"/>
-      <c r="E229" s="18" t="n"/>
-      <c r="F229" s="18" t="n"/>
-    </row>
-    <row r="230" ht="160" customHeight="1">
-      <c r="A230" s="19" t="inlineStr">
+      <c r="B249" s="35" t="n"/>
+      <c r="C249" s="35" t="n"/>
+      <c r="D249" s="35" t="n"/>
+      <c r="E249" s="35" t="n"/>
+      <c r="F249" s="35" t="n"/>
+    </row>
+    <row r="250" ht="160" customHeight="1">
+      <c r="A250" s="36" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -10333,265 +10657,265 @@
         </is>
       </c>
     </row>
-    <row r="231" ht="6" customHeight="1"/>
-    <row r="232" ht="22" customHeight="1">
-      <c r="A232" s="7" t="inlineStr">
+    <row r="251" ht="6" customHeight="1"/>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="24" t="inlineStr">
         <is>
           <t>진주 피지컨트롤 파우더    [진주 / 피지컨트롤 / 파우더]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B232" s="8" t="n"/>
-      <c r="C232" s="8" t="n"/>
-      <c r="D232" s="8" t="n"/>
-      <c r="E232" s="8" t="n"/>
-      <c r="F232" s="8" t="n"/>
-    </row>
-    <row r="233" ht="15" customHeight="1">
-      <c r="A233" s="9" t="inlineStr">
+      <c r="B252" s="25" t="n"/>
+      <c r="C252" s="25" t="n"/>
+      <c r="D252" s="25" t="n"/>
+      <c r="E252" s="25" t="n"/>
+      <c r="F252" s="25" t="n"/>
+    </row>
+    <row r="253" ht="15" customHeight="1">
+      <c r="A253" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B233" s="9" t="inlineStr">
+      <c r="B253" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C233" s="9" t="inlineStr">
+      <c r="C253" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D233" s="9" t="inlineStr">
+      <c r="D253" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E233" s="9" t="inlineStr">
+      <c r="E253" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F233" s="9" t="inlineStr">
+      <c r="F253" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="32" customHeight="1">
-      <c r="A234" s="20" t="inlineStr">
+    <row r="254" ht="32" customHeight="1">
+      <c r="A254" s="37" t="inlineStr">
         <is>
           <t>진주분말</t>
         </is>
       </c>
-      <c r="B234" s="20" t="inlineStr">
+      <c r="B254" s="37" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C234" s="21" t="inlineStr">
+      <c r="C254" s="38" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D234" s="24" t="inlineStr">
+      <c r="D254" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E234" s="20" t="inlineStr">
+      <c r="E254" s="37" t="inlineStr">
         <is>
           <t>진주분말, 미네럴 공급, 피지컨트롤</t>
         </is>
       </c>
-      <c r="F234" s="20" t="inlineStr"/>
-    </row>
-    <row r="235" ht="96" customHeight="1">
-      <c r="A235" s="20" t="inlineStr">
+      <c r="F254" s="37" t="inlineStr"/>
+    </row>
+    <row r="255" ht="96" customHeight="1">
+      <c r="A255" s="37" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B235" s="20" t="inlineStr">
+      <c r="B255" s="37" t="inlineStr">
         <is>
           <t>29g</t>
         </is>
       </c>
-      <c r="C235" s="21" t="inlineStr">
+      <c r="C255" s="38" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D235" s="14" t="inlineStr">
+      <c r="D255" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E235" s="20" t="inlineStr">
+      <c r="E255" s="37" t="inlineStr">
         <is>
           <t>피지흡착, 뽀송뽀송</t>
         </is>
       </c>
-      <c r="F235" s="20" t="inlineStr">
+      <c r="F255" s="37" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="48" customHeight="1">
-      <c r="A236" s="20" t="inlineStr">
+    <row r="256" ht="48" customHeight="1">
+      <c r="A256" s="37" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B236" s="20" t="inlineStr">
+      <c r="B256" s="37" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C236" s="21" t="inlineStr">
+      <c r="C256" s="38" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D236" s="24" t="inlineStr">
+      <c r="D256" s="41" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E236" s="20" t="inlineStr">
+      <c r="E256" s="37" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F236" s="20" t="inlineStr">
+      <c r="F256" s="37" t="inlineStr">
         <is>
           <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="48" customHeight="1">
-      <c r="A237" s="20" t="inlineStr">
+    <row r="257" ht="48" customHeight="1">
+      <c r="A257" s="37" t="inlineStr">
         <is>
           <t>로즈제라늄 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B237" s="20" t="inlineStr">
+      <c r="B257" s="37" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C237" s="21" t="inlineStr">
+      <c r="C257" s="38" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D237" s="13" t="inlineStr">
+      <c r="D257" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E237" s="20" t="inlineStr">
+      <c r="E257" s="37" t="inlineStr">
         <is>
           <t>고가의 장미오일은 아니지만 장미향이 나는 제라늄. 모든 피부 사용. 피지조절</t>
         </is>
       </c>
-      <c r="F237" s="20" t="inlineStr">
+      <c r="F257" s="37" t="inlineStr">
         <is>
           <t>원하는 에센셜오일.</t>
         </is>
       </c>
     </row>
-    <row r="238" ht="96" customHeight="1">
-      <c r="A238" s="20" t="inlineStr">
+    <row r="258" ht="96" customHeight="1">
+      <c r="A258" s="37" t="inlineStr">
         <is>
           <t>카오링클레이</t>
         </is>
       </c>
-      <c r="B238" s="20" t="inlineStr">
+      <c r="B258" s="37" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C238" s="21" t="inlineStr">
+      <c r="C258" s="38" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D238" s="23" t="inlineStr">
+      <c r="D258" s="40" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E238" s="20" t="inlineStr">
+      <c r="E258" s="37" t="inlineStr">
         <is>
           <t>중국 고령이 원산지인 클레이, 영어발음은 카오링, 현재 세계 다양한 지역에 분포, 채취. 미네럴공급, 화장품, 제약, 식품 등 다양한 용도로 사용됨. 피지컨트롤</t>
         </is>
       </c>
-      <c r="F238" s="20" t="inlineStr">
+      <c r="F258" s="37" t="inlineStr">
         <is>
           <t>화이트클레이</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="64" customHeight="1">
-      <c r="A239" s="20" t="inlineStr">
+    <row r="259" ht="64" customHeight="1">
+      <c r="A259" s="37" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B239" s="20" t="inlineStr">
+      <c r="B259" s="37" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C239" s="21" t="inlineStr">
+      <c r="C259" s="38" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D239" s="13" t="inlineStr">
+      <c r="D259" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E239" s="20" t="inlineStr">
+      <c r="E259" s="37" t="inlineStr">
         <is>
           <t>진정, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="F239" s="20" t="inlineStr">
+      <c r="F259" s="37" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="14" customHeight="1">
-      <c r="A240" s="15" t="inlineStr">
+    <row r="260" ht="14" customHeight="1">
+      <c r="A260" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 18 · 향 1 · 색소 16 · 기타 65</t>
         </is>
       </c>
-      <c r="B240" s="16" t="n"/>
-      <c r="C240" s="16" t="n"/>
-      <c r="D240" s="16" t="n"/>
-      <c r="E240" s="16" t="n"/>
-      <c r="F240" s="16" t="n"/>
-    </row>
-    <row r="241" ht="14" customHeight="1">
-      <c r="A241" s="17" t="inlineStr">
+      <c r="B260" s="33" t="n"/>
+      <c r="C260" s="33" t="n"/>
+      <c r="D260" s="33" t="n"/>
+      <c r="E260" s="33" t="n"/>
+      <c r="F260" s="33" t="n"/>
+    </row>
+    <row r="261" ht="14" customHeight="1">
+      <c r="A261" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B241" s="18" t="n"/>
-      <c r="C241" s="18" t="n"/>
-      <c r="D241" s="18" t="n"/>
-      <c r="E241" s="18" t="n"/>
-      <c r="F241" s="18" t="n"/>
-    </row>
-    <row r="242" ht="384" customHeight="1">
-      <c r="A242" s="25" t="inlineStr">
+      <c r="B261" s="35" t="n"/>
+      <c r="C261" s="35" t="n"/>
+      <c r="D261" s="35" t="n"/>
+      <c r="E261" s="35" t="n"/>
+      <c r="F261" s="35" t="n"/>
+    </row>
+    <row r="262" ht="384" customHeight="1">
+      <c r="A262" s="42" t="inlineStr">
         <is>
           <t>여름이면 저에게 고민이 하나 생기는데요..
 오전에는 괜찮지만 오후가 되면 번들녀로 변합니다. (변신~)
@@ -10616,14 +10940,14 @@
 허준 선생이 동의보감에 기술한 진주(珍珠)의 효능을 보면</t>
         </is>
       </c>
-      <c r="B242" s="26" t="n"/>
-      <c r="C242" s="26" t="n"/>
-      <c r="D242" s="26" t="n"/>
-      <c r="E242" s="26" t="n"/>
-      <c r="F242" s="26" t="n"/>
-    </row>
-    <row r="243" ht="208" customHeight="1">
-      <c r="A243" s="25" t="inlineStr">
+      <c r="B262" s="23" t="n"/>
+      <c r="C262" s="23" t="n"/>
+      <c r="D262" s="23" t="n"/>
+      <c r="E262" s="23" t="n"/>
+      <c r="F262" s="23" t="n"/>
+    </row>
+    <row r="263" ht="208" customHeight="1">
+      <c r="A263" s="42" t="inlineStr">
         <is>
           <t>"진주가루를 유즙(乳汁)에 섞어 바르면 검은 반점을 제거하며, 얼굴을 윤기나게하여 안색을 좋게한다.",
 "진주는 성질이 차고 무독(無毒)하여 심신을 평안케하며 눈을 밝게 하고 피부의 종기를 다스린다."라고
@@ -10638,26 +10962,26 @@
 위생상 퍼프만 새로 바꿔주세요.</t>
         </is>
       </c>
-      <c r="B243" s="26" t="n"/>
-      <c r="C243" s="26" t="n"/>
-      <c r="D243" s="26" t="n"/>
-      <c r="E243" s="26" t="n"/>
-      <c r="F243" s="26" t="n"/>
-    </row>
-    <row r="244" ht="14" customHeight="1">
-      <c r="A244" s="17" t="inlineStr">
+      <c r="B263" s="23" t="n"/>
+      <c r="C263" s="23" t="n"/>
+      <c r="D263" s="23" t="n"/>
+      <c r="E263" s="23" t="n"/>
+      <c r="F263" s="23" t="n"/>
+    </row>
+    <row r="264" ht="14" customHeight="1">
+      <c r="A264" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B244" s="18" t="n"/>
-      <c r="C244" s="18" t="n"/>
-      <c r="D244" s="18" t="n"/>
-      <c r="E244" s="18" t="n"/>
-      <c r="F244" s="18" t="n"/>
-    </row>
-    <row r="245" ht="176" customHeight="1">
-      <c r="A245" s="25" t="inlineStr">
+      <c r="B264" s="35" t="n"/>
+      <c r="C264" s="35" t="n"/>
+      <c r="D264" s="35" t="n"/>
+      <c r="E264" s="35" t="n"/>
+      <c r="F264" s="35" t="n"/>
+    </row>
+    <row r="265" ht="176" customHeight="1">
+      <c r="A265" s="42" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.지퍼백에 모든 재료를 계량하세요.
@@ -10671,148 +10995,168 @@
 9. 완성</t>
         </is>
       </c>
-      <c r="B245" s="26" t="n"/>
-      <c r="C245" s="26" t="n"/>
-      <c r="D245" s="26" t="n"/>
-      <c r="E245" s="26" t="n"/>
-      <c r="F245" s="26" t="n"/>
-    </row>
-    <row r="246" ht="6" customHeight="1"/>
+      <c r="B265" s="23" t="n"/>
+      <c r="C265" s="23" t="n"/>
+      <c r="D265" s="23" t="n"/>
+      <c r="E265" s="23" t="n"/>
+      <c r="F265" s="23" t="n"/>
+    </row>
+    <row r="266" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="A205:F205"/>
+  <mergeCells count="133">
+    <mergeCell ref="A174:F174"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A183:F183"/>
     <mergeCell ref="A84:F84"/>
-    <mergeCell ref="A189:F189"/>
-    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A238:F238"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A160:F160"/>
     <mergeCell ref="A175:F175"/>
-    <mergeCell ref="A144:F144"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A263:F263"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A265:F265"/>
     <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A249:F249"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A202:F202"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A226:F226"/>
-    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A241:F241"/>
-    <mergeCell ref="A228:F228"/>
+    <mergeCell ref="A260:F260"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A250:F250"/>
+    <mergeCell ref="A172:F172"/>
     <mergeCell ref="A212:F212"/>
-    <mergeCell ref="A243:F243"/>
-    <mergeCell ref="A108:F108"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A214:F214"/>
+    <mergeCell ref="A252:F252"/>
+    <mergeCell ref="A221:F221"/>
+    <mergeCell ref="A236:F236"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A223:F223"/>
     <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A213:F213"/>
-    <mergeCell ref="A151:F151"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A262:F262"/>
+    <mergeCell ref="B8:F8"/>
     <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A240:F240"/>
-    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A215:F215"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A125:F125"/>
     <mergeCell ref="A190:F190"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A112:F112"/>
     <mergeCell ref="A199:F199"/>
-    <mergeCell ref="A230:F230"/>
-    <mergeCell ref="A167:F167"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A232:F232"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="B9:F9"/>
     <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A216:F216"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A225:F225"/>
     <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A153:F153"/>
-    <mergeCell ref="A218:F218"/>
-    <mergeCell ref="A227:F227"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A105:F105"/>
-    <mergeCell ref="A154:F154"/>
-    <mergeCell ref="A179:F179"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A242:F242"/>
-    <mergeCell ref="A203:F203"/>
-    <mergeCell ref="A244:F244"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A165:F165"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A173:F173"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A143:F143"/>
-    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="A92:F92"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A192:F192"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A246:F246"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A264:F264"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A248:F248"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A235:F235"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A247:F247"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A234:F234"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A170:F170"/>
-    <mergeCell ref="A155:F155"/>
-    <mergeCell ref="A201:F201"/>
-    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A220:F220"/>
+    <mergeCell ref="A261:F261"/>
+    <mergeCell ref="A222:F222"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A146:F146"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A170" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A205" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>

--- a/카드_아키타입/09_색조.xlsx
+++ b/카드_아키타입/09_색조.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +70,13 @@
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B3A7A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -178,6 +183,16 @@
         <fgColor rgb="00EEF3F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF8FD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -210,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -302,6 +317,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -850,7 +872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31810325"/>
+    <pos x="7848600" y="31972250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -870,7 +892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31810325"/>
+    <pos x="9696450" y="31972250"/>
     <ext cx="1809750" cy="1476375"/>
     <pic>
       <nvPicPr>
@@ -890,7 +912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31810325"/>
+    <pos x="11544300" y="31972250"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -910,7 +932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31810325"/>
+    <pos x="13392150" y="31972250"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -930,7 +952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33658175"/>
+    <pos x="7848600" y="33820100"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -950,7 +972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="33658175"/>
+    <pos x="9696450" y="33820100"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -970,7 +992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="33658175"/>
+    <pos x="11544300" y="33820100"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -990,7 +1012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="33658175"/>
+    <pos x="13392150" y="33820100"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1010,7 +1032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="35506025"/>
+    <pos x="7848600" y="35667950"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1030,7 +1052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="35506025"/>
+    <pos x="9696450" y="35667950"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1050,7 +1072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="35506025"/>
+    <pos x="11544300" y="35667950"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1070,7 +1092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="35506025"/>
+    <pos x="13392150" y="35667950"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1090,7 +1112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37353875"/>
+    <pos x="7848600" y="37515800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1110,7 +1132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37353875"/>
+    <pos x="9696450" y="37515800"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1130,7 +1152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39277925"/>
+    <pos x="7848600" y="39439849"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1150,7 +1172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="39277925"/>
+    <pos x="9696450" y="39439849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1170,7 +1192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="39277925"/>
+    <pos x="11544300" y="39439849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1190,7 +1212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="39277925"/>
+    <pos x="13392150" y="39439849"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1210,7 +1232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="41125775"/>
+    <pos x="7848600" y="41287699"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1230,7 +1252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="41125775"/>
+    <pos x="9696450" y="41287699"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1250,7 +1272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="41125775"/>
+    <pos x="11544300" y="41287699"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1270,7 +1292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="41125775"/>
+    <pos x="13392150" y="41287699"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1290,7 +1312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="42973625"/>
+    <pos x="7848600" y="43135549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1310,7 +1332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="42973625"/>
+    <pos x="9696450" y="43135549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1330,7 +1352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="42973625"/>
+    <pos x="11544300" y="43135549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1350,7 +1372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="42973625"/>
+    <pos x="13392150" y="43135549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1370,7 +1392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="44821475"/>
+    <pos x="7848600" y="44983399"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1390,7 +1412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="44821475"/>
+    <pos x="9696450" y="44983399"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1410,7 +1432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="44821475"/>
+    <pos x="11544300" y="44983399"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1430,7 +1452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="47266225"/>
+    <pos x="7848600" y="48367949"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1450,7 +1472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="47266225"/>
+    <pos x="9696450" y="48367949"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1470,7 +1492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="47266225"/>
+    <pos x="11544300" y="48367949"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1490,7 +1512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="47266225"/>
+    <pos x="13392150" y="48367949"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1510,7 +1532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="49114075"/>
+    <pos x="7848600" y="50215799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1530,7 +1552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="49114075"/>
+    <pos x="9696450" y="50215799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1550,7 +1572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="49114075"/>
+    <pos x="11544300" y="50215799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1570,7 +1592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="49114075"/>
+    <pos x="13392150" y="50215799"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1590,7 +1612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="52612925"/>
+    <pos x="7848600" y="54273450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1610,7 +1632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="52612925"/>
+    <pos x="9696450" y="54273450"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1630,7 +1652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="52612925"/>
+    <pos x="11544300" y="54273450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1650,7 +1672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="52612925"/>
+    <pos x="13392150" y="54273450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1670,7 +1692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="54460775"/>
+    <pos x="7848600" y="56121300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1690,7 +1712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="54460775"/>
+    <pos x="9696450" y="56121300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1710,7 +1732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="54460775"/>
+    <pos x="11544300" y="56121300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1730,7 +1752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="54460775"/>
+    <pos x="13392150" y="56121300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1750,7 +1772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="56308625"/>
+    <pos x="7848600" y="57969150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1770,7 +1792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="56308625"/>
+    <pos x="9696450" y="57969150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1790,7 +1812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="56308625"/>
+    <pos x="11544300" y="57969150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1810,7 +1832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="56308625"/>
+    <pos x="13392150" y="57969150"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1830,7 +1852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="58156475"/>
+    <pos x="7848600" y="59817000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1850,7 +1872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="58156475"/>
+    <pos x="9696450" y="59817000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1870,7 +1892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="58156475"/>
+    <pos x="11544300" y="59817000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1890,7 +1912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="58156475"/>
+    <pos x="13392150" y="59817000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1910,7 +1932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="60004325"/>
+    <pos x="7848600" y="61664850"/>
     <ext cx="3857625" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1930,7 +1952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="65262125"/>
+    <pos x="7848600" y="66922650"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1950,7 +1972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="65262125"/>
+    <pos x="9696450" y="66922650"/>
     <ext cx="1809750" cy="781050"/>
     <pic>
       <nvPicPr>
@@ -1970,7 +1992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="65262125"/>
+    <pos x="11544300" y="66922650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1990,7 +2012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="65262125"/>
+    <pos x="13392150" y="66922650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2010,7 +2032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="67109975"/>
+    <pos x="7848600" y="68770500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2030,7 +2052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="67109975"/>
+    <pos x="9696450" y="68770500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2050,7 +2072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="67109975"/>
+    <pos x="11544300" y="68770500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2070,7 +2092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="67109975"/>
+    <pos x="13392150" y="68770500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2090,7 +2112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68957825"/>
+    <pos x="7848600" y="70618350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2110,7 +2132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="68957825"/>
+    <pos x="9696450" y="70618350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2130,7 +2152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="68957825"/>
+    <pos x="11544300" y="70618350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2150,7 +2172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="68957825"/>
+    <pos x="13392150" y="70618350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2170,7 +2192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="70805675"/>
+    <pos x="7848600" y="72466200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2190,7 +2212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="70805675"/>
+    <pos x="9696450" y="72466200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2210,7 +2232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="70805675"/>
+    <pos x="11544300" y="72466200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2230,7 +2252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="70805675"/>
+    <pos x="13392150" y="72466200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2250,7 +2272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="72653525"/>
+    <pos x="7848600" y="74314050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2270,7 +2292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="72653525"/>
+    <pos x="9696450" y="74314050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2290,7 +2312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="72653525"/>
+    <pos x="11544300" y="74314050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2310,7 +2332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="72653525"/>
+    <pos x="13392150" y="74314050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2330,7 +2352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="74577575"/>
+    <pos x="7848600" y="76238100"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2350,7 +2372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="74577575"/>
+    <pos x="9696450" y="76238100"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2370,7 +2392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="74577575"/>
+    <pos x="11544300" y="76238100"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2390,7 +2412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="74577575"/>
+    <pos x="13392150" y="76238100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2410,7 +2432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="76425425"/>
+    <pos x="7848600" y="78085950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2430,7 +2452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="76425425"/>
+    <pos x="9696450" y="78085950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2450,7 +2472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="76425425"/>
+    <pos x="11544300" y="78085950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2470,7 +2492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="76425425"/>
+    <pos x="13392150" y="78085950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2490,7 +2512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78273275"/>
+    <pos x="7848600" y="79933800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2510,7 +2532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78273275"/>
+    <pos x="9696450" y="79933800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2530,7 +2552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78273275"/>
+    <pos x="11544300" y="79933800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2550,7 +2572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78273275"/>
+    <pos x="13392150" y="79933800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2570,7 +2592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="80121125"/>
+    <pos x="7848600" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2590,7 +2612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="80121125"/>
+    <pos x="9696450" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2610,7 +2632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="80121125"/>
+    <pos x="11544300" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2630,7 +2652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="80121125"/>
+    <pos x="13392150" y="81781650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2650,7 +2672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81968975"/>
+    <pos x="7848600" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2670,7 +2692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="81968975"/>
+    <pos x="9696450" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2690,7 +2712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="81968975"/>
+    <pos x="11544300" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2710,7 +2732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="81968975"/>
+    <pos x="13392150" y="83629500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2730,7 +2752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="83816825"/>
+    <pos x="7848600" y="85477350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2750,7 +2772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85740875"/>
+    <pos x="7848600" y="87401400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2770,7 +2792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="85740875"/>
+    <pos x="9696450" y="87401400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2790,7 +2812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="85740875"/>
+    <pos x="11544300" y="87401400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2810,7 +2832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="85740875"/>
+    <pos x="13392150" y="87401400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2830,7 +2852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87588725"/>
+    <pos x="7848600" y="89249250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2850,7 +2872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="87588725"/>
+    <pos x="9696450" y="89249250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2870,7 +2892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="87588725"/>
+    <pos x="11544300" y="89249250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2890,7 +2912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="87588725"/>
+    <pos x="13392150" y="89249250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2910,7 +2932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="89436575"/>
+    <pos x="7848600" y="91097100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2930,7 +2952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="89436575"/>
+    <pos x="9696450" y="91097100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2950,7 +2972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="89436575"/>
+    <pos x="11544300" y="91097100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2970,7 +2992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="89436575"/>
+    <pos x="13392150" y="91097100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2990,7 +3012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91284425"/>
+    <pos x="7848600" y="92944950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3010,7 +3032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="91284425"/>
+    <pos x="9696450" y="92944950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3030,7 +3052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="91284425"/>
+    <pos x="11544300" y="92944950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3050,7 +3072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="91284425"/>
+    <pos x="13392150" y="92944950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3070,7 +3092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="93132275"/>
+    <pos x="7848600" y="94792800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3090,7 +3112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="93132275"/>
+    <pos x="9696450" y="94792800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3110,7 +3132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="95056325"/>
+    <pos x="7848600" y="97167700"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -3130,7 +3152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="95056325"/>
+    <pos x="9696450" y="97167700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3150,7 +3172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="95056325"/>
+    <pos x="11544300" y="97167700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3170,7 +3192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="95056325"/>
+    <pos x="13392150" y="97167700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3190,7 +3212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="96904175"/>
+    <pos x="7848600" y="99015550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3210,7 +3232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="96904175"/>
+    <pos x="9696450" y="99015550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3230,7 +3252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="96904175"/>
+    <pos x="11544300" y="99015550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3250,7 +3272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="96904175"/>
+    <pos x="13392150" y="99015550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3270,7 +3292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="98752025"/>
+    <pos x="7848600" y="100863400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -3290,7 +3312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="108124625"/>
+    <pos x="7848600" y="111556800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3310,7 +3332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="108124625"/>
+    <pos x="9696450" y="111556800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3330,7 +3352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="108124625"/>
+    <pos x="11544300" y="111556800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3350,7 +3372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="108124625"/>
+    <pos x="13392150" y="111556800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3370,7 +3392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="109972475"/>
+    <pos x="7848600" y="113404650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3390,7 +3412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="109972475"/>
+    <pos x="9696450" y="113404650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3410,7 +3432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="109972475"/>
+    <pos x="11544300" y="113404650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3430,7 +3452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="109972475"/>
+    <pos x="13392150" y="113404650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3450,7 +3472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="111820325"/>
+    <pos x="7848600" y="115252500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3470,7 +3492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="111820325"/>
+    <pos x="9696450" y="115252500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3490,7 +3512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="111820325"/>
+    <pos x="11544300" y="115252500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3510,7 +3532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="111820325"/>
+    <pos x="13392150" y="115252500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3530,7 +3552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="113668175"/>
+    <pos x="7848600" y="117100350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3550,7 +3572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="113668175"/>
+    <pos x="9696450" y="117100350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3570,7 +3592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="113668175"/>
+    <pos x="11544300" y="117100350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3590,7 +3612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="113668175"/>
+    <pos x="13392150" y="117100350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3610,7 +3632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="115516025"/>
+    <pos x="7848600" y="118948200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3630,7 +3652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="115516025"/>
+    <pos x="9696450" y="118948200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3650,7 +3672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="115516025"/>
+    <pos x="11544300" y="118948200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3670,7 +3692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="115516025"/>
+    <pos x="13392150" y="118948200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3690,7 +3712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="117363875"/>
+    <pos x="7848600" y="120796050"/>
     <ext cx="4057650" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -3710,7 +3732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="122621675"/>
+    <pos x="7848600" y="126053850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3730,7 +3752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="122621675"/>
+    <pos x="9696450" y="126053850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3750,7 +3772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="122621675"/>
+    <pos x="11544300" y="126053850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3770,7 +3792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="122621675"/>
+    <pos x="13392150" y="126053850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3790,7 +3812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="124469525"/>
+    <pos x="7848600" y="127901700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3810,7 +3832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="124469525"/>
+    <pos x="9696450" y="127901700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3830,7 +3852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="124469525"/>
+    <pos x="11544300" y="127901700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3850,7 +3872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="124469525"/>
+    <pos x="13392150" y="127901700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3870,7 +3892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="126317375"/>
+    <pos x="7848600" y="129749550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3890,7 +3912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="126317375"/>
+    <pos x="9696450" y="129749550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3910,7 +3932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="126317375"/>
+    <pos x="11544300" y="129749550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3930,7 +3952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="126317375"/>
+    <pos x="13392150" y="129749550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3950,7 +3972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="128165225"/>
+    <pos x="7848600" y="131597400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3970,7 +3992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="128165225"/>
+    <pos x="9696450" y="131597400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3990,7 +4012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="128165225"/>
+    <pos x="11544300" y="131597400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4010,7 +4032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="128165225"/>
+    <pos x="13392150" y="131597400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4030,7 +4052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="130013075"/>
+    <pos x="7848600" y="133445250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4050,7 +4072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="130013075"/>
+    <pos x="9696450" y="133445250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4070,7 +4092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="130013075"/>
+    <pos x="11544300" y="133445250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4090,7 +4112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="130013075"/>
+    <pos x="13392150" y="133445250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4110,7 +4132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="131860925"/>
+    <pos x="7848600" y="135293100"/>
     <ext cx="4057650" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -4130,7 +4152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="137118725"/>
+    <pos x="7848600" y="140550900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4150,7 +4172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="137118725"/>
+    <pos x="9696450" y="140550900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4170,7 +4192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="137118725"/>
+    <pos x="11544300" y="140550900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4190,7 +4212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="137118725"/>
+    <pos x="13392150" y="140550900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4210,7 +4232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="138966575"/>
+    <pos x="7848600" y="142398750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4230,7 +4252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="138966575"/>
+    <pos x="9696450" y="142398750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4250,7 +4272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="138966575"/>
+    <pos x="11544300" y="142398750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4270,7 +4292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="138966575"/>
+    <pos x="13392150" y="142398750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4290,7 +4312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="140814425"/>
+    <pos x="7848600" y="144246600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4310,7 +4332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="140814425"/>
+    <pos x="9696450" y="144246600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4330,7 +4352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="140814425"/>
+    <pos x="11544300" y="144246600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4350,7 +4372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="140814425"/>
+    <pos x="13392150" y="144246600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4370,7 +4392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="142662275"/>
+    <pos x="7848600" y="146094450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4390,7 +4412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="142662275"/>
+    <pos x="9696450" y="146094450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4410,7 +4432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="142662275"/>
+    <pos x="11544300" y="146094450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4430,7 +4452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="142662275"/>
+    <pos x="13392150" y="146094450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4450,7 +4472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="144510125"/>
+    <pos x="7848600" y="147942300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4470,7 +4492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="144510125"/>
+    <pos x="9696450" y="147942300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4490,7 +4512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="144510125"/>
+    <pos x="11544300" y="147942300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4510,7 +4532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="146357975"/>
+    <pos x="7848600" y="149790150"/>
     <ext cx="4057650" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -4530,7 +4552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="151615775"/>
+    <pos x="7848600" y="155047950"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -4550,7 +4572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="151615775"/>
+    <pos x="9696450" y="155047950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4570,7 +4592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="151615775"/>
+    <pos x="11544300" y="155047950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4590,7 +4612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="151615775"/>
+    <pos x="13392150" y="155047950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4610,7 +4632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="153463625"/>
+    <pos x="7848600" y="156895800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4630,7 +4652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="153463625"/>
+    <pos x="9696450" y="156895800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4650,7 +4672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="153463625"/>
+    <pos x="11544300" y="156895800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4670,7 +4692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="153463625"/>
+    <pos x="13392150" y="156895800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4690,7 +4712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="155311475"/>
+    <pos x="7848600" y="158743650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4710,7 +4732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="155311475"/>
+    <pos x="9696450" y="158743650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4730,7 +4752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="155311475"/>
+    <pos x="11544300" y="158743650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4750,7 +4772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="158791275"/>
+    <pos x="7848600" y="162782250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4770,7 +4792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="158791275"/>
+    <pos x="9696450" y="162782250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4790,7 +4812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="158791275"/>
+    <pos x="11544300" y="162782250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4810,7 +4832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="158791275"/>
+    <pos x="13392150" y="162782250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4830,7 +4852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="160639125"/>
+    <pos x="7848600" y="164630100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4850,7 +4872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="160639125"/>
+    <pos x="9696450" y="164630100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4870,7 +4892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="162486975"/>
+    <pos x="7848600" y="166477950"/>
     <ext cx="5143500" cy="2895600"/>
     <pic>
       <nvPicPr>
@@ -4890,7 +4912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="167185975"/>
+    <pos x="7848600" y="171735750"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -4910,7 +4932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="167185975"/>
+    <pos x="9696450" y="171735750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4930,7 +4952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="167185975"/>
+    <pos x="11544300" y="171735750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4950,7 +4972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="167185975"/>
+    <pos x="13392150" y="171735750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4970,7 +4992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="169033825"/>
+    <pos x="7848600" y="173583600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -4990,7 +5012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="169033825"/>
+    <pos x="9696450" y="173583600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5010,7 +5032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="169033825"/>
+    <pos x="11544300" y="173583600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5030,7 +5052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="170881675"/>
+    <pos x="7848600" y="175431450"/>
     <ext cx="4276725" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -5050,7 +5072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="177815875"/>
+    <pos x="7848600" y="183495950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5070,7 +5092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="177815875"/>
+    <pos x="9696450" y="183495950"/>
     <ext cx="1809750" cy="1371600"/>
     <pic>
       <nvPicPr>
@@ -5090,7 +5112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="177815875"/>
+    <pos x="11544300" y="183495950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5110,7 +5132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="177815875"/>
+    <pos x="13392150" y="183495950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5130,7 +5152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179663725"/>
+    <pos x="7848600" y="185343800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5150,7 +5172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179663725"/>
+    <pos x="9696450" y="185343800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5170,7 +5192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179663725"/>
+    <pos x="11544300" y="185343800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5190,7 +5212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179663725"/>
+    <pos x="13392150" y="185343800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5210,7 +5232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="187226575"/>
+    <pos x="7848600" y="193846450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -5230,7 +5252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="187226575"/>
+    <pos x="9696450" y="193846450"/>
     <ext cx="1447800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -5250,7 +5272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="187226575"/>
+    <pos x="11544300" y="193846450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5270,7 +5292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="187226575"/>
+    <pos x="13392150" y="193846450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5290,7 +5312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="189074425"/>
+    <pos x="7848600" y="195694300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5310,7 +5332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="189074425"/>
+    <pos x="9696450" y="195694300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5330,7 +5352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="189074425"/>
+    <pos x="11544300" y="195694300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5350,7 +5372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="189074425"/>
+    <pos x="13392150" y="195694300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5370,7 +5392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="190922275"/>
+    <pos x="7848600" y="197542150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5390,7 +5412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="190922275"/>
+    <pos x="9696450" y="197542150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5410,7 +5432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="190922275"/>
+    <pos x="11544300" y="197542150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -5721,7 +5743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F265"/>
+  <dimension ref="A1:F298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6245,298 +6267,319 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="221.5" customHeight="1"/>
-    <row r="37" ht="6" customHeight="1"/>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B36" s="38" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="38" t="n"/>
+      <c r="E36" s="38" t="n"/>
+      <c r="F36" s="38" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 88%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 (겁나게 촉촉) 립밤(88%)로 보습막·발림 설계.
+· 마무리: 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="162.5000000000001" customHeight="1"/>
+    <row r="39" ht="6" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>멀티밤 bb    [1..베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="25" t="n"/>
-      <c r="E38" s="25" t="n"/>
-      <c r="F38" s="25" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="25" t="n"/>
+      <c r="F40" s="25" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B39" s="26" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D41" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E41" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="F41" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="37" t="inlineStr">
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>멀티오일베이스</t>
         </is>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B42" s="40" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C40" s="38" t="inlineStr">
+      <c r="C42" s="41" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D40" s="29" t="inlineStr">
+      <c r="D42" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E40" s="37" t="inlineStr">
+      <c r="E42" s="40" t="inlineStr">
         <is>
           <t>MCT, 로즈힙, 유기농 호호바, 녹차씨, 발효동백, 스쿠알란, 비타민E 등</t>
         </is>
       </c>
-      <c r="F40" s="37" t="inlineStr">
+      <c r="F42" s="40" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="37" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>유기농 / 코포아수버터</t>
         </is>
       </c>
-      <c r="B41" s="37" t="inlineStr">
+      <c r="B43" s="40" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C41" s="38" t="inlineStr">
+      <c r="C43" s="41" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E41" s="37" t="inlineStr">
+      <c r="E43" s="40" t="inlineStr">
         <is>
           <t>식물성 버터 · 끈적임 적고 수분함량 높고 아주 부드러움</t>
         </is>
       </c>
-      <c r="F41" s="37" t="inlineStr">
+      <c r="F43" s="40" t="inlineStr">
         <is>
           <t>망고버터 등</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="37" t="inlineStr">
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B42" s="37" t="inlineStr">
+      <c r="B44" s="40" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C42" s="38" t="inlineStr">
+      <c r="C44" s="41" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D42" s="39" t="inlineStr">
+      <c r="D44" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E42" s="37" t="inlineStr">
+      <c r="E44" s="40" t="inlineStr">
         <is>
           <t>식물성 왁스, 단단하게.</t>
         </is>
       </c>
-      <c r="F42" s="37" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="37" t="inlineStr">
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
         <is>
           <t>칼라믹스 / 파운데이션</t>
         </is>
       </c>
-      <c r="B43" s="37" t="inlineStr">
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C43" s="38" t="inlineStr">
+      <c r="C45" s="41" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D43" s="40" t="inlineStr">
+      <c r="D45" s="43" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E43" s="37" t="inlineStr">
+      <c r="E45" s="40" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 함유 · 파운데이션 파우더</t>
         </is>
       </c>
-      <c r="F43" s="37" t="inlineStr"/>
-    </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="37" t="inlineStr">
+      <c r="F45" s="40" t="inlineStr"/>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="40" t="inlineStr">
         <is>
           <t>보르피린</t>
         </is>
       </c>
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B46" s="40" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C44" s="38" t="inlineStr">
+      <c r="C46" s="41" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D44" s="41" t="inlineStr">
+      <c r="D46" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E44" s="37" t="inlineStr">
+      <c r="E46" s="40" t="inlineStr">
         <is>
           <t>볼륨업, 주름</t>
         </is>
       </c>
-      <c r="F44" s="37" t="inlineStr">
+      <c r="F46" s="40" t="inlineStr">
         <is>
           <t>10 g(10%)을 원한다면 로즈워터를 5g 줄여서 40g이 되도록 해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="37" t="inlineStr">
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="40" t="inlineStr">
         <is>
           <t>알파 비사보롤</t>
         </is>
       </c>
-      <c r="B45" s="37" t="inlineStr">
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>0.3g / (10방울)</t>
         </is>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C47" s="41" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D45" s="31" t="inlineStr">
+      <c r="D47" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E45" s="37" t="inlineStr">
+      <c r="E47" s="40" t="inlineStr">
         <is>
           <t>식약처 인증, 미백 원료</t>
         </is>
       </c>
-      <c r="F45" s="37" t="inlineStr">
+      <c r="F47" s="40" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="37" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="40" t="inlineStr">
         <is>
           <t>버가못에센셜오일</t>
         </is>
       </c>
-      <c r="B46" s="37" t="inlineStr">
+      <c r="B48" s="40" t="inlineStr">
         <is>
           <t>0.7g / 10~14방울</t>
         </is>
       </c>
-      <c r="C46" s="38" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D46" s="30" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E46" s="37" t="inlineStr">
+      <c r="E48" s="40" t="inlineStr">
         <is>
           <t>FCF, 버갑텐 프리 · 감귤껍질오일, 아로마테라피</t>
         </is>
       </c>
-      <c r="F46" s="37" t="inlineStr">
+      <c r="F48" s="40" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="32" t="inlineStr">
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 61 · 경화 16 · 활성 6 · 향 2 · 색소 13 · 기타 1</t>
         </is>
       </c>
-      <c r="B47" s="33" t="n"/>
-      <c r="C47" s="33" t="n"/>
-      <c r="D47" s="33" t="n"/>
-      <c r="E47" s="33" t="n"/>
-      <c r="F47" s="33" t="n"/>
-    </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="B49" s="33" t="n"/>
+      <c r="C49" s="33" t="n"/>
+      <c r="D49" s="33" t="n"/>
+      <c r="E49" s="33" t="n"/>
+      <c r="F49" s="33" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="35" t="n"/>
-      <c r="F48" s="35" t="n"/>
-    </row>
-    <row r="49" ht="336" customHeight="1">
-      <c r="A49" s="42" t="inlineStr">
+      <c r="B50" s="35" t="n"/>
+      <c r="C50" s="35" t="n"/>
+      <c r="D50" s="35" t="n"/>
+      <c r="E50" s="35" t="n"/>
+      <c r="F50" s="35" t="n"/>
+    </row>
+    <row r="51" ht="336" customHeight="1">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>이 레시피는 2015년에
 문화센터에서 반응이 좋다며
@@ -6561,26 +6604,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B49" s="23" t="n"/>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="23" t="n"/>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="23" t="n"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B50" s="35" t="n"/>
-      <c r="C50" s="35" t="n"/>
-      <c r="D50" s="35" t="n"/>
-      <c r="E50" s="35" t="n"/>
-      <c r="F50" s="35" t="n"/>
-    </row>
-    <row r="51" ht="176" customHeight="1">
-      <c r="A51" s="42" t="inlineStr">
+      <c r="B52" s="35" t="n"/>
+      <c r="C52" s="35" t="n"/>
+      <c r="D52" s="35" t="n"/>
+      <c r="E52" s="35" t="n"/>
+      <c r="F52" s="35" t="n"/>
+    </row>
+    <row r="53" ht="176" customHeight="1">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>1. 멀티오일베이스를 계량하세요.
 2. 왁스와 버터를 계량한 후
@@ -6595,302 +6638,316 @@
 굳으면 완성</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="23" t="n"/>
-    </row>
-    <row r="52" ht="61.25000000000006" customHeight="1">
-      <c r="A52" s="23" t="n"/>
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="23" t="n"/>
-      <c r="E52" s="23" t="n"/>
-      <c r="F52" s="23" t="n"/>
-    </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
+      <c r="E53" s="23" t="n"/>
+      <c r="F53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B54" s="38" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="38" t="n"/>
+      <c r="E54" s="38" t="n"/>
+      <c r="F54" s="38" t="n"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 무수+경화 16% → 밤·스틱류. 왁스 비율이 굳기를 결정(늘리면 단단, 줄이면 말랑).
+· 베이스: 유상 중심, 주 오일 멀티오일베이스(39%)로 보습막·발림 설계.
+· 기능: 활성 합 6%(보르피린 6%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 2% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="6" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
         <is>
           <t>카렌듈라 썬밤    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="B57" s="25" t="n"/>
+      <c r="C57" s="25" t="n"/>
+      <c r="D57" s="25" t="n"/>
+      <c r="E57" s="25" t="n"/>
+      <c r="F57" s="25" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B55" s="26" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
+      <c r="C58" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E58" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F58" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
+    <row r="59" ht="48" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B56" s="27" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C56" s="28" t="inlineStr">
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D56" s="29" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E56" s="27" t="inlineStr">
+      <c r="E59" s="27" t="inlineStr">
         <is>
           <t>피지성분 비슷 · 가벼운 오일 또는 액상왁스</t>
         </is>
       </c>
-      <c r="F56" s="27" t="inlineStr">
+      <c r="F59" s="27" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B57" s="27" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C57" s="28" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D57" s="29" t="inlineStr">
+      <c r="D60" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일, 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="F57" s="27" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr">
         <is>
           <t>캐모마일인퓨즈오일</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="64" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B58" s="27" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C58" s="28" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D58" s="41" t="inlineStr">
+      <c r="D61" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
+      <c r="E61" s="27" t="inlineStr">
         <is>
           <t>산화방지.</t>
         </is>
       </c>
-      <c r="F58" s="27" t="inlineStr">
+      <c r="F61" s="27" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
-      <c r="B59" s="27" t="inlineStr">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C59" s="28" t="inlineStr">
+      <c r="C62" s="28" t="inlineStr">
         <is>
           <t>27%</t>
         </is>
       </c>
-      <c r="D59" s="39" t="inlineStr">
+      <c r="D62" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E59" s="27" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="F59" s="27" t="inlineStr">
+      <c r="F62" s="27" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>산화 아연 분말</t>
         </is>
       </c>
-      <c r="B60" s="27" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C60" s="28" t="inlineStr">
+      <c r="C63" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D60" s="31" t="inlineStr">
+      <c r="D63" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E60" s="27" t="inlineStr">
+      <c r="E63" s="27" t="inlineStr">
         <is>
           <t>전체양의 23%</t>
         </is>
       </c>
-      <c r="F60" s="27" t="inlineStr">
+      <c r="F63" s="27" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>3~9방울</t>
         </is>
       </c>
-      <c r="C61" s="28" t="inlineStr">
+      <c r="C64" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D61" s="30" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E61" s="27" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>썬번, 진정, 아로마테라피</t>
         </is>
       </c>
-      <c r="F61" s="27" t="inlineStr">
+      <c r="F64" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="32" t="inlineStr">
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 47 · 경화 27 · 활성 1 · 향 1 · 기타 24</t>
         </is>
       </c>
-      <c r="B62" s="33" t="n"/>
-      <c r="C62" s="33" t="n"/>
-      <c r="D62" s="33" t="n"/>
-      <c r="E62" s="33" t="n"/>
-      <c r="F62" s="33" t="n"/>
-    </row>
-    <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="34" t="inlineStr">
+      <c r="B65" s="33" t="n"/>
+      <c r="C65" s="33" t="n"/>
+      <c r="D65" s="33" t="n"/>
+      <c r="E65" s="33" t="n"/>
+      <c r="F65" s="33" t="n"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B63" s="35" t="n"/>
-      <c r="C63" s="35" t="n"/>
-      <c r="D63" s="35" t="n"/>
-      <c r="E63" s="35" t="n"/>
-      <c r="F63" s="35" t="n"/>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="36" t="inlineStr">
+      <c r="B66" s="35" t="n"/>
+      <c r="C66" s="35" t="n"/>
+      <c r="D66" s="35" t="n"/>
+      <c r="E66" s="35" t="n"/>
+      <c r="F66" s="35" t="n"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
         <is>
           <t>초정밀 과정</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="34" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B65" s="35" t="n"/>
-      <c r="C65" s="35" t="n"/>
-      <c r="D65" s="35" t="n"/>
-      <c r="E65" s="35" t="n"/>
-      <c r="F65" s="35" t="n"/>
-    </row>
-    <row r="66" ht="192" customHeight="1">
-      <c r="A66" s="36" t="inlineStr">
+      <c r="B68" s="35" t="n"/>
+      <c r="C68" s="35" t="n"/>
+      <c r="D68" s="35" t="n"/>
+      <c r="E68" s="35" t="n"/>
+      <c r="F68" s="35" t="n"/>
+    </row>
+    <row r="69" ht="192" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>1. 징크옥사이드를 종이에 계량하세요.
 2. 비커에 1번 재료를 계량합니다.
@@ -6907,328 +6964,350 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="102.9999999999997" customHeight="1"/>
-    <row r="68" ht="6" customHeight="1"/>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="24" t="inlineStr">
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B70" s="38" t="n"/>
+      <c r="C70" s="38" t="n"/>
+      <c r="D70" s="38" t="n"/>
+      <c r="E70" s="38" t="n"/>
+      <c r="F70" s="38" t="n"/>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 무수+경화 27% → 밤·스틱류. 왁스 비율이 굳기를 결정(늘리면 단단, 줄이면 말랑).
+· 베이스: 유상 중심, 주 오일 호호바오일(24%)로 보습막·발림 설계.
+· 기능: 활성 합 1%(비타민E 1%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="28.99999999999963" customHeight="1"/>
+    <row r="73" ht="6" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="24" t="inlineStr">
         <is>
           <t>내추럴 립스틱    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B69" s="25" t="n"/>
-      <c r="C69" s="25" t="n"/>
-      <c r="D69" s="25" t="n"/>
-      <c r="E69" s="25" t="n"/>
-      <c r="F69" s="25" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="B74" s="25" t="n"/>
+      <c r="C74" s="25" t="n"/>
+      <c r="D74" s="25" t="n"/>
+      <c r="E74" s="25" t="n"/>
+      <c r="F74" s="25" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="B75" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="C75" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="D75" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E70" s="26" t="inlineStr">
+      <c r="E75" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F70" s="26" t="inlineStr">
+      <c r="F75" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="48" customHeight="1">
-      <c r="A71" s="37" t="inlineStr">
+    <row r="76" ht="48" customHeight="1">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>정제 호호바오일</t>
         </is>
       </c>
-      <c r="B71" s="37" t="inlineStr">
+      <c r="B76" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C71" s="38" t="inlineStr">
+      <c r="C76" s="41" t="inlineStr">
         <is>
           <t>26%</t>
         </is>
       </c>
-      <c r="D71" s="29" t="inlineStr">
+      <c r="D76" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E71" s="37" t="inlineStr">
+      <c r="E76" s="40" t="inlineStr">
         <is>
           <t>가벼운오일, 보습</t>
         </is>
       </c>
-      <c r="F71" s="37" t="inlineStr">
+      <c r="F76" s="40" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="37" t="inlineStr">
+    <row r="77" ht="48" customHeight="1">
+      <c r="A77" s="40" t="inlineStr">
         <is>
           <t>립베이스 레드27</t>
         </is>
       </c>
-      <c r="B72" s="37" t="inlineStr">
+      <c r="B77" s="40" t="inlineStr">
         <is>
           <t>0.4g</t>
         </is>
       </c>
-      <c r="C72" s="38" t="inlineStr">
+      <c r="C77" s="41" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D72" s="31" t="inlineStr">
+      <c r="D77" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E72" s="37" t="inlineStr">
+      <c r="E77" s="40" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="F72" s="37" t="inlineStr">
+      <c r="F77" s="40" t="inlineStr">
         <is>
           <t>더 진한 색을 원하면 · 양을 추가하세요.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="37" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="40" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B73" s="37" t="inlineStr">
+      <c r="B78" s="40" t="inlineStr">
         <is>
           <t>3.5g</t>
         </is>
       </c>
-      <c r="C73" s="38" t="inlineStr">
+      <c r="C78" s="41" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D73" s="39" t="inlineStr">
+      <c r="D78" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E73" s="37" t="inlineStr">
+      <c r="E78" s="40" t="inlineStr">
         <is>
           <t>식물성왁스. 경화제</t>
         </is>
       </c>
-      <c r="F73" s="37" t="inlineStr">
+      <c r="F78" s="40" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="37" t="inlineStr">
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="40" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B74" s="37" t="inlineStr">
+      <c r="B79" s="40" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C74" s="38" t="inlineStr">
+      <c r="C79" s="41" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="D74" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E74" s="37" t="inlineStr">
+      <c r="E79" s="40" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습</t>
         </is>
       </c>
-      <c r="F74" s="37" t="inlineStr">
+      <c r="F79" s="40" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="37" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="40" t="inlineStr">
         <is>
           <t>발효 동백오일</t>
         </is>
       </c>
-      <c r="B75" s="37" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C75" s="38" t="inlineStr">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D75" s="41" t="inlineStr">
+      <c r="D80" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E75" s="37" t="inlineStr">
+      <c r="E80" s="40" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F75" s="37" t="inlineStr">
+      <c r="F80" s="40" t="inlineStr">
         <is>
           <t>아르간, 마유 등</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="64" customHeight="1">
-      <c r="A76" s="37" t="inlineStr">
+    <row r="81" ht="64" customHeight="1">
+      <c r="A81" s="40" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B76" s="37" t="inlineStr">
+      <c r="B81" s="40" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C76" s="38" t="inlineStr">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D76" s="41" t="inlineStr">
+      <c r="D81" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E76" s="37" t="inlineStr">
+      <c r="E81" s="40" t="inlineStr">
         <is>
           <t>산화방지, 고보습</t>
         </is>
       </c>
-      <c r="F76" s="37" t="inlineStr">
+      <c r="F81" s="40" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="48" customHeight="1">
-      <c r="A77" s="37" t="inlineStr">
+    <row r="82" ht="48" customHeight="1">
+      <c r="A82" s="40" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
-      <c r="B77" s="37" t="inlineStr">
+      <c r="B82" s="40" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C77" s="38" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D82" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E77" s="37" t="inlineStr">
+      <c r="E82" s="40" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F77" s="37" t="inlineStr">
+      <c r="F82" s="40" t="inlineStr">
         <is>
           <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="32" t="inlineStr">
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 58 · 경화 23 · 활성 14 · 향 2 · 기타 3</t>
         </is>
       </c>
-      <c r="B78" s="33" t="n"/>
-      <c r="C78" s="33" t="n"/>
-      <c r="D78" s="33" t="n"/>
-      <c r="E78" s="33" t="n"/>
-      <c r="F78" s="33" t="n"/>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="34" t="inlineStr">
+      <c r="B83" s="33" t="n"/>
+      <c r="C83" s="33" t="n"/>
+      <c r="D83" s="33" t="n"/>
+      <c r="E83" s="33" t="n"/>
+      <c r="F83" s="33" t="n"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B79" s="35" t="n"/>
-      <c r="C79" s="35" t="n"/>
-      <c r="D79" s="35" t="n"/>
-      <c r="E79" s="35" t="n"/>
-      <c r="F79" s="35" t="n"/>
-    </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="42" t="inlineStr">
+      <c r="B84" s="35" t="n"/>
+      <c r="C84" s="35" t="n"/>
+      <c r="D84" s="35" t="n"/>
+      <c r="E84" s="35" t="n"/>
+      <c r="F84" s="35" t="n"/>
+    </row>
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="45" t="inlineStr">
         <is>
           <t>촉촉한 립밤에 색상을 더했습니다. 내추럴 립스틱!
 가루날림이 없는 립베이스로 원하는 색상을 만들어보세요.
 오일에 미리 개어서 원하는 색상을 만든 후 적용하면 됩니다.</t>
         </is>
       </c>
-      <c r="B80" s="23" t="n"/>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n"/>
-      <c r="E80" s="23" t="n"/>
-      <c r="F80" s="23" t="n"/>
-    </row>
-    <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="34" t="inlineStr">
+      <c r="B85" s="23" t="n"/>
+      <c r="C85" s="23" t="n"/>
+      <c r="D85" s="23" t="n"/>
+      <c r="E85" s="23" t="n"/>
+      <c r="F85" s="23" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B81" s="35" t="n"/>
-      <c r="C81" s="35" t="n"/>
-      <c r="D81" s="35" t="n"/>
-      <c r="E81" s="35" t="n"/>
-      <c r="F81" s="35" t="n"/>
-    </row>
-    <row r="82" ht="208" customHeight="1">
-      <c r="A82" s="42" t="inlineStr">
+      <c r="B86" s="35" t="n"/>
+      <c r="C86" s="35" t="n"/>
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="35" t="n"/>
+      <c r="F86" s="35" t="n"/>
+    </row>
+    <row r="87" ht="208" customHeight="1">
+      <c r="A87" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 속뚜껑을 닫고 뒤집어 주세요.
@@ -7245,147 +7324,169 @@
 12.꺼내서 넘친 부분도 다듬어 닦습니다. 스티커를 붙이고 겉뚜껑을 닫으면 완성.</t>
         </is>
       </c>
-      <c r="B82" s="23" t="n"/>
-      <c r="C82" s="23" t="n"/>
-      <c r="D82" s="23" t="n"/>
-      <c r="E82" s="23" t="n"/>
-      <c r="F82" s="23" t="n"/>
-    </row>
-    <row r="83" ht="6" customHeight="1"/>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="24" t="inlineStr">
+      <c r="B87" s="23" t="n"/>
+      <c r="C87" s="23" t="n"/>
+      <c r="D87" s="23" t="n"/>
+      <c r="E87" s="23" t="n"/>
+      <c r="F87" s="23" t="n"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B88" s="38" t="n"/>
+      <c r="C88" s="38" t="n"/>
+      <c r="D88" s="38" t="n"/>
+      <c r="E88" s="38" t="n"/>
+      <c r="F88" s="38" t="n"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 무수+경화 23% → 밤·스틱류. 왁스 비율이 굳기를 결정(늘리면 단단, 줄이면 말랑).
+· 베이스: 유상 중심, 주 오일 피마자오일(32%)로 보습막·발림 설계.
+· 기능: 활성 합 14%(발효 동백오일 13%, 비타민E 1%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 2% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="6" customHeight="1"/>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
         <is>
           <t>립스틱/글로스 컬러베이스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B84" s="25" t="n"/>
-      <c r="C84" s="25" t="n"/>
-      <c r="D84" s="25" t="n"/>
-      <c r="E84" s="25" t="n"/>
-      <c r="F84" s="25" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="B91" s="25" t="n"/>
+      <c r="C91" s="25" t="n"/>
+      <c r="D91" s="25" t="n"/>
+      <c r="E91" s="25" t="n"/>
+      <c r="F91" s="25" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B85" s="26" t="inlineStr">
+      <c r="B92" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C85" s="26" t="inlineStr">
+      <c r="C92" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D85" s="26" t="inlineStr">
+      <c r="D92" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E85" s="26" t="inlineStr">
+      <c r="E92" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F85" s="26" t="inlineStr">
+      <c r="F92" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="27" t="inlineStr">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>(골든)호호바오일</t>
         </is>
       </c>
-      <c r="B86" s="27" t="inlineStr">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C86" s="28" t="inlineStr">
+      <c r="C93" s="28" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D86" s="29" t="inlineStr">
+      <c r="D93" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E86" s="27" t="inlineStr">
+      <c r="E93" s="27" t="inlineStr">
         <is>
           <t>액상왁스, 가벼운 오일</t>
         </is>
       </c>
-      <c r="F86" s="27" t="inlineStr">
+      <c r="F93" s="27" t="inlineStr">
         <is>
           <t>마카다미아넛오일</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="32" customHeight="1">
-      <c r="A87" s="27" t="inlineStr">
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>립 컬러베이스 7</t>
         </is>
       </c>
-      <c r="B87" s="27" t="inlineStr">
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C87" s="28" t="inlineStr">
+      <c r="C94" s="28" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D87" s="31" t="inlineStr">
+      <c r="D94" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E87" s="27" t="inlineStr">
+      <c r="E94" s="27" t="inlineStr">
         <is>
           <t>핑크</t>
         </is>
       </c>
-      <c r="F87" s="27" t="inlineStr">
+      <c r="F94" s="27" t="inlineStr">
         <is>
           <t>9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="32" t="inlineStr">
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 89 · 기타 11</t>
         </is>
       </c>
-      <c r="B88" s="33" t="n"/>
-      <c r="C88" s="33" t="n"/>
-      <c r="D88" s="33" t="n"/>
-      <c r="E88" s="33" t="n"/>
-      <c r="F88" s="33" t="n"/>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="34" t="inlineStr">
+      <c r="B95" s="33" t="n"/>
+      <c r="C95" s="33" t="n"/>
+      <c r="D95" s="33" t="n"/>
+      <c r="E95" s="33" t="n"/>
+      <c r="F95" s="33" t="n"/>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B89" s="35" t="n"/>
-      <c r="C89" s="35" t="n"/>
-      <c r="D89" s="35" t="n"/>
-      <c r="E89" s="35" t="n"/>
-      <c r="F89" s="35" t="n"/>
-    </row>
-    <row r="90" ht="192" customHeight="1">
-      <c r="A90" s="36" t="inlineStr">
+      <c r="B96" s="35" t="n"/>
+      <c r="C96" s="35" t="n"/>
+      <c r="D96" s="35" t="n"/>
+      <c r="E96" s="35" t="n"/>
+      <c r="F96" s="35" t="n"/>
+    </row>
+    <row r="97" ht="192" customHeight="1">
+      <c r="A97" s="36" t="inlineStr">
         <is>
           <t>원하는 색상의 립제품 만들기 좋은 립컬러 베이스가 나왔습니다.
 쉽게 활용하는 법을 안내해드립니다.
@@ -7402,20 +7503,20 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="34" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B91" s="35" t="n"/>
-      <c r="C91" s="35" t="n"/>
-      <c r="D91" s="35" t="n"/>
-      <c r="E91" s="35" t="n"/>
-      <c r="F91" s="35" t="n"/>
-    </row>
-    <row r="92" ht="96" customHeight="1">
-      <c r="A92" s="36" t="inlineStr">
+      <c r="B98" s="35" t="n"/>
+      <c r="C98" s="35" t="n"/>
+      <c r="D98" s="35" t="n"/>
+      <c r="E98" s="35" t="n"/>
+      <c r="F98" s="35" t="n"/>
+    </row>
+    <row r="99" ht="96" customHeight="1">
+      <c r="A99" s="36" t="inlineStr">
         <is>
           <t>1. (골든)호호바오일 4g을 먼저 계량합니다.
 2.원하는 립컬러 베이스를 비커에 발라주세요.
@@ -7425,269 +7526,289 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="6" customHeight="1"/>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="24" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B100" s="38" t="n"/>
+      <c r="C100" s="38" t="n"/>
+      <c r="D100" s="38" t="n"/>
+      <c r="E100" s="38" t="n"/>
+      <c r="F100" s="38" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 89%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 (골든)호호바오일(89%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="6" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="24" t="inlineStr">
         <is>
           <t>블루밍 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B94" s="25" t="n"/>
-      <c r="C94" s="25" t="n"/>
-      <c r="D94" s="25" t="n"/>
-      <c r="E94" s="25" t="n"/>
-      <c r="F94" s="25" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="26" t="inlineStr">
+      <c r="B103" s="25" t="n"/>
+      <c r="C103" s="25" t="n"/>
+      <c r="D103" s="25" t="n"/>
+      <c r="E103" s="25" t="n"/>
+      <c r="F103" s="25" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B95" s="26" t="inlineStr">
+      <c r="B104" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C95" s="26" t="inlineStr">
+      <c r="C104" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D95" s="26" t="inlineStr">
+      <c r="D104" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E95" s="26" t="inlineStr">
+      <c r="E104" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F95" s="26" t="inlineStr">
+      <c r="F104" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="32" customHeight="1">
-      <c r="A96" s="37" t="inlineStr">
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="40" t="inlineStr">
         <is>
           <t>발효 마유</t>
         </is>
       </c>
-      <c r="B96" s="37" t="inlineStr">
+      <c r="B105" s="40" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C96" s="38" t="inlineStr">
+      <c r="C105" s="41" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D96" s="41" t="inlineStr">
+      <c r="D105" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E96" s="37" t="inlineStr">
+      <c r="E105" s="40" t="inlineStr">
         <is>
           <t>오래가는 보습</t>
         </is>
       </c>
-      <c r="F96" s="37" t="inlineStr">
+      <c r="F105" s="40" t="inlineStr">
         <is>
           <t>동백, 아르간오일 등</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="48" customHeight="1">
-      <c r="A97" s="37" t="inlineStr">
+    <row r="106" ht="48" customHeight="1">
+      <c r="A106" s="40" t="inlineStr">
         <is>
           <t>피마자유</t>
         </is>
       </c>
-      <c r="B97" s="37" t="inlineStr">
+      <c r="B106" s="40" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C97" s="38" t="inlineStr">
+      <c r="C106" s="41" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D97" s="31" t="inlineStr">
+      <c r="D106" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E97" s="37" t="inlineStr">
+      <c r="E106" s="40" t="inlineStr">
         <is>
           <t>끈적, 오래가는 보습 · 아주까리유</t>
         </is>
       </c>
-      <c r="F97" s="37" t="inlineStr">
+      <c r="F106" s="40" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="64" customHeight="1">
-      <c r="A98" s="37" t="inlineStr">
+    <row r="107" ht="64" customHeight="1">
+      <c r="A107" s="40" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B98" s="37" t="inlineStr">
+      <c r="B107" s="40" t="inlineStr">
         <is>
           <t>0.1g</t>
         </is>
       </c>
-      <c r="C98" s="38" t="inlineStr">
+      <c r="C107" s="41" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D98" s="41" t="inlineStr">
+      <c r="D107" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E98" s="37" t="inlineStr">
+      <c r="E107" s="40" t="inlineStr">
         <is>
           <t>산화방지제</t>
         </is>
       </c>
-      <c r="F98" s="37" t="inlineStr">
+      <c r="F107" s="40" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="37" t="inlineStr">
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="40" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B99" s="37" t="inlineStr">
+      <c r="B108" s="40" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C99" s="38" t="inlineStr">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="D99" s="39" t="inlineStr">
+      <c r="D108" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E99" s="37" t="inlineStr">
+      <c r="E108" s="40" t="inlineStr">
         <is>
           <t>경화제</t>
         </is>
       </c>
-      <c r="F99" s="37" t="inlineStr">
+      <c r="F108" s="40" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="48" customHeight="1">
-      <c r="A100" s="37" t="inlineStr">
+    <row r="109" ht="48" customHeight="1">
+      <c r="A109" s="40" t="inlineStr">
         <is>
           <t>립 컬러베이스 / (액상)</t>
         </is>
       </c>
-      <c r="B100" s="37" t="inlineStr">
+      <c r="B109" s="40" t="inlineStr">
         <is>
           <t>4.5g</t>
         </is>
       </c>
-      <c r="C100" s="38" t="inlineStr">
+      <c r="C109" s="41" t="inlineStr">
         <is>
           <t>35%</t>
         </is>
       </c>
-      <c r="D100" s="29" t="inlineStr">
+      <c r="D109" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E100" s="37" t="inlineStr">
+      <c r="E109" s="40" t="inlineStr">
         <is>
           <t>미리 만들어놓으세요. · 호호바오일 4g · 원하는 립컬러베이스 0.5g · 상세 만들기 방법 참고</t>
         </is>
       </c>
-      <c r="F100" s="37" t="inlineStr">
+      <c r="F109" s="40" t="inlineStr">
         <is>
           <t>미리 만들어놓은 · 9가지 립컬러베이스 중 원하는 것</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="37" t="inlineStr">
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="40" t="inlineStr">
         <is>
           <t>로즈우드EO</t>
         </is>
       </c>
-      <c r="B101" s="37" t="inlineStr">
+      <c r="B110" s="40" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C101" s="38" t="inlineStr">
+      <c r="C110" s="41" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D101" s="30" t="inlineStr">
+      <c r="D110" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E101" s="37" t="inlineStr">
+      <c r="E110" s="40" t="inlineStr">
         <is>
           <t>향, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="F101" s="37" t="inlineStr">
+      <c r="F110" s="40" t="inlineStr">
         <is>
           <t>원하는에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="32" t="inlineStr">
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 35 · 경화 8 · 활성 16 · 향 2 · 기타 39</t>
         </is>
       </c>
-      <c r="B102" s="33" t="n"/>
-      <c r="C102" s="33" t="n"/>
-      <c r="D102" s="33" t="n"/>
-      <c r="E102" s="33" t="n"/>
-      <c r="F102" s="33" t="n"/>
-    </row>
-    <row r="103" ht="14" customHeight="1">
-      <c r="A103" s="34" t="inlineStr">
+      <c r="B111" s="33" t="n"/>
+      <c r="C111" s="33" t="n"/>
+      <c r="D111" s="33" t="n"/>
+      <c r="E111" s="33" t="n"/>
+      <c r="F111" s="33" t="n"/>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B103" s="35" t="n"/>
-      <c r="C103" s="35" t="n"/>
-      <c r="D103" s="35" t="n"/>
-      <c r="E103" s="35" t="n"/>
-      <c r="F103" s="35" t="n"/>
-    </row>
-    <row r="104" ht="112" customHeight="1">
-      <c r="A104" s="42" t="inlineStr">
+      <c r="B112" s="35" t="n"/>
+      <c r="C112" s="35" t="n"/>
+      <c r="D112" s="35" t="n"/>
+      <c r="E112" s="35" t="n"/>
+      <c r="F112" s="35" t="n"/>
+    </row>
+    <row r="113" ht="112" customHeight="1">
+      <c r="A113" s="45" t="inlineStr">
         <is>
           <t>위)달달한 핑크, 아래)갸우뚱 레드
 위)알쏭달쏭 핑크레드(27번+ 레드6) , 아래)단물 빠진 와인 (레드33)
@@ -7698,26 +7819,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B104" s="23" t="n"/>
-      <c r="C104" s="23" t="n"/>
-      <c r="D104" s="23" t="n"/>
-      <c r="E104" s="23" t="n"/>
-      <c r="F104" s="23" t="n"/>
-    </row>
-    <row r="105" ht="14" customHeight="1">
-      <c r="A105" s="34" t="inlineStr">
+      <c r="B113" s="23" t="n"/>
+      <c r="C113" s="23" t="n"/>
+      <c r="D113" s="23" t="n"/>
+      <c r="E113" s="23" t="n"/>
+      <c r="F113" s="23" t="n"/>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B105" s="35" t="n"/>
-      <c r="C105" s="35" t="n"/>
-      <c r="D105" s="35" t="n"/>
-      <c r="E105" s="35" t="n"/>
-      <c r="F105" s="35" t="n"/>
-    </row>
-    <row r="106" ht="160" customHeight="1">
-      <c r="A106" s="42" t="inlineStr">
+      <c r="B114" s="35" t="n"/>
+      <c r="C114" s="35" t="n"/>
+      <c r="D114" s="35" t="n"/>
+      <c r="E114" s="35" t="n"/>
+      <c r="F114" s="35" t="n"/>
+    </row>
+    <row r="115" ht="160" customHeight="1">
+      <c r="A115" s="45" t="inlineStr">
         <is>
           <t>1.미리 만들어놓은 색을 먼저 선택하세요. (달달한 핑크나
 2.잘익은 홍시 등 색상표를 참고해 만들어보세요.)
@@ -7730,163 +7851,176 @@
 9.용기에 담아서 속뚜껑 닫으면 완성~!</t>
         </is>
       </c>
-      <c r="B106" s="23" t="n"/>
-      <c r="C106" s="23" t="n"/>
-      <c r="D106" s="23" t="n"/>
-      <c r="E106" s="23" t="n"/>
-      <c r="F106" s="23" t="n"/>
-    </row>
-    <row r="107" ht="409" customHeight="1">
-      <c r="A107" s="23" t="n"/>
-      <c r="B107" s="23" t="n"/>
-      <c r="C107" s="23" t="n"/>
-      <c r="D107" s="23" t="n"/>
-      <c r="E107" s="23" t="n"/>
-      <c r="F107" s="23" t="n"/>
-    </row>
-    <row r="108" ht="6" customHeight="1">
-      <c r="A108" s="23" t="n"/>
-      <c r="B108" s="23" t="n"/>
-      <c r="C108" s="23" t="n"/>
-      <c r="D108" s="23" t="n"/>
-      <c r="E108" s="23" t="n"/>
-      <c r="F108" s="23" t="n"/>
-    </row>
-    <row r="109" ht="6" customHeight="1"/>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="24" t="inlineStr">
+      <c r="B115" s="23" t="n"/>
+      <c r="C115" s="23" t="n"/>
+      <c r="D115" s="23" t="n"/>
+      <c r="E115" s="23" t="n"/>
+      <c r="F115" s="23" t="n"/>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B116" s="38" t="n"/>
+      <c r="C116" s="38" t="n"/>
+      <c r="D116" s="38" t="n"/>
+      <c r="E116" s="38" t="n"/>
+      <c r="F116" s="38" t="n"/>
+    </row>
+    <row r="117" ht="45" customHeight="1">
+      <c r="A117" s="39" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 립 컬러베이스 / (액상)(35%)로 보습막·발림 설계.
+· 기능: 활성 합 16%(발효 마유 16%, 비타민E 1%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 2% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="356" customHeight="1">
+      <c r="A118" s="23" t="n"/>
+      <c r="B118" s="23" t="n"/>
+      <c r="C118" s="23" t="n"/>
+      <c r="D118" s="23" t="n"/>
+      <c r="E118" s="23" t="n"/>
+      <c r="F118" s="23" t="n"/>
+    </row>
+    <row r="119" ht="6" customHeight="1"/>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="24" t="inlineStr">
         <is>
           <t>촉촉 쁘띠 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B110" s="25" t="n"/>
-      <c r="C110" s="25" t="n"/>
-      <c r="D110" s="25" t="n"/>
-      <c r="E110" s="25" t="n"/>
-      <c r="F110" s="25" t="n"/>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="26" t="inlineStr">
+      <c r="B120" s="25" t="n"/>
+      <c r="C120" s="25" t="n"/>
+      <c r="D120" s="25" t="n"/>
+      <c r="E120" s="25" t="n"/>
+      <c r="F120" s="25" t="n"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B111" s="26" t="inlineStr">
+      <c r="B121" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C111" s="26" t="inlineStr">
+      <c r="C121" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D111" s="26" t="inlineStr">
+      <c r="D121" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E111" s="26" t="inlineStr">
+      <c r="E121" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F111" s="26" t="inlineStr">
+      <c r="F121" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="48" customHeight="1">
-      <c r="A112" s="27" t="inlineStr">
+    <row r="122" ht="48" customHeight="1">
+      <c r="A122" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B112" s="27" t="inlineStr">
+      <c r="B122" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C112" s="28" t="inlineStr">
+      <c r="C122" s="28" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D112" s="29" t="inlineStr">
+      <c r="D122" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E112" s="27" t="inlineStr">
+      <c r="E122" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F112" s="27" t="inlineStr">
+      <c r="F122" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="27" t="inlineStr">
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B113" s="27" t="inlineStr">
+      <c r="B123" s="27" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C113" s="28" t="inlineStr">
+      <c r="C123" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D113" s="30" t="inlineStr">
+      <c r="D123" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E113" s="27" t="inlineStr">
+      <c r="E123" s="27" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="F113" s="27" t="inlineStr">
+      <c r="F123" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="32" t="inlineStr">
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 95 · 향 5</t>
         </is>
       </c>
-      <c r="B114" s="33" t="n"/>
-      <c r="C114" s="33" t="n"/>
-      <c r="D114" s="33" t="n"/>
-      <c r="E114" s="33" t="n"/>
-      <c r="F114" s="33" t="n"/>
-    </row>
-    <row r="115" ht="14" customHeight="1">
-      <c r="A115" s="34" t="inlineStr">
+      <c r="B124" s="33" t="n"/>
+      <c r="C124" s="33" t="n"/>
+      <c r="D124" s="33" t="n"/>
+      <c r="E124" s="33" t="n"/>
+      <c r="F124" s="33" t="n"/>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B115" s="35" t="n"/>
-      <c r="C115" s="35" t="n"/>
-      <c r="D115" s="35" t="n"/>
-      <c r="E115" s="35" t="n"/>
-      <c r="F115" s="35" t="n"/>
-    </row>
-    <row r="116" ht="80" customHeight="1">
-      <c r="A116" s="36" t="inlineStr">
+      <c r="B125" s="35" t="n"/>
+      <c r="C125" s="35" t="n"/>
+      <c r="D125" s="35" t="n"/>
+      <c r="E125" s="35" t="n"/>
+      <c r="F125" s="35" t="n"/>
+    </row>
+    <row r="126" ht="80" customHeight="1">
+      <c r="A126" s="36" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -7896,20 +8030,20 @@
         </is>
       </c>
     </row>
-    <row r="117" ht="14" customHeight="1">
-      <c r="A117" s="34" t="inlineStr">
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B117" s="35" t="n"/>
-      <c r="C117" s="35" t="n"/>
-      <c r="D117" s="35" t="n"/>
-      <c r="E117" s="35" t="n"/>
-      <c r="F117" s="35" t="n"/>
-    </row>
-    <row r="118" ht="384" customHeight="1">
-      <c r="A118" s="36" t="inlineStr">
+      <c r="B127" s="35" t="n"/>
+      <c r="C127" s="35" t="n"/>
+      <c r="D127" s="35" t="n"/>
+      <c r="E127" s="35" t="n"/>
+      <c r="F127" s="35" t="n"/>
+    </row>
+    <row r="128" ht="384" customHeight="1">
+      <c r="A128" s="36" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -7936,142 +8070,163 @@
         </is>
       </c>
     </row>
-    <row r="119" ht="120.5" customHeight="1"/>
-    <row r="120" ht="6" customHeight="1"/>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="24" t="inlineStr">
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B129" s="38" t="n"/>
+      <c r="C129" s="38" t="n"/>
+      <c r="D129" s="38" t="n"/>
+      <c r="E129" s="38" t="n"/>
+      <c r="F129" s="38" t="n"/>
+    </row>
+    <row r="130" ht="45" customHeight="1">
+      <c r="A130" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 95%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 립스틱베이스(95%)로 보습막·발림 설계.
+· 마무리: 향 5% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="61.5" customHeight="1"/>
+    <row r="132" ht="6" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="24" t="inlineStr">
         <is>
           <t>픽미업 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B121" s="25" t="n"/>
-      <c r="C121" s="25" t="n"/>
-      <c r="D121" s="25" t="n"/>
-      <c r="E121" s="25" t="n"/>
-      <c r="F121" s="25" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="26" t="inlineStr">
+      <c r="B133" s="25" t="n"/>
+      <c r="C133" s="25" t="n"/>
+      <c r="D133" s="25" t="n"/>
+      <c r="E133" s="25" t="n"/>
+      <c r="F133" s="25" t="n"/>
+    </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B122" s="26" t="inlineStr">
+      <c r="B134" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C122" s="26" t="inlineStr">
+      <c r="C134" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D122" s="26" t="inlineStr">
+      <c r="D134" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E122" s="26" t="inlineStr">
+      <c r="E134" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F122" s="26" t="inlineStr">
+      <c r="F134" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="48" customHeight="1">
-      <c r="A123" s="37" t="inlineStr">
+    <row r="135" ht="48" customHeight="1">
+      <c r="A135" s="40" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B123" s="37" t="inlineStr">
+      <c r="B135" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C123" s="38" t="inlineStr">
+      <c r="C135" s="41" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D123" s="29" t="inlineStr">
+      <c r="D135" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E123" s="37" t="inlineStr">
+      <c r="E135" s="40" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F123" s="37" t="inlineStr">
+      <c r="F135" s="40" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="37" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="40" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B124" s="37" t="inlineStr">
+      <c r="B136" s="40" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C124" s="38" t="inlineStr">
+      <c r="C136" s="41" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D124" s="30" t="inlineStr">
+      <c r="D136" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E124" s="37" t="inlineStr">
+      <c r="E136" s="40" t="inlineStr">
         <is>
           <t>장미향이 나는 균형의 오일</t>
         </is>
       </c>
-      <c r="F124" s="37" t="inlineStr">
+      <c r="F136" s="40" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="32" t="inlineStr">
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 95 · 향 5</t>
         </is>
       </c>
-      <c r="B125" s="33" t="n"/>
-      <c r="C125" s="33" t="n"/>
-      <c r="D125" s="33" t="n"/>
-      <c r="E125" s="33" t="n"/>
-      <c r="F125" s="33" t="n"/>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="34" t="inlineStr">
+      <c r="B137" s="33" t="n"/>
+      <c r="C137" s="33" t="n"/>
+      <c r="D137" s="33" t="n"/>
+      <c r="E137" s="33" t="n"/>
+      <c r="F137" s="33" t="n"/>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B126" s="35" t="n"/>
-      <c r="C126" s="35" t="n"/>
-      <c r="D126" s="35" t="n"/>
-      <c r="E126" s="35" t="n"/>
-      <c r="F126" s="35" t="n"/>
-    </row>
-    <row r="127" ht="224" customHeight="1">
-      <c r="A127" s="42" t="inlineStr">
+      <c r="B138" s="35" t="n"/>
+      <c r="C138" s="35" t="n"/>
+      <c r="D138" s="35" t="n"/>
+      <c r="E138" s="35" t="n"/>
+      <c r="F138" s="35" t="n"/>
+    </row>
+    <row r="139" ht="224" customHeight="1">
+      <c r="A139" s="45" t="inlineStr">
         <is>
           <t>와인, 브라운, 오렌지...
 가을, 겨울에 잘 어울리는 색상을
@@ -8089,26 +8244,26 @@
 진하기를 조절하세요.</t>
         </is>
       </c>
-      <c r="B127" s="23" t="n"/>
-      <c r="C127" s="23" t="n"/>
-      <c r="D127" s="23" t="n"/>
-      <c r="E127" s="23" t="n"/>
-      <c r="F127" s="23" t="n"/>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="34" t="inlineStr">
+      <c r="B139" s="23" t="n"/>
+      <c r="C139" s="23" t="n"/>
+      <c r="D139" s="23" t="n"/>
+      <c r="E139" s="23" t="n"/>
+      <c r="F139" s="23" t="n"/>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B128" s="35" t="n"/>
-      <c r="C128" s="35" t="n"/>
-      <c r="D128" s="35" t="n"/>
-      <c r="E128" s="35" t="n"/>
-      <c r="F128" s="35" t="n"/>
-    </row>
-    <row r="129" ht="384" customHeight="1">
-      <c r="A129" s="42" t="inlineStr">
+      <c r="B140" s="35" t="n"/>
+      <c r="C140" s="35" t="n"/>
+      <c r="D140" s="35" t="n"/>
+      <c r="E140" s="35" t="n"/>
+      <c r="F140" s="35" t="n"/>
+    </row>
+    <row r="141" ht="384" customHeight="1">
+      <c r="A141" s="45" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -8134,247 +8289,268 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B129" s="23" t="n"/>
-      <c r="C129" s="23" t="n"/>
-      <c r="D129" s="23" t="n"/>
-      <c r="E129" s="23" t="n"/>
-      <c r="F129" s="23" t="n"/>
-    </row>
-    <row r="130" ht="122.0000000000007" customHeight="1">
-      <c r="A130" s="23" t="n"/>
-      <c r="B130" s="23" t="n"/>
-      <c r="C130" s="23" t="n"/>
-      <c r="D130" s="23" t="n"/>
-      <c r="E130" s="23" t="n"/>
-      <c r="F130" s="23" t="n"/>
-    </row>
-    <row r="131" ht="6" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="24" t="inlineStr">
+      <c r="B141" s="23" t="n"/>
+      <c r="C141" s="23" t="n"/>
+      <c r="D141" s="23" t="n"/>
+      <c r="E141" s="23" t="n"/>
+      <c r="F141" s="23" t="n"/>
+    </row>
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B142" s="38" t="n"/>
+      <c r="C142" s="38" t="n"/>
+      <c r="D142" s="38" t="n"/>
+      <c r="E142" s="38" t="n"/>
+      <c r="F142" s="38" t="n"/>
+    </row>
+    <row r="143" ht="45" customHeight="1">
+      <c r="A143" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 95%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 립스틱베이스(95%)로 보습막·발림 설계.
+· 마무리: 향 5% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="63" customHeight="1">
+      <c r="A144" s="23" t="n"/>
+      <c r="B144" s="23" t="n"/>
+      <c r="C144" s="23" t="n"/>
+      <c r="D144" s="23" t="n"/>
+      <c r="E144" s="23" t="n"/>
+      <c r="F144" s="23" t="n"/>
+    </row>
+    <row r="145" ht="6" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="24" t="inlineStr">
         <is>
           <t>생기ON~ 립스틱    [1. 립밤 베이스 / (52.5g)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B132" s="25" t="n"/>
-      <c r="C132" s="25" t="n"/>
-      <c r="D132" s="25" t="n"/>
-      <c r="E132" s="25" t="n"/>
-      <c r="F132" s="25" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="26" t="inlineStr">
+      <c r="B146" s="25" t="n"/>
+      <c r="C146" s="25" t="n"/>
+      <c r="D146" s="25" t="n"/>
+      <c r="E146" s="25" t="n"/>
+      <c r="F146" s="25" t="n"/>
+    </row>
+    <row r="147" ht="15" customHeight="1">
+      <c r="A147" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B133" s="26" t="inlineStr">
+      <c r="B147" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C133" s="26" t="inlineStr">
+      <c r="C147" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D133" s="26" t="inlineStr">
+      <c r="D147" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E133" s="26" t="inlineStr">
+      <c r="E147" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F133" s="26" t="inlineStr">
+      <c r="F147" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="48" customHeight="1">
-      <c r="A134" s="27" t="inlineStr">
+    <row r="148" ht="48" customHeight="1">
+      <c r="A148" s="27" t="inlineStr">
         <is>
           <t>자초립밤 / 오일 베이스</t>
         </is>
       </c>
-      <c r="B134" s="27" t="inlineStr">
+      <c r="B148" s="27" t="inlineStr">
         <is>
           <t>43g</t>
         </is>
       </c>
-      <c r="C134" s="28" t="inlineStr">
+      <c r="C148" s="28" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D134" s="29" t="inlineStr">
+      <c r="D148" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E134" s="27" t="inlineStr">
+      <c r="E148" s="27" t="inlineStr">
         <is>
           <t>자근추출물, 호호바오일, 아몬드오일, 피마자오일, 해바라기씨오일, 비타민E</t>
         </is>
       </c>
-      <c r="F134" s="27" t="inlineStr">
+      <c r="F148" s="27" t="inlineStr">
         <is>
           <t>자초인퓨즈오일, 원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="27" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="27" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B135" s="27" t="inlineStr">
+      <c r="B149" s="27" t="inlineStr">
         <is>
           <t>9.5g</t>
         </is>
       </c>
-      <c r="C135" s="28" t="inlineStr">
+      <c r="C149" s="28" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="D135" s="39" t="inlineStr">
+      <c r="D149" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E135" s="27" t="inlineStr">
+      <c r="E149" s="27" t="inlineStr">
         <is>
           <t>식물성 경화제</t>
         </is>
       </c>
-      <c r="F135" s="27" t="inlineStr">
+      <c r="F149" s="27" t="inlineStr">
         <is>
           <t>밀랍</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="27" t="inlineStr">
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="27" t="inlineStr">
         <is>
           <t>립밤 베이스</t>
         </is>
       </c>
-      <c r="B136" s="27" t="inlineStr">
+      <c r="B150" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C136" s="28" t="inlineStr">
+      <c r="C150" s="28" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D136" s="31" t="inlineStr">
+      <c r="D150" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E136" s="27" t="inlineStr">
+      <c r="E150" s="27" t="inlineStr">
         <is>
           <t>위의 레시피로 · 미리 만들것.</t>
         </is>
       </c>
-      <c r="F136" s="27" t="inlineStr">
+      <c r="F150" s="27" t="inlineStr">
         <is>
           <t>립스틱 베이스</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="27" t="inlineStr">
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="27" t="inlineStr">
         <is>
           <t>립 컬러 베이스</t>
         </is>
       </c>
-      <c r="B137" s="27" t="inlineStr">
+      <c r="B151" s="27" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C137" s="28" t="inlineStr">
+      <c r="C151" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D137" s="31" t="inlineStr">
+      <c r="D151" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E137" s="27" t="inlineStr">
+      <c r="E151" s="27" t="inlineStr">
         <is>
           <t>레드27 + 레드21</t>
         </is>
       </c>
-      <c r="F137" s="27" t="inlineStr">
+      <c r="F151" s="27" t="inlineStr">
         <is>
           <t>원하는 · 색상</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="27" t="inlineStr">
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="27" t="inlineStr">
         <is>
           <t>에센셜오일 (EO)</t>
         </is>
       </c>
-      <c r="B138" s="27" t="inlineStr">
+      <c r="B152" s="27" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C138" s="28" t="inlineStr">
+      <c r="C152" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D138" s="30" t="inlineStr">
+      <c r="D152" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E138" s="27" t="inlineStr"/>
-      <c r="F138" s="27" t="inlineStr">
+      <c r="E152" s="27" t="inlineStr"/>
+      <c r="F152" s="27" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="14" customHeight="1">
-      <c r="A139" s="32" t="inlineStr">
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 75 · 경화 17 · 향 0 · 기타 8</t>
         </is>
       </c>
-      <c r="B139" s="33" t="n"/>
-      <c r="C139" s="33" t="n"/>
-      <c r="D139" s="33" t="n"/>
-      <c r="E139" s="33" t="n"/>
-      <c r="F139" s="33" t="n"/>
-    </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="34" t="inlineStr">
+      <c r="B153" s="33" t="n"/>
+      <c r="C153" s="33" t="n"/>
+      <c r="D153" s="33" t="n"/>
+      <c r="E153" s="33" t="n"/>
+      <c r="F153" s="33" t="n"/>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B140" s="35" t="n"/>
-      <c r="C140" s="35" t="n"/>
-      <c r="D140" s="35" t="n"/>
-      <c r="E140" s="35" t="n"/>
-      <c r="F140" s="35" t="n"/>
-    </row>
-    <row r="141" ht="176" customHeight="1">
-      <c r="A141" s="36" t="inlineStr">
+      <c r="B154" s="35" t="n"/>
+      <c r="C154" s="35" t="n"/>
+      <c r="D154" s="35" t="n"/>
+      <c r="E154" s="35" t="n"/>
+      <c r="F154" s="35" t="n"/>
+    </row>
+    <row r="155" ht="176" customHeight="1">
+      <c r="A155" s="36" t="inlineStr">
         <is>
           <t>가볍고 촉촉한 자초립밤오일베이스로 립스틱들 만들어보세요.
 호호바오일, 피마자오일, 해바라기오일, 비타민E에
@@ -8390,20 +8566,20 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="34" t="inlineStr">
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B142" s="35" t="n"/>
-      <c r="C142" s="35" t="n"/>
-      <c r="D142" s="35" t="n"/>
-      <c r="E142" s="35" t="n"/>
-      <c r="F142" s="35" t="n"/>
-    </row>
-    <row r="143" ht="352" customHeight="1">
-      <c r="A143" s="36" t="inlineStr">
+      <c r="B156" s="35" t="n"/>
+      <c r="C156" s="35" t="n"/>
+      <c r="D156" s="35" t="n"/>
+      <c r="E156" s="35" t="n"/>
+      <c r="F156" s="35" t="n"/>
+    </row>
+    <row r="157" ht="352" customHeight="1">
+      <c r="A157" s="36" t="inlineStr">
         <is>
           <t>1.자초립밤오일베이스와 칸데릴라왁스를 계량한 후
 2. 섞으면서 녹입니다.
@@ -8430,454 +8606,473 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="8.500000000000028" customHeight="1"/>
-    <row r="145" ht="6" customHeight="1"/>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="24" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B158" s="38" t="n"/>
+      <c r="C158" s="38" t="n"/>
+      <c r="D158" s="38" t="n"/>
+      <c r="E158" s="38" t="n"/>
+      <c r="F158" s="38" t="n"/>
+    </row>
+    <row r="159" ht="30" customHeight="1">
+      <c r="A159" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 무수+경화 17% → 밤·스틱류. 왁스 비율이 굳기를 결정(늘리면 단단, 줄이면 말랑).
+· 베이스: 유상 중심, 주 오일 자초립밤 / 오일 베이스(75%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="6" customHeight="1"/>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="24" t="inlineStr">
         <is>
           <t>수딩썬로션    [오일/ / 유화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B146" s="25" t="n"/>
-      <c r="C146" s="25" t="n"/>
-      <c r="D146" s="25" t="n"/>
-      <c r="E146" s="25" t="n"/>
-      <c r="F146" s="25" t="n"/>
-    </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="26" t="inlineStr">
+      <c r="B161" s="25" t="n"/>
+      <c r="C161" s="25" t="n"/>
+      <c r="D161" s="25" t="n"/>
+      <c r="E161" s="25" t="n"/>
+      <c r="F161" s="25" t="n"/>
+    </row>
+    <row r="162" ht="15" customHeight="1">
+      <c r="A162" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B147" s="26" t="inlineStr">
+      <c r="B162" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C147" s="26" t="inlineStr">
+      <c r="C162" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D147" s="26" t="inlineStr">
+      <c r="D162" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E147" s="26" t="inlineStr">
+      <c r="E162" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F147" s="26" t="inlineStr">
+      <c r="F162" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="32" customHeight="1">
-      <c r="A148" s="37" t="inlineStr">
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="40" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B148" s="37" t="inlineStr">
+      <c r="B163" s="40" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C148" s="38" t="inlineStr">
+      <c r="C163" s="41" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="D148" s="29" t="inlineStr">
+      <c r="D163" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E148" s="37" t="inlineStr">
+      <c r="E163" s="40" t="inlineStr">
         <is>
           <t>금잔화 인퓨즈오일 · 민감, 트러블 피부</t>
         </is>
       </c>
-      <c r="F148" s="37" t="inlineStr">
+      <c r="F163" s="40" t="inlineStr">
         <is>
           <t>캐모마일 · 오일</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="48" customHeight="1">
-      <c r="A149" s="37" t="inlineStr">
+    <row r="164" ht="48" customHeight="1">
+      <c r="A164" s="40" t="inlineStr">
         <is>
           <t>올리브에스터오일</t>
         </is>
       </c>
-      <c r="B149" s="37" t="inlineStr">
+      <c r="B164" s="40" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C149" s="38" t="inlineStr">
+      <c r="C164" s="41" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D149" s="29" t="inlineStr">
+      <c r="D164" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E149" s="37" t="inlineStr">
+      <c r="E164" s="40" t="inlineStr">
         <is>
           <t>올리브오일유래, 초기사용감은 · 실리콘오일처럼 가볍지만 보습력지속</t>
         </is>
       </c>
-      <c r="F149" s="37" t="inlineStr">
+      <c r="F164" s="40" t="inlineStr">
         <is>
           <t>호호바</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="48" customHeight="1">
-      <c r="A150" s="37" t="inlineStr">
+    <row r="165" ht="48" customHeight="1">
+      <c r="A165" s="40" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B150" s="37" t="inlineStr">
+      <c r="B165" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C150" s="38" t="inlineStr">
+      <c r="C165" s="41" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D150" s="43" t="inlineStr">
+      <c r="D165" s="46" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E150" s="37" t="inlineStr">
+      <c r="E165" s="40" t="inlineStr">
         <is>
           <t>에코인증 · 물 · 오일분리 저지</t>
         </is>
       </c>
-      <c r="F150" s="37" t="inlineStr">
+      <c r="F165" s="40" t="inlineStr">
         <is>
           <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="37" t="inlineStr">
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="40" t="inlineStr">
         <is>
           <t>올리왁스LC</t>
         </is>
       </c>
-      <c r="B151" s="37" t="inlineStr">
+      <c r="B166" s="40" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C151" s="38" t="inlineStr">
+      <c r="C166" s="41" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D151" s="39" t="inlineStr">
+      <c r="D166" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E151" s="37" t="inlineStr">
+      <c r="E166" s="40" t="inlineStr">
         <is>
           <t>유화 보조제 · 백탁 현상 완화</t>
         </is>
       </c>
-      <c r="F151" s="37" t="inlineStr">
+      <c r="F166" s="40" t="inlineStr">
         <is>
           <t>세틸알콜</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="32" customHeight="1">
-      <c r="A152" s="37" t="inlineStr">
+    <row r="167" ht="32" customHeight="1">
+      <c r="A167" s="40" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B152" s="37" t="inlineStr">
+      <c r="B167" s="40" t="inlineStr">
         <is>
           <t>32g</t>
         </is>
       </c>
-      <c r="C152" s="38" t="inlineStr">
+      <c r="C167" s="41" t="inlineStr">
         <is>
           <t>32%</t>
         </is>
       </c>
-      <c r="D152" s="44" t="inlineStr">
+      <c r="D167" s="47" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E152" s="37" t="inlineStr">
+      <c r="E167" s="40" t="inlineStr">
         <is>
           <t>5차 필터링 · UV살균처리 정제수</t>
         </is>
       </c>
-      <c r="F152" s="37" t="inlineStr">
+      <c r="F167" s="40" t="inlineStr">
         <is>
           <t>원하는 · 플로럴워터</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="48" customHeight="1">
-      <c r="A153" s="37" t="inlineStr">
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="40" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B153" s="37" t="inlineStr">
+      <c r="B168" s="40" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C153" s="38" t="inlineStr">
+      <c r="C168" s="41" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D153" s="41" t="inlineStr">
+      <c r="D168" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E153" s="37" t="inlineStr">
+      <c r="E168" s="40" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은 · 수분감이 풍부한 겔</t>
         </is>
       </c>
-      <c r="F153" s="37" t="inlineStr">
+      <c r="F168" s="40" t="inlineStr">
         <is>
           <t>허브누리 베라겔 · 네롤리 · 플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="32" customHeight="1">
-      <c r="A154" s="37" t="inlineStr">
+    <row r="169" ht="32" customHeight="1">
+      <c r="A169" s="40" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
-      <c r="B154" s="37" t="inlineStr">
+      <c r="B169" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C154" s="38" t="inlineStr">
+      <c r="C169" s="41" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D154" s="41" t="inlineStr">
+      <c r="D169" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E154" s="37" t="inlineStr">
+      <c r="E169" s="40" t="inlineStr">
         <is>
           <t>고중저분자 · 트리플 히아루론산</t>
         </is>
       </c>
-      <c r="F154" s="37" t="inlineStr">
+      <c r="F169" s="40" t="inlineStr">
         <is>
           <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="48" customHeight="1">
-      <c r="A155" s="37" t="inlineStr">
+    <row r="170" ht="48" customHeight="1">
+      <c r="A170" s="40" t="inlineStr">
         <is>
           <t>수딩4 컴플렉스</t>
         </is>
       </c>
-      <c r="B155" s="37" t="inlineStr">
+      <c r="B170" s="40" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C155" s="38" t="inlineStr">
+      <c r="C170" s="41" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D155" s="41" t="inlineStr">
+      <c r="D170" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E155" s="37" t="inlineStr">
+      <c r="E170" s="40" t="inlineStr">
         <is>
           <t>알로에베라잎추출물, 참마뿌리추출물 · 흰목이버섯추출물, 미역추출물 복합추출물</t>
         </is>
       </c>
-      <c r="F155" s="37" t="inlineStr"/>
-    </row>
-    <row r="156" ht="64" customHeight="1">
-      <c r="A156" s="37" t="inlineStr">
+      <c r="F170" s="40" t="inlineStr"/>
+    </row>
+    <row r="171" ht="64" customHeight="1">
+      <c r="A171" s="40" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B156" s="37" t="inlineStr">
+      <c r="B171" s="40" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C156" s="38" t="inlineStr">
+      <c r="C171" s="41" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D156" s="45" t="inlineStr">
+      <c r="D171" s="48" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E156" s="37" t="inlineStr">
+      <c r="E171" s="40" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="F156" s="37" t="inlineStr">
+      <c r="F171" s="40" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (정제수의 양을 31g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="37" t="inlineStr">
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="40" t="inlineStr">
         <is>
           <t>징크옥사이드분산액</t>
         </is>
       </c>
-      <c r="B157" s="37" t="inlineStr">
+      <c r="B172" s="40" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C157" s="38" t="inlineStr">
+      <c r="C172" s="41" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D157" s="40" t="inlineStr">
+      <c r="D172" s="43" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E157" s="37" t="inlineStr">
+      <c r="E172" s="40" t="inlineStr">
         <is>
           <t>UV-A를 주로 난반사</t>
         </is>
       </c>
-      <c r="F157" s="37" t="inlineStr">
+      <c r="F172" s="40" t="inlineStr">
         <is>
           <t>칼라민파우더</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="37" t="inlineStr">
+    <row r="173" ht="32" customHeight="1">
+      <c r="A173" s="40" t="inlineStr">
         <is>
           <t>티타늄디옥사이드 / 분산액</t>
         </is>
       </c>
-      <c r="B158" s="37" t="inlineStr">
+      <c r="B173" s="40" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C158" s="38" t="inlineStr">
+      <c r="C173" s="41" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D158" s="40" t="inlineStr">
+      <c r="D173" s="43" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E158" s="37" t="inlineStr">
+      <c r="E173" s="40" t="inlineStr">
         <is>
           <t>자외선UV-B를 주로 난반사</t>
         </is>
       </c>
-      <c r="F158" s="37" t="inlineStr"/>
-    </row>
-    <row r="159" ht="48" customHeight="1">
-      <c r="A159" s="37" t="inlineStr">
+      <c r="F173" s="40" t="inlineStr"/>
+    </row>
+    <row r="174" ht="48" customHeight="1">
+      <c r="A174" s="40" t="inlineStr">
         <is>
           <t>베베보 블렌딩오일</t>
         </is>
       </c>
-      <c r="B159" s="37" t="inlineStr">
+      <c r="B174" s="40" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C159" s="38" t="inlineStr">
+      <c r="C174" s="41" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D159" s="29" t="inlineStr">
+      <c r="D174" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E159" s="37" t="inlineStr">
+      <c r="E174" s="40" t="inlineStr">
         <is>
           <t>라벤더. 만다린 로먼캐모마일 에센셜오일 · 민감피부를 위한 블렌딩</t>
         </is>
       </c>
-      <c r="F159" s="37" t="inlineStr">
+      <c r="F174" s="40" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="14" customHeight="1">
-      <c r="A160" s="32" t="inlineStr">
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 32 · 유상 17 · 유화 4 · 경화 2 · 활성 29 · 색소 15 · 방부 1</t>
         </is>
       </c>
-      <c r="B160" s="33" t="n"/>
-      <c r="C160" s="33" t="n"/>
-      <c r="D160" s="33" t="n"/>
-      <c r="E160" s="33" t="n"/>
-      <c r="F160" s="33" t="n"/>
-    </row>
-    <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="34" t="inlineStr">
+      <c r="B175" s="33" t="n"/>
+      <c r="C175" s="33" t="n"/>
+      <c r="D175" s="33" t="n"/>
+      <c r="E175" s="33" t="n"/>
+      <c r="F175" s="33" t="n"/>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B161" s="35" t="n"/>
-      <c r="C161" s="35" t="n"/>
-      <c r="D161" s="35" t="n"/>
-      <c r="E161" s="35" t="n"/>
-      <c r="F161" s="35" t="n"/>
-    </row>
-    <row r="162" ht="352" customHeight="1">
-      <c r="A162" s="42" t="inlineStr">
+      <c r="B176" s="35" t="n"/>
+      <c r="C176" s="35" t="n"/>
+      <c r="D176" s="35" t="n"/>
+      <c r="E176" s="35" t="n"/>
+      <c r="F176" s="35" t="n"/>
+    </row>
+    <row r="177" ht="352" customHeight="1">
+      <c r="A177" s="45" t="inlineStr">
         <is>
           <t>수딩썬로션
 (100g)
@@ -8903,26 +9098,26 @@
 우리 가족 안심 썬로션 만들기해보세요 .</t>
         </is>
       </c>
-      <c r="B162" s="23" t="n"/>
-      <c r="C162" s="23" t="n"/>
-      <c r="D162" s="23" t="n"/>
-      <c r="E162" s="23" t="n"/>
-      <c r="F162" s="23" t="n"/>
-    </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="34" t="inlineStr">
+      <c r="B177" s="23" t="n"/>
+      <c r="C177" s="23" t="n"/>
+      <c r="D177" s="23" t="n"/>
+      <c r="E177" s="23" t="n"/>
+      <c r="F177" s="23" t="n"/>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B163" s="35" t="n"/>
-      <c r="C163" s="35" t="n"/>
-      <c r="D163" s="35" t="n"/>
-      <c r="E163" s="35" t="n"/>
-      <c r="F163" s="35" t="n"/>
-    </row>
-    <row r="164" ht="112" customHeight="1">
-      <c r="A164" s="42" t="inlineStr">
+      <c r="B178" s="35" t="n"/>
+      <c r="C178" s="35" t="n"/>
+      <c r="D178" s="35" t="n"/>
+      <c r="E178" s="35" t="n"/>
+      <c r="F178" s="35" t="n"/>
+    </row>
+    <row r="179" ht="112" customHeight="1">
+      <c r="A179" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 2개의 비커에 오일/유화제, 워터를 계량합니다.
@@ -8933,175 +9128,198 @@
 6. 골고루 섞어주면 완성.</t>
         </is>
       </c>
-      <c r="B164" s="23" t="n"/>
-      <c r="C164" s="23" t="n"/>
-      <c r="D164" s="23" t="n"/>
-      <c r="E164" s="23" t="n"/>
-      <c r="F164" s="23" t="n"/>
-    </row>
-    <row r="165" ht="6" customHeight="1"/>
-    <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="24" t="inlineStr">
+      <c r="B179" s="23" t="n"/>
+      <c r="C179" s="23" t="n"/>
+      <c r="D179" s="23" t="n"/>
+      <c r="E179" s="23" t="n"/>
+      <c r="F179" s="23" t="n"/>
+    </row>
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B180" s="38" t="n"/>
+      <c r="C180" s="38" t="n"/>
+      <c r="D180" s="38" t="n"/>
+      <c r="E180" s="38" t="n"/>
+      <c r="F180" s="38" t="n"/>
+    </row>
+    <row r="181" ht="90" customHeight="1">
+      <c r="A181" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 유화 4% + 유상 17% → 로션~크림 경계 겨냥(유화제가 물·오일을 묶어 분리를 막음).
+· 베이스: 수상 32%(정제수 32%)가 제형의 뼈대·수분 공급.
+· 기능: 활성 합 29%(로즈플라워겔 15%, 수딩4 컴플렉스 10%, 다중 히아루론산 4%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="6" customHeight="1"/>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="24" t="inlineStr">
         <is>
           <t>레드 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B166" s="25" t="n"/>
-      <c r="C166" s="25" t="n"/>
-      <c r="D166" s="25" t="n"/>
-      <c r="E166" s="25" t="n"/>
-      <c r="F166" s="25" t="n"/>
-    </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="26" t="inlineStr">
+      <c r="B183" s="25" t="n"/>
+      <c r="C183" s="25" t="n"/>
+      <c r="D183" s="25" t="n"/>
+      <c r="E183" s="25" t="n"/>
+      <c r="F183" s="25" t="n"/>
+    </row>
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B167" s="26" t="inlineStr">
+      <c r="B184" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C167" s="26" t="inlineStr">
+      <c r="C184" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D167" s="26" t="inlineStr">
+      <c r="D184" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E167" s="26" t="inlineStr">
+      <c r="E184" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F167" s="26" t="inlineStr">
+      <c r="F184" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="48" customHeight="1">
-      <c r="A168" s="27" t="inlineStr">
+    <row r="185" ht="48" customHeight="1">
+      <c r="A185" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 / (불투명)</t>
         </is>
       </c>
-      <c r="B168" s="27" t="inlineStr">
+      <c r="B185" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C168" s="28" t="inlineStr">
+      <c r="C185" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D168" s="29" t="inlineStr">
+      <c r="D185" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E168" s="27" t="inlineStr">
+      <c r="E185" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F168" s="27" t="inlineStr">
+      <c r="F185" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="64" customHeight="1">
-      <c r="A169" s="27" t="inlineStr">
+    <row r="186" ht="64" customHeight="1">
+      <c r="A186" s="27" t="inlineStr">
         <is>
           <t>레드 립 컬러</t>
         </is>
       </c>
-      <c r="B169" s="27" t="inlineStr">
+      <c r="B186" s="27" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C169" s="28" t="inlineStr">
+      <c r="C186" s="28" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D169" s="31" t="inlineStr">
+      <c r="D186" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E169" s="27" t="inlineStr">
+      <c r="E186" s="27" t="inlineStr">
         <is>
           <t>레드21번 0.5g + 레드7번 0.2g+ 옐로우6번 0.1g+ 레드6번 0.2g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F169" s="27" t="inlineStr"/>
-    </row>
-    <row r="170" ht="32" customHeight="1">
-      <c r="A170" s="27" t="inlineStr">
+      <c r="F186" s="27" t="inlineStr"/>
+    </row>
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" s="27" t="inlineStr">
         <is>
           <t>브라이트닝블렌딩오일</t>
         </is>
       </c>
-      <c r="B170" s="27" t="inlineStr">
+      <c r="B187" s="27" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C170" s="28" t="inlineStr">
+      <c r="C187" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D170" s="29" t="inlineStr">
+      <c r="D187" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E170" s="27" t="inlineStr">
+      <c r="E187" s="27" t="inlineStr">
         <is>
           <t>네롤리, 프랑킨센스, 버가못EO 블렌딩</t>
         </is>
       </c>
-      <c r="F170" s="27" t="inlineStr">
+      <c r="F187" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="32" t="inlineStr">
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
-      <c r="B171" s="33" t="n"/>
-      <c r="C171" s="33" t="n"/>
-      <c r="D171" s="33" t="n"/>
-      <c r="E171" s="33" t="n"/>
-      <c r="F171" s="33" t="n"/>
-    </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="34" t="inlineStr">
+      <c r="B188" s="33" t="n"/>
+      <c r="C188" s="33" t="n"/>
+      <c r="D188" s="33" t="n"/>
+      <c r="E188" s="33" t="n"/>
+      <c r="F188" s="33" t="n"/>
+    </row>
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B172" s="35" t="n"/>
-      <c r="C172" s="35" t="n"/>
-      <c r="D172" s="35" t="n"/>
-      <c r="E172" s="35" t="n"/>
-      <c r="F172" s="35" t="n"/>
-    </row>
-    <row r="173" ht="224" customHeight="1">
-      <c r="A173" s="36" t="inlineStr">
+      <c r="B189" s="35" t="n"/>
+      <c r="C189" s="35" t="n"/>
+      <c r="D189" s="35" t="n"/>
+      <c r="E189" s="35" t="n"/>
+      <c r="F189" s="35" t="n"/>
+    </row>
+    <row r="190" ht="224" customHeight="1">
+      <c r="A190" s="36" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -9120,20 +9338,20 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="14" customHeight="1">
-      <c r="A174" s="34" t="inlineStr">
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B174" s="35" t="n"/>
-      <c r="C174" s="35" t="n"/>
-      <c r="D174" s="35" t="n"/>
-      <c r="E174" s="35" t="n"/>
-      <c r="F174" s="35" t="n"/>
-    </row>
-    <row r="175" ht="304" customHeight="1">
-      <c r="A175" s="36" t="inlineStr">
+      <c r="B191" s="35" t="n"/>
+      <c r="C191" s="35" t="n"/>
+      <c r="D191" s="35" t="n"/>
+      <c r="E191" s="35" t="n"/>
+      <c r="F191" s="35" t="n"/>
+    </row>
+    <row r="192" ht="304" customHeight="1">
+      <c r="A192" s="36" t="inlineStr">
         <is>
           <t>2.녹인 것을 캔용기에 부어서
 4. 굳히세요. 식히면 단단해집니다.
@@ -9156,170 +9374,190 @@
         </is>
       </c>
     </row>
-    <row r="176" ht="384.5" customHeight="1"/>
-    <row r="177" ht="6" customHeight="1"/>
-    <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="24" t="inlineStr">
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B193" s="38" t="n"/>
+      <c r="C193" s="38" t="n"/>
+      <c r="D193" s="38" t="n"/>
+      <c r="E193" s="38" t="n"/>
+      <c r="F193" s="38" t="n"/>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 81%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 립스틱베이스 / (불투명)(77%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="340.5" customHeight="1"/>
+    <row r="196" ht="6" customHeight="1"/>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="24" t="inlineStr">
         <is>
           <t>벚꽃 썸띵 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B178" s="25" t="n"/>
-      <c r="C178" s="25" t="n"/>
-      <c r="D178" s="25" t="n"/>
-      <c r="E178" s="25" t="n"/>
-      <c r="F178" s="25" t="n"/>
-    </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="26" t="inlineStr">
+      <c r="B197" s="25" t="n"/>
+      <c r="C197" s="25" t="n"/>
+      <c r="D197" s="25" t="n"/>
+      <c r="E197" s="25" t="n"/>
+      <c r="F197" s="25" t="n"/>
+    </row>
+    <row r="198" ht="15" customHeight="1">
+      <c r="A198" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B179" s="26" t="inlineStr">
+      <c r="B198" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C179" s="26" t="inlineStr">
+      <c r="C198" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D179" s="26" t="inlineStr">
+      <c r="D198" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E179" s="26" t="inlineStr">
+      <c r="E198" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F179" s="26" t="inlineStr">
+      <c r="F198" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="48" customHeight="1">
-      <c r="A180" s="37" t="inlineStr">
+    <row r="199" ht="48" customHeight="1">
+      <c r="A199" s="40" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B180" s="37" t="inlineStr">
+      <c r="B199" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C180" s="38" t="inlineStr">
+      <c r="C199" s="41" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D180" s="29" t="inlineStr">
+      <c r="D199" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E180" s="37" t="inlineStr">
+      <c r="E199" s="40" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F180" s="37" t="inlineStr">
+      <c r="F199" s="40" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="64" customHeight="1">
-      <c r="A181" s="37" t="inlineStr">
+    <row r="200" ht="64" customHeight="1">
+      <c r="A200" s="40" t="inlineStr">
         <is>
           <t>벚꽃 립 컬러</t>
         </is>
       </c>
-      <c r="B181" s="37" t="inlineStr">
+      <c r="B200" s="40" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C181" s="38" t="inlineStr">
+      <c r="C200" s="41" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D181" s="31" t="inlineStr">
+      <c r="D200" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E181" s="37" t="inlineStr">
+      <c r="E200" s="40" t="inlineStr">
         <is>
           <t>레드27번 0.3g + 레드40번 0.2g+ 아이론옐로우 0.1g+ 화이트 0.4g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F181" s="37" t="inlineStr"/>
-    </row>
-    <row r="182" ht="32" customHeight="1">
-      <c r="A182" s="37" t="inlineStr">
+      <c r="F200" s="40" t="inlineStr"/>
+    </row>
+    <row r="201" ht="32" customHeight="1">
+      <c r="A201" s="40" t="inlineStr">
         <is>
           <t>레몬쥬스블렌딩오일</t>
         </is>
       </c>
-      <c r="B182" s="37" t="inlineStr">
+      <c r="B201" s="40" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C182" s="38" t="inlineStr">
+      <c r="C201" s="41" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D182" s="29" t="inlineStr">
+      <c r="D201" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E182" s="37" t="inlineStr">
+      <c r="E201" s="40" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드 · 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F182" s="37" t="inlineStr">
+      <c r="F201" s="40" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="14" customHeight="1">
-      <c r="A183" s="32" t="inlineStr">
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
-      <c r="B183" s="33" t="n"/>
-      <c r="C183" s="33" t="n"/>
-      <c r="D183" s="33" t="n"/>
-      <c r="E183" s="33" t="n"/>
-      <c r="F183" s="33" t="n"/>
-    </row>
-    <row r="184" ht="14" customHeight="1">
-      <c r="A184" s="34" t="inlineStr">
+      <c r="B202" s="33" t="n"/>
+      <c r="C202" s="33" t="n"/>
+      <c r="D202" s="33" t="n"/>
+      <c r="E202" s="33" t="n"/>
+      <c r="F202" s="33" t="n"/>
+    </row>
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B184" s="35" t="n"/>
-      <c r="C184" s="35" t="n"/>
-      <c r="D184" s="35" t="n"/>
-      <c r="E184" s="35" t="n"/>
-      <c r="F184" s="35" t="n"/>
-    </row>
-    <row r="185" ht="192" customHeight="1">
-      <c r="A185" s="42" t="inlineStr">
+      <c r="B203" s="35" t="n"/>
+      <c r="C203" s="35" t="n"/>
+      <c r="D203" s="35" t="n"/>
+      <c r="E203" s="35" t="n"/>
+      <c r="F203" s="35" t="n"/>
+    </row>
+    <row r="204" ht="192" customHeight="1">
+      <c r="A204" s="45" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -9335,26 +9573,26 @@
 완성도 높은 립스틱 만들기해보세요.</t>
         </is>
       </c>
-      <c r="B185" s="23" t="n"/>
-      <c r="C185" s="23" t="n"/>
-      <c r="D185" s="23" t="n"/>
-      <c r="E185" s="23" t="n"/>
-      <c r="F185" s="23" t="n"/>
-    </row>
-    <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="34" t="inlineStr">
+      <c r="B204" s="23" t="n"/>
+      <c r="C204" s="23" t="n"/>
+      <c r="D204" s="23" t="n"/>
+      <c r="E204" s="23" t="n"/>
+      <c r="F204" s="23" t="n"/>
+    </row>
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B186" s="35" t="n"/>
-      <c r="C186" s="35" t="n"/>
-      <c r="D186" s="35" t="n"/>
-      <c r="E186" s="35" t="n"/>
-      <c r="F186" s="35" t="n"/>
-    </row>
-    <row r="187" ht="384" customHeight="1">
-      <c r="A187" s="42" t="inlineStr">
+      <c r="B205" s="35" t="n"/>
+      <c r="C205" s="35" t="n"/>
+      <c r="D205" s="35" t="n"/>
+      <c r="E205" s="35" t="n"/>
+      <c r="F205" s="35" t="n"/>
+    </row>
+    <row r="206" ht="384" customHeight="1">
+      <c r="A206" s="45" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -9381,183 +9619,203 @@
 18. 짜잔 매끈하게 몰드에서 분리됩니다. 완성.</t>
         </is>
       </c>
-      <c r="B187" s="23" t="n"/>
-      <c r="C187" s="23" t="n"/>
-      <c r="D187" s="23" t="n"/>
-      <c r="E187" s="23" t="n"/>
-      <c r="F187" s="23" t="n"/>
-    </row>
-    <row r="188" ht="336.5000000000001" customHeight="1">
-      <c r="A188" s="23" t="n"/>
-      <c r="B188" s="23" t="n"/>
-      <c r="C188" s="23" t="n"/>
-      <c r="D188" s="23" t="n"/>
-      <c r="E188" s="23" t="n"/>
-      <c r="F188" s="23" t="n"/>
-    </row>
-    <row r="189" ht="6" customHeight="1"/>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="24" t="inlineStr">
+      <c r="B206" s="23" t="n"/>
+      <c r="C206" s="23" t="n"/>
+      <c r="D206" s="23" t="n"/>
+      <c r="E206" s="23" t="n"/>
+      <c r="F206" s="23" t="n"/>
+    </row>
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B207" s="38" t="n"/>
+      <c r="C207" s="38" t="n"/>
+      <c r="D207" s="38" t="n"/>
+      <c r="E207" s="38" t="n"/>
+      <c r="F207" s="38" t="n"/>
+    </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 81%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 립스틱베이스(77%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="292.5" customHeight="1">
+      <c r="A209" s="23" t="n"/>
+      <c r="B209" s="23" t="n"/>
+      <c r="C209" s="23" t="n"/>
+      <c r="D209" s="23" t="n"/>
+      <c r="E209" s="23" t="n"/>
+      <c r="F209" s="23" t="n"/>
+    </row>
+    <row r="210" ht="6" customHeight="1"/>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="24" t="inlineStr">
         <is>
           <t>피치코랄 립스틱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B190" s="25" t="n"/>
-      <c r="C190" s="25" t="n"/>
-      <c r="D190" s="25" t="n"/>
-      <c r="E190" s="25" t="n"/>
-      <c r="F190" s="25" t="n"/>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="26" t="inlineStr">
+      <c r="B211" s="25" t="n"/>
+      <c r="C211" s="25" t="n"/>
+      <c r="D211" s="25" t="n"/>
+      <c r="E211" s="25" t="n"/>
+      <c r="F211" s="25" t="n"/>
+    </row>
+    <row r="212" ht="15" customHeight="1">
+      <c r="A212" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B191" s="26" t="inlineStr">
+      <c r="B212" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C191" s="26" t="inlineStr">
+      <c r="C212" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D191" s="26" t="inlineStr">
+      <c r="D212" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E191" s="26" t="inlineStr">
+      <c r="E212" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F191" s="26" t="inlineStr">
+      <c r="F212" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="48" customHeight="1">
-      <c r="A192" s="27" t="inlineStr">
+    <row r="213" ht="48" customHeight="1">
+      <c r="A213" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
-      <c r="B192" s="27" t="inlineStr">
+      <c r="B213" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C192" s="28" t="inlineStr">
+      <c r="C213" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D192" s="29" t="inlineStr">
+      <c r="D213" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E192" s="27" t="inlineStr">
+      <c r="E213" s="27" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서 · 사용해도 됩니다.</t>
         </is>
       </c>
-      <c r="F192" s="27" t="inlineStr">
+      <c r="F213" s="27" t="inlineStr">
         <is>
           <t>립스틱베이스 · (불투명)</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="64" customHeight="1">
-      <c r="A193" s="27" t="inlineStr">
+    <row r="214" ht="64" customHeight="1">
+      <c r="A214" s="27" t="inlineStr">
         <is>
           <t>피치코랄 립 컬러</t>
         </is>
       </c>
-      <c r="B193" s="27" t="inlineStr">
+      <c r="B214" s="27" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C193" s="28" t="inlineStr">
+      <c r="C214" s="28" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D193" s="31" t="inlineStr">
+      <c r="D214" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E193" s="27" t="inlineStr">
+      <c r="E214" s="27" t="inlineStr">
         <is>
           <t>레드6번 0.3g + 아이론옐로우 0.1g · + 레드27번 0.2g + 화이트 0.2g · 0.5g은 촉촉 · 1g은 좀더 매트 색상 색양 조절가능.</t>
         </is>
       </c>
-      <c r="F193" s="27" t="inlineStr"/>
-    </row>
-    <row r="194" ht="32" customHeight="1">
-      <c r="A194" s="27" t="inlineStr">
+      <c r="F214" s="27" t="inlineStr"/>
+    </row>
+    <row r="215" ht="32" customHeight="1">
+      <c r="A215" s="27" t="inlineStr">
         <is>
           <t>라임캔디 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B194" s="27" t="inlineStr">
+      <c r="B215" s="27" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C194" s="28" t="inlineStr">
+      <c r="C215" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D194" s="29" t="inlineStr">
+      <c r="D215" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E194" s="27" t="inlineStr">
+      <c r="E215" s="27" t="inlineStr">
         <is>
           <t>라임, 스윗오렌지, 레몬, 로즈마리 · 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F194" s="27" t="inlineStr">
+      <c r="F215" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="14" customHeight="1">
-      <c r="A195" s="32" t="inlineStr">
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 81 · 기타 19</t>
         </is>
       </c>
-      <c r="B195" s="33" t="n"/>
-      <c r="C195" s="33" t="n"/>
-      <c r="D195" s="33" t="n"/>
-      <c r="E195" s="33" t="n"/>
-      <c r="F195" s="33" t="n"/>
-    </row>
-    <row r="196" ht="14" customHeight="1">
-      <c r="A196" s="34" t="inlineStr">
+      <c r="B216" s="33" t="n"/>
+      <c r="C216" s="33" t="n"/>
+      <c r="D216" s="33" t="n"/>
+      <c r="E216" s="33" t="n"/>
+      <c r="F216" s="33" t="n"/>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B196" s="35" t="n"/>
-      <c r="C196" s="35" t="n"/>
-      <c r="D196" s="35" t="n"/>
-      <c r="E196" s="35" t="n"/>
-      <c r="F196" s="35" t="n"/>
-    </row>
-    <row r="197" ht="192" customHeight="1">
-      <c r="A197" s="36" t="inlineStr">
+      <c r="B217" s="35" t="n"/>
+      <c r="C217" s="35" t="n"/>
+      <c r="D217" s="35" t="n"/>
+      <c r="E217" s="35" t="n"/>
+      <c r="F217" s="35" t="n"/>
+    </row>
+    <row r="218" ht="192" customHeight="1">
+      <c r="A218" s="36" t="inlineStr">
         <is>
           <t>촉촉함은 기본, 컬러감까지 짱짱하게 살렸습니다.
 식물성오일로 만든 멀티밤오일베이스와 멀티왁스를
@@ -9574,20 +9832,20 @@
         </is>
       </c>
     </row>
-    <row r="198" ht="14" customHeight="1">
-      <c r="A198" s="34" t="inlineStr">
+    <row r="219" ht="14" customHeight="1">
+      <c r="A219" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B198" s="35" t="n"/>
-      <c r="C198" s="35" t="n"/>
-      <c r="D198" s="35" t="n"/>
-      <c r="E198" s="35" t="n"/>
-      <c r="F198" s="35" t="n"/>
-    </row>
-    <row r="199" ht="384" customHeight="1">
-      <c r="A199" s="36" t="inlineStr">
+      <c r="B219" s="35" t="n"/>
+      <c r="C219" s="35" t="n"/>
+      <c r="D219" s="35" t="n"/>
+      <c r="E219" s="35" t="n"/>
+      <c r="F219" s="35" t="n"/>
+    </row>
+    <row r="220" ht="384" customHeight="1">
+      <c r="A220" s="36" t="inlineStr">
         <is>
           <t>공통 만들기 과정
 [립스틱베이스 만들기]
@@ -9615,234 +9873,254 @@
         </is>
       </c>
     </row>
-    <row r="200" ht="336.5000000000001" customHeight="1"/>
-    <row r="201" ht="6" customHeight="1"/>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="24" t="inlineStr">
+    <row r="221" ht="14" customHeight="1">
+      <c r="A221" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B221" s="38" t="n"/>
+      <c r="C221" s="38" t="n"/>
+      <c r="D221" s="38" t="n"/>
+      <c r="E221" s="38" t="n"/>
+      <c r="F221" s="38" t="n"/>
+    </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 81%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 립스틱베이스(77%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="292.5" customHeight="1"/>
+    <row r="224" ht="6" customHeight="1"/>
+    <row r="225" ht="22" customHeight="1">
+      <c r="A225" s="24" t="inlineStr">
         <is>
           <t>워터리 립글로스    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B202" s="25" t="n"/>
-      <c r="C202" s="25" t="n"/>
-      <c r="D202" s="25" t="n"/>
-      <c r="E202" s="25" t="n"/>
-      <c r="F202" s="25" t="n"/>
-    </row>
-    <row r="203" ht="15" customHeight="1">
-      <c r="A203" s="26" t="inlineStr">
+      <c r="B225" s="25" t="n"/>
+      <c r="C225" s="25" t="n"/>
+      <c r="D225" s="25" t="n"/>
+      <c r="E225" s="25" t="n"/>
+      <c r="F225" s="25" t="n"/>
+    </row>
+    <row r="226" ht="15" customHeight="1">
+      <c r="A226" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B203" s="26" t="inlineStr">
+      <c r="B226" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C203" s="26" t="inlineStr">
+      <c r="C226" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D203" s="26" t="inlineStr">
+      <c r="D226" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E203" s="26" t="inlineStr">
+      <c r="E226" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F203" s="26" t="inlineStr">
+      <c r="F226" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="32" customHeight="1">
-      <c r="A204" s="37" t="inlineStr">
+    <row r="227" ht="32" customHeight="1">
+      <c r="A227" s="40" t="inlineStr">
         <is>
           <t>립밤베이스</t>
         </is>
       </c>
-      <c r="B204" s="37" t="inlineStr">
+      <c r="B227" s="40" t="inlineStr">
         <is>
           <t>4.6g</t>
         </is>
       </c>
-      <c r="C204" s="38" t="inlineStr">
+      <c r="C227" s="41" t="inlineStr">
         <is>
           <t>34%</t>
         </is>
       </c>
-      <c r="D204" s="29" t="inlineStr">
+      <c r="D227" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E204" s="37" t="inlineStr">
+      <c r="E227" s="40" t="inlineStr">
         <is>
           <t>멀티밤오일베이스 43g+ · 멀티왁스9.5g 로 미리 굳혀서</t>
         </is>
       </c>
-      <c r="F204" s="37" t="inlineStr">
+      <c r="F227" s="40" t="inlineStr">
         <is>
           <t>립스틱베이스</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="32" customHeight="1">
-      <c r="A205" s="37" t="inlineStr">
+    <row r="228" ht="32" customHeight="1">
+      <c r="A228" s="40" t="inlineStr">
         <is>
           <t>립 컬러</t>
         </is>
       </c>
-      <c r="B205" s="37" t="inlineStr">
+      <c r="B228" s="40" t="inlineStr">
         <is>
           <t>0.5~1g</t>
         </is>
       </c>
-      <c r="C205" s="38" t="inlineStr">
+      <c r="C228" s="41" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D205" s="31" t="inlineStr">
+      <c r="D228" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E205" s="37" t="inlineStr">
+      <c r="E228" s="40" t="inlineStr">
         <is>
           <t>색상사진은 아래의 · 립스틱 발색 사진과 처방 참고</t>
         </is>
       </c>
-      <c r="F205" s="37" t="inlineStr"/>
-    </row>
-    <row r="206" ht="32" customHeight="1">
-      <c r="A206" s="37" t="inlineStr">
+      <c r="F228" s="40" t="inlineStr"/>
+    </row>
+    <row r="229" ht="32" customHeight="1">
+      <c r="A229" s="40" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B206" s="37" t="inlineStr">
+      <c r="B229" s="40" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C206" s="38" t="inlineStr">
+      <c r="C229" s="41" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D206" s="29" t="inlineStr">
+      <c r="D229" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E206" s="37" t="inlineStr">
+      <c r="E229" s="40" t="inlineStr">
         <is>
           <t>피지성분과 비슷 · 가벼운 사용감</t>
         </is>
       </c>
-      <c r="F206" s="37" t="inlineStr">
+      <c r="F229" s="40" t="inlineStr">
         <is>
           <t>스위트아몬드오일 · 동백오일 등</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="48" customHeight="1">
-      <c r="A207" s="37" t="inlineStr">
+    <row r="230" ht="48" customHeight="1">
+      <c r="A230" s="40" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B207" s="37" t="inlineStr">
+      <c r="B230" s="40" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C207" s="38" t="inlineStr">
+      <c r="C230" s="41" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D207" s="29" t="inlineStr">
+      <c r="D230" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E207" s="37" t="inlineStr">
+      <c r="E230" s="40" t="inlineStr">
         <is>
           <t>오래가는 보습오일</t>
         </is>
       </c>
-      <c r="F207" s="37" t="inlineStr">
+      <c r="F230" s="40" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="48" customHeight="1">
-      <c r="A208" s="37" t="inlineStr">
+    <row r="231" ht="48" customHeight="1">
+      <c r="A231" s="40" t="inlineStr">
         <is>
           <t>로즈파워 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B208" s="37" t="inlineStr">
+      <c r="B231" s="40" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C208" s="38" t="inlineStr">
+      <c r="C231" s="41" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D208" s="29" t="inlineStr">
+      <c r="D231" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E208" s="37" t="inlineStr">
+      <c r="E231" s="40" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄, 로즈우드, 프랑킨센스 에센셜오일 블렌딩</t>
         </is>
       </c>
-      <c r="F208" s="37" t="inlineStr">
+      <c r="F231" s="40" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="14" customHeight="1">
-      <c r="A209" s="32" t="inlineStr">
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 94 · 기타 6</t>
         </is>
       </c>
-      <c r="B209" s="33" t="n"/>
-      <c r="C209" s="33" t="n"/>
-      <c r="D209" s="33" t="n"/>
-      <c r="E209" s="33" t="n"/>
-      <c r="F209" s="33" t="n"/>
-    </row>
-    <row r="210" ht="14" customHeight="1">
-      <c r="A210" s="34" t="inlineStr">
+      <c r="B232" s="33" t="n"/>
+      <c r="C232" s="33" t="n"/>
+      <c r="D232" s="33" t="n"/>
+      <c r="E232" s="33" t="n"/>
+      <c r="F232" s="33" t="n"/>
+    </row>
+    <row r="233" ht="14" customHeight="1">
+      <c r="A233" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B210" s="35" t="n"/>
-      <c r="C210" s="35" t="n"/>
-      <c r="D210" s="35" t="n"/>
-      <c r="E210" s="35" t="n"/>
-      <c r="F210" s="35" t="n"/>
-    </row>
-    <row r="211" ht="96" customHeight="1">
-      <c r="A211" s="42" t="inlineStr">
+      <c r="B233" s="35" t="n"/>
+      <c r="C233" s="35" t="n"/>
+      <c r="D233" s="35" t="n"/>
+      <c r="E233" s="35" t="n"/>
+      <c r="F233" s="35" t="n"/>
+    </row>
+    <row r="234" ht="96" customHeight="1">
+      <c r="A234" s="45" t="inlineStr">
         <is>
           <t>무제 문서
 워터리 립글로스는
@@ -9852,26 +10130,26 @@
 다양한 색상처방은 아래에서 참고하세요.</t>
         </is>
       </c>
-      <c r="B211" s="23" t="n"/>
-      <c r="C211" s="23" t="n"/>
-      <c r="D211" s="23" t="n"/>
-      <c r="E211" s="23" t="n"/>
-      <c r="F211" s="23" t="n"/>
-    </row>
-    <row r="212" ht="14" customHeight="1">
-      <c r="A212" s="34" t="inlineStr">
+      <c r="B234" s="23" t="n"/>
+      <c r="C234" s="23" t="n"/>
+      <c r="D234" s="23" t="n"/>
+      <c r="E234" s="23" t="n"/>
+      <c r="F234" s="23" t="n"/>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B212" s="35" t="n"/>
-      <c r="C212" s="35" t="n"/>
-      <c r="D212" s="35" t="n"/>
-      <c r="E212" s="35" t="n"/>
-      <c r="F212" s="35" t="n"/>
-    </row>
-    <row r="213" ht="192" customHeight="1">
-      <c r="A213" s="42" t="inlineStr">
+      <c r="B235" s="35" t="n"/>
+      <c r="C235" s="35" t="n"/>
+      <c r="D235" s="35" t="n"/>
+      <c r="E235" s="35" t="n"/>
+      <c r="F235" s="35" t="n"/>
+    </row>
+    <row r="236" ht="192" customHeight="1">
+      <c r="A236" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 [립밤베이스 만들기]
@@ -9887,143 +10165,163 @@
 9. 튜브나 립솔용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B213" s="23" t="n"/>
-      <c r="C213" s="23" t="n"/>
-      <c r="D213" s="23" t="n"/>
-      <c r="E213" s="23" t="n"/>
-      <c r="F213" s="23" t="n"/>
-    </row>
-    <row r="214" ht="6" customHeight="1"/>
-    <row r="215" ht="22" customHeight="1">
-      <c r="A215" s="24" t="inlineStr">
+      <c r="B236" s="23" t="n"/>
+      <c r="C236" s="23" t="n"/>
+      <c r="D236" s="23" t="n"/>
+      <c r="E236" s="23" t="n"/>
+      <c r="F236" s="23" t="n"/>
+    </row>
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B237" s="38" t="n"/>
+      <c r="C237" s="38" t="n"/>
+      <c r="D237" s="38" t="n"/>
+      <c r="E237" s="38" t="n"/>
+      <c r="F237" s="38" t="n"/>
+    </row>
+    <row r="238" ht="30" customHeight="1">
+      <c r="A238" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 94%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 피마자오일(37%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="6" customHeight="1"/>
+    <row r="240" ht="22" customHeight="1">
+      <c r="A240" s="24" t="inlineStr">
         <is>
           <t>커피헤나염색    ↗ 원본</t>
         </is>
       </c>
-      <c r="B215" s="25" t="n"/>
-      <c r="C215" s="25" t="n"/>
-      <c r="D215" s="25" t="n"/>
-      <c r="E215" s="25" t="n"/>
-      <c r="F215" s="25" t="n"/>
-    </row>
-    <row r="216" ht="15" customHeight="1">
-      <c r="A216" s="26" t="inlineStr">
+      <c r="B240" s="25" t="n"/>
+      <c r="C240" s="25" t="n"/>
+      <c r="D240" s="25" t="n"/>
+      <c r="E240" s="25" t="n"/>
+      <c r="F240" s="25" t="n"/>
+    </row>
+    <row r="241" ht="15" customHeight="1">
+      <c r="A241" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B216" s="26" t="inlineStr">
+      <c r="B241" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C216" s="26" t="inlineStr">
+      <c r="C241" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D216" s="26" t="inlineStr">
+      <c r="D241" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E216" s="26" t="inlineStr">
+      <c r="E241" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F216" s="26" t="inlineStr">
+      <c r="F241" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="27" t="inlineStr">
+    <row r="242" ht="16" customHeight="1">
+      <c r="A242" s="27" t="inlineStr">
         <is>
           <t>헤나분말</t>
         </is>
       </c>
-      <c r="B217" s="27" t="inlineStr">
+      <c r="B242" s="27" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C217" s="28" t="inlineStr">
+      <c r="C242" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D217" s="31" t="inlineStr">
+      <c r="D242" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E217" s="27" t="inlineStr">
+      <c r="E242" s="27" t="inlineStr">
         <is>
           <t>100% 헤나 분말</t>
         </is>
       </c>
-      <c r="F217" s="27" t="inlineStr"/>
-    </row>
-    <row r="218" ht="64" customHeight="1">
-      <c r="A218" s="27" t="inlineStr">
+      <c r="F242" s="27" t="inlineStr"/>
+    </row>
+    <row r="243" ht="64" customHeight="1">
+      <c r="A243" s="27" t="inlineStr">
         <is>
           <t>물</t>
         </is>
       </c>
-      <c r="B218" s="27" t="inlineStr">
+      <c r="B243" s="27" t="inlineStr">
         <is>
           <t>130g 내외</t>
         </is>
       </c>
-      <c r="C218" s="28" t="inlineStr">
+      <c r="C243" s="28" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="D218" s="44" t="inlineStr">
+      <c r="D243" s="47" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E218" s="27" t="inlineStr">
+      <c r="E243" s="27" t="inlineStr">
         <is>
           <t>맑은 물(정수기, 수돗물 등등)</t>
         </is>
       </c>
-      <c r="F218" s="27" t="inlineStr">
+      <c r="F243" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="14" customHeight="1">
-      <c r="A219" s="32" t="inlineStr">
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 76 · 기타 24</t>
         </is>
       </c>
-      <c r="B219" s="33" t="n"/>
-      <c r="C219" s="33" t="n"/>
-      <c r="D219" s="33" t="n"/>
-      <c r="E219" s="33" t="n"/>
-      <c r="F219" s="33" t="n"/>
-    </row>
-    <row r="220" ht="14" customHeight="1">
-      <c r="A220" s="34" t="inlineStr">
+      <c r="B244" s="33" t="n"/>
+      <c r="C244" s="33" t="n"/>
+      <c r="D244" s="33" t="n"/>
+      <c r="E244" s="33" t="n"/>
+      <c r="F244" s="33" t="n"/>
+    </row>
+    <row r="245" ht="14" customHeight="1">
+      <c r="A245" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B220" s="35" t="n"/>
-      <c r="C220" s="35" t="n"/>
-      <c r="D220" s="35" t="n"/>
-      <c r="E220" s="35" t="n"/>
-      <c r="F220" s="35" t="n"/>
-    </row>
-    <row r="221" ht="352" customHeight="1">
-      <c r="A221" s="36" t="inlineStr">
+      <c r="B245" s="35" t="n"/>
+      <c r="C245" s="35" t="n"/>
+      <c r="D245" s="35" t="n"/>
+      <c r="E245" s="35" t="n"/>
+      <c r="F245" s="35" t="n"/>
+    </row>
+    <row r="246" ht="352" customHeight="1">
+      <c r="A246" s="36" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -10049,20 +10347,20 @@
         </is>
       </c>
     </row>
-    <row r="222" ht="14" customHeight="1">
-      <c r="A222" s="34" t="inlineStr">
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B222" s="35" t="n"/>
-      <c r="C222" s="35" t="n"/>
-      <c r="D222" s="35" t="n"/>
-      <c r="E222" s="35" t="n"/>
-      <c r="F222" s="35" t="n"/>
-    </row>
-    <row r="223" ht="144" customHeight="1">
-      <c r="A223" s="36" t="inlineStr">
+      <c r="B247" s="35" t="n"/>
+      <c r="C247" s="35" t="n"/>
+      <c r="D247" s="35" t="n"/>
+      <c r="E247" s="35" t="n"/>
+      <c r="F247" s="35" t="n"/>
+    </row>
+    <row r="248" ht="144" customHeight="1">
+      <c r="A248" s="36" t="inlineStr">
         <is>
           <t>1. 염색 전 샴푸한 후 물기를 닦아주세요. 두피 피지와 오염물이 없으면 염색이 더 잘 됩니다.
 2. 인스턴트 커피 40~60g
@@ -10075,237 +10373,257 @@
         </is>
       </c>
     </row>
-    <row r="224" ht="6" customHeight="1"/>
-    <row r="225" ht="22" customHeight="1">
-      <c r="A225" s="24" t="inlineStr">
+    <row r="249" ht="14" customHeight="1">
+      <c r="A249" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B249" s="38" t="n"/>
+      <c r="C249" s="38" t="n"/>
+      <c r="D249" s="38" t="n"/>
+      <c r="E249" s="38" t="n"/>
+      <c r="F249" s="38" t="n"/>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 수상 76% 중심 → 토너·미스트·젤 등 수상 제형(오일 넣으려면 가용화 필요).
+· 베이스: 수상 76%(물 76%)가 제형의 뼈대·수분 공급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="6" customHeight="1"/>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="24" t="inlineStr">
         <is>
           <t>자초딸기립글로스(솔타입)    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B225" s="25" t="n"/>
-      <c r="C225" s="25" t="n"/>
-      <c r="D225" s="25" t="n"/>
-      <c r="E225" s="25" t="n"/>
-      <c r="F225" s="25" t="n"/>
-    </row>
-    <row r="226" ht="15" customHeight="1">
-      <c r="A226" s="26" t="inlineStr">
+      <c r="B252" s="25" t="n"/>
+      <c r="C252" s="25" t="n"/>
+      <c r="D252" s="25" t="n"/>
+      <c r="E252" s="25" t="n"/>
+      <c r="F252" s="25" t="n"/>
+    </row>
+    <row r="253" ht="15" customHeight="1">
+      <c r="A253" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B226" s="26" t="inlineStr">
+      <c r="B253" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C226" s="26" t="inlineStr">
+      <c r="C253" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D226" s="26" t="inlineStr">
+      <c r="D253" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E226" s="26" t="inlineStr">
+      <c r="E253" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F226" s="26" t="inlineStr">
+      <c r="F253" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="112" customHeight="1">
-      <c r="A227" s="37" t="inlineStr">
+    <row r="254" ht="112" customHeight="1">
+      <c r="A254" s="40" t="inlineStr">
         <is>
           <t>자초인퓨즈 / 호호바오일</t>
         </is>
       </c>
-      <c r="B227" s="37" t="inlineStr">
+      <c r="B254" s="40" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C227" s="38" t="inlineStr">
+      <c r="C254" s="41" t="inlineStr">
         <is>
           <t>29%</t>
         </is>
       </c>
-      <c r="D227" s="41" t="inlineStr">
+      <c r="D254" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E227" s="37" t="inlineStr">
+      <c r="E254" s="40" t="inlineStr">
         <is>
           <t>한약재, 자초, 지치의 뿌리, 자주색을 띈다하여 자초, 뿌리는 굵고 자주색, 오일에는 붉은 색이 우러나지만 알콜, 물에는 갈변합니다. 천연염색, 민간 약재로 사용, 호호바오일에 담궈서 유효성분을 우림</t>
         </is>
       </c>
-      <c r="F227" s="37" t="inlineStr">
+      <c r="F254" s="40" t="inlineStr">
         <is>
           <t>원하는 · 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="80" customHeight="1">
-      <c r="A228" s="37" t="inlineStr">
+    <row r="255" ht="80" customHeight="1">
+      <c r="A255" s="40" t="inlineStr">
         <is>
           <t>피마자오일</t>
         </is>
       </c>
-      <c r="B228" s="37" t="inlineStr">
+      <c r="B255" s="40" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C228" s="38" t="inlineStr">
+      <c r="C255" s="41" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D228" s="29" t="inlineStr">
+      <c r="D255" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E228" s="37" t="inlineStr">
+      <c r="E255" s="40" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F228" s="37" t="inlineStr">
+      <c r="F255" s="40" t="inlineStr">
         <is>
           <t>비타민E를 피마자오일양 중 일부로 대체</t>
         </is>
       </c>
     </row>
-    <row r="229" ht="48" customHeight="1">
-      <c r="A229" s="37" t="inlineStr">
+    <row r="256" ht="48" customHeight="1">
+      <c r="A256" s="40" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B229" s="37" t="inlineStr">
+      <c r="B256" s="40" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C229" s="38" t="inlineStr">
+      <c r="C256" s="41" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D229" s="29" t="inlineStr">
+      <c r="D256" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E229" s="37" t="inlineStr">
+      <c r="E256" s="40" t="inlineStr">
         <is>
           <t>식물성 버터, 카리테나무 열매에서 채취 · 보습효과짱^^</t>
         </is>
       </c>
-      <c r="F229" s="37" t="inlineStr">
+      <c r="F256" s="40" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="32" customHeight="1">
-      <c r="A230" s="37" t="inlineStr">
+    <row r="257" ht="32" customHeight="1">
+      <c r="A257" s="40" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B230" s="37" t="inlineStr">
+      <c r="B257" s="40" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C230" s="38" t="inlineStr">
+      <c r="C257" s="41" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D230" s="39" t="inlineStr">
+      <c r="D257" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E230" s="37" t="inlineStr">
+      <c r="E257" s="40" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취 · 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="F230" s="37" t="inlineStr">
+      <c r="F257" s="40" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="16" customHeight="1">
-      <c r="A231" s="37" t="inlineStr">
+    <row r="258" ht="16" customHeight="1">
+      <c r="A258" s="40" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B231" s="37" t="inlineStr">
+      <c r="B258" s="40" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C231" s="38" t="inlineStr">
+      <c r="C258" s="41" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D231" s="30" t="inlineStr">
+      <c r="D258" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E231" s="37" t="inlineStr">
+      <c r="E258" s="40" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="F231" s="37" t="inlineStr">
+      <c r="F258" s="40" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="14" customHeight="1">
-      <c r="A232" s="32" t="inlineStr">
+    <row r="259" ht="14" customHeight="1">
+      <c r="A259" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 65 · 경화 4 · 활성 29 · 향 2</t>
         </is>
       </c>
-      <c r="B232" s="33" t="n"/>
-      <c r="C232" s="33" t="n"/>
-      <c r="D232" s="33" t="n"/>
-      <c r="E232" s="33" t="n"/>
-      <c r="F232" s="33" t="n"/>
-    </row>
-    <row r="233" ht="14" customHeight="1">
-      <c r="A233" s="34" t="inlineStr">
+      <c r="B259" s="33" t="n"/>
+      <c r="C259" s="33" t="n"/>
+      <c r="D259" s="33" t="n"/>
+      <c r="E259" s="33" t="n"/>
+      <c r="F259" s="33" t="n"/>
+    </row>
+    <row r="260" ht="14" customHeight="1">
+      <c r="A260" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B233" s="35" t="n"/>
-      <c r="C233" s="35" t="n"/>
-      <c r="D233" s="35" t="n"/>
-      <c r="E233" s="35" t="n"/>
-      <c r="F233" s="35" t="n"/>
-    </row>
-    <row r="234" ht="288" customHeight="1">
-      <c r="A234" s="42" t="inlineStr">
+      <c r="B260" s="35" t="n"/>
+      <c r="C260" s="35" t="n"/>
+      <c r="D260" s="35" t="n"/>
+      <c r="E260" s="35" t="n"/>
+      <c r="F260" s="35" t="n"/>
+    </row>
+    <row r="261" ht="288" customHeight="1">
+      <c r="A261" s="45" t="inlineStr">
         <is>
           <t>2009년부터 만들기 시작한 자초인퓨즈오일로 만든 립밤이 있었죠.
 자초인퓨즈오일, 피마자오일, 시어버터, 칸데릴라왁스, 딸기플레이버오일로 만든 겁나게 촉촉한 립밤인데요
@@ -10323,26 +10641,26 @@
 5ml블랙캡립글로스</t>
         </is>
       </c>
-      <c r="B234" s="23" t="n"/>
-      <c r="C234" s="23" t="n"/>
-      <c r="D234" s="23" t="n"/>
-      <c r="E234" s="23" t="n"/>
-      <c r="F234" s="23" t="n"/>
-    </row>
-    <row r="235" ht="14" customHeight="1">
-      <c r="A235" s="34" t="inlineStr">
+      <c r="B261" s="23" t="n"/>
+      <c r="C261" s="23" t="n"/>
+      <c r="D261" s="23" t="n"/>
+      <c r="E261" s="23" t="n"/>
+      <c r="F261" s="23" t="n"/>
+    </row>
+    <row r="262" ht="14" customHeight="1">
+      <c r="A262" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B235" s="35" t="n"/>
-      <c r="C235" s="35" t="n"/>
-      <c r="D235" s="35" t="n"/>
-      <c r="E235" s="35" t="n"/>
-      <c r="F235" s="35" t="n"/>
-    </row>
-    <row r="236" ht="176" customHeight="1">
-      <c r="A236" s="42" t="inlineStr">
+      <c r="B262" s="35" t="n"/>
+      <c r="C262" s="35" t="n"/>
+      <c r="D262" s="35" t="n"/>
+      <c r="E262" s="35" t="n"/>
+      <c r="F262" s="35" t="n"/>
+    </row>
+    <row r="263" ht="176" customHeight="1">
+      <c r="A263" s="45" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -10354,267 +10672,290 @@
 3. 체에 걸러 낸 후 사용한다.</t>
         </is>
       </c>
-      <c r="B236" s="23" t="n"/>
-      <c r="C236" s="23" t="n"/>
-      <c r="D236" s="23" t="n"/>
-      <c r="E236" s="23" t="n"/>
-      <c r="F236" s="23" t="n"/>
-    </row>
-    <row r="237" ht="6" customHeight="1"/>
-    <row r="238" ht="22" customHeight="1">
-      <c r="A238" s="24" t="inlineStr">
+      <c r="B263" s="23" t="n"/>
+      <c r="C263" s="23" t="n"/>
+      <c r="D263" s="23" t="n"/>
+      <c r="E263" s="23" t="n"/>
+      <c r="F263" s="23" t="n"/>
+    </row>
+    <row r="264" ht="14" customHeight="1">
+      <c r="A264" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B264" s="38" t="n"/>
+      <c r="C264" s="38" t="n"/>
+      <c r="D264" s="38" t="n"/>
+      <c r="E264" s="38" t="n"/>
+      <c r="F264" s="38" t="n"/>
+    </row>
+    <row r="265" ht="75" customHeight="1">
+      <c r="A265" s="39" t="inlineStr">
+        <is>
+          <t>· 제형: 오일 65%(무수) → 페이스·바디오일. 방부 불필요·물 유입 금지.
+· 베이스: 유상 중심, 주 오일 피마자오일(51%)로 보습막·발림 설계.
+· 기능: 활성 합 29%(자초인퓨즈 / 호호바오일 29%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 2% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="6" customHeight="1"/>
+    <row r="267" ht="22" customHeight="1">
+      <c r="A267" s="24" t="inlineStr">
         <is>
           <t>레드(펄)립글로스    [1.베이스오일/경화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B238" s="25" t="n"/>
-      <c r="C238" s="25" t="n"/>
-      <c r="D238" s="25" t="n"/>
-      <c r="E238" s="25" t="n"/>
-      <c r="F238" s="25" t="n"/>
-    </row>
-    <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="26" t="inlineStr">
+      <c r="B267" s="25" t="n"/>
+      <c r="C267" s="25" t="n"/>
+      <c r="D267" s="25" t="n"/>
+      <c r="E267" s="25" t="n"/>
+      <c r="F267" s="25" t="n"/>
+    </row>
+    <row r="268" ht="15" customHeight="1">
+      <c r="A268" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B239" s="26" t="inlineStr">
+      <c r="B268" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C239" s="26" t="inlineStr">
+      <c r="C268" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D239" s="26" t="inlineStr">
+      <c r="D268" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E239" s="26" t="inlineStr">
+      <c r="E268" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F239" s="26" t="inlineStr">
+      <c r="F268" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="64" customHeight="1">
-      <c r="A240" s="27" t="inlineStr">
+    <row r="269" ht="64" customHeight="1">
+      <c r="A269" s="27" t="inlineStr">
         <is>
           <t>유기농아르간오일</t>
         </is>
       </c>
-      <c r="B240" s="27" t="inlineStr">
+      <c r="B269" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C240" s="28" t="inlineStr">
+      <c r="C269" s="28" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D240" s="29" t="inlineStr">
+      <c r="D269" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E240" s="27" t="inlineStr">
+      <c r="E269" s="27" t="inlineStr">
         <is>
           <t>전통적으로 모로코 원주민들의 치료와 섭생의 목적으로 사용, 모로코의 올리브오일, 천연비타민E풍부</t>
         </is>
       </c>
-      <c r="F240" s="27" t="inlineStr">
+      <c r="F269" s="27" t="inlineStr">
         <is>
           <t>원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="241" ht="80" customHeight="1">
-      <c r="A241" s="27" t="inlineStr">
+    <row r="270" ht="80" customHeight="1">
+      <c r="A270" s="27" t="inlineStr">
         <is>
           <t>(자초인퓨즈) / 피마자오일</t>
         </is>
       </c>
-      <c r="B241" s="27" t="inlineStr">
+      <c r="B270" s="27" t="inlineStr">
         <is>
           <t>9g</t>
         </is>
       </c>
-      <c r="C241" s="28" t="inlineStr">
+      <c r="C270" s="28" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D241" s="41" t="inlineStr">
+      <c r="D270" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E241" s="27" t="inlineStr">
+      <c r="E270" s="27" t="inlineStr">
         <is>
           <t>아주까리 종자에서 채취. 불포화도가 낮아 점성이 강함. 산소와 화합하기 어려워 공기 속에 방치하여도 건조하지 않은 오일로 립밤 등 입술에 많이 사용</t>
         </is>
       </c>
-      <c r="F241" s="27" t="inlineStr"/>
-    </row>
-    <row r="242" ht="64" customHeight="1">
-      <c r="A242" s="27" t="inlineStr">
+      <c r="F270" s="27" t="inlineStr"/>
+    </row>
+    <row r="271" ht="64" customHeight="1">
+      <c r="A271" s="27" t="inlineStr">
         <is>
           <t>코코아버터</t>
         </is>
       </c>
-      <c r="B242" s="27" t="inlineStr">
+      <c r="B271" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C242" s="28" t="inlineStr">
+      <c r="C271" s="28" t="inlineStr">
         <is>
           <t>11%</t>
         </is>
       </c>
-      <c r="D242" s="29" t="inlineStr">
+      <c r="D271" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E242" s="27" t="inlineStr">
+      <c r="E271" s="27" t="inlineStr">
         <is>
           <t>알려진 오일 중 가장 안정적인 것 중 하나 자연적인 산화방지제가 들어있어 산패를 막아주며 부드러운 향, 촉감제공</t>
         </is>
       </c>
-      <c r="F242" s="27" t="inlineStr">
+      <c r="F271" s="27" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="32" customHeight="1">
-      <c r="A243" s="27" t="inlineStr">
+    <row r="272" ht="32" customHeight="1">
+      <c r="A272" s="27" t="inlineStr">
         <is>
           <t>칸데릴라왁스</t>
         </is>
       </c>
-      <c r="B243" s="27" t="inlineStr">
+      <c r="B272" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C243" s="28" t="inlineStr">
+      <c r="C272" s="28" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D243" s="39" t="inlineStr">
+      <c r="D272" s="42" t="inlineStr">
         <is>
           <t>경화</t>
         </is>
       </c>
-      <c r="E243" s="27" t="inlineStr">
+      <c r="E272" s="27" t="inlineStr">
         <is>
           <t>칸데릴라라는 식물에서 채취, 단단하게 굳히는 역할</t>
         </is>
       </c>
-      <c r="F243" s="27" t="inlineStr">
+      <c r="F272" s="27" t="inlineStr">
         <is>
           <t>밀랍, 유기농밀랍</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="32" customHeight="1">
-      <c r="A244" s="27" t="inlineStr">
+    <row r="273" ht="32" customHeight="1">
+      <c r="A273" s="27" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B244" s="27" t="inlineStr">
+      <c r="B273" s="27" t="inlineStr">
         <is>
           <t>9방울</t>
         </is>
       </c>
-      <c r="C244" s="28" t="inlineStr">
+      <c r="C273" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D244" s="30" t="inlineStr">
+      <c r="D273" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E244" s="27" t="inlineStr">
+      <c r="E273" s="27" t="inlineStr">
         <is>
           <t>합성 딸기식향</t>
         </is>
       </c>
-      <c r="F244" s="27" t="inlineStr">
+      <c r="F273" s="27" t="inlineStr">
         <is>
           <t>원하는 플레이버오일, 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="32" customHeight="1">
-      <c r="A245" s="27" t="inlineStr">
+    <row r="274" ht="32" customHeight="1">
+      <c r="A274" s="27" t="inlineStr">
         <is>
           <t>실버펄</t>
         </is>
       </c>
-      <c r="B245" s="27" t="inlineStr">
+      <c r="B274" s="27" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C245" s="28" t="inlineStr">
+      <c r="C274" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D245" s="40" t="inlineStr">
+      <c r="D274" s="43" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E245" s="27" t="inlineStr">
+      <c r="E274" s="27" t="inlineStr">
         <is>
           <t>글로시한 느낌 · 기호에 맞게 조절, 넣지 않아도 됨</t>
         </is>
       </c>
-      <c r="F245" s="27" t="inlineStr"/>
-    </row>
-    <row r="246" ht="14" customHeight="1">
-      <c r="A246" s="32" t="inlineStr">
+      <c r="F274" s="27" t="inlineStr"/>
+    </row>
+    <row r="275" ht="14" customHeight="1">
+      <c r="A275" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 39 · 경화 6 · 활성 51 · 향 3 · 색소 2</t>
         </is>
       </c>
-      <c r="B246" s="33" t="n"/>
-      <c r="C246" s="33" t="n"/>
-      <c r="D246" s="33" t="n"/>
-      <c r="E246" s="33" t="n"/>
-      <c r="F246" s="33" t="n"/>
-    </row>
-    <row r="247" ht="14" customHeight="1">
-      <c r="A247" s="34" t="inlineStr">
+      <c r="B275" s="33" t="n"/>
+      <c r="C275" s="33" t="n"/>
+      <c r="D275" s="33" t="n"/>
+      <c r="E275" s="33" t="n"/>
+      <c r="F275" s="33" t="n"/>
+    </row>
+    <row r="276" ht="14" customHeight="1">
+      <c r="A276" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B247" s="35" t="n"/>
-      <c r="C247" s="35" t="n"/>
-      <c r="D247" s="35" t="n"/>
-      <c r="E247" s="35" t="n"/>
-      <c r="F247" s="35" t="n"/>
-    </row>
-    <row r="248" ht="192" customHeight="1">
-      <c r="A248" s="36" t="inlineStr">
+      <c r="B276" s="35" t="n"/>
+      <c r="C276" s="35" t="n"/>
+      <c r="D276" s="35" t="n"/>
+      <c r="E276" s="35" t="n"/>
+      <c r="F276" s="35" t="n"/>
+    </row>
+    <row r="277" ht="192" customHeight="1">
+      <c r="A277" s="36" t="inlineStr">
         <is>
           <t>입술에 영양과 윤기를 동시에 줄 수 있는립글로스입니다.
 튜브용기에 넣어서 사용하기 더욱 더 간편하게 만들어봤어요.
@@ -10631,20 +10972,20 @@
         </is>
       </c>
     </row>
-    <row r="249" ht="14" customHeight="1">
-      <c r="A249" s="34" t="inlineStr">
+    <row r="278" ht="14" customHeight="1">
+      <c r="A278" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B249" s="35" t="n"/>
-      <c r="C249" s="35" t="n"/>
-      <c r="D249" s="35" t="n"/>
-      <c r="E249" s="35" t="n"/>
-      <c r="F249" s="35" t="n"/>
-    </row>
-    <row r="250" ht="160" customHeight="1">
-      <c r="A250" s="36" t="inlineStr">
+      <c r="B278" s="35" t="n"/>
+      <c r="C278" s="35" t="n"/>
+      <c r="D278" s="35" t="n"/>
+      <c r="E278" s="35" t="n"/>
+      <c r="F278" s="35" t="n"/>
+    </row>
+    <row r="279" ht="160" customHeight="1">
+      <c r="A279" s="36" t="inlineStr">
         <is>
           <t>만들기과정
 1.①재료를 계량한 후 스푼으로 저으면서 녹인다.
@@ -10657,265 +10998,287 @@
         </is>
       </c>
     </row>
-    <row r="251" ht="6" customHeight="1"/>
-    <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="24" t="inlineStr">
+    <row r="280" ht="14" customHeight="1">
+      <c r="A280" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B280" s="38" t="n"/>
+      <c r="C280" s="38" t="n"/>
+      <c r="D280" s="38" t="n"/>
+      <c r="E280" s="38" t="n"/>
+      <c r="F280" s="38" t="n"/>
+    </row>
+    <row r="281" ht="60" customHeight="1">
+      <c r="A281" s="39" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 유기농아르간오일(28%)로 보습막·발림 설계.
+· 기능: 활성 합 51%((자초인퓨즈) / 피마자오일 51%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 3% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="6" customHeight="1"/>
+    <row r="283" ht="22" customHeight="1">
+      <c r="A283" s="24" t="inlineStr">
         <is>
           <t>진주 피지컨트롤 파우더    [진주 / 피지컨트롤 / 파우더]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B252" s="25" t="n"/>
-      <c r="C252" s="25" t="n"/>
-      <c r="D252" s="25" t="n"/>
-      <c r="E252" s="25" t="n"/>
-      <c r="F252" s="25" t="n"/>
-    </row>
-    <row r="253" ht="15" customHeight="1">
-      <c r="A253" s="26" t="inlineStr">
+      <c r="B283" s="25" t="n"/>
+      <c r="C283" s="25" t="n"/>
+      <c r="D283" s="25" t="n"/>
+      <c r="E283" s="25" t="n"/>
+      <c r="F283" s="25" t="n"/>
+    </row>
+    <row r="284" ht="15" customHeight="1">
+      <c r="A284" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B253" s="26" t="inlineStr">
+      <c r="B284" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C253" s="26" t="inlineStr">
+      <c r="C284" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D253" s="26" t="inlineStr">
+      <c r="D284" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E253" s="26" t="inlineStr">
+      <c r="E284" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F253" s="26" t="inlineStr">
+      <c r="F284" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="32" customHeight="1">
-      <c r="A254" s="37" t="inlineStr">
+    <row r="285" ht="32" customHeight="1">
+      <c r="A285" s="40" t="inlineStr">
         <is>
           <t>진주분말</t>
         </is>
       </c>
-      <c r="B254" s="37" t="inlineStr">
+      <c r="B285" s="40" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C254" s="38" t="inlineStr">
+      <c r="C285" s="41" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D254" s="41" t="inlineStr">
+      <c r="D285" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E254" s="37" t="inlineStr">
+      <c r="E285" s="40" t="inlineStr">
         <is>
           <t>진주분말, 미네럴 공급, 피지컨트롤</t>
         </is>
       </c>
-      <c r="F254" s="37" t="inlineStr"/>
-    </row>
-    <row r="255" ht="96" customHeight="1">
-      <c r="A255" s="37" t="inlineStr">
+      <c r="F285" s="40" t="inlineStr"/>
+    </row>
+    <row r="286" ht="96" customHeight="1">
+      <c r="A286" s="40" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B255" s="37" t="inlineStr">
+      <c r="B286" s="40" t="inlineStr">
         <is>
           <t>29g</t>
         </is>
       </c>
-      <c r="C255" s="38" t="inlineStr">
+      <c r="C286" s="41" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="D255" s="31" t="inlineStr">
+      <c r="D286" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E255" s="37" t="inlineStr">
+      <c r="E286" s="40" t="inlineStr">
         <is>
           <t>피지흡착, 뽀송뽀송</t>
         </is>
       </c>
-      <c r="F255" s="37" t="inlineStr">
+      <c r="F286" s="40" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="48" customHeight="1">
-      <c r="A256" s="37" t="inlineStr">
+    <row r="287" ht="48" customHeight="1">
+      <c r="A287" s="40" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B256" s="37" t="inlineStr">
+      <c r="B287" s="40" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C256" s="38" t="inlineStr">
+      <c r="C287" s="41" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D256" s="41" t="inlineStr">
+      <c r="D287" s="44" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E256" s="37" t="inlineStr">
+      <c r="E287" s="40" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F256" s="37" t="inlineStr">
+      <c r="F287" s="40" t="inlineStr">
         <is>
           <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="257" ht="48" customHeight="1">
-      <c r="A257" s="37" t="inlineStr">
+    <row r="288" ht="48" customHeight="1">
+      <c r="A288" s="40" t="inlineStr">
         <is>
           <t>로즈제라늄 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B257" s="37" t="inlineStr">
+      <c r="B288" s="40" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C257" s="38" t="inlineStr">
+      <c r="C288" s="41" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D257" s="30" t="inlineStr">
+      <c r="D288" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E257" s="37" t="inlineStr">
+      <c r="E288" s="40" t="inlineStr">
         <is>
           <t>고가의 장미오일은 아니지만 장미향이 나는 제라늄. 모든 피부 사용. 피지조절</t>
         </is>
       </c>
-      <c r="F257" s="37" t="inlineStr">
+      <c r="F288" s="40" t="inlineStr">
         <is>
           <t>원하는 에센셜오일.</t>
         </is>
       </c>
     </row>
-    <row r="258" ht="96" customHeight="1">
-      <c r="A258" s="37" t="inlineStr">
+    <row r="289" ht="96" customHeight="1">
+      <c r="A289" s="40" t="inlineStr">
         <is>
           <t>카오링클레이</t>
         </is>
       </c>
-      <c r="B258" s="37" t="inlineStr">
+      <c r="B289" s="40" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C258" s="38" t="inlineStr">
+      <c r="C289" s="41" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D258" s="40" t="inlineStr">
+      <c r="D289" s="43" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E258" s="37" t="inlineStr">
+      <c r="E289" s="40" t="inlineStr">
         <is>
           <t>중국 고령이 원산지인 클레이, 영어발음은 카오링, 현재 세계 다양한 지역에 분포, 채취. 미네럴공급, 화장품, 제약, 식품 등 다양한 용도로 사용됨. 피지컨트롤</t>
         </is>
       </c>
-      <c r="F258" s="37" t="inlineStr">
+      <c r="F289" s="40" t="inlineStr">
         <is>
           <t>화이트클레이</t>
         </is>
       </c>
     </row>
-    <row r="259" ht="64" customHeight="1">
-      <c r="A259" s="37" t="inlineStr">
+    <row r="290" ht="64" customHeight="1">
+      <c r="A290" s="40" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B259" s="37" t="inlineStr">
+      <c r="B290" s="40" t="inlineStr">
         <is>
           <t>4방울</t>
         </is>
       </c>
-      <c r="C259" s="38" t="inlineStr">
+      <c r="C290" s="41" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D259" s="30" t="inlineStr">
+      <c r="D290" s="30" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E259" s="37" t="inlineStr">
+      <c r="E290" s="40" t="inlineStr">
         <is>
           <t>진정, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="F259" s="37" t="inlineStr">
+      <c r="F290" s="40" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="260" ht="14" customHeight="1">
-      <c r="A260" s="32" t="inlineStr">
+    <row r="291" ht="14" customHeight="1">
+      <c r="A291" s="32" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 18 · 향 1 · 색소 16 · 기타 65</t>
         </is>
       </c>
-      <c r="B260" s="33" t="n"/>
-      <c r="C260" s="33" t="n"/>
-      <c r="D260" s="33" t="n"/>
-      <c r="E260" s="33" t="n"/>
-      <c r="F260" s="33" t="n"/>
-    </row>
-    <row r="261" ht="14" customHeight="1">
-      <c r="A261" s="34" t="inlineStr">
+      <c r="B291" s="33" t="n"/>
+      <c r="C291" s="33" t="n"/>
+      <c r="D291" s="33" t="n"/>
+      <c r="E291" s="33" t="n"/>
+      <c r="F291" s="33" t="n"/>
+    </row>
+    <row r="292" ht="14" customHeight="1">
+      <c r="A292" s="34" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B261" s="35" t="n"/>
-      <c r="C261" s="35" t="n"/>
-      <c r="D261" s="35" t="n"/>
-      <c r="E261" s="35" t="n"/>
-      <c r="F261" s="35" t="n"/>
-    </row>
-    <row r="262" ht="384" customHeight="1">
-      <c r="A262" s="42" t="inlineStr">
+      <c r="B292" s="35" t="n"/>
+      <c r="C292" s="35" t="n"/>
+      <c r="D292" s="35" t="n"/>
+      <c r="E292" s="35" t="n"/>
+      <c r="F292" s="35" t="n"/>
+    </row>
+    <row r="293" ht="384" customHeight="1">
+      <c r="A293" s="45" t="inlineStr">
         <is>
           <t>여름이면 저에게 고민이 하나 생기는데요..
 오전에는 괜찮지만 오후가 되면 번들녀로 변합니다. (변신~)
@@ -10940,14 +11303,14 @@
 허준 선생이 동의보감에 기술한 진주(珍珠)의 효능을 보면</t>
         </is>
       </c>
-      <c r="B262" s="23" t="n"/>
-      <c r="C262" s="23" t="n"/>
-      <c r="D262" s="23" t="n"/>
-      <c r="E262" s="23" t="n"/>
-      <c r="F262" s="23" t="n"/>
-    </row>
-    <row r="263" ht="208" customHeight="1">
-      <c r="A263" s="42" t="inlineStr">
+      <c r="B293" s="23" t="n"/>
+      <c r="C293" s="23" t="n"/>
+      <c r="D293" s="23" t="n"/>
+      <c r="E293" s="23" t="n"/>
+      <c r="F293" s="23" t="n"/>
+    </row>
+    <row r="294" ht="208" customHeight="1">
+      <c r="A294" s="45" t="inlineStr">
         <is>
           <t>"진주가루를 유즙(乳汁)에 섞어 바르면 검은 반점을 제거하며, 얼굴을 윤기나게하여 안색을 좋게한다.",
 "진주는 성질이 차고 무독(無毒)하여 심신을 평안케하며 눈을 밝게 하고 피부의 종기를 다스린다."라고
@@ -10962,26 +11325,26 @@
 위생상 퍼프만 새로 바꿔주세요.</t>
         </is>
       </c>
-      <c r="B263" s="23" t="n"/>
-      <c r="C263" s="23" t="n"/>
-      <c r="D263" s="23" t="n"/>
-      <c r="E263" s="23" t="n"/>
-      <c r="F263" s="23" t="n"/>
-    </row>
-    <row r="264" ht="14" customHeight="1">
-      <c r="A264" s="34" t="inlineStr">
+      <c r="B294" s="23" t="n"/>
+      <c r="C294" s="23" t="n"/>
+      <c r="D294" s="23" t="n"/>
+      <c r="E294" s="23" t="n"/>
+      <c r="F294" s="23" t="n"/>
+    </row>
+    <row r="295" ht="14" customHeight="1">
+      <c r="A295" s="34" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B264" s="35" t="n"/>
-      <c r="C264" s="35" t="n"/>
-      <c r="D264" s="35" t="n"/>
-      <c r="E264" s="35" t="n"/>
-      <c r="F264" s="35" t="n"/>
-    </row>
-    <row r="265" ht="176" customHeight="1">
-      <c r="A265" s="42" t="inlineStr">
+      <c r="B295" s="35" t="n"/>
+      <c r="C295" s="35" t="n"/>
+      <c r="D295" s="35" t="n"/>
+      <c r="E295" s="35" t="n"/>
+      <c r="F295" s="35" t="n"/>
+    </row>
+    <row r="296" ht="176" customHeight="1">
+      <c r="A296" s="45" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.지퍼백에 모든 재료를 계량하세요.
@@ -10995,168 +11358,224 @@
 9. 완성</t>
         </is>
       </c>
-      <c r="B265" s="23" t="n"/>
-      <c r="C265" s="23" t="n"/>
-      <c r="D265" s="23" t="n"/>
-      <c r="E265" s="23" t="n"/>
-      <c r="F265" s="23" t="n"/>
-    </row>
-    <row r="266" ht="6" customHeight="1"/>
+      <c r="B296" s="23" t="n"/>
+      <c r="C296" s="23" t="n"/>
+      <c r="D296" s="23" t="n"/>
+      <c r="E296" s="23" t="n"/>
+      <c r="F296" s="23" t="n"/>
+    </row>
+    <row r="297" ht="14" customHeight="1">
+      <c r="A297" s="37" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B297" s="38" t="n"/>
+      <c r="C297" s="38" t="n"/>
+      <c r="D297" s="38" t="n"/>
+      <c r="E297" s="38" t="n"/>
+      <c r="F297" s="38" t="n"/>
+    </row>
+    <row r="298" ht="30" customHeight="1">
+      <c r="A298" s="39" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 18%(진주분말 16%, 알란토인분말 2%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="133">
-    <mergeCell ref="A174:F174"/>
+  <mergeCells count="169">
+    <mergeCell ref="A205:F205"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A183:F183"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A118:F118"/>
-    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A158:F158"/>
     <mergeCell ref="A238:F238"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A95:F95"/>
     <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A263:F263"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A97:F97"/>
     <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A265:F265"/>
-    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A280:F280"/>
     <mergeCell ref="A161:F161"/>
     <mergeCell ref="A249:F249"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A202:F202"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A82:F82"/>
     <mergeCell ref="A260:F260"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A250:F250"/>
-    <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A212:F212"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A237:F237"/>
     <mergeCell ref="A252:F252"/>
+    <mergeCell ref="A283:F283"/>
+    <mergeCell ref="A99:F99"/>
     <mergeCell ref="A221:F221"/>
+    <mergeCell ref="A277:F277"/>
+    <mergeCell ref="A292:F292"/>
     <mergeCell ref="A236:F236"/>
+    <mergeCell ref="A267:F267"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A223:F223"/>
-    <mergeCell ref="A195:F195"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A294:F294"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A213:F213"/>
+    <mergeCell ref="A204:F204"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A278:F278"/>
+    <mergeCell ref="A188:F188"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A259:F259"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A206:F206"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A240:F240"/>
     <mergeCell ref="A262:F262"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A215:F215"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A125:F125"/>
     <mergeCell ref="A190:F190"/>
-    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A112:F112"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="A127:F127"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A176:F176"/>
     <mergeCell ref="A232:F232"/>
     <mergeCell ref="A114:F114"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A216:F216"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A191:F191"/>
     <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A296:F296"/>
     <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A218:F218"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A71:F71"/>
     <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A203:F203"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A244:F244"/>
+    <mergeCell ref="A100:F100"/>
     <mergeCell ref="A140:F140"/>
-    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A180:F180"/>
     <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A293:F293"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A68:F68"/>
     <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A295:F295"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A143:F143"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A279:F279"/>
     <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A281:F281"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="A246:F246"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A193:F193"/>
     <mergeCell ref="A264:F264"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A120:F120"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A192:F192"/>
     <mergeCell ref="A248:F248"/>
-    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A297:F297"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A235:F235"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="A247:F247"/>
-    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A298:F298"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A234:F234"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A156:F156"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A220:F220"/>
+    <mergeCell ref="A130:F130"/>
     <mergeCell ref="A261:F261"/>
+    <mergeCell ref="A275:F275"/>
     <mergeCell ref="A222:F222"/>
-    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A138:F138"/>
     <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A146:F146"/>
-    <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
-    <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A215" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A238" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A161" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A211" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A225" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A240" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A267" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
